--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7754A4F-2AC4-466D-A557-C73FB9A03364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FB558-D1FD-4027-A410-D94FFDC86B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45976,10 +45976,10 @@
     <row r="128" spans="1:18" x14ac:dyDescent="0.35">
       <c r="M128"/>
     </row>
-    <row r="129" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:17" x14ac:dyDescent="0.35">
       <c r="M129"/>
     </row>
-    <row r="130" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C130" s="173" t="s">
         <v>136</v>
       </c>
@@ -45989,7 +45989,7 @@
       </c>
       <c r="M130"/>
     </row>
-    <row r="131" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C131" s="12" t="s">
         <v>137</v>
       </c>
@@ -45999,7 +45999,7 @@
       </c>
       <c r="M131"/>
     </row>
-    <row r="132" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C132" t="s">
         <v>138</v>
       </c>
@@ -46133,14 +46133,14 @@
       </c>
       <c r="M132"/>
     </row>
-    <row r="133" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="3:17" x14ac:dyDescent="0.35">
       <c r="D133" s="172" t="str" cm="1">
         <f t="array" ref="D133">_xll.PE.crs.AsProjString(D4)</f>
         <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
       </c>
       <c r="M133"/>
     </row>
-    <row r="134" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:17" x14ac:dyDescent="0.35">
       <c r="D134" s="172" t="str" cm="1">
         <f t="array" ref="D134">_xll.PE.crs.AsWktString(D4)</f>
         <v>PROJCRS["Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)",
@@ -46187,33 +46187,50 @@
       </c>
       <c r="M134"/>
     </row>
-    <row r="135" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:17" x14ac:dyDescent="0.35">
       <c r="D135" s="174" t="str" cm="1">
         <f t="array" ref="D135">_xll.PE.crs.Axis.Abbreviation(D4,0,TRUE)</f>
         <v>Y</v>
       </c>
       <c r="M135"/>
     </row>
-    <row r="136" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:17" x14ac:dyDescent="0.35">
       <c r="D136" s="174" cm="1">
         <f t="array" ref="D136">_xll.PE.crs.Axis.Count(D4,TRUE)</f>
         <v>2</v>
       </c>
       <c r="M136"/>
     </row>
-    <row r="137" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M137"/>
     </row>
-    <row r="138" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="M138"/>
-    </row>
-    <row r="139" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C138" s="182" t="str" cm="1">
+        <f t="array" ref="C138">_xll.PE.trf.Options2()</f>
+        <v>Authority=EPSG; Accuracy=; Area=; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; AllowDeprecatedCrs=False; StrictContains=False; IntermediateCrsUsage=Auto; CandidateIndex=0; BestOnly=False; ForceOver=False</v>
+      </c>
+      <c r="D138" s="183"/>
+      <c r="E138" s="183"/>
+      <c r="F138" s="183"/>
+      <c r="G138" s="183"/>
+      <c r="H138" s="183"/>
+      <c r="I138" s="183"/>
+      <c r="J138" s="183"/>
+      <c r="K138" s="183"/>
+      <c r="L138" s="183"/>
+      <c r="M138" s="183"/>
+      <c r="N138" s="183"/>
+      <c r="O138" s="205"/>
+      <c r="P138" s="183"/>
+      <c r="Q138" s="184"/>
+    </row>
+    <row r="139" spans="3:17" x14ac:dyDescent="0.35">
       <c r="M139"/>
     </row>
-    <row r="140" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M140"/>
     </row>
-    <row r="141" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C141" s="182" t="str" cm="1">
         <f t="array" ref="C141:G143">_xll.PE.xfm.ListTransformPipelines($D$4,$D$5)</f>
         <v>PipelineID</v>
@@ -46236,7 +46253,7 @@
       <c r="K141" s="61"/>
       <c r="M141"/>
     </row>
-    <row r="142" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C142" s="199">
         <v>1</v>
       </c>
@@ -46255,7 +46272,7 @@
       <c r="K142" s="61"/>
       <c r="M142"/>
     </row>
-    <row r="143" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C143" s="201">
         <v>2</v>
       </c>
@@ -46274,7 +46291,7 @@
       <c r="K143" s="61"/>
       <c r="M143"/>
     </row>
-    <row r="144" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K144" s="61"/>
       <c r="M144"/>
     </row>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FB558-D1FD-4027-A410-D94FFDC86B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8C95E4-1D27-45B0-96F1-0D90AFDD773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="142">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -618,12 +618,15 @@
   <si>
     <t>Transform options</t>
   </si>
+  <si>
+    <t xml:space="preserve"> CRS is deprecated</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000000"/>
@@ -631,6 +634,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1199,7 +1203,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1694,6 +1698,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="15" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1705,10 +1720,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FFFFFFCC"/>
       <color rgb="FF66FFFF"/>
       <color rgb="FF66CCFF"/>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFFFFFCC"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FF0000FF"/>
     </mruColors>
@@ -39438,7 +39453,7 @@
     <col min="2" max="2" width="6.36328125" style="61" customWidth="1"/>
     <col min="3" max="3" width="25.7265625" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15.90625" customWidth="1"/>
     <col min="6" max="6" width="14.54296875" customWidth="1"/>
     <col min="7" max="7" width="13.36328125" customWidth="1"/>
     <col min="8" max="8" width="12.36328125" customWidth="1"/>
@@ -39463,19 +39478,18 @@
       <c r="D3" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="56"/>
       <c r="G3" s="56"/>
       <c r="H3" s="56"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
       <c r="K3" s="56"/>
       <c r="L3" s="57"/>
-      <c r="M3" s="50" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="4" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C4" s="51" t="s">
@@ -39484,28 +39498,21 @@
       <c r="D4" s="49">
         <v>2462</v>
       </c>
-      <c r="E4" s="65" t="str" cm="1">
-        <f t="array" ref="E4">_xll.PE.crs.AsProjString(D4)</f>
+      <c r="E4" s="213" t="b" cm="1">
+        <f t="array" ref="E4">_xll.PE.crs.IsDeprecated(D4)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="210" t="str" cm="1">
+        <f t="array" ref="F4">_xll.PE.crs.AsProjString(D4)</f>
         <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
       </c>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="166" cm="1">
-        <f t="array" ref="O4">_xll.PE.crs.UsageArea.Center.X(D4)</f>
-        <v>4426173.5325582689</v>
-      </c>
-      <c r="P4" s="167" cm="1">
-        <f t="array" ref="P4">_xll.PE.crs.UsageArea.Center.Y(D4)</f>
-        <v>4558658.032843451</v>
-      </c>
+      <c r="G4" s="211"/>
+      <c r="H4" s="211"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="212"/>
+      <c r="P4" s="167"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C5" s="52" t="s">
@@ -39514,20 +39521,20 @@
       <c r="D5" s="48">
         <v>4326</v>
       </c>
-      <c r="E5" s="62" t="str" cm="1">
-        <f t="array" ref="E5">_xll.PE.crs.AsProjString(D5)</f>
+      <c r="E5" s="213" t="b" cm="1">
+        <f t="array" ref="E5">_xll.PE.crs.IsDeprecated(D5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="182" t="str" cm="1">
+        <f t="array" ref="F5">_xll.PE.crs.AsProjString(D5)</f>
         <v>+proj=longlat +datum=WGS84 +no_defs +type=crs</v>
       </c>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="53" t="s">
-        <v>17</v>
-      </c>
+      <c r="G5" s="183"/>
+      <c r="H5" s="183"/>
+      <c r="I5" s="183"/>
+      <c r="J5" s="183"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="214"/>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M6"/>
@@ -45538,36 +45545,36 @@
         <f>E119-$D$7*COS(RADIANS(O119))</f>
         <v>4452852.3097855086</v>
       </c>
-      <c r="F118" s="132" cm="1">
-        <f t="array" ref="F118:G118">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D118,E118)</f>
-        <v>20.155244386653319</v>
-      </c>
-      <c r="G118" s="134">
-        <v>40.205795085677487</v>
-      </c>
-      <c r="H118" s="132" t="str" cm="1">
+      <c r="F118" s="132" t="e" cm="1">
+        <f t="array" ref="F118:G118">_xll.PE.trf.ApplyForwardEx($D$4,$D$5,D118:E118,0,$C$127)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="G118" s="134" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H118" s="132" t="e" cm="1">
         <f t="array" ref="H118">_xll.PE.deg.AsString(F118)</f>
-        <v>20 09 19</v>
-      </c>
-      <c r="I118" s="133" t="str" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I118" s="133" t="e" cm="1">
         <f t="array" ref="I118">_xll.PE.deg.AsString(G118)</f>
-        <v>40 12 21</v>
-      </c>
-      <c r="J118" s="132" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J118" s="132" t="e" cm="1">
         <f t="array" ref="J118">_xll.PE.deg.FromString(H118)</f>
-        <v>20.155277777777776</v>
-      </c>
-      <c r="K118" s="134" cm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K118" s="134" t="e" cm="1">
         <f t="array" ref="K118">_xll.PE.deg.FromString(I118)</f>
-        <v>40.205833333333338</v>
-      </c>
-      <c r="L118" s="83">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L118" s="83" t="e">
         <f t="shared" ref="L118:M123" si="48">F118-J118</f>
-        <v>-3.3391124457438082E-5</v>
-      </c>
-      <c r="M118" s="79">
+        <v>#NUM!</v>
+      </c>
+      <c r="M118" s="79" t="e">
         <f t="shared" si="48"/>
-        <v>-3.824765585136447E-5</v>
+        <v>#NUM!</v>
       </c>
       <c r="N118" s="8">
         <f>SQRT((D119-D118)^2+(E119-E118)^2)</f>
@@ -45578,13 +45585,13 @@
         <v>54.497692329086064</v>
       </c>
       <c r="P118" s="94"/>
-      <c r="Q118" s="44" t="str">
+      <c r="Q118" s="44" t="e">
         <f t="shared" ref="Q118:Q123" si="49">CONCATENATE(TEXT(F118,"#.00000000"),",",TEXT(G118,"#.00000000"))</f>
-        <v>20.15524439,40.20579509</v>
-      </c>
-      <c r="R118" s="98" t="str">
+        <v>#NUM!</v>
+      </c>
+      <c r="R118" s="98" t="e">
         <f t="shared" ref="R118:R123" si="50">CONCATENATE("&lt;trkpt lon=""",TEXT(F118,"#.00000000"),""" lat=""",TEXT(G118,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B118,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.15524439" lat="40.20579509"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45959,27 +45966,52 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D126" s="198">
-        <f>AVERAGE(D16:D123)</f>
-        <v>4425866.9868022082</v>
-      </c>
-      <c r="E126" s="198">
-        <f>AVERAGE(E16:E123)</f>
-        <v>4471010.5922981566</v>
-      </c>
+    <row r="126" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D126" s="198"/>
+      <c r="E126" s="198"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="M127"/>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C127" s="182" t="str" cm="1">
+        <f t="array" ref="C127">_xll.PE.trf.Options(,,,,,1.01,,,,,,,,,1,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=1.01; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=1; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D127" s="183"/>
+      <c r="E127" s="183"/>
+      <c r="F127" s="183"/>
+      <c r="G127" s="183"/>
+      <c r="H127" s="183"/>
+      <c r="I127" s="183"/>
+      <c r="J127" s="183"/>
+      <c r="K127" s="183"/>
+      <c r="L127" s="183"/>
+      <c r="M127" s="183"/>
+      <c r="N127" s="183"/>
+      <c r="O127" s="205"/>
+      <c r="P127" s="183"/>
+      <c r="Q127" s="184"/>
+    </row>
+    <row r="128" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M128"/>
     </row>
-    <row r="129" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F129" s="182" cm="1">
+        <f t="array" ref="F129:G129">_xll.PE.trf.LatLongToWebMercatorEx(G123,F123,C127)</f>
+        <v>4488904.7260120427</v>
+      </c>
+      <c r="G129" s="184">
+        <v>2316761.8960968899</v>
+      </c>
+      <c r="I129" s="182" cm="1">
+        <f t="array" ref="I129:J129">_xll.PE.trf.LatLongToWebMercator(G123,F123)</f>
+        <v>2267435.056226131</v>
+      </c>
+      <c r="J129" s="184">
+        <v>4913212.9116666559</v>
+      </c>
       <c r="M129"/>
     </row>
-    <row r="130" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C130" s="173" t="s">
         <v>136</v>
       </c>
@@ -45987,9 +46019,21 @@
         <f t="array" ref="D130">_xll.PE.crs.GeodeticCRS.Name(D4)</f>
         <v>Albanian 1987</v>
       </c>
+      <c r="F130" s="215">
+        <v>2267435.056226131</v>
+      </c>
+      <c r="G130" s="216">
+        <v>4913212.9116666559</v>
+      </c>
+      <c r="I130" s="215">
+        <v>2267435.056226131</v>
+      </c>
+      <c r="J130" s="216">
+        <v>4913212.9116666559</v>
+      </c>
       <c r="M130"/>
     </row>
-    <row r="131" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C131" s="12" t="s">
         <v>137</v>
       </c>
@@ -45997,9 +46041,25 @@
         <f t="array" ref="D131">_xll.PE.crs.GeodeticCRS.Type(D4)</f>
         <v>Geographic2DCrs</v>
       </c>
+      <c r="F131" s="217">
+        <f>F129-F130</f>
+        <v>2221469.6697859117</v>
+      </c>
+      <c r="G131" s="218">
+        <f>G129-G130</f>
+        <v>-2596451.0155697661</v>
+      </c>
+      <c r="I131" s="217">
+        <f>I129-I130</f>
+        <v>0</v>
+      </c>
+      <c r="J131" s="218">
+        <f>J129-J130</f>
+        <v>0</v>
+      </c>
       <c r="M131"/>
     </row>
-    <row r="132" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C132" t="s">
         <v>138</v>
       </c>
@@ -46133,14 +46193,14 @@
       </c>
       <c r="M132"/>
     </row>
-    <row r="133" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D133" s="172" t="str" cm="1">
         <f t="array" ref="D133">_xll.PE.crs.AsProjString(D4)</f>
         <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
       </c>
       <c r="M133"/>
     </row>
-    <row r="134" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D134" s="172" t="str" cm="1">
         <f t="array" ref="D134">_xll.PE.crs.AsWktString(D4)</f>
         <v>PROJCRS["Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)",
@@ -46187,50 +46247,30 @@
       </c>
       <c r="M134"/>
     </row>
-    <row r="135" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D135" s="174" t="str" cm="1">
         <f t="array" ref="D135">_xll.PE.crs.Axis.Abbreviation(D4,0,TRUE)</f>
         <v>Y</v>
       </c>
       <c r="M135"/>
     </row>
-    <row r="136" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D136" s="174" cm="1">
         <f t="array" ref="D136">_xll.PE.crs.Axis.Count(D4,TRUE)</f>
         <v>2</v>
       </c>
       <c r="M136"/>
     </row>
-    <row r="137" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="3:13" x14ac:dyDescent="0.35">
       <c r="M137"/>
     </row>
-    <row r="138" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C138" s="182" t="str" cm="1">
-        <f t="array" ref="C138">_xll.PE.trf.Options2()</f>
-        <v>Authority=EPSG; Accuracy=; Area=; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; AllowDeprecatedCrs=False; StrictContains=False; IntermediateCrsUsage=Auto; CandidateIndex=0; BestOnly=False; ForceOver=False</v>
-      </c>
-      <c r="D138" s="183"/>
-      <c r="E138" s="183"/>
-      <c r="F138" s="183"/>
-      <c r="G138" s="183"/>
-      <c r="H138" s="183"/>
-      <c r="I138" s="183"/>
-      <c r="J138" s="183"/>
-      <c r="K138" s="183"/>
-      <c r="L138" s="183"/>
-      <c r="M138" s="183"/>
-      <c r="N138" s="183"/>
-      <c r="O138" s="205"/>
-      <c r="P138" s="183"/>
-      <c r="Q138" s="184"/>
-    </row>
-    <row r="139" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="3:13" x14ac:dyDescent="0.35">
       <c r="M139"/>
     </row>
-    <row r="140" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M140"/>
     </row>
-    <row r="141" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C141" s="182" t="str" cm="1">
         <f t="array" ref="C141:G143">_xll.PE.xfm.ListTransformPipelines($D$4,$D$5)</f>
         <v>PipelineID</v>
@@ -46253,7 +46293,7 @@
       <c r="K141" s="61"/>
       <c r="M141"/>
     </row>
-    <row r="142" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C142" s="199">
         <v>1</v>
       </c>
@@ -46272,7 +46312,7 @@
       <c r="K142" s="61"/>
       <c r="M142"/>
     </row>
-    <row r="143" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C143" s="201">
         <v>2</v>
       </c>
@@ -46291,7 +46331,7 @@
       <c r="K143" s="61"/>
       <c r="M143"/>
     </row>
-    <row r="144" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K144" s="61"/>
       <c r="M144"/>
     </row>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8C95E4-1D27-45B0-96F1-0D90AFDD773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F25A3F-A08A-4B5B-825D-2C1AA26364AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="144">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -620,6 +620,12 @@
   </si>
   <si>
     <t xml:space="preserve"> CRS is deprecated</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1209,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1684,17 +1690,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -1709,6 +1709,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1720,11 +1727,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF66CCFF"/>
+      <color rgb="FF66FFFF"/>
+      <color rgb="FFCCFFCC"/>
+      <color rgb="FFFFFFCC"/>
       <color rgb="FFCCFFFF"/>
-      <color rgb="FFFFFFCC"/>
-      <color rgb="FF66FFFF"/>
-      <color rgb="FF66CCFF"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
@@ -39446,12 +39453,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55C8259-B2F0-4599-98D4-024E12781605}">
-  <dimension ref="A2:T305"/>
+  <dimension ref="A2:T311"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.36328125" style="61" customWidth="1"/>
-    <col min="3" max="3" width="25.7265625" customWidth="1"/>
+    <col min="3" max="3" width="32.7265625" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" customWidth="1"/>
     <col min="5" max="5" width="15.90625" customWidth="1"/>
     <col min="6" max="6" width="14.54296875" customWidth="1"/>
@@ -39462,8 +39469,8 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="14.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.6328125" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="61" customWidth="1"/>
-    <col min="16" max="16" width="14.6328125" customWidth="1"/>
+    <col min="15" max="15" width="23.81640625" style="61" customWidth="1"/>
+    <col min="16" max="16" width="27.81640625" customWidth="1"/>
     <col min="17" max="17" width="30.81640625" customWidth="1"/>
     <col min="18" max="18" width="85.54296875" customWidth="1"/>
     <col min="21" max="21" width="26.08984375" customWidth="1"/>
@@ -39498,20 +39505,20 @@
       <c r="D4" s="49">
         <v>2462</v>
       </c>
-      <c r="E4" s="213" t="b" cm="1">
+      <c r="E4" s="211" t="b" cm="1">
         <f t="array" ref="E4">_xll.PE.crs.IsDeprecated(D4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="210" t="str" cm="1">
+      <c r="F4" s="208" t="str" cm="1">
         <f t="array" ref="F4">_xll.PE.crs.AsProjString(D4)</f>
         <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
       </c>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="212"/>
+      <c r="G4" s="209"/>
+      <c r="H4" s="209"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="209"/>
+      <c r="K4" s="209"/>
+      <c r="L4" s="210"/>
       <c r="P4" s="167"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39521,7 +39528,7 @@
       <c r="D5" s="48">
         <v>4326</v>
       </c>
-      <c r="E5" s="213" t="b" cm="1">
+      <c r="E5" s="211" t="b" cm="1">
         <f t="array" ref="E5">_xll.PE.crs.IsDeprecated(D5)</f>
         <v>0</v>
       </c>
@@ -39534,7 +39541,7 @@
       <c r="I5" s="183"/>
       <c r="J5" s="183"/>
       <c r="K5" s="183"/>
-      <c r="L5" s="214"/>
+      <c r="L5" s="212"/>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M6"/>
@@ -39586,7 +39593,7 @@
         <v>File version</v>
       </c>
       <c r="E11" s="179" t="str">
-        <v>1.0.261013.1335</v>
+        <v>1.0.261016.1155</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39595,7 +39602,7 @@
         <v>Info version</v>
       </c>
       <c r="E12" s="181" t="str">
-        <v>1.0.261013.1335</v>
+        <v>1.0.261016.1155</v>
       </c>
       <c r="Q12" s="100" t="s">
         <v>44</v>
@@ -39624,7 +39631,7 @@
     <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C14" s="172" t="str" cm="1">
         <f t="array" ref="C14">_xll.PE.trf.Options(0,0,0,0,0,0,"auto",0)</f>
-        <v>NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; AllowDeprecatedCrs=False; StrictContains=False; IntermediateCrsUsage=Auto; CandidateIndex=0</v>
+        <v>Authority=0; Area=0,0,0,0; Accuracy=0; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
       </c>
       <c r="D14" s="172"/>
       <c r="E14" s="172"/>
@@ -39635,7 +39642,7 @@
       <c r="J14" s="172"/>
       <c r="K14" s="172"/>
       <c r="L14" s="172"/>
-      <c r="M14" s="209"/>
+      <c r="M14" s="207"/>
       <c r="N14" s="172"/>
       <c r="Q14" s="47" t="s">
         <v>20</v>
@@ -39715,28 +39722,36 @@
         <f>E17-$D$7*COS(RADIANS(O17))</f>
         <v>4511477.2929155556</v>
       </c>
-      <c r="F16" s="132" t="e" cm="1">
-        <f t="array" ref="F16:I16">_xll.PE.xfm.TransformCoordinateAuto($D$4,$D$5,D16,E16)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="G16" s="134" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H16" s="204">
-        <v>2</v>
-      </c>
-      <c r="I16" s="133" t="str">
-        <v>Multiple pipelines exist; auto-selected ID=2, Name=Albanian 1987 to WGS 84 (1), Accuracy=1m.</v>
-      </c>
-      <c r="J16" s="132"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="83" t="e">
+      <c r="F16" s="132" cm="1">
+        <f t="array" ref="F16:G16">_xll.PE.trf.Transform($D$4,$D$5,D16,E16,C128)</f>
+        <v>19.627501288698802</v>
+      </c>
+      <c r="G16" s="134">
+        <v>40.728657406572829</v>
+      </c>
+      <c r="H16" s="135" t="str" cm="1">
+        <f t="array" ref="H16">_xll.PE.deg.AsString(F16)</f>
+        <v>19 37 39</v>
+      </c>
+      <c r="I16" s="136" t="str" cm="1">
+        <f t="array" ref="I16">_xll.PE.deg.AsString(G16)</f>
+        <v>40 43 43</v>
+      </c>
+      <c r="J16" s="135" cm="1">
+        <f t="array" ref="J16">_xll.PE.deg.FromString(H16)</f>
+        <v>19.627500000000001</v>
+      </c>
+      <c r="K16" s="137" cm="1">
+        <f t="array" ref="K16">_xll.PE.deg.FromString(I16)</f>
+        <v>40.728611111111114</v>
+      </c>
+      <c r="L16" s="83">
         <f t="shared" ref="L16:M21" si="0">F16-J16</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="M16" s="79" t="e">
+        <v>1.2886988010052391E-6</v>
+      </c>
+      <c r="M16" s="79">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
+        <v>4.629546171486254E-5</v>
       </c>
       <c r="N16" s="8">
         <f>SQRT((D17-D16)^2+(E17-E16)^2)</f>
@@ -39747,13 +39762,13 @@
         <v>79.278834728222535</v>
       </c>
       <c r="P16" s="89"/>
-      <c r="Q16" s="44" t="e">
+      <c r="Q16" s="44" t="str">
         <f t="shared" ref="Q16:Q21" si="1">CONCATENATE(TEXT(F16,"#.00000000"),",",TEXT(G16,"#.00000000"))</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R16" s="98" t="e">
+        <v>19.62750129,40.72865741</v>
+      </c>
+      <c r="R16" s="98" t="str">
         <f t="shared" ref="R16:R21" si="2">CONCATENATE("&lt;trkpt lon=""",TEXT(F16,"#.00000000"),""" lat=""",TEXT(G16,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B16,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>#NUM!</v>
+        <v>&lt;trkpt lon="19.62750129" lat="40.72865741"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39772,28 +39787,36 @@
         <f>E18-$D$8*COS(RADIANS(O18))</f>
         <v>4512035.3816660317</v>
       </c>
-      <c r="F17" s="207" t="str" cm="1">
-        <f t="array" ref="F17">_xll.PE.xfm.TransformCoordinate($D$4,$D$5,D17, E17,C146)</f>
-        <v>Error: Pipeline with ID 0 not found for this CRS pair.</v>
-      </c>
-      <c r="G17" s="137"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="136"/>
+      <c r="F17" s="135" cm="1">
+        <f t="array" ref="F17:G17">_xll.PE.trf.Transform($D$4,$D$5,D17,E17)</f>
+        <v>19.662282485406411</v>
+      </c>
+      <c r="G17" s="137">
+        <v>40.734091192706153</v>
+      </c>
+      <c r="H17" s="135" t="str" cm="1">
+        <f t="array" ref="H17">_xll.PE.deg.AsString(F17)</f>
+        <v>19 39 44</v>
+      </c>
+      <c r="I17" s="136" t="str" cm="1">
+        <f t="array" ref="I17">_xll.PE.deg.AsString(G17)</f>
+        <v>40 44 03</v>
+      </c>
       <c r="J17" s="135" cm="1">
         <f t="array" ref="J17">_xll.PE.deg.FromString(H17)</f>
-        <v>0</v>
+        <v>19.662222222222219</v>
       </c>
       <c r="K17" s="137" cm="1">
         <f t="array" ref="K17">_xll.PE.deg.FromString(I17)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="84" t="e">
+        <v>40.734166666666667</v>
+      </c>
+      <c r="L17" s="84">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>6.0263184192166364E-5</v>
       </c>
       <c r="M17" s="80">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7.5473960514216287E-5</v>
       </c>
       <c r="N17" s="39">
         <f>SQRT((D18-D17)^2+(E18-E17)^2)</f>
@@ -39808,11 +39831,11 @@
       </c>
       <c r="Q17" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>Error: Pipeline with ID 0 not found for this CRS pair.,.00000000</v>
+        <v>19.66228249,40.73409119</v>
       </c>
       <c r="R17" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="Error: Pipeline with ID 0 not found for this CRS pair." lat=".00000000"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="19.66228249" lat="40.73409119"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39829,36 +39852,36 @@
       <c r="E18" s="190">
         <v>4512779.5</v>
       </c>
-      <c r="F18" s="138" t="e" cm="1">
-        <f t="array" ref="F18:G18">_xll.PE.trf.ApplyForwardEx($D$4,$D$5,D18:E18,0,1,C14)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="G18" s="140" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H18" s="138" t="e" cm="1">
+      <c r="F18" s="138" cm="1">
+        <f t="array" ref="F18:G18">_xll.PE.trf.Transform($D$4,$D$5,D18,E18)</f>
+        <v>19.708666633032713</v>
+      </c>
+      <c r="G18" s="140">
+        <v>40.741320058972271</v>
+      </c>
+      <c r="H18" s="138" t="str" cm="1">
         <f t="array" ref="H18">_xll.PE.deg.AsString(F18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I18" s="139" t="e" cm="1">
+        <v>19 42 31</v>
+      </c>
+      <c r="I18" s="139" t="str" cm="1">
         <f t="array" ref="I18">_xll.PE.deg.AsString(G18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J18" s="138" t="e" cm="1">
+        <v>40 44 29</v>
+      </c>
+      <c r="J18" s="138" cm="1">
         <f t="array" ref="J18">_xll.PE.deg.FromString(H18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K18" s="140" t="e" cm="1">
+        <v>19.708611111111111</v>
+      </c>
+      <c r="K18" s="140" cm="1">
         <f t="array" ref="K18">_xll.PE.deg.FromString(I18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L18" s="85" t="e">
+        <v>40.741388888888892</v>
+      </c>
+      <c r="L18" s="85">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="M18" s="81" t="e">
+        <v>5.5521921602519342E-5</v>
+      </c>
+      <c r="M18" s="81">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
+        <v>-6.8829916621382381E-5</v>
       </c>
       <c r="N18" s="10">
         <f>SQRT((D19-D18)^2+(E19-E18)^2)</f>
@@ -39872,13 +39895,13 @@
         <f t="array" ref="P18">_xll.PE.crs.GeodesicDistance($D$4,D17:E20)</f>
         <v>29753.732339481572</v>
       </c>
-      <c r="Q18" s="44" t="e">
+      <c r="Q18" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="R18" s="98" t="e">
+        <v>19.70866663,40.74132006</v>
+      </c>
+      <c r="R18" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>#NUM!</v>
+        <v>&lt;trkpt lon="19.70866663" lat="40.74132006"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39896,7 +39919,7 @@
         <v>4516827</v>
       </c>
       <c r="F19" s="138" cm="1">
-        <f t="array" ref="F19:G19">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D19,E19)</f>
+        <f t="array" ref="F19:G19">_xll.PE.trf.Transform($D$4,$D$5,D19,E19)</f>
         <v>19.961147921469532</v>
       </c>
       <c r="G19" s="140">
@@ -40068,9 +40091,9 @@
       <c r="O21" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="P21" s="90" t="str" cm="1">
+      <c r="P21" s="90" cm="1">
         <f t="array" ref="P21">_xll.PE.crs.GeodesicDistance($D$5,J17:K20)</f>
-        <v>#ERR: Specified cast is not valid.</v>
+        <v>29750.260289015008</v>
       </c>
       <c r="Q21" s="44" t="str">
         <f t="shared" si="1"/>
@@ -45545,36 +45568,36 @@
         <f>E119-$D$7*COS(RADIANS(O119))</f>
         <v>4452852.3097855086</v>
       </c>
-      <c r="F118" s="132" t="e" cm="1">
-        <f t="array" ref="F118:G118">_xll.PE.trf.ApplyForwardEx($D$4,$D$5,D118:E118,0,$C$127)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="G118" s="134" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H118" s="132" t="e" cm="1">
+      <c r="F118" s="132" cm="1">
+        <f t="array" ref="F118:G118">_xll.PE.trf.Transform($D$4,$D$5,D118,E118,$C$128)</f>
+        <v>20.155244386653319</v>
+      </c>
+      <c r="G118" s="134">
+        <v>40.205795085677487</v>
+      </c>
+      <c r="H118" s="132" t="str" cm="1">
         <f t="array" ref="H118">_xll.PE.deg.AsString(F118)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I118" s="133" t="e" cm="1">
+        <v>20 09 19</v>
+      </c>
+      <c r="I118" s="133" t="str" cm="1">
         <f t="array" ref="I118">_xll.PE.deg.AsString(G118)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J118" s="132" t="e" cm="1">
+        <v>40 12 21</v>
+      </c>
+      <c r="J118" s="132" cm="1">
         <f t="array" ref="J118">_xll.PE.deg.FromString(H118)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="K118" s="134" t="e" cm="1">
+        <v>20.155277777777776</v>
+      </c>
+      <c r="K118" s="134" cm="1">
         <f t="array" ref="K118">_xll.PE.deg.FromString(I118)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L118" s="83" t="e">
+        <v>40.205833333333338</v>
+      </c>
+      <c r="L118" s="83">
         <f t="shared" ref="L118:M123" si="48">F118-J118</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="M118" s="79" t="e">
+        <v>-3.3391124457438082E-5</v>
+      </c>
+      <c r="M118" s="79">
         <f t="shared" si="48"/>
-        <v>#NUM!</v>
+        <v>-3.824765585136447E-5</v>
       </c>
       <c r="N118" s="8">
         <f>SQRT((D119-D118)^2+(E119-E118)^2)</f>
@@ -45585,13 +45608,13 @@
         <v>54.497692329086064</v>
       </c>
       <c r="P118" s="94"/>
-      <c r="Q118" s="44" t="e">
+      <c r="Q118" s="44" t="str">
         <f t="shared" ref="Q118:Q123" si="49">CONCATENATE(TEXT(F118,"#.00000000"),",",TEXT(G118,"#.00000000"))</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R118" s="98" t="e">
+        <v>20.15524439,40.20579509</v>
+      </c>
+      <c r="R118" s="98" t="str">
         <f t="shared" ref="R118:R123" si="50">CONCATENATE("&lt;trkpt lon=""",TEXT(F118,"#.00000000"),""" lat=""",TEXT(G118,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B118,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>#NUM!</v>
+        <v>&lt;trkpt lon="20.15524439" lat="40.20579509"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45973,8 +45996,8 @@
     </row>
     <row r="127" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C127" s="182" t="str" cm="1">
-        <f t="array" ref="C127">_xll.PE.trf.Options(,,,,,1.01,,,,,,,,,1,)</f>
-        <v>Authority=EPSG; Area=; Accuracy=1.01; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=1; AllowDeprecatedCrs=False</v>
+        <f t="array" ref="C127">_xll.PE.trf.Options(,,,,,1,,,,,,,,,1,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=1; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=1; AllowDeprecatedCrs=False</v>
       </c>
       <c r="D127" s="183"/>
       <c r="E127" s="183"/>
@@ -45987,26 +46010,43 @@
       <c r="L127" s="183"/>
       <c r="M127" s="183"/>
       <c r="N127" s="183"/>
-      <c r="O127" s="205"/>
+      <c r="O127" s="204"/>
       <c r="P127" s="183"/>
       <c r="Q127" s="184"/>
     </row>
     <row r="128" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M128"/>
+      <c r="C128" s="182" t="str" cm="1">
+        <f t="array" ref="C128">_xll.PE.trf.Options(,,,,,,,,,,,,,,0,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D128" s="183"/>
+      <c r="E128" s="183"/>
+      <c r="F128" s="183"/>
+      <c r="G128" s="183"/>
+      <c r="H128" s="183"/>
+      <c r="I128" s="183"/>
+      <c r="J128" s="183"/>
+      <c r="K128" s="183"/>
+      <c r="L128" s="183"/>
+      <c r="M128" s="183"/>
+      <c r="N128" s="183"/>
+      <c r="O128" s="204"/>
+      <c r="P128" s="183"/>
+      <c r="Q128" s="184"/>
     </row>
     <row r="129" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F129" s="182" cm="1">
+      <c r="F129" s="180" cm="1">
         <f t="array" ref="F129:G129">_xll.PE.trf.LatLongToWebMercatorEx(G123,F123,C127)</f>
         <v>4488904.7260120427</v>
       </c>
-      <c r="G129" s="184">
+      <c r="G129" s="181">
         <v>2316761.8960968899</v>
       </c>
-      <c r="I129" s="182" cm="1">
+      <c r="I129" s="180" cm="1">
         <f t="array" ref="I129:J129">_xll.PE.trf.LatLongToWebMercator(G123,F123)</f>
         <v>2267435.056226131</v>
       </c>
-      <c r="J129" s="184">
+      <c r="J129" s="181">
         <v>4913212.9116666559</v>
       </c>
       <c r="M129"/>
@@ -46019,16 +46059,16 @@
         <f t="array" ref="D130">_xll.PE.crs.GeodeticCRS.Name(D4)</f>
         <v>Albanian 1987</v>
       </c>
-      <c r="F130" s="215">
+      <c r="F130" s="213">
+        <v>2267435.0562261301</v>
+      </c>
+      <c r="G130" s="214">
+        <v>4913212.9116666559</v>
+      </c>
+      <c r="I130" s="213">
         <v>2267435.056226131</v>
       </c>
-      <c r="G130" s="216">
-        <v>4913212.9116666559</v>
-      </c>
-      <c r="I130" s="215">
-        <v>2267435.056226131</v>
-      </c>
-      <c r="J130" s="216">
+      <c r="J130" s="214">
         <v>4913212.9116666559</v>
       </c>
       <c r="M130"/>
@@ -46041,19 +46081,19 @@
         <f t="array" ref="D131">_xll.PE.crs.GeodeticCRS.Type(D4)</f>
         <v>Geographic2DCrs</v>
       </c>
-      <c r="F131" s="217">
+      <c r="F131" s="215">
         <f>F129-F130</f>
-        <v>2221469.6697859117</v>
-      </c>
-      <c r="G131" s="218">
+        <v>2221469.6697859126</v>
+      </c>
+      <c r="G131" s="216">
         <f>G129-G130</f>
         <v>-2596451.0155697661</v>
       </c>
-      <c r="I131" s="217">
+      <c r="I131" s="215">
         <f>I129-I130</f>
         <v>0</v>
       </c>
-      <c r="J131" s="218">
+      <c r="J131" s="216">
         <f>J129-J130</f>
         <v>0</v>
       </c>
@@ -46361,7 +46401,7 @@
       <c r="J145" s="183" t="str">
         <v>UsageArea</v>
       </c>
-      <c r="K145" s="205" t="str">
+      <c r="K145" s="204" t="str">
         <v>Pros</v>
       </c>
       <c r="L145" s="184" t="str">
@@ -46460,7 +46500,7 @@
       <c r="J148" s="202" t="str">
         <v/>
       </c>
-      <c r="K148" s="206" t="str">
+      <c r="K148" s="205" t="str">
         <v>Available; Non-ballpark; Default selection</v>
       </c>
       <c r="L148" s="203" t="str">
@@ -46469,165 +46509,150 @@
       <c r="M148"/>
     </row>
     <row r="149" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="K149" s="61"/>
       <c r="M149"/>
     </row>
     <row r="150" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C150" s="172" t="str" cm="1">
-        <f t="array" ref="C150:D248">_xll.PE.trf.ListTransformInfo($D$4,$D$5)</f>
+      <c r="K150" s="61"/>
+      <c r="M150"/>
+    </row>
+    <row r="151" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C151">
+        <v>2462</v>
+      </c>
+      <c r="K151" s="61"/>
+      <c r="M151"/>
+    </row>
+    <row r="152" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C152" s="217">
+        <v>4326</v>
+      </c>
+      <c r="D152" t="s">
+        <v>142</v>
+      </c>
+      <c r="K152" s="61"/>
+      <c r="M152"/>
+    </row>
+    <row r="153" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C153" s="217">
+        <v>3857</v>
+      </c>
+      <c r="D153" t="s">
+        <v>143</v>
+      </c>
+      <c r="K153" s="61"/>
+      <c r="M153"/>
+    </row>
+    <row r="154" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="K154" s="61"/>
+      <c r="M154"/>
+    </row>
+    <row r="155" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="M155"/>
+    </row>
+    <row r="156" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C156" s="172" t="str" cm="1">
+        <f t="array" ref="C156:D246">_xll.PE.trf.ListTransformInfo(C151,C152)</f>
         <v>SourceCrs</v>
       </c>
-      <c r="D150" t="str">
+      <c r="D156" t="str">
         <v>2462</v>
-      </c>
-      <c r="M150"/>
-    </row>
-    <row r="151" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C151" s="172" t="str">
-        <v>DestinationCrs</v>
-      </c>
-      <c r="D151" t="str">
-        <v>4326</v>
-      </c>
-      <c r="M151"/>
-    </row>
-    <row r="152" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C152" s="172" t="str">
-        <v>Transform.RuntimeType</v>
-      </c>
-      <c r="D152" t="str">
-        <v>SharpProj.CoordinateTransformList</v>
-      </c>
-      <c r="M152"/>
-    </row>
-    <row r="153" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C153" s="172" t="str">
-        <v>Transform.PublicProperties</v>
-      </c>
-      <c r="D153" t="str">
-        <v>Accuracy, Context, Count, GridUsages, HasBallParkTransformation, HasInverse, Identifier, Identifiers, IsAvailable, MethodName, Name, Parameters, Remarks, Scope, SourceCRS, TargetCRS, Type, UsageArea</v>
-      </c>
-      <c r="M153"/>
-    </row>
-    <row r="154" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C154" s="172" t="str">
-        <v>Transform.Name</v>
-      </c>
-      <c r="D154" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4 + Albanian 1987 to WGS 84 (1) + axis order change (2D)</v>
-      </c>
-      <c r="M154"/>
-    </row>
-    <row r="155" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C155" s="172" t="str">
-        <v>Transform.Type</v>
-      </c>
-      <c r="D155" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="M155"/>
-    </row>
-    <row r="156" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C156" s="172" t="str">
-        <v>Transform.Identifier</v>
-      </c>
-      <c r="D156" t="str">
-        <v/>
       </c>
       <c r="M156"/>
     </row>
     <row r="157" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C157" s="172" t="str">
-        <v>Transform.Identifiers</v>
+        <v>DestinationCrs</v>
       </c>
       <c r="D157" t="str">
-        <v/>
+        <v>4326</v>
       </c>
       <c r="M157"/>
     </row>
     <row r="158" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C158" s="172" t="str">
-        <v>Transform.Accuracy</v>
+        <v>Transform.Name</v>
       </c>
       <c r="D158" t="str">
-        <v>1</v>
+        <v>Inverse of 6-degree Gauss-Kruger zone 4 + Albanian 1987 to WGS 84 (1) + axis order change (2D)</v>
       </c>
       <c r="M158"/>
     </row>
     <row r="159" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C159" s="172" t="str">
-        <v>Transform.Count</v>
+        <v>Transform.Type</v>
       </c>
       <c r="D159" t="str">
-        <v>3</v>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="M159"/>
     </row>
     <row r="160" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C160" s="172" t="str">
-        <v>Transform.IsAvailable</v>
+        <v>Transform.Identifier</v>
       </c>
       <c r="D160" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="M160"/>
     </row>
     <row r="161" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C161" s="172" t="str">
-        <v>Transform.HasBallParkTransformation</v>
+        <v>Transform.Identifiers</v>
       </c>
       <c r="D161" t="str">
-        <v>False</v>
+        <v/>
       </c>
       <c r="M161"/>
     </row>
     <row r="162" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C162" s="172" t="str">
-        <v>Transform.HasInverse</v>
+        <v>Transform.Accuracy</v>
       </c>
       <c r="D162" t="str">
-        <v>True</v>
+        <v>1</v>
       </c>
       <c r="M162"/>
     </row>
     <row r="163" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C163" s="172" t="str">
-        <v>Transform.MethodName</v>
+        <v>Transform.Count</v>
       </c>
       <c r="D163" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="M163"/>
     </row>
     <row r="164" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C164" s="172" t="str">
-        <v>Transform.Scope</v>
+        <v>Transform.IsAvailable</v>
       </c>
       <c r="D164" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="M164"/>
     </row>
     <row r="165" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C165" s="172" t="str">
-        <v>Transform.Remarks</v>
+        <v>Transform.HasBallParkTransformation</v>
       </c>
       <c r="D165" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="M165"/>
     </row>
     <row r="166" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C166" s="172" t="str">
-        <v>Transform.GridUsages</v>
+        <v>Transform.HasInverse</v>
       </c>
       <c r="D166" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="M166"/>
     </row>
     <row r="167" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C167" s="172" t="str">
-        <v>Transform.Parameters</v>
+        <v>Transform.MethodName</v>
       </c>
       <c r="D167" t="str">
         <v/>
@@ -46636,352 +46661,641 @@
     </row>
     <row r="168" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C168" s="172" t="str">
-        <v>Transform.SourceCRS</v>
+        <v>Transform.Scope</v>
       </c>
       <c r="D168" t="str">
-        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="M168"/>
     </row>
     <row r="169" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C169" s="172" t="str">
-        <v>Transform.TargetCRS</v>
+        <v>Transform.Remarks</v>
       </c>
       <c r="D169" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="M169"/>
     </row>
     <row r="170" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C170" s="172" t="str">
-        <v>Transform.Context</v>
+        <v>Transform.GridUsages</v>
       </c>
       <c r="D170" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v/>
       </c>
       <c r="M170"/>
     </row>
     <row r="171" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C171" s="172" t="str">
-        <v>Transform.UsageArea</v>
+        <v>Transform.Parameters</v>
       </c>
       <c r="D171" t="str">
-        <v>SharpProj.Proj.UsageArea</v>
+        <v/>
       </c>
       <c r="M171"/>
     </row>
     <row r="172" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C172" s="172" t="str">
-        <v>Transform.UsageArea.Name</v>
+        <v>Transform.SourceCRS</v>
       </c>
       <c r="D172" t="str">
-        <v>Albania - onshore.</v>
+        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
       </c>
       <c r="M172"/>
     </row>
     <row r="173" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C173" s="172" t="str">
-        <v>Transform.UsageArea.WestLongitude</v>
+        <v>Transform.TargetCRS</v>
       </c>
       <c r="D173" t="str">
-        <v>19.22</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="M173"/>
     </row>
     <row r="174" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C174" s="172" t="str">
-        <v>Transform.UsageArea.SouthLatitude</v>
+        <v>Transform.Context</v>
       </c>
       <c r="D174" t="str">
-        <v>39.64</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="M174"/>
     </row>
     <row r="175" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C175" s="172" t="str">
-        <v>Transform.UsageArea.EastLongitude</v>
+        <v>Transform.UsageArea</v>
       </c>
       <c r="D175" t="str">
-        <v>21.06</v>
+        <v>SharpProj.Proj.UsageArea</v>
       </c>
       <c r="M175"/>
     </row>
     <row r="176" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C176" s="172" t="str">
-        <v>Transform.UsageArea.NorthLatitude</v>
+        <v>Transform.UsageArea.Name</v>
       </c>
       <c r="D176" t="str">
-        <v>42.67</v>
+        <v>Albania - onshore.</v>
       </c>
       <c r="M176"/>
     </row>
     <row r="177" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C177" s="172" t="str">
-        <v>Transform.UsageArea.Center</v>
+        <v>Transform.UsageArea.WestLongitude</v>
       </c>
       <c r="D177" t="str">
-        <v>X=4426173.53255827, Y=4558658.03284345</v>
+        <v>19.22</v>
       </c>
       <c r="M177"/>
     </row>
     <row r="178" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C178" s="172" t="str">
-        <v>Transform.EnumerableCount</v>
+        <v>Transform.UsageArea.SouthLatitude</v>
       </c>
       <c r="D178" t="str">
-        <v>3</v>
+        <v>39.64</v>
       </c>
       <c r="M178"/>
     </row>
     <row r="179" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C179" s="172" t="str">
+        <v>Transform.UsageArea.EastLongitude</v>
+      </c>
+      <c r="D179" t="str">
+        <v>21.06</v>
+      </c>
+      <c r="M179"/>
+    </row>
+    <row r="180" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C180" s="172" t="str">
+        <v>Transform.UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D180" t="str">
+        <v>42.67</v>
+      </c>
+      <c r="M180"/>
+    </row>
+    <row r="181" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C181" s="172" t="str">
+        <v>Transform.UsageArea.Center</v>
+      </c>
+      <c r="D181" t="str">
+        <v>X=4426173.53255827, Y=4558658.03284345</v>
+      </c>
+      <c r="M181"/>
+    </row>
+    <row r="182" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C182" s="172" t="str">
+        <v>Transform.EnumerableCount</v>
+      </c>
+      <c r="D182" t="str">
+        <v>3</v>
+      </c>
+      <c r="M182"/>
+    </row>
+    <row r="183" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C183" s="172" t="str">
         <v>Transform.EnumerableItems</v>
       </c>
-      <c r="D179" t="str">
+      <c r="D183" t="str">
         <v>Inverse of 6-degree Gauss-Kruger zone 4 | Albanian 1987 to WGS 84 (1) | axis order change (2D)</v>
       </c>
-      <c r="M179"/>
-    </row>
-    <row r="180" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C180" s="208" t="str">
-        <v>Candidate[0].RuntimeType</v>
-      </c>
-      <c r="D180" t="str">
-        <v>SharpProj.CoordinateOperation</v>
-      </c>
-      <c r="M180"/>
-    </row>
-    <row r="181" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C181" s="208" t="str">
-        <v>Candidate[0].PublicProperties</v>
-      </c>
-      <c r="D181" t="str">
-        <v>Accuracy, Context, GridUsages, HasBallParkTransformation, HasInverse, Identifier, Identifiers, IsAvailable, MethodName, Name, Parameters, Remarks, Scope, SourceCRS, TargetCRS, Type, UsageArea</v>
-      </c>
-      <c r="M181"/>
-    </row>
-    <row r="182" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C182" s="208" t="str">
+      <c r="H183" s="173" t="str" cm="1">
+        <f t="array" ref="H183:K206">_xll.PE.trf.TransformList(C151,C152)</f>
+        <v>TransformNo.</v>
+      </c>
+      <c r="I183" s="219">
+        <v>0</v>
+      </c>
+      <c r="J183" s="219">
+        <v>1</v>
+      </c>
+      <c r="K183" s="219">
+        <v>2</v>
+      </c>
+      <c r="M183"/>
+    </row>
+    <row r="184" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C184" s="206" t="str">
         <v>Candidate[0].Name</v>
       </c>
-      <c r="D182" t="str">
+      <c r="D184" t="str">
         <v>Albanian 1987 to WGS 84 (1)</v>
       </c>
-      <c r="M182"/>
-    </row>
-    <row r="183" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C183" s="208" t="str">
+      <c r="H184" s="173" t="str">
+        <v>Name</v>
+      </c>
+      <c r="I184" s="218" t="str">
+        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
+      </c>
+      <c r="J184" s="218" t="str">
+        <v>Albanian 1987 to WGS 84 (1)</v>
+      </c>
+      <c r="K184" s="218" t="str">
+        <v>axis order change (2D)</v>
+      </c>
+      <c r="M184"/>
+    </row>
+    <row r="185" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C185" s="206" t="str">
         <v>Candidate[0].Type</v>
       </c>
-      <c r="D183" t="str">
+      <c r="D185" t="str">
         <v>Transformation</v>
       </c>
-      <c r="M183"/>
-    </row>
-    <row r="184" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C184" s="208" t="str">
+      <c r="H185" s="173" t="str">
+        <v>Type</v>
+      </c>
+      <c r="I185" s="218" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="J185" s="218" t="str">
+        <v>Transformation</v>
+      </c>
+      <c r="K185" s="218" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="M185"/>
+    </row>
+    <row r="186" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C186" s="206" t="str">
         <v>Candidate[0].Identifier</v>
       </c>
-      <c r="D184" t="str">
+      <c r="D186" t="str">
         <v>DERIVED_FROM(EPSG):7834</v>
       </c>
-      <c r="M184"/>
-    </row>
-    <row r="185" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C185" s="208" t="str">
+      <c r="H186" s="173" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="I186" s="218" t="str">
+        <v>INVERSE(EPSG):16204</v>
+      </c>
+      <c r="J186" s="218" t="str">
+        <v>DERIVED_FROM(EPSG):7834</v>
+      </c>
+      <c r="K186" s="218" t="str">
+        <v>EPSG:15498</v>
+      </c>
+      <c r="M186"/>
+    </row>
+    <row r="187" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C187" s="206" t="str">
         <v>Candidate[0].Identifiers</v>
       </c>
-      <c r="D185" t="str">
+      <c r="D187" t="str">
         <v>DERIVED_FROM(EPSG):7834</v>
       </c>
-      <c r="M185"/>
-    </row>
-    <row r="186" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C186" s="208" t="str">
+      <c r="H187" s="173" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="I187" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="J187" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="K187" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M187"/>
+    </row>
+    <row r="188" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C188" s="206" t="str">
         <v>Candidate[0].Accuracy</v>
       </c>
-      <c r="D186" t="str">
+      <c r="D188" t="str">
         <v>1</v>
       </c>
-      <c r="M186"/>
-    </row>
-    <row r="187" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C187" s="208" t="str">
+      <c r="H188" s="173" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="I188" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="J188" s="218" t="str">
+        <v>1</v>
+      </c>
+      <c r="K188" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M188"/>
+    </row>
+    <row r="189" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C189" s="206" t="str">
         <v>Candidate[0].IsAvailable</v>
-      </c>
-      <c r="D187" t="str">
-        <v>True</v>
-      </c>
-      <c r="M187"/>
-    </row>
-    <row r="188" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C188" s="208" t="str">
-        <v>Candidate[0].HasBallParkTransformation</v>
-      </c>
-      <c r="D188" t="str">
-        <v>False</v>
-      </c>
-      <c r="M188"/>
-    </row>
-    <row r="189" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C189" s="208" t="str">
-        <v>Candidate[0].HasInverse</v>
       </c>
       <c r="D189" t="str">
         <v>True</v>
       </c>
+      <c r="H189" s="173" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="I189" s="218" t="str">
+        <v>True</v>
+      </c>
+      <c r="J189" s="218" t="str">
+        <v>True</v>
+      </c>
+      <c r="K189" s="218" t="str">
+        <v>True</v>
+      </c>
       <c r="M189"/>
     </row>
     <row r="190" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C190" s="208" t="str">
+      <c r="C190" s="206" t="str">
+        <v>Candidate[0].HasBallParkTransformation</v>
+      </c>
+      <c r="D190" t="str">
+        <v>False</v>
+      </c>
+      <c r="H190" s="173" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="I190" s="218" t="str">
+        <v>False</v>
+      </c>
+      <c r="J190" s="218" t="str">
+        <v>False</v>
+      </c>
+      <c r="K190" s="218" t="str">
+        <v>False</v>
+      </c>
+      <c r="M190"/>
+    </row>
+    <row r="191" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C191" s="206" t="str">
+        <v>Candidate[0].HasInverse</v>
+      </c>
+      <c r="D191" t="str">
+        <v>True</v>
+      </c>
+      <c r="H191" s="173" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="I191" s="218" t="str">
+        <v>True</v>
+      </c>
+      <c r="J191" s="218" t="str">
+        <v>True</v>
+      </c>
+      <c r="K191" s="218" t="str">
+        <v>True</v>
+      </c>
+      <c r="M191"/>
+    </row>
+    <row r="192" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C192" s="206" t="str">
         <v>Candidate[0].MethodName</v>
       </c>
-      <c r="D190" t="str">
+      <c r="D192" t="str">
         <v>Coordinate Frame rotation (geog2D domain)</v>
       </c>
-      <c r="M190"/>
-    </row>
-    <row r="191" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C191" s="208" t="str">
+      <c r="H192" s="173" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="I192" s="218" t="str">
+        <v>Inverse of Transverse Mercator</v>
+      </c>
+      <c r="J192" s="218" t="str">
+        <v>Coordinate Frame rotation (geog2D domain)</v>
+      </c>
+      <c r="K192" s="218" t="str">
+        <v>Axis Order Reversal (2D)</v>
+      </c>
+      <c r="M192"/>
+    </row>
+    <row r="193" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C193" s="206" t="str">
         <v>Candidate[0].Scope</v>
       </c>
-      <c r="D191" t="str">
+      <c r="D193" t="str">
         <v>(null/copy) Approximation for medium and low accuracy applications assuming equality between plate-fixed static and earth-fixed dynamic CRSs, ignoring static/dynamic CRS differences.</v>
       </c>
-      <c r="M191"/>
-    </row>
-    <row r="192" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C192" s="208" t="str">
+      <c r="H193" s="173" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="I193" s="218" t="str">
+        <v>Topographic mapping (medium scale).</v>
+      </c>
+      <c r="J193" s="218" t="str">
+        <v>(null/copy) Approximation for medium and low accuracy applications assuming equality between plate-fixed static and earth-fixed dynamic CRSs, ignoring static/dynamic CRS differences.</v>
+      </c>
+      <c r="K193" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M193"/>
+    </row>
+    <row r="194" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C194" s="206" t="str">
         <v>Candidate[0].Remarks</v>
       </c>
-      <c r="D192" t="str">
+      <c r="D194" t="str">
         <v>Parameter values from Albanian 1987 to ETRS89 (1) (code 7833). Assumes ETRS89 and WGS 84 can be considered the same to within the accuracy of the transformation.</v>
       </c>
-      <c r="M192"/>
-    </row>
-    <row r="193" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C193" s="208" t="str">
+      <c r="H194" s="173" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="I194" s="218" t="str">
+        <v>Also found with zone truncated from false easting: see 6-degree Gauss-Kruger CM 21E (code 16304).</v>
+      </c>
+      <c r="J194" s="218" t="str">
+        <v>Parameter values from Albanian 1987 to ETRS89 (1) (code 7833). Assumes ETRS89 and WGS 84 can be considered the same to within the accuracy of the transformation.</v>
+      </c>
+      <c r="K194" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M194"/>
+    </row>
+    <row r="195" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C195" s="206" t="str">
         <v>Candidate[0].GridUsages</v>
       </c>
-      <c r="D193" t="str">
+      <c r="D195" t="str">
         <v/>
       </c>
-      <c r="M193"/>
-    </row>
-    <row r="194" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C194" s="208" t="str">
+      <c r="H195" s="173" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="I195" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="J195" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="K195" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M195"/>
+    </row>
+    <row r="196" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C196" s="206" t="str">
         <v>Candidate[0].Parameters</v>
       </c>
-      <c r="D194" t="str">
+      <c r="D196" t="str">
         <v>UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-44.183; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-0.58; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-38.489; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.3867; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.7072; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=3.5196; UnitCategory=scale; UnitCode=9202; UnitAuthName=EPSG; UnitName=parts per million; UnitConversionFactor=1E-06; ValueString=-8.2703</v>
       </c>
-      <c r="M194"/>
-    </row>
-    <row r="195" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C195" s="208" t="str">
+      <c r="H196" s="173" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="I196" s="218" t="str">
+        <v>UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; Value=0; UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; ValueString=21; UnitCategory=scale; UnitCode=9201; UnitAuthName=EPSG; UnitName=unity; UnitConversionFactor=1; ValueString=1; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=4500000; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; Value=0</v>
+      </c>
+      <c r="J196" s="218" t="str">
+        <v>UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-44.183; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-0.58; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-38.489; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.3867; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.7072; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=3.5196; UnitCategory=scale; UnitCode=9202; UnitAuthName=EPSG; UnitName=parts per million; UnitConversionFactor=1E-06; ValueString=-8.2703</v>
+      </c>
+      <c r="K196" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M196"/>
+    </row>
+    <row r="197" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C197" s="206" t="str">
         <v>Candidate[0].SourceCRS</v>
       </c>
-      <c r="D195" t="str">
+      <c r="D197" t="str">
         <v>Albanian 1987</v>
       </c>
-      <c r="M195"/>
-    </row>
-    <row r="196" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C196" s="208" t="str">
+      <c r="H197" s="173" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="I197" s="218" t="str">
+        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="J197" s="218" t="str">
+        <v>Albanian 1987</v>
+      </c>
+      <c r="K197" s="218" t="str">
+        <v>WGS 84</v>
+      </c>
+      <c r="M197"/>
+    </row>
+    <row r="198" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C198" s="206" t="str">
         <v>Candidate[0].TargetCRS</v>
       </c>
-      <c r="D196" t="str">
+      <c r="D198" t="str">
         <v>WGS 84</v>
       </c>
-      <c r="M196"/>
-    </row>
-    <row r="197" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C197" s="208" t="str">
+      <c r="H198" s="173" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="I198" s="218" t="str">
+        <v>Albanian 1987</v>
+      </c>
+      <c r="J198" s="218" t="str">
+        <v>WGS 84</v>
+      </c>
+      <c r="K198" s="218" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="M198"/>
+    </row>
+    <row r="199" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C199" s="206" t="str">
         <v>Candidate[0].Context</v>
       </c>
-      <c r="D197" t="str">
+      <c r="D199" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="M197"/>
-    </row>
-    <row r="198" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C198" s="208" t="str">
+      <c r="H199" s="173" t="str">
+        <v>Context</v>
+      </c>
+      <c r="I199" s="218" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="J199" s="218" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="K199" s="218" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M199"/>
+    </row>
+    <row r="200" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C200" s="206" t="str">
         <v>Candidate[0].UsageArea</v>
       </c>
-      <c r="D198" t="str">
+      <c r="D200" t="str">
         <v>SharpProj.Proj.UsageArea</v>
       </c>
-      <c r="M198"/>
-    </row>
-    <row r="199" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C199" s="208" t="str">
+      <c r="H200" s="173" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="I200" s="218" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="J200" s="218" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="K200" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M200"/>
+    </row>
+    <row r="201" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C201" s="206" t="str">
         <v>Candidate[0].UsageArea.Name</v>
       </c>
-      <c r="D199" t="str">
+      <c r="D201" t="str">
         <v>Albania - onshore.</v>
       </c>
-      <c r="M199"/>
-    </row>
-    <row r="200" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C200" s="208" t="str">
+      <c r="H201" s="173" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="I201" s="218" t="str">
+        <v>Between 18°E and 24°E.</v>
+      </c>
+      <c r="J201" s="218" t="str">
+        <v>Albania - onshore.</v>
+      </c>
+      <c r="K201" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M201"/>
+    </row>
+    <row r="202" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C202" s="206" t="str">
         <v>Candidate[0].UsageArea.WestLongitude</v>
       </c>
-      <c r="D200" t="str">
+      <c r="D202" t="str">
         <v>19.22</v>
       </c>
-      <c r="M200"/>
-    </row>
-    <row r="201" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C201" s="208" t="str">
+      <c r="H202" s="173" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="I202" s="218" t="str">
+        <v>18</v>
+      </c>
+      <c r="J202" s="218" t="str">
+        <v>19.22</v>
+      </c>
+      <c r="K202" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M202"/>
+    </row>
+    <row r="203" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C203" s="206" t="str">
         <v>Candidate[0].UsageArea.SouthLatitude</v>
       </c>
-      <c r="D201" t="str">
+      <c r="D203" t="str">
         <v>39.64</v>
       </c>
-      <c r="M201"/>
-    </row>
-    <row r="202" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C202" s="208" t="str">
+      <c r="H203" s="173" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="I203" s="218" t="str">
+        <v>-80</v>
+      </c>
+      <c r="J203" s="218" t="str">
+        <v>39.64</v>
+      </c>
+      <c r="K203" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M203"/>
+    </row>
+    <row r="204" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C204" s="206" t="str">
         <v>Candidate[0].UsageArea.EastLongitude</v>
       </c>
-      <c r="D202" t="str">
+      <c r="D204" t="str">
         <v>21.06</v>
       </c>
-      <c r="M202"/>
-    </row>
-    <row r="203" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C203" s="208" t="str">
+      <c r="H204" s="173" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="I204" s="218" t="str">
+        <v>24</v>
+      </c>
+      <c r="J204" s="218" t="str">
+        <v>21.06</v>
+      </c>
+      <c r="K204" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M204"/>
+    </row>
+    <row r="205" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C205" s="206" t="str">
         <v>Candidate[0].UsageArea.NorthLatitude</v>
       </c>
-      <c r="D203" t="str">
+      <c r="D205" t="str">
         <v>42.67</v>
       </c>
-      <c r="M203"/>
-    </row>
-    <row r="204" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C204" s="208" t="str">
+      <c r="H205" s="173" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="I205" s="218" t="str">
+        <v>84</v>
+      </c>
+      <c r="J205" s="218" t="str">
+        <v>42.67</v>
+      </c>
+      <c r="K205" s="218" t="str">
+        <v>&lt;null&gt;</v>
+      </c>
+      <c r="M205"/>
+    </row>
+    <row r="206" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C206" s="206" t="str">
         <v>Candidate[0].UsageArea.Center</v>
       </c>
-      <c r="D204" t="str">
+      <c r="D206" t="str">
         <v>X=41.155, Y=20.14</v>
       </c>
-      <c r="M204"/>
-    </row>
-    <row r="205" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C205" s="172" t="str">
-        <v>Candidate[1].RuntimeType</v>
-      </c>
-      <c r="D205" t="str">
-        <v>SharpProj.CoordinateOperation</v>
-      </c>
-      <c r="M205"/>
-    </row>
-    <row r="206" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C206" s="172" t="str">
-        <v>Candidate[1].PublicProperties</v>
-      </c>
-      <c r="D206" t="str">
-        <v>Accuracy, Context, GridUsages, HasBallParkTransformation, HasInverse, Identifier, Identifiers, IsAvailable, MethodName, Name, Parameters, Remarks, Scope, SourceCRS, TargetCRS, Type, UsageArea</v>
+      <c r="H206" s="173" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="I206" s="218" t="str">
+        <v>X=4500000, Y=223053.008659147</v>
+      </c>
+      <c r="J206" s="218" t="str">
+        <v>X=41.155, Y=20.14</v>
+      </c>
+      <c r="K206" s="218" t="str">
+        <v>&lt;null&gt;</v>
       </c>
       <c r="M206"/>
     </row>
@@ -47147,7 +47461,7 @@
       </c>
       <c r="M224"/>
     </row>
-    <row r="225" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C225" s="172" t="str">
         <v>Candidate[1].UsageArea.WestLongitude</v>
       </c>
@@ -47156,7 +47470,7 @@
       </c>
       <c r="M225"/>
     </row>
-    <row r="226" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C226" s="172" t="str">
         <v>Candidate[1].UsageArea.SouthLatitude</v>
       </c>
@@ -47165,7 +47479,7 @@
       </c>
       <c r="M226"/>
     </row>
-    <row r="227" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C227" s="172" t="str">
         <v>Candidate[1].UsageArea.EastLongitude</v>
       </c>
@@ -47174,7 +47488,7 @@
       </c>
       <c r="M227"/>
     </row>
-    <row r="228" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C228" s="172" t="str">
         <v>Candidate[1].UsageArea.NorthLatitude</v>
       </c>
@@ -47183,7 +47497,7 @@
       </c>
       <c r="M228"/>
     </row>
-    <row r="229" spans="3:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C229" s="172" t="str">
         <v>Candidate[1].UsageArea.Center</v>
       </c>
@@ -47192,379 +47506,435 @@
       </c>
       <c r="M229"/>
     </row>
-    <row r="230" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C230" s="208" t="str">
-        <v>Candidate[2].RuntimeType</v>
+    <row r="230" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C230" s="206" t="str">
+        <v>Candidate[2].Name</v>
       </c>
       <c r="D230" t="str">
-        <v>SharpProj.CoordinateOperation</v>
+        <v>axis order change (2D)</v>
       </c>
       <c r="M230"/>
-    </row>
-    <row r="231" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C231" s="208" t="str">
-        <v>Candidate[2].PublicProperties</v>
+      <c r="O230"/>
+    </row>
+    <row r="231" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C231" s="206" t="str">
+        <v>Candidate[2].Type</v>
       </c>
       <c r="D231" t="str">
-        <v>Accuracy, Context, GridUsages, HasBallParkTransformation, HasInverse, Identifier, Identifiers, IsAvailable, MethodName, Name, Parameters, Remarks, Scope, SourceCRS, TargetCRS, Type, UsageArea</v>
+        <v>Conversion</v>
       </c>
       <c r="M231"/>
-    </row>
-    <row r="232" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C232" s="208" t="str">
-        <v>Candidate[2].Name</v>
+      <c r="O231"/>
+    </row>
+    <row r="232" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C232" s="206" t="str">
+        <v>Candidate[2].Identifier</v>
       </c>
       <c r="D232" t="str">
-        <v>axis order change (2D)</v>
+        <v>EPSG:15498</v>
       </c>
       <c r="M232"/>
-    </row>
-    <row r="233" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C233" s="208" t="str">
-        <v>Candidate[2].Type</v>
+      <c r="O232"/>
+    </row>
+    <row r="233" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C233" s="206" t="str">
+        <v>Candidate[2].Identifiers</v>
       </c>
       <c r="D233" t="str">
-        <v>Conversion</v>
+        <v>EPSG:15498</v>
       </c>
       <c r="M233"/>
-    </row>
-    <row r="234" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C234" s="208" t="str">
-        <v>Candidate[2].Identifier</v>
+      <c r="O233"/>
+    </row>
+    <row r="234" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C234" s="206" t="str">
+        <v>Candidate[2].Accuracy</v>
       </c>
       <c r="D234" t="str">
-        <v>EPSG:15498</v>
+        <v/>
       </c>
       <c r="M234"/>
-    </row>
-    <row r="235" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C235" s="208" t="str">
-        <v>Candidate[2].Identifiers</v>
+      <c r="O234"/>
+    </row>
+    <row r="235" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C235" s="206" t="str">
+        <v>Candidate[2].IsAvailable</v>
       </c>
       <c r="D235" t="str">
-        <v>EPSG:15498</v>
+        <v>True</v>
       </c>
       <c r="M235"/>
-    </row>
-    <row r="236" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C236" s="208" t="str">
-        <v>Candidate[2].Accuracy</v>
+      <c r="O235"/>
+    </row>
+    <row r="236" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C236" s="206" t="str">
+        <v>Candidate[2].HasBallParkTransformation</v>
       </c>
       <c r="D236" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="M236"/>
-    </row>
-    <row r="237" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C237" s="208" t="str">
-        <v>Candidate[2].IsAvailable</v>
+      <c r="O236"/>
+    </row>
+    <row r="237" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C237" s="206" t="str">
+        <v>Candidate[2].HasInverse</v>
       </c>
       <c r="D237" t="str">
         <v>True</v>
       </c>
       <c r="M237"/>
-    </row>
-    <row r="238" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C238" s="208" t="str">
-        <v>Candidate[2].HasBallParkTransformation</v>
+      <c r="O237"/>
+    </row>
+    <row r="238" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C238" s="206" t="str">
+        <v>Candidate[2].MethodName</v>
       </c>
       <c r="D238" t="str">
-        <v>False</v>
+        <v>Axis Order Reversal (2D)</v>
       </c>
       <c r="M238"/>
-    </row>
-    <row r="239" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C239" s="208" t="str">
-        <v>Candidate[2].HasInverse</v>
+      <c r="O238"/>
+    </row>
+    <row r="239" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C239" s="206" t="str">
+        <v>Candidate[2].Scope</v>
       </c>
       <c r="D239" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="M239"/>
-    </row>
-    <row r="240" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C240" s="208" t="str">
-        <v>Candidate[2].MethodName</v>
+      <c r="O239"/>
+    </row>
+    <row r="240" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C240" s="206" t="str">
+        <v>Candidate[2].Remarks</v>
       </c>
       <c r="D240" t="str">
-        <v>Axis Order Reversal (2D)</v>
+        <v/>
       </c>
       <c r="M240"/>
-    </row>
-    <row r="241" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C241" s="208" t="str">
-        <v>Candidate[2].Scope</v>
+      <c r="O240"/>
+    </row>
+    <row r="241" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C241" s="206" t="str">
+        <v>Candidate[2].GridUsages</v>
       </c>
       <c r="D241" t="str">
         <v/>
       </c>
       <c r="M241"/>
-    </row>
-    <row r="242" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C242" s="208" t="str">
-        <v>Candidate[2].Remarks</v>
+      <c r="O241"/>
+    </row>
+    <row r="242" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C242" s="206" t="str">
+        <v>Candidate[2].Parameters</v>
       </c>
       <c r="D242" t="str">
         <v/>
       </c>
       <c r="M242"/>
-    </row>
-    <row r="243" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C243" s="208" t="str">
-        <v>Candidate[2].GridUsages</v>
+      <c r="O242"/>
+    </row>
+    <row r="243" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C243" s="206" t="str">
+        <v>Candidate[2].SourceCRS</v>
       </c>
       <c r="D243" t="str">
+        <v>WGS 84</v>
+      </c>
+      <c r="M243"/>
+      <c r="O243"/>
+    </row>
+    <row r="244" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C244" s="206" t="str">
+        <v>Candidate[2].TargetCRS</v>
+      </c>
+      <c r="D244" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="M244"/>
+      <c r="O244"/>
+    </row>
+    <row r="245" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C245" s="206" t="str">
+        <v>Candidate[2].Context</v>
+      </c>
+      <c r="D245" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M245"/>
+      <c r="O245"/>
+    </row>
+    <row r="246" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C246" s="206" t="str">
+        <v>Candidate[2].UsageArea</v>
+      </c>
+      <c r="D246" t="str">
         <v/>
       </c>
-      <c r="M243"/>
-    </row>
-    <row r="244" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C244" s="208" t="str">
-        <v>Candidate[2].Parameters</v>
-      </c>
-      <c r="D244" t="str">
-        <v/>
-      </c>
-      <c r="M244"/>
-    </row>
-    <row r="245" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C245" s="208" t="str">
-        <v>Candidate[2].SourceCRS</v>
-      </c>
-      <c r="D245" t="str">
-        <v>WGS 84</v>
-      </c>
-      <c r="M245"/>
-    </row>
-    <row r="246" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C246" s="208" t="str">
-        <v>Candidate[2].TargetCRS</v>
-      </c>
-      <c r="D246" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
       <c r="M246"/>
-    </row>
-    <row r="247" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C247" s="208" t="str">
-        <v>Candidate[2].Context</v>
-      </c>
-      <c r="D247" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
+      <c r="O246"/>
+    </row>
+    <row r="247" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M247"/>
-    </row>
-    <row r="248" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C248" s="208" t="str">
-        <v>Candidate[2].UsageArea</v>
-      </c>
-      <c r="D248" t="str">
-        <v/>
-      </c>
+      <c r="O247"/>
+    </row>
+    <row r="248" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M248"/>
-    </row>
-    <row r="249" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O248"/>
+    </row>
+    <row r="249" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M249"/>
-    </row>
-    <row r="250" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O249"/>
+    </row>
+    <row r="250" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M250"/>
-    </row>
-    <row r="251" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O250"/>
+    </row>
+    <row r="251" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M251"/>
-    </row>
-    <row r="252" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O251"/>
+    </row>
+    <row r="252" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M252"/>
-    </row>
-    <row r="253" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O252"/>
+    </row>
+    <row r="253" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M253"/>
-    </row>
-    <row r="254" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O253"/>
+    </row>
+    <row r="254" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M254"/>
-    </row>
-    <row r="255" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O254"/>
+    </row>
+    <row r="255" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M255"/>
-    </row>
-    <row r="256" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="O255"/>
+    </row>
+    <row r="256" spans="3:15" x14ac:dyDescent="0.35">
       <c r="M256"/>
+      <c r="O256"/>
     </row>
     <row r="257" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M257"/>
-      <c r="O257" s="111"/>
+      <c r="O257"/>
     </row>
     <row r="258" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M258"/>
-      <c r="O258" s="111"/>
+      <c r="O258"/>
     </row>
     <row r="259" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M259"/>
-      <c r="O259" s="111"/>
+      <c r="O259"/>
     </row>
     <row r="260" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M260"/>
-      <c r="O260" s="111"/>
+      <c r="O260"/>
     </row>
     <row r="261" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M261"/>
-      <c r="O261" s="111"/>
+      <c r="O261"/>
     </row>
     <row r="262" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M262"/>
-      <c r="O262" s="111"/>
+      <c r="O262"/>
     </row>
     <row r="263" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M263"/>
-      <c r="O263" s="111"/>
+      <c r="O263"/>
     </row>
     <row r="264" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M264"/>
-      <c r="O264" s="111"/>
+      <c r="O264"/>
     </row>
     <row r="265" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M265"/>
-      <c r="O265" s="111"/>
+      <c r="O265"/>
     </row>
     <row r="266" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M266"/>
-      <c r="O266" s="111"/>
+      <c r="O266"/>
     </row>
     <row r="267" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M267"/>
-      <c r="O267" s="111"/>
+      <c r="O267"/>
     </row>
     <row r="268" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M268"/>
-      <c r="O268" s="111"/>
+      <c r="O268"/>
     </row>
     <row r="269" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M269"/>
-      <c r="O269" s="111"/>
+      <c r="O269"/>
     </row>
     <row r="270" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M270"/>
-      <c r="O270" s="111"/>
+      <c r="O270"/>
     </row>
     <row r="271" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M271"/>
-      <c r="O271" s="111"/>
+      <c r="O271"/>
     </row>
     <row r="272" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M272"/>
-      <c r="O272" s="111"/>
+      <c r="O272"/>
     </row>
     <row r="273" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M273"/>
-      <c r="O273" s="111"/>
+      <c r="O273"/>
     </row>
     <row r="274" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M274"/>
-      <c r="O274" s="111"/>
+      <c r="O274"/>
     </row>
     <row r="275" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M275"/>
-      <c r="O275" s="111"/>
+      <c r="O275"/>
     </row>
     <row r="276" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M276"/>
-      <c r="O276" s="111"/>
+      <c r="O276"/>
     </row>
     <row r="277" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M277"/>
-      <c r="O277" s="111"/>
+      <c r="O277"/>
     </row>
     <row r="278" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M278"/>
-      <c r="O278" s="111"/>
+      <c r="O278"/>
     </row>
     <row r="279" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M279"/>
-      <c r="O279" s="111"/>
+      <c r="O279"/>
     </row>
     <row r="280" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M280"/>
-      <c r="O280" s="111"/>
+      <c r="O280"/>
     </row>
     <row r="281" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M281"/>
-      <c r="O281" s="111"/>
+      <c r="O281"/>
     </row>
     <row r="282" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M282"/>
-      <c r="O282" s="111"/>
+      <c r="O282"/>
     </row>
     <row r="283" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M283"/>
-      <c r="O283" s="111"/>
+      <c r="O283"/>
     </row>
     <row r="284" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M284"/>
-      <c r="O284" s="111"/>
+      <c r="O284"/>
     </row>
     <row r="285" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M285"/>
-      <c r="O285" s="111"/>
+      <c r="O285"/>
     </row>
     <row r="286" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M286"/>
-      <c r="O286" s="111"/>
+      <c r="O286"/>
     </row>
     <row r="287" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M287"/>
-      <c r="O287" s="111"/>
+      <c r="O287"/>
     </row>
     <row r="288" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M288"/>
-      <c r="O288" s="111"/>
-    </row>
-    <row r="289" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O288"/>
+    </row>
+    <row r="289" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M289"/>
-    </row>
-    <row r="290" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O289"/>
+    </row>
+    <row r="290" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M290"/>
-    </row>
-    <row r="291" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O290"/>
+    </row>
+    <row r="291" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M291"/>
-    </row>
-    <row r="292" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O291"/>
+    </row>
+    <row r="292" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M292"/>
-    </row>
-    <row r="293" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O292"/>
+    </row>
+    <row r="293" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M293"/>
-    </row>
-    <row r="294" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O293"/>
+    </row>
+    <row r="294" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M294"/>
-    </row>
-    <row r="295" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O294"/>
+    </row>
+    <row r="295" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M295"/>
-    </row>
-    <row r="296" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O295"/>
+    </row>
+    <row r="296" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M296"/>
-    </row>
-    <row r="297" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O296"/>
+    </row>
+    <row r="297" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M297"/>
-    </row>
-    <row r="298" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O297"/>
+    </row>
+    <row r="298" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M298"/>
-    </row>
-    <row r="299" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O298"/>
+    </row>
+    <row r="299" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M299"/>
-    </row>
-    <row r="300" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O299"/>
+    </row>
+    <row r="300" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M300"/>
-    </row>
-    <row r="301" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O300"/>
+    </row>
+    <row r="301" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M301"/>
-    </row>
-    <row r="302" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O301"/>
+    </row>
+    <row r="302" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M302"/>
-    </row>
-    <row r="303" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O302"/>
+    </row>
+    <row r="303" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M303"/>
-    </row>
-    <row r="304" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O303"/>
+    </row>
+    <row r="304" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M304"/>
-    </row>
-    <row r="305" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="O304"/>
+    </row>
+    <row r="305" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M305"/>
+      <c r="O305"/>
+    </row>
+    <row r="306" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M306"/>
+      <c r="O306"/>
+    </row>
+    <row r="307" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M307"/>
+      <c r="O307"/>
+    </row>
+    <row r="308" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M308"/>
+      <c r="O308"/>
+    </row>
+    <row r="309" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M309"/>
+      <c r="O309"/>
+    </row>
+    <row r="310" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M310"/>
+      <c r="O310"/>
+    </row>
+    <row r="311" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="M311"/>
+      <c r="O311"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F25A3F-A08A-4B5B-825D-2C1AA26364AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E954868-DF13-473D-9848-C4DD558A8D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="146">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -622,17 +622,23 @@
     <t xml:space="preserve"> CRS is deprecated</t>
   </si>
   <si>
-    <t>From</t>
+    <t>Source Crs</t>
   </si>
   <si>
-    <t>To</t>
+    <t>Target Crs</t>
+  </si>
+  <si>
+    <t>NAD27 / Alaska Albers</t>
+  </si>
+  <si>
+    <t>WGS 84</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000000"/>
@@ -640,9 +646,8 @@
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,8 +749,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,12 +843,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF66FFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66CCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1209,7 +1214,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1684,7 +1689,6 @@
     <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
@@ -1696,8 +1700,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1705,17 +1707,50 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1727,11 +1762,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF66CCFF"/>
+      <color rgb="FFCCFFFF"/>
       <color rgb="FF66FFFF"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFFFFFCC"/>
-      <color rgb="FFCCFFFF"/>
+      <color rgb="FF66CCFF"/>
       <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
@@ -39453,15 +39488,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55C8259-B2F0-4599-98D4-024E12781605}">
-  <dimension ref="A2:T311"/>
+  <dimension ref="A2:T286"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.36328125" style="61" customWidth="1"/>
     <col min="3" max="3" width="32.7265625" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.90625" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
     <col min="7" max="7" width="13.36328125" customWidth="1"/>
     <col min="8" max="8" width="12.36328125" customWidth="1"/>
     <col min="9" max="10" width="13.36328125" customWidth="1"/>
@@ -39505,20 +39540,20 @@
       <c r="D4" s="49">
         <v>2462</v>
       </c>
-      <c r="E4" s="211" t="b" cm="1">
+      <c r="E4" s="208" t="b" cm="1">
         <f t="array" ref="E4">_xll.PE.crs.IsDeprecated(D4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="208" t="str" cm="1">
+      <c r="F4" s="205" t="str" cm="1">
         <f t="array" ref="F4">_xll.PE.crs.AsProjString(D4)</f>
         <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
       </c>
-      <c r="G4" s="209"/>
-      <c r="H4" s="209"/>
-      <c r="I4" s="209"/>
-      <c r="J4" s="209"/>
-      <c r="K4" s="209"/>
-      <c r="L4" s="210"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="207"/>
       <c r="P4" s="167"/>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39528,7 +39563,7 @@
       <c r="D5" s="48">
         <v>4326</v>
       </c>
-      <c r="E5" s="211" t="b" cm="1">
+      <c r="E5" s="208" t="b" cm="1">
         <f t="array" ref="E5">_xll.PE.crs.IsDeprecated(D5)</f>
         <v>0</v>
       </c>
@@ -39541,7 +39576,7 @@
       <c r="I5" s="183"/>
       <c r="J5" s="183"/>
       <c r="K5" s="183"/>
-      <c r="L5" s="212"/>
+      <c r="L5" s="209"/>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M6"/>
@@ -39593,7 +39628,7 @@
         <v>File version</v>
       </c>
       <c r="E11" s="179" t="str">
-        <v>1.0.261016.1155</v>
+        <v>1.0.261019.1326</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39602,7 +39637,7 @@
         <v>Info version</v>
       </c>
       <c r="E12" s="181" t="str">
-        <v>1.0.261016.1155</v>
+        <v>1.0.261019.1326</v>
       </c>
       <c r="Q12" s="100" t="s">
         <v>44</v>
@@ -39612,13 +39647,13 @@
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="180" t="str">
+      <c r="D13" s="178" t="str">
         <v>Proj version</v>
       </c>
-      <c r="E13" s="181" t="str">
+      <c r="E13" s="179" t="str">
         <v>9.5.1</v>
       </c>
       <c r="Q13" s="46" t="s">
@@ -39629,21 +39664,23 @@
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C14" s="172" t="str" cm="1">
-        <f t="array" ref="C14">_xll.PE.trf.Options(0,0,0,0,0,0,"auto",0)</f>
+      <c r="C14" s="182" t="str" cm="1">
+        <f t="array" ref="C14">_xll.PE.trf.Options(0,0,0,0,0,0,"auto",0,,,,,,,,)</f>
         <v>Authority=0; Area=0,0,0,0; Accuracy=0; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
       </c>
-      <c r="D14" s="172"/>
-      <c r="E14" s="172"/>
-      <c r="F14" s="172"/>
-      <c r="G14" s="172"/>
-      <c r="H14" s="172"/>
-      <c r="I14" s="172"/>
-      <c r="J14" s="172"/>
-      <c r="K14" s="172"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="207"/>
-      <c r="N14" s="172"/>
+      <c r="D14" s="183"/>
+      <c r="E14" s="183"/>
+      <c r="F14" s="183"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="183"/>
+      <c r="L14" s="183"/>
+      <c r="M14" s="218"/>
+      <c r="N14" s="183"/>
+      <c r="O14" s="203"/>
+      <c r="P14" s="184"/>
       <c r="Q14" s="47" t="s">
         <v>20</v>
       </c>
@@ -39722,11 +39759,11 @@
         <f>E17-$D$7*COS(RADIANS(O17))</f>
         <v>4511477.2929155556</v>
       </c>
-      <c r="F16" s="132" cm="1">
-        <f t="array" ref="F16:G16">_xll.PE.trf.Transform($D$4,$D$5,D16,E16,C128)</f>
+      <c r="F16" s="135" cm="1">
+        <f t="array" ref="F16:G16">_xll.PE.trf.Transform($D$4,$D$5,D16,E16)</f>
         <v>19.627501288698802</v>
       </c>
-      <c r="G16" s="134">
+      <c r="G16" s="137">
         <v>40.728657406572829</v>
       </c>
       <c r="H16" s="135" t="str" cm="1">
@@ -39987,7 +40024,7 @@
         <v>4517571.1183339683</v>
       </c>
       <c r="F20" s="135" cm="1">
-        <f t="array" ref="F20:G20">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D20,E20)</f>
+        <f t="array" ref="F20:G20">_xll.PE.trf.Transform($D$4,$D$5,D20,E20)</f>
         <v>20.007599027220387</v>
       </c>
       <c r="G20" s="137">
@@ -40054,7 +40091,7 @@
         <v>4518129.2070844444</v>
       </c>
       <c r="F21" s="141" cm="1">
-        <f t="array" ref="F21:G21">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D21,E21)</f>
+        <f t="array" ref="F21:G21">_xll.PE.trf.Transform($D$4,$D$5,D21,E21)</f>
         <v>20.042444089865263</v>
       </c>
       <c r="G21" s="143">
@@ -40179,7 +40216,7 @@
         <v>4509248.2137425337</v>
       </c>
       <c r="F24" s="132" cm="1">
-        <f t="array" ref="F24:G24">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D24,E24)</f>
+        <f t="array" ref="F24:G24">_xll.PE.trf.Transform($D$4,$D$5,D24,E24)</f>
         <v>19.667912708680866</v>
       </c>
       <c r="G24" s="134">
@@ -40244,7 +40281,7 @@
         <v>4509971.1221385906</v>
       </c>
       <c r="F25" s="135" cm="1">
-        <f t="array" ref="F25:G25">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D25,E25)</f>
+        <f t="array" ref="F25:G25">_xll.PE.trf.Transform($D$4,$D$5,D25,E25)</f>
         <v>19.702232192676256</v>
       </c>
       <c r="G25" s="137">
@@ -40307,7 +40344,7 @@
         <v>4510935</v>
       </c>
       <c r="F26" s="138" cm="1">
-        <f t="array" ref="F26:G26">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D26,E26)</f>
+        <f t="array" ref="F26:G26">_xll.PE.trf.Transform($D$4,$D$5,D26,E26)</f>
         <v>19.748002911094968</v>
       </c>
       <c r="G26" s="140">
@@ -40372,7 +40409,7 @@
         <v>4513180</v>
       </c>
       <c r="F27" s="138" cm="1">
-        <f t="array" ref="F27:G27">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D27,E27)</f>
+        <f t="array" ref="F27:G27">_xll.PE.trf.Transform($D$4,$D$5,D27,E27)</f>
         <v>19.854659382414237</v>
       </c>
       <c r="G27" s="140">
@@ -40438,7 +40475,7 @@
         <v>4518740</v>
       </c>
       <c r="F28" s="138" cm="1">
-        <f t="array" ref="F28:G28">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D28,E28)</f>
+        <f t="array" ref="F28:G28">_xll.PE.trf.Transform($D$4,$D$5,D28,E28)</f>
         <v>20.099124970644958</v>
       </c>
       <c r="G28" s="140">
@@ -40506,7 +40543,7 @@
         <v>4519777.2910376322</v>
       </c>
       <c r="F29" s="135" cm="1">
-        <f t="array" ref="F29:G29">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D29,E29)</f>
+        <f t="array" ref="F29:G29">_xll.PE.trf.Transform($D$4,$D$5,D29,E29)</f>
         <v>20.144776595350073</v>
       </c>
       <c r="G29" s="137">
@@ -40573,7 +40610,7 @@
         <v>4520555.2593158567</v>
       </c>
       <c r="F30" s="141" cm="1">
-        <f t="array" ref="F30:G30">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D30,E30)</f>
+        <f t="array" ref="F30:G30">_xll.PE.trf.Transform($D$4,$D$5,D30,E30)</f>
         <v>20.17902421260742</v>
       </c>
       <c r="G30" s="143">
@@ -40698,7 +40735,7 @@
         <v>4525483.832561858</v>
       </c>
       <c r="F33" s="132" cm="1">
-        <f t="array" ref="F33:G33">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D33,E33)</f>
+        <f t="array" ref="F33:G33">_xll.PE.trf.Transform($D$4,$D$5,D33,E33)</f>
         <v>19.701095294756342</v>
       </c>
       <c r="G33" s="134">
@@ -40763,7 +40800,7 @@
         <v>4524196.0807782048</v>
       </c>
       <c r="F34" s="135" cm="1">
-        <f t="array" ref="F34:G34">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D34,E34)</f>
+        <f t="array" ref="F34:G34">_xll.PE.trf.Transform($D$4,$D$5,D34,E34)</f>
         <v>19.733442649612513</v>
       </c>
       <c r="G34" s="137">
@@ -40826,7 +40863,7 @@
         <v>4522479.0784</v>
       </c>
       <c r="F35" s="138" cm="1">
-        <f t="array" ref="F35:G35">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D35,E35)</f>
+        <f t="array" ref="F35:G35">_xll.PE.trf.Transform($D$4,$D$5,D35,E35)</f>
         <v>19.776555734991796</v>
       </c>
       <c r="G35" s="140">
@@ -40891,7 +40928,7 @@
         <v>4517866.0075000003</v>
       </c>
       <c r="F36" s="138" cm="1">
-        <f t="array" ref="F36:G36">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D36,E36)</f>
+        <f t="array" ref="F36:G36">_xll.PE.trf.Transform($D$4,$D$5,D36,E36)</f>
         <v>19.892292936682402</v>
       </c>
       <c r="G36" s="140">
@@ -40957,7 +40994,7 @@
         <v>4514669.1546</v>
       </c>
       <c r="F37" s="138" cm="1">
-        <f t="array" ref="F37:G37">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D37,E37)</f>
+        <f t="array" ref="F37:G37">_xll.PE.trf.Transform($D$4,$D$5,D37,E37)</f>
         <v>19.965689392996619</v>
       </c>
       <c r="G37" s="140">
@@ -41025,7 +41062,7 @@
         <v>4512826.2181084193</v>
       </c>
       <c r="F38" s="135" cm="1">
-        <f t="array" ref="F38:G38">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D38,E38)</f>
+        <f t="array" ref="F38:G38">_xll.PE.trf.Transform($D$4,$D$5,D38,E38)</f>
         <v>20.007973540197661</v>
       </c>
       <c r="G38" s="137">
@@ -41092,7 +41129,7 @@
         <v>4511444.0157397343</v>
       </c>
       <c r="F39" s="141" cm="1">
-        <f t="array" ref="F39:G39">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D39,E39)</f>
+        <f t="array" ref="F39:G39">_xll.PE.trf.Transform($D$4,$D$5,D39,E39)</f>
         <v>20.039673311207402</v>
       </c>
       <c r="G39" s="143">
@@ -41217,7 +41254,7 @@
         <v>4466849.4596596127</v>
       </c>
       <c r="F42" s="132" cm="1">
-        <f t="array" ref="F42:G42">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D42,E42)</f>
+        <f t="array" ref="F42:G42">_xll.PE.trf.Transform($D$4,$D$5,D42,E42)</f>
         <v>19.873652457410753</v>
       </c>
       <c r="G42" s="134">
@@ -41282,7 +41319,7 @@
         <v>4467896.6912340643</v>
       </c>
       <c r="F43" s="135" cm="1">
-        <f t="array" ref="F43:G43">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D43,E43)</f>
+        <f t="array" ref="F43:G43">_xll.PE.trf.Transform($D$4,$D$5,D43,E43)</f>
         <v>19.906574728018438</v>
       </c>
       <c r="G43" s="137">
@@ -41347,7 +41384,7 @@
         <v>4469293</v>
       </c>
       <c r="F44" s="138" cm="1">
-        <f t="array" ref="F44:G44">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D44,E44)</f>
+        <f t="array" ref="F44:G44">_xll.PE.trf.Transform($D$4,$D$5,D44,E44)</f>
         <v>19.950486102913491</v>
       </c>
       <c r="G44" s="140">
@@ -41413,7 +41450,7 @@
         <v>4479111.9987000003</v>
       </c>
       <c r="F45" s="138" cm="1">
-        <f t="array" ref="F45:G45">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D45,E45)</f>
+        <f t="array" ref="F45:G45">_xll.PE.trf.Transform($D$4,$D$5,D45,E45)</f>
         <v>20.259758719416958</v>
       </c>
       <c r="G45" s="140">
@@ -41481,7 +41518,7 @@
         <v>4480508.3074659361</v>
       </c>
       <c r="F46" s="135" cm="1">
-        <f t="array" ref="F46:G46">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D46,E46)</f>
+        <f t="array" ref="F46:G46">_xll.PE.trf.Transform($D$4,$D$5,D46,E46)</f>
         <v>20.303807202490884</v>
       </c>
       <c r="G46" s="137">
@@ -41548,7 +41585,7 @@
         <v>4481555.5390403876</v>
       </c>
       <c r="F47" s="141" cm="1">
-        <f t="array" ref="F47:G47">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D47,E47)</f>
+        <f t="array" ref="F47:G47">_xll.PE.trf.Transform($D$4,$D$5,D47,E47)</f>
         <v>20.336854707752281</v>
       </c>
       <c r="G47" s="143">
@@ -41673,7 +41710,7 @@
         <v>4464929.1109348536</v>
       </c>
       <c r="F50" s="132" cm="1">
-        <f t="array" ref="F50:G50">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D50,E50)</f>
+        <f t="array" ref="F50:G50">_xll.PE.trf.Transform($D$4,$D$5,D50,E50)</f>
         <v>19.900207757522892</v>
       </c>
       <c r="G50" s="134">
@@ -41738,7 +41775,7 @@
         <v>4465879.6348627731</v>
       </c>
       <c r="F51" s="135" cm="1">
-        <f t="array" ref="F51:G51">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D51,E51)</f>
+        <f t="array" ref="F51:G51">_xll.PE.trf.Transform($D$4,$D$5,D51,E51)</f>
         <v>19.933541273379543</v>
       </c>
       <c r="G51" s="137">
@@ -41803,7 +41840,7 @@
         <v>4467147.0000999998</v>
       </c>
       <c r="F52" s="138" cm="1">
-        <f t="array" ref="F52:G52">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D52,E52)</f>
+        <f t="array" ref="F52:G52">_xll.PE.trf.Transform($D$4,$D$5,D52,E52)</f>
         <v>19.97799981976652</v>
       </c>
       <c r="G52" s="140">
@@ -41869,7 +41906,7 @@
         <v>4475048.0003000004</v>
       </c>
       <c r="F53" s="138" cm="1">
-        <f t="array" ref="F53:G53">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D53,E53)</f>
+        <f t="array" ref="F53:G53">_xll.PE.trf.Transform($D$4,$D$5,D53,E53)</f>
         <v>20.255518710888996</v>
       </c>
       <c r="G53" s="140">
@@ -41937,7 +41974,7 @@
         <v>4476315.3655372271</v>
       </c>
       <c r="F54" s="135" cm="1">
-        <f t="array" ref="F54:G54">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D54,E54)</f>
+        <f t="array" ref="F54:G54">_xll.PE.trf.Transform($D$4,$D$5,D54,E54)</f>
         <v>20.300091131624491</v>
       </c>
       <c r="G54" s="137">
@@ -42004,7 +42041,7 @@
         <v>4477265.8894651467</v>
       </c>
       <c r="F55" s="141" cm="1">
-        <f t="array" ref="F55:G55">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D55,E55)</f>
+        <f t="array" ref="F55:G55">_xll.PE.trf.Transform($D$4,$D$5,D55,E55)</f>
         <v>20.333530712767278</v>
       </c>
       <c r="G55" s="143">
@@ -42129,7 +42166,7 @@
         <v>4463055.1312818611</v>
       </c>
       <c r="F58" s="132" cm="1">
-        <f t="array" ref="F58:G58">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D58,E58)</f>
+        <f t="array" ref="F58:G58">_xll.PE.trf.Transform($D$4,$D$5,D58,E58)</f>
         <v>19.925860955743484</v>
       </c>
       <c r="G58" s="134">
@@ -42194,7 +42231,7 @@
         <v>4463865.0748896347</v>
       </c>
       <c r="F59" s="135" cm="1">
-        <f t="array" ref="F59:G59">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D59,E59)</f>
+        <f t="array" ref="F59:G59">_xll.PE.trf.Transform($D$4,$D$5,D59,E59)</f>
         <v>19.959716888540239</v>
       </c>
       <c r="G59" s="137">
@@ -42259,7 +42296,7 @@
         <v>4464944.9996999996</v>
       </c>
       <c r="F60" s="138" cm="1">
-        <f t="array" ref="F60:G60">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D60,E60)</f>
+        <f t="array" ref="F60:G60">_xll.PE.trf.Transform($D$4,$D$5,D60,E60)</f>
         <v>20.00487023617189</v>
       </c>
       <c r="G60" s="140">
@@ -42325,7 +42362,7 @@
         <v>4470817.0005000001</v>
       </c>
       <c r="F61" s="138" cm="1">
-        <f t="array" ref="F61:G61">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D61,E61)</f>
+        <f t="array" ref="F61:G61">_xll.PE.trf.Transform($D$4,$D$5,D61,E61)</f>
         <v>20.250628652514411</v>
       </c>
       <c r="G61" s="140">
@@ -42393,7 +42430,7 @@
         <v>4471896.9253103649</v>
       </c>
       <c r="F62" s="135" cm="1">
-        <f t="array" ref="F62:G62">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D62,E62)</f>
+        <f t="array" ref="F62:G62">_xll.PE.trf.Transform($D$4,$D$5,D62,E62)</f>
         <v>20.295870360336661</v>
       </c>
       <c r="G62" s="137">
@@ -42460,7 +42497,7 @@
         <v>4472706.8689181386</v>
       </c>
       <c r="F63" s="141" cm="1">
-        <f t="array" ref="F63:G63">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D63,E63)</f>
+        <f t="array" ref="F63:G63">_xll.PE.trf.Transform($D$4,$D$5,D63,E63)</f>
         <v>20.32981057815698</v>
       </c>
       <c r="G63" s="143">
@@ -42581,7 +42618,7 @@
         <v>4450574.3227219004</v>
       </c>
       <c r="F66" s="132" cm="1">
-        <f t="array" ref="F66:G66">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D66,E66)</f>
+        <f t="array" ref="F66:G66">_xll.PE.trf.Transform($D$4,$D$5,D66,E66)</f>
         <v>19.99171711359562</v>
       </c>
       <c r="G66" s="134">
@@ -42646,7 +42683,7 @@
         <v>4452180.0220553717</v>
       </c>
       <c r="F67" s="135" cm="1">
-        <f t="array" ref="F67:G67">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D67,E67)</f>
+        <f t="array" ref="F67:G67">_xll.PE.trf.Transform($D$4,$D$5,D67,E67)</f>
         <v>20.021260198241439</v>
       </c>
       <c r="G67" s="137">
@@ -42709,7 +42746,7 @@
         <v>4454320.9545</v>
       </c>
       <c r="F68" s="138" cm="1">
-        <f t="array" ref="F68:G68">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D68,E68)</f>
+        <f t="array" ref="F68:G68">_xll.PE.trf.Transform($D$4,$D$5,D68,E68)</f>
         <v>20.06067098541865</v>
       </c>
       <c r="G68" s="140">
@@ -42774,7 +42811,7 @@
         <v>4459903.6739999996</v>
       </c>
       <c r="F69" s="138" cm="1">
-        <f t="array" ref="F69:G69">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D69,E69)</f>
+        <f t="array" ref="F69:G69">_xll.PE.trf.Transform($D$4,$D$5,D69,E69)</f>
         <v>20.163546599470713</v>
       </c>
       <c r="G69" s="140">
@@ -42840,7 +42877,7 @@
         <v>4465830.3525</v>
       </c>
       <c r="F70" s="138" cm="1">
-        <f t="array" ref="F70:G70">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D70,E70)</f>
+        <f t="array" ref="F70:G70">_xll.PE.trf.Transform($D$4,$D$5,D70,E70)</f>
         <v>20.236972394273813</v>
       </c>
       <c r="G70" s="140">
@@ -42908,7 +42945,7 @@
         <v>4468571.8112974633</v>
       </c>
       <c r="F71" s="135" cm="1">
-        <f t="array" ref="F71:G71">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D71,E71)</f>
+        <f t="array" ref="F71:G71">_xll.PE.trf.Transform($D$4,$D$5,D71,E71)</f>
         <v>20.270975922742149</v>
       </c>
       <c r="G71" s="137">
@@ -42975,7 +43012,7 @@
         <v>4470627.9053955609</v>
       </c>
       <c r="F72" s="141" cm="1">
-        <f t="array" ref="F72:G72">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D72,E72)</f>
+        <f t="array" ref="F72:G72">_xll.PE.trf.Transform($D$4,$D$5,D72,E72)</f>
         <v>20.296494997345555</v>
       </c>
       <c r="G72" s="143">
@@ -43100,7 +43137,7 @@
         <v>4441250.3036329644</v>
       </c>
       <c r="F75" s="132" cm="1">
-        <f t="array" ref="F75:G75">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D75,E75)</f>
+        <f t="array" ref="F75:G75">_xll.PE.trf.Transform($D$4,$D$5,D75,E75)</f>
         <v>20.009021806680682</v>
       </c>
       <c r="G75" s="134">
@@ -43165,7 +43202,7 @@
         <v>4442758.5208331225</v>
       </c>
       <c r="F76" s="135" cm="1">
-        <f t="array" ref="F76:G76">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D76,E76)</f>
+        <f t="array" ref="F76:G76">_xll.PE.trf.Transform($D$4,$D$5,D76,E76)</f>
         <v>20.039239468543986</v>
       </c>
       <c r="G76" s="137">
@@ -43228,7 +43265,7 @@
         <v>4444769.4770999998</v>
       </c>
       <c r="F77" s="138" cm="1">
-        <f t="array" ref="F77:G77">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D77,E77)</f>
+        <f t="array" ref="F77:G77">_xll.PE.trf.Transform($D$4,$D$5,D77,E77)</f>
         <v>20.079548896305266</v>
       </c>
       <c r="G77" s="140">
@@ -43293,7 +43330,7 @@
         <v>4450616.7803999996</v>
       </c>
       <c r="F78" s="138" cm="1">
-        <f t="array" ref="F78:G78">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D78,E78)</f>
+        <f t="array" ref="F78:G78">_xll.PE.trf.Transform($D$4,$D$5,D78,E78)</f>
         <v>20.196882297215772</v>
       </c>
       <c r="G78" s="140">
@@ -43359,7 +43396,7 @@
         <v>4459612.6317999996</v>
       </c>
       <c r="F79" s="138" cm="1">
-        <f t="array" ref="F79:G79">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D79,E79)</f>
+        <f t="array" ref="F79:G79">_xll.PE.trf.Transform($D$4,$D$5,D79,E79)</f>
         <v>20.333399268047305</v>
       </c>
       <c r="G79" s="140">
@@ -43427,7 +43464,7 @@
         <v>4462051.4748460185</v>
       </c>
       <c r="F80" s="135" cm="1">
-        <f t="array" ref="F80:G80">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D80,E80)</f>
+        <f t="array" ref="F80:G80">_xll.PE.trf.Transform($D$4,$D$5,D80,E80)</f>
         <v>20.370466902167522</v>
       </c>
       <c r="G80" s="137">
@@ -43494,7 +43531,7 @@
         <v>4463880.6071305331</v>
       </c>
       <c r="F81" s="141" cm="1">
-        <f t="array" ref="F81:G81">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D81,E81)</f>
+        <f t="array" ref="F81:G81">_xll.PE.trf.Transform($D$4,$D$5,D81,E81)</f>
         <v>20.398283565718462</v>
       </c>
       <c r="G81" s="143">
@@ -43619,7 +43656,7 @@
         <v>4429507.8151147934</v>
       </c>
       <c r="F84" s="132" cm="1">
-        <f t="array" ref="F84:G84">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D84,E84)</f>
+        <f t="array" ref="F84:G84">_xll.PE.trf.Transform($D$4,$D$5,D84,E84)</f>
         <v>20.069993444467798</v>
       </c>
       <c r="G84" s="134">
@@ -43684,7 +43721,7 @@
         <v>4431013.8744655959</v>
       </c>
       <c r="F85" s="135" cm="1">
-        <f t="array" ref="F85:G85">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D85,E85)</f>
+        <f t="array" ref="F85:G85">_xll.PE.trf.Transform($D$4,$D$5,D85,E85)</f>
         <v>20.100192626928944</v>
       </c>
       <c r="G85" s="137">
@@ -43747,7 +43784,7 @@
         <v>4433021.9535999997</v>
       </c>
       <c r="F86" s="138" cm="1">
-        <f t="array" ref="F86:G86">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D86,E86)</f>
+        <f t="array" ref="F86:G86">_xll.PE.trf.Transform($D$4,$D$5,D86,E86)</f>
         <v>20.140477274654241</v>
       </c>
       <c r="G86" s="140">
@@ -43812,7 +43849,7 @@
         <v>4439871.5713</v>
       </c>
       <c r="F87" s="138" cm="1">
-        <f t="array" ref="F87:G87">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D87,E87)</f>
+        <f t="array" ref="F87:G87">_xll.PE.trf.Transform($D$4,$D$5,D87,E87)</f>
         <v>20.278053401830466</v>
       </c>
       <c r="G87" s="140">
@@ -43878,7 +43915,7 @@
         <v>4450775.5307999998</v>
       </c>
       <c r="F88" s="138" cm="1">
-        <f t="array" ref="F88:G88">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D88,E88)</f>
+        <f t="array" ref="F88:G88">_xll.PE.trf.Transform($D$4,$D$5,D88,E88)</f>
         <v>20.472740821899968</v>
       </c>
       <c r="G88" s="140">
@@ -43946,7 +43983,7 @@
         <v>4452965.229134731</v>
       </c>
       <c r="F89" s="135" cm="1">
-        <f t="array" ref="F89:G89">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D89,E89)</f>
+        <f t="array" ref="F89:G89">_xll.PE.trf.Transform($D$4,$D$5,D89,E89)</f>
         <v>20.511905954708112</v>
       </c>
       <c r="G89" s="137">
@@ -44013,7 +44050,7 @@
         <v>4454607.5028857794</v>
       </c>
       <c r="F90" s="141" cm="1">
-        <f t="array" ref="F90:G90">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D90,E90)</f>
+        <f t="array" ref="F90:G90">_xll.PE.trf.Transform($D$4,$D$5,D90,E90)</f>
         <v>20.541294879939993</v>
       </c>
       <c r="G90" s="143">
@@ -44138,7 +44175,7 @@
         <v>4468581.3680245327</v>
       </c>
       <c r="F93" s="132" cm="1">
-        <f t="array" ref="F93:G93">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D93,E93)</f>
+        <f t="array" ref="F93:G93">_xll.PE.trf.Transform($D$4,$D$5,D93,E93)</f>
         <v>20.041822842787745</v>
       </c>
       <c r="G93" s="134">
@@ -44203,7 +44240,7 @@
         <v>4466546.5277140187</v>
       </c>
       <c r="F94" s="135" cm="1">
-        <f t="array" ref="F94:G94">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D94,E94)</f>
+        <f t="array" ref="F94:G94">_xll.PE.trf.Transform($D$4,$D$5,D94,E94)</f>
         <v>20.068017585449915</v>
       </c>
       <c r="G94" s="137">
@@ -44266,7 +44303,7 @@
         <v>4463833.4073000001</v>
       </c>
       <c r="F95" s="138" cm="1">
-        <f t="array" ref="F95:G95">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D95,E95)</f>
+        <f t="array" ref="F95:G95">_xll.PE.trf.Transform($D$4,$D$5,D95,E95)</f>
         <v>20.102922159653534</v>
       </c>
       <c r="G95" s="140">
@@ -44331,7 +44368,7 @@
         <v>4452879.6354</v>
       </c>
       <c r="F96" s="138" cm="1">
-        <f t="array" ref="F96:G96">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D96,E96)</f>
+        <f t="array" ref="F96:G96">_xll.PE.trf.Transform($D$4,$D$5,D96,E96)</f>
         <v>20.243591327481912</v>
       </c>
       <c r="G96" s="140">
@@ -44397,7 +44434,7 @@
         <v>4437480.8546000002</v>
       </c>
       <c r="F97" s="138" cm="1">
-        <f t="array" ref="F97:G97">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D97,E97)</f>
+        <f t="array" ref="F97:G97">_xll.PE.trf.Transform($D$4,$D$5,D97,E97)</f>
         <v>20.435390220595277</v>
       </c>
       <c r="G97" s="140">
@@ -44465,7 +44502,7 @@
         <v>4434727.9086254323</v>
       </c>
       <c r="F98" s="135" cm="1">
-        <f t="array" ref="F98:G98">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D98,E98)</f>
+        <f t="array" ref="F98:G98">_xll.PE.trf.Transform($D$4,$D$5,D98,E98)</f>
         <v>20.469598076487333</v>
       </c>
       <c r="G98" s="137">
@@ -44532,7 +44569,7 @@
         <v>4432663.1991445068</v>
       </c>
       <c r="F99" s="141" cm="1">
-        <f t="array" ref="F99:G99">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D99,E99)</f>
+        <f t="array" ref="F99:G99">_xll.PE.trf.Transform($D$4,$D$5,D99,E99)</f>
         <v>20.495237819768231</v>
       </c>
       <c r="G99" s="143">
@@ -44657,7 +44694,7 @@
         <v>4468437.1458815532</v>
       </c>
       <c r="F102" s="132" cm="1">
-        <f t="array" ref="F102:G102">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D102,E102)</f>
+        <f t="array" ref="F102:G102">_xll.PE.trf.Transform($D$4,$D$5,D102,E102)</f>
         <v>20.122614090696832</v>
       </c>
       <c r="G102" s="134">
@@ -44722,7 +44759,7 @@
         <v>4466599.7976466017</v>
       </c>
       <c r="F103" s="135" cm="1">
-        <f t="array" ref="F103:G103">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D103,E103)</f>
+        <f t="array" ref="F103:G103">_xll.PE.trf.Transform($D$4,$D$5,D103,E103)</f>
         <v>20.150731246325268</v>
       </c>
       <c r="G103" s="137">
@@ -44787,7 +44824,7 @@
         <v>4464150</v>
       </c>
       <c r="F104" s="138" cm="1">
-        <f t="array" ref="F104:G104">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D104,E104)</f>
+        <f t="array" ref="F104:G104">_xll.PE.trf.Transform($D$4,$D$5,D104,E104)</f>
         <v>20.188199773372965</v>
       </c>
       <c r="G104" s="140">
@@ -44853,7 +44890,7 @@
         <v>4445370</v>
       </c>
       <c r="F105" s="138" cm="1">
-        <f t="array" ref="F105:G105">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D105,E105)</f>
+        <f t="array" ref="F105:G105">_xll.PE.trf.Transform($D$4,$D$5,D105,E105)</f>
         <v>20.474635225434131</v>
       </c>
       <c r="G105" s="140">
@@ -44921,7 +44958,7 @@
         <v>4442920.2023533983</v>
       </c>
       <c r="F106" s="135" cm="1">
-        <f t="array" ref="F106:G106">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D106,E106)</f>
+        <f t="array" ref="F106:G106">_xll.PE.trf.Transform($D$4,$D$5,D106,E106)</f>
         <v>20.511896311461349</v>
       </c>
       <c r="G106" s="137">
@@ -44988,7 +45025,7 @@
         <v>4441082.8541184468</v>
       </c>
       <c r="F107" s="141" cm="1">
-        <f t="array" ref="F107:G107">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D107,E107)</f>
+        <f t="array" ref="F107:G107">_xll.PE.trf.Transform($D$4,$D$5,D107,E107)</f>
         <v>20.53982646884727</v>
       </c>
       <c r="G107" s="143">
@@ -45113,7 +45150,7 @@
         <v>4456901.3573793834</v>
       </c>
       <c r="F110" s="132" cm="1">
-        <f t="array" ref="F110:G110">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D110,E110)</f>
+        <f t="array" ref="F110:G110">_xll.PE.trf.Transform($D$4,$D$5,D110,E110)</f>
         <v>19.980295097411723</v>
       </c>
       <c r="G110" s="134">
@@ -45178,7 +45215,7 @@
         <v>4454655.0613596477</v>
       </c>
       <c r="F111" s="135" cm="1">
-        <f t="array" ref="F111:G111">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D111,E111)</f>
+        <f t="array" ref="F111:G111">_xll.PE.trf.Transform($D$4,$D$5,D111,E111)</f>
         <v>20.003956316830397</v>
       </c>
       <c r="G111" s="137">
@@ -45243,7 +45280,7 @@
         <v>4451660</v>
       </c>
       <c r="F112" s="138" cm="1">
-        <f t="array" ref="F112:G112">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D112,E112)</f>
+        <f t="array" ref="F112:G112">_xll.PE.trf.Transform($D$4,$D$5,D112,E112)</f>
         <v>20.035482907483946</v>
       </c>
       <c r="G112" s="140">
@@ -45309,7 +45346,7 @@
         <v>4430146</v>
       </c>
       <c r="F113" s="138" cm="1">
-        <f t="array" ref="F113:G113">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D113,E113)</f>
+        <f t="array" ref="F113:G113">_xll.PE.trf.Transform($D$4,$D$5,D113,E113)</f>
         <v>20.261217584877354</v>
       </c>
       <c r="G113" s="140">
@@ -45377,7 +45414,7 @@
         <v>4427150.9386403523</v>
       </c>
       <c r="F114" s="135" cm="1">
-        <f t="array" ref="F114:G114">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D114,E114)</f>
+        <f t="array" ref="F114:G114">_xll.PE.trf.Transform($D$4,$D$5,D114,E114)</f>
         <v>20.292542535155217</v>
       </c>
       <c r="G114" s="137">
@@ -45444,7 +45481,7 @@
         <v>4424904.6426206166</v>
       </c>
       <c r="F115" s="141" cm="1">
-        <f t="array" ref="F115:G115">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D115,E115)</f>
+        <f t="array" ref="F115:G115">_xll.PE.trf.Transform($D$4,$D$5,D115,E115)</f>
         <v>20.316020182948577</v>
       </c>
       <c r="G115" s="143">
@@ -45568,11 +45605,11 @@
         <f>E119-$D$7*COS(RADIANS(O119))</f>
         <v>4452852.3097855086</v>
       </c>
-      <c r="F118" s="132" cm="1">
-        <f t="array" ref="F118:G118">_xll.PE.trf.Transform($D$4,$D$5,D118,E118,$C$128)</f>
+      <c r="F118" s="135" cm="1">
+        <f t="array" ref="F118:G118">_xll.PE.trf.Transform($D$4,$D$5,D118,E118)</f>
         <v>20.155244386653319</v>
       </c>
-      <c r="G118" s="134">
+      <c r="G118" s="137">
         <v>40.205795085677487</v>
       </c>
       <c r="H118" s="132" t="str" cm="1">
@@ -45634,7 +45671,7 @@
         <v>4454594.5170202907</v>
       </c>
       <c r="F119" s="135" cm="1">
-        <f t="array" ref="F119:G119">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D119,E119)</f>
+        <f t="array" ref="F119:G119">_xll.PE.trf.Transform($D$4,$D$5,D119,E119)</f>
         <v>20.183739389448178</v>
       </c>
       <c r="G119" s="137">
@@ -45699,7 +45736,7 @@
         <v>4456917.46</v>
       </c>
       <c r="F120" s="138" cm="1">
-        <f t="array" ref="F120:G120">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D120,E120)</f>
+        <f t="array" ref="F120:G120">_xll.PE.trf.Transform($D$4,$D$5,D120,E120)</f>
         <v>20.22175353346173</v>
       </c>
       <c r="G120" s="140">
@@ -45765,7 +45802,7 @@
         <v>4461819.1283</v>
       </c>
       <c r="F121" s="138" cm="1">
-        <f t="array" ref="F121:G121">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D121,E121)</f>
+        <f t="array" ref="F121:G121">_xll.PE.trf.Transform($D$4,$D$5,D121,E121)</f>
         <v>20.302045697642804</v>
       </c>
       <c r="G121" s="140">
@@ -45833,7 +45870,7 @@
         <v>4464142.0712797092</v>
       </c>
       <c r="F122" s="135" cm="1">
-        <f t="array" ref="F122:G122">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D122,E122)</f>
+        <f t="array" ref="F122:G122">_xll.PE.trf.Transform($D$4,$D$5,D122,E122)</f>
         <v>20.340133885134307</v>
       </c>
       <c r="G122" s="137">
@@ -45900,7 +45937,7 @@
         <v>4465884.2785144914</v>
       </c>
       <c r="F123" s="141" cm="1">
-        <f t="array" ref="F123:G123">_xll.PE.trf.FromEpsgNoToEpsgNo($D$4,$D$5,D123,E123)</f>
+        <f t="array" ref="F123:G123">_xll.PE.trf.Transform($D$4,$D$5,D123,E123)</f>
         <v>20.3687156675634</v>
       </c>
       <c r="G123" s="143">
@@ -45990,1729 +46027,2144 @@
       </c>
     </row>
     <row r="126" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D126" s="198"/>
-      <c r="E126" s="198"/>
+      <c r="K126" s="61"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C127" s="182" t="str" cm="1">
-        <f t="array" ref="C127">_xll.PE.trf.Options(,,,,,1,,,,,,,,,1,)</f>
-        <v>Authority=EPSG; Area=; Accuracy=1; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=1; AllowDeprecatedCrs=False</v>
-      </c>
-      <c r="D127" s="183"/>
-      <c r="E127" s="183"/>
-      <c r="F127" s="183"/>
-      <c r="G127" s="183"/>
-      <c r="H127" s="183"/>
-      <c r="I127" s="183"/>
-      <c r="J127" s="183"/>
-      <c r="K127" s="183"/>
-      <c r="L127" s="183"/>
-      <c r="M127" s="183"/>
-      <c r="N127" s="183"/>
-      <c r="O127" s="204"/>
-      <c r="P127" s="183"/>
-      <c r="Q127" s="184"/>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="C127" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D127" s="224">
+        <f>D4</f>
+        <v>2462</v>
+      </c>
     </row>
     <row r="128" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C128" s="182" t="str" cm="1">
-        <f t="array" ref="C128">_xll.PE.trf.Options(,,,,,,,,,,,,,,0,)</f>
+      <c r="C128" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D128" s="225">
+        <f>D5</f>
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="129" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C129" s="227" t="str">
+        <f>C14</f>
+        <v>Authority=0; Area=0,0,0,0; Accuracy=0; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D129" s="228"/>
+      <c r="E129" s="228"/>
+      <c r="F129" s="228"/>
+      <c r="G129" s="228"/>
+      <c r="H129" s="228"/>
+      <c r="I129" s="228"/>
+      <c r="J129" s="228"/>
+      <c r="K129" s="228"/>
+      <c r="L129" s="228"/>
+      <c r="M129" s="229"/>
+      <c r="N129" s="228"/>
+      <c r="O129" s="230"/>
+      <c r="P129" s="231"/>
+    </row>
+    <row r="130" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C130" s="226" t="str" cm="1">
+        <f t="array" ref="C130:D153">_xll.PE.trf.TransformList(D127,D128,C129,"nil")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D130" s="103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C131" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D131" s="216" t="str">
+        <v>Inverse of 6-degree Gauss-Kruger zone 4 + Ballpark geographic offset from Albanian 1987 to WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="132" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C132" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D132" s="216" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+    </row>
+    <row r="133" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C133" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D133" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="134" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C134" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D134" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="135" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C135" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D135" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="136" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C136" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D136" s="216" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="137" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C137" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D137" s="216" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="138" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C138" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D138" s="216" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="139" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C139" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D139" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="140" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C140" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D140" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="141" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C141" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D141" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="142" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C142" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D142" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="143" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C143" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D143" s="216" t="str">
+        <v>nil</v>
+      </c>
+    </row>
+    <row r="144" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C144" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D144" s="216" t="str">
+        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C145" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D145" s="216" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="146" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C146" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D146" s="216" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+    </row>
+    <row r="147" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C147" s="12" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D147" s="216" t="str">
+        <v>UsageArea</v>
+      </c>
+    </row>
+    <row r="148" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C148" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D148" s="216" t="str">
+        <v>World</v>
+      </c>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C149" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D149" s="216" t="str">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C150" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D150" s="216" t="str">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="151" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C151" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D151" s="216" t="str">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="152" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C152" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D152" s="216" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="153" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C153" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D153" s="217" t="str">
+        <v>X=5696153.94925188, Y=484326.958550755</v>
+      </c>
+    </row>
+    <row r="154" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="M154"/>
+    </row>
+    <row r="155" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M155"/>
+    </row>
+    <row r="156" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C156" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D156" s="210">
+        <v>3857</v>
+      </c>
+      <c r="K156" s="61"/>
+      <c r="M156"/>
+    </row>
+    <row r="157" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C157" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D157" s="211">
+        <v>23095</v>
+      </c>
+      <c r="K157" s="61"/>
+      <c r="M157"/>
+    </row>
+    <row r="158" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C158" s="182" t="str" cm="1">
+        <f t="array" ref="C158">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,,1)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=True</v>
+      </c>
+      <c r="D158" s="183"/>
+      <c r="E158" s="183"/>
+      <c r="F158" s="183"/>
+      <c r="G158" s="183"/>
+      <c r="H158" s="183"/>
+      <c r="I158" s="183"/>
+      <c r="J158" s="183"/>
+      <c r="K158" s="183"/>
+      <c r="L158" s="183"/>
+      <c r="M158" s="183"/>
+      <c r="N158" s="183"/>
+      <c r="O158" s="184"/>
+      <c r="P158" s="184"/>
+    </row>
+    <row r="159" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C159" s="223" t="str" cm="1">
+        <f t="array" ref="C159:I182">_xll.PE.trf.TransformList(D156,D157,C158,"")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D159" s="215">
+        <v>0</v>
+      </c>
+      <c r="E159" s="215">
+        <v>1</v>
+      </c>
+      <c r="F159" s="215">
+        <v>2</v>
+      </c>
+      <c r="G159" s="215">
+        <v>3</v>
+      </c>
+      <c r="H159" s="215">
+        <v>4</v>
+      </c>
+      <c r="I159" s="5">
+        <v>5</v>
+      </c>
+      <c r="M159"/>
+    </row>
+    <row r="160" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C160" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D160" s="212" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (18) + TM 5 NE</v>
+      </c>
+      <c r="E160" s="212" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (32) + TM 5 NE</v>
+      </c>
+      <c r="F160" s="212" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
+      </c>
+      <c r="G160" s="172" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (1) + TM 5 NE</v>
+      </c>
+      <c r="H160" s="172" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
+      </c>
+      <c r="I160" s="179" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
+      </c>
+      <c r="M160"/>
+    </row>
+    <row r="161" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C161" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D161" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="E161" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="F161" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="G161" s="172" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="H161" s="172" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="I161" s="179" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="M161"/>
+    </row>
+    <row r="162" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C162" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D162" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E162" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F162" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G162" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H162" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I162" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M162"/>
+    </row>
+    <row r="163" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C163" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D163" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E163" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F163" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G163" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H163" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I163" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M163"/>
+    </row>
+    <row r="164" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C164" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D164" s="212" t="str">
+        <v>1</v>
+      </c>
+      <c r="E164" s="212" t="str">
+        <v>5</v>
+      </c>
+      <c r="F164" s="212" t="str">
+        <v>6</v>
+      </c>
+      <c r="G164" s="172" t="str">
+        <v>10</v>
+      </c>
+      <c r="H164" s="172" t="str">
+        <v>1</v>
+      </c>
+      <c r="I164" s="179" t="str">
+        <v>2</v>
+      </c>
+      <c r="M164"/>
+    </row>
+    <row r="165" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C165" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D165" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="E165" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="F165" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="G165" s="172" t="str">
+        <v>True</v>
+      </c>
+      <c r="H165" s="172" t="str">
+        <v>True</v>
+      </c>
+      <c r="I165" s="179" t="str">
+        <v>True</v>
+      </c>
+      <c r="M165"/>
+    </row>
+    <row r="166" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C166" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D166" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="E166" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="F166" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="G166" s="172" t="str">
+        <v>False</v>
+      </c>
+      <c r="H166" s="172" t="str">
+        <v>False</v>
+      </c>
+      <c r="I166" s="179" t="str">
+        <v>False</v>
+      </c>
+      <c r="M166"/>
+    </row>
+    <row r="167" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C167" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D167" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="E167" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="F167" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="G167" s="172" t="str">
+        <v>True</v>
+      </c>
+      <c r="H167" s="172" t="str">
+        <v>True</v>
+      </c>
+      <c r="I167" s="179" t="str">
+        <v>True</v>
+      </c>
+      <c r="M167"/>
+    </row>
+    <row r="168" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C168" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D168" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E168" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F168" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G168" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H168" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I168" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M168"/>
+    </row>
+    <row r="169" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C169" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D169" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E169" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F169" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G169" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H169" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I169" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M169"/>
+    </row>
+    <row r="170" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C170" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D170" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E170" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F170" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G170" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H170" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I170" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M170"/>
+    </row>
+    <row r="171" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C171" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D171" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E171" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F171" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G171" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H171" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I171" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M171"/>
+    </row>
+    <row r="172" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C172" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D172" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E172" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F172" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G172" s="172" t="str">
+        <v/>
+      </c>
+      <c r="H172" s="172" t="str">
+        <v/>
+      </c>
+      <c r="I172" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M172"/>
+    </row>
+    <row r="173" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C173" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D173" s="212" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="E173" s="212" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="F173" s="212" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="G173" s="172" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="H173" s="172" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="I173" s="179" t="str">
+        <v>WGS 84 / Pseudo-Mercator</v>
+      </c>
+      <c r="M173"/>
+    </row>
+    <row r="174" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C174" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D174" s="212" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="E174" s="212" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="F174" s="212" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="G174" s="172" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="H174" s="172" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="I174" s="179" t="str">
+        <v>ED50 / TM 5 NE</v>
+      </c>
+      <c r="M174"/>
+    </row>
+    <row r="175" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C175" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D175" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="E175" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="F175" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="G175" s="172" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="H175" s="172" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="I175" s="179" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M175"/>
+    </row>
+    <row r="176" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C176" s="12" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D176" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="E176" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="F176" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="G176" s="172" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="H176" s="172" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="I176" s="179" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="M176"/>
+    </row>
+    <row r="177" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C177" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D177" s="212" t="str">
+        <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
+      </c>
+      <c r="E177" s="212" t="str">
+        <v>Netherlands - offshore North Sea.</v>
+      </c>
+      <c r="F177" s="212" t="str">
+        <v>Austria; Denmark; France; Germany (west); Netherlands; Switzerland.</v>
+      </c>
+      <c r="G177" s="172" t="str">
+        <v>Austria; Belgium; Denmark; Finland; Faroe islands; France; Germany (west); Gibraltar; Greece; Italy; Luxembourg; Netherlands; Norway; Portugal; Spain; Sweden; Switzerland.</v>
+      </c>
+      <c r="H177" s="172" t="str">
+        <v>Germany - offshore North Sea.</v>
+      </c>
+      <c r="I177" s="179" t="str">
+        <v>France - onshore and offshore, mainland and Corsica (France métropolitaine including Corsica).</v>
+      </c>
+      <c r="M177"/>
+    </row>
+    <row r="178" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C178" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D178" s="212" t="str">
+        <v>-16.1</v>
+      </c>
+      <c r="E178" s="212" t="str">
+        <v>2.53</v>
+      </c>
+      <c r="F178" s="212" t="str">
+        <v>-4.87</v>
+      </c>
+      <c r="G178" s="172" t="str">
+        <v>-9.56</v>
+      </c>
+      <c r="H178" s="172" t="str">
+        <v>3.34</v>
+      </c>
+      <c r="I178" s="179" t="str">
+        <v>-9.86</v>
+      </c>
+      <c r="M178"/>
+    </row>
+    <row r="179" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C179" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D179" s="212" t="str">
+        <v>47.42</v>
+      </c>
+      <c r="E179" s="212" t="str">
+        <v>51.44</v>
+      </c>
+      <c r="F179" s="212" t="str">
+        <v>42.33</v>
+      </c>
+      <c r="G179" s="172" t="str">
+        <v>34.88</v>
+      </c>
+      <c r="H179" s="172" t="str">
+        <v>53.58</v>
+      </c>
+      <c r="I179" s="179" t="str">
+        <v>41.15</v>
+      </c>
+      <c r="M179"/>
+    </row>
+    <row r="180" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C180" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D180" s="212" t="str">
+        <v>10.86</v>
+      </c>
+      <c r="E180" s="212" t="str">
+        <v>6.37</v>
+      </c>
+      <c r="F180" s="212" t="str">
+        <v>17.17</v>
+      </c>
+      <c r="G180" s="172" t="str">
+        <v>31.59</v>
+      </c>
+      <c r="H180" s="172" t="str">
+        <v>8.88</v>
+      </c>
+      <c r="I180" s="179" t="str">
+        <v>10.38</v>
+      </c>
+      <c r="M180"/>
+    </row>
+    <row r="181" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C181" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D181" s="212" t="str">
+        <v>63.89</v>
+      </c>
+      <c r="E181" s="212" t="str">
+        <v>55.77</v>
+      </c>
+      <c r="F181" s="212" t="str">
+        <v>57.8</v>
+      </c>
+      <c r="G181" s="172" t="str">
+        <v>71.24</v>
+      </c>
+      <c r="H181" s="172" t="str">
+        <v>55.92</v>
+      </c>
+      <c r="I181" s="179" t="str">
+        <v>51.56</v>
+      </c>
+      <c r="M181"/>
+    </row>
+    <row r="182" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C182" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D182" s="213" t="str">
+        <v>X=-291657.065878377, Y=7666392.98144475</v>
+      </c>
+      <c r="E182" s="213" t="str">
+        <v>X=495371.734030067, Y=7106130.774072</v>
+      </c>
+      <c r="F182" s="213" t="str">
+        <v>X=684614.868378632, Y=6567980.67490485</v>
+      </c>
+      <c r="G182" s="214" t="str">
+        <v>X=1226184.19108791, Y=7816211.44812981</v>
+      </c>
+      <c r="H182" s="214" t="str">
+        <v>X=680162.088746901, Y=7316758.79219274</v>
+      </c>
+      <c r="I182" s="181" t="str">
+        <v>X=28943.0676062511, Y=5877723.68014364</v>
+      </c>
+      <c r="M182"/>
+    </row>
+    <row r="183" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="M183"/>
+    </row>
+    <row r="184" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M184"/>
+    </row>
+    <row r="185" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C185" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D185" s="210">
+        <v>2964</v>
+      </c>
+      <c r="E185" s="222" t="s">
+        <v>144</v>
+      </c>
+      <c r="M185"/>
+    </row>
+    <row r="186" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C186" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D186" s="221">
+        <v>4326</v>
+      </c>
+      <c r="E186" s="222" t="s">
+        <v>145</v>
+      </c>
+      <c r="M186"/>
+    </row>
+    <row r="187" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C187" s="182" t="str" cm="1">
+        <f t="array" ref="C187">_xll.PE.trf.Options(,,,,,,,,,,,,0,,,)</f>
         <v>Authority=EPSG; Area=; Accuracy=; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
       </c>
-      <c r="D128" s="183"/>
-      <c r="E128" s="183"/>
-      <c r="F128" s="183"/>
-      <c r="G128" s="183"/>
-      <c r="H128" s="183"/>
-      <c r="I128" s="183"/>
-      <c r="J128" s="183"/>
-      <c r="K128" s="183"/>
-      <c r="L128" s="183"/>
-      <c r="M128" s="183"/>
-      <c r="N128" s="183"/>
-      <c r="O128" s="204"/>
-      <c r="P128" s="183"/>
-      <c r="Q128" s="184"/>
-    </row>
-    <row r="129" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F129" s="180" cm="1">
-        <f t="array" ref="F129:G129">_xll.PE.trf.LatLongToWebMercatorEx(G123,F123,C127)</f>
-        <v>4488904.7260120427</v>
-      </c>
-      <c r="G129" s="181">
-        <v>2316761.8960968899</v>
-      </c>
-      <c r="I129" s="180" cm="1">
-        <f t="array" ref="I129:J129">_xll.PE.trf.LatLongToWebMercator(G123,F123)</f>
-        <v>2267435.056226131</v>
-      </c>
-      <c r="J129" s="181">
-        <v>4913212.9116666559</v>
-      </c>
-      <c r="M129"/>
-    </row>
-    <row r="130" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C130" s="173" t="s">
-        <v>136</v>
-      </c>
-      <c r="D130" s="172" t="str" cm="1">
-        <f t="array" ref="D130">_xll.PE.crs.GeodeticCRS.Name(D4)</f>
-        <v>Albanian 1987</v>
-      </c>
-      <c r="F130" s="213">
-        <v>2267435.0562261301</v>
-      </c>
-      <c r="G130" s="214">
-        <v>4913212.9116666559</v>
-      </c>
-      <c r="I130" s="213">
-        <v>2267435.056226131</v>
-      </c>
-      <c r="J130" s="214">
-        <v>4913212.9116666559</v>
-      </c>
-      <c r="M130"/>
-    </row>
-    <row r="131" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C131" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="D131" s="172" t="str" cm="1">
-        <f t="array" ref="D131">_xll.PE.crs.GeodeticCRS.Type(D4)</f>
-        <v>Geographic2DCrs</v>
-      </c>
-      <c r="F131" s="215">
-        <f>F129-F130</f>
-        <v>2221469.6697859126</v>
-      </c>
-      <c r="G131" s="216">
-        <f>G129-G130</f>
-        <v>-2596451.0155697661</v>
-      </c>
-      <c r="I131" s="215">
-        <f>I129-I130</f>
+      <c r="D187" s="183"/>
+      <c r="E187" s="183"/>
+      <c r="F187" s="183"/>
+      <c r="G187" s="183"/>
+      <c r="H187" s="183"/>
+      <c r="I187" s="183"/>
+      <c r="J187" s="183"/>
+      <c r="K187" s="183"/>
+      <c r="L187" s="183"/>
+      <c r="M187" s="183"/>
+      <c r="N187" s="183"/>
+      <c r="O187" s="184"/>
+      <c r="P187" s="184"/>
+    </row>
+    <row r="188" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B188"/>
+      <c r="C188" s="223" t="str" cm="1">
+        <f t="array" ref="C188:M211">_xll.PE.trf.TransformList(D185,D186,C187, "")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D188" s="215">
         <v>0</v>
       </c>
-      <c r="J131" s="216">
-        <f>J129-J130</f>
+      <c r="E188" s="215">
+        <v>1</v>
+      </c>
+      <c r="F188" s="215">
+        <v>2</v>
+      </c>
+      <c r="G188" s="215">
+        <v>3</v>
+      </c>
+      <c r="H188" s="215">
+        <v>4</v>
+      </c>
+      <c r="I188" s="215">
+        <v>5</v>
+      </c>
+      <c r="J188" s="215">
+        <v>6</v>
+      </c>
+      <c r="K188" s="215">
+        <v>7</v>
+      </c>
+      <c r="L188" s="215">
+        <v>8</v>
+      </c>
+      <c r="M188" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B189"/>
+      <c r="C189" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
+      </c>
+      <c r="E189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
+      </c>
+      <c r="F189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
+      </c>
+      <c r="G189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
+      </c>
+      <c r="H189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
+      </c>
+      <c r="I189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
+      </c>
+      <c r="J189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
+      </c>
+      <c r="K189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
+      </c>
+      <c r="L189" s="212" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
+      </c>
+      <c r="M189" s="219" t="str">
+        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="190" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B190"/>
+      <c r="C190" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="E190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="F190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="G190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="H190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="I190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="J190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="K190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="L190" s="212" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="M190" s="219" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+    </row>
+    <row r="191" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B191"/>
+      <c r="C191" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L191" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M191" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B192"/>
+      <c r="C192" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L192" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M192" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B193"/>
+      <c r="C193" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D193" s="212" t="str">
+        <v>5</v>
+      </c>
+      <c r="E193" s="212" t="str">
+        <v>12</v>
+      </c>
+      <c r="F193" s="212" t="str">
+        <v>2</v>
+      </c>
+      <c r="G193" s="212" t="str">
+        <v>20</v>
+      </c>
+      <c r="H193" s="212" t="str">
+        <v>8</v>
+      </c>
+      <c r="I193" s="212" t="str">
+        <v>10</v>
+      </c>
+      <c r="J193" s="212" t="str">
+        <v>13</v>
+      </c>
+      <c r="K193" s="212" t="str">
+        <v>15</v>
+      </c>
+      <c r="L193" s="212" t="str">
+        <v>18</v>
+      </c>
+      <c r="M193" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B194"/>
+      <c r="C194" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="E194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="F194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="G194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="H194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="I194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="J194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="K194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="L194" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="M194" s="219" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="195" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B195"/>
+      <c r="C195" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="E195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="F195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="G195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="H195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="I195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="J195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="K195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="L195" s="212" t="str">
+        <v>False</v>
+      </c>
+      <c r="M195" s="219" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="196" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B196"/>
+      <c r="C196" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="E196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="F196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="G196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="H196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="I196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="J196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="K196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="L196" s="212" t="str">
+        <v>True</v>
+      </c>
+      <c r="M196" s="219" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="197" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B197"/>
+      <c r="C197" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L197" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M197" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B198"/>
+      <c r="C198" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L198" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M198" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B199"/>
+      <c r="C199" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L199" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M199" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B200"/>
+      <c r="C200" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L200" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M200" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B201"/>
+      <c r="C201" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="E201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="F201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="G201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="H201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="I201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="J201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="K201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="L201" s="212" t="str">
+        <v/>
+      </c>
+      <c r="M201" s="219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B202"/>
+      <c r="C202" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="E202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="F202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="G202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="H202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="I202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="J202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="K202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="L202" s="212" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="M202" s="219" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+    </row>
+    <row r="203" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B203"/>
+      <c r="C203" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="E203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="F203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="G203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="H203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="I203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="J203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="K203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="L203" s="212" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="M203" s="219" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="204" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B204"/>
+      <c r="C204" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="E204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="F204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="G204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="H204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="I204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="J204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="K204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="L204" s="212" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M204" s="219" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+    </row>
+    <row r="205" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B205"/>
+      <c r="C205" s="12" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="E205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="F205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="G205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="H205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="I205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="J205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="K205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="L205" s="212" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="M205" s="219" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="O205"/>
+    </row>
+    <row r="206" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B206"/>
+      <c r="C206" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D206" s="212" t="str">
+        <v>United States (USA) - Alaska including EEZ.</v>
+      </c>
+      <c r="E206" s="212" t="str">
+        <v>United States (USA) - Alaska mainland.</v>
+      </c>
+      <c r="F206" s="212" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="G206" s="212" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="H206" s="212" t="str">
+        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
+      </c>
+      <c r="I206" s="212" t="str">
+        <v>Canada - Yukon.</v>
+      </c>
+      <c r="J206" s="212" t="str">
+        <v>Canada - Alberta; British Columbia.</v>
+      </c>
+      <c r="K206" s="212" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
+      </c>
+      <c r="L206" s="212" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
+      </c>
+      <c r="M206" s="219" t="str">
+        <v>World</v>
+      </c>
+      <c r="O206"/>
+    </row>
+    <row r="207" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B207"/>
+      <c r="C207" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D207" s="212" t="str">
+        <v>167.65</v>
+      </c>
+      <c r="E207" s="212" t="str">
+        <v>-168.26</v>
+      </c>
+      <c r="F207" s="212" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="G207" s="212" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="H207" s="212" t="str">
+        <v>-136.46</v>
+      </c>
+      <c r="I207" s="212" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="J207" s="212" t="str">
+        <v>-139.04</v>
+      </c>
+      <c r="K207" s="212" t="str">
+        <v>-178.3</v>
+      </c>
+      <c r="L207" s="212" t="str">
+        <v>172.42</v>
+      </c>
+      <c r="M207" s="219" t="str">
+        <v>-180</v>
+      </c>
+      <c r="O207"/>
+    </row>
+    <row r="208" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B208"/>
+      <c r="C208" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D208" s="212" t="str">
+        <v>47.88</v>
+      </c>
+      <c r="E208" s="212" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="F208" s="212" t="str">
+        <v>40</v>
+      </c>
+      <c r="G208" s="212" t="str">
+        <v>40</v>
+      </c>
+      <c r="H208" s="212" t="str">
+        <v>49</v>
+      </c>
+      <c r="I208" s="212" t="str">
+        <v>59.99</v>
+      </c>
+      <c r="J208" s="212" t="str">
+        <v>48.25</v>
+      </c>
+      <c r="K208" s="212" t="str">
+        <v>51.54</v>
+      </c>
+      <c r="L208" s="212" t="str">
+        <v>51.3</v>
+      </c>
+      <c r="M208" s="219" t="str">
+        <v>-90</v>
+      </c>
+      <c r="O208"/>
+    </row>
+    <row r="209" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B209"/>
+      <c r="C209" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D209" s="212" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="E209" s="212" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="F209" s="212" t="str">
+        <v>-44</v>
+      </c>
+      <c r="G209" s="212" t="str">
+        <v>-44</v>
+      </c>
+      <c r="H209" s="212" t="str">
+        <v>-60.72</v>
+      </c>
+      <c r="I209" s="212" t="str">
+        <v>-123.91</v>
+      </c>
+      <c r="J209" s="212" t="str">
+        <v>-109.98</v>
+      </c>
+      <c r="K209" s="212" t="str">
+        <v>-164.84</v>
+      </c>
+      <c r="L209" s="212" t="str">
+        <v>179.86</v>
+      </c>
+      <c r="M209" s="219" t="str">
+        <v>180</v>
+      </c>
+      <c r="O209"/>
+    </row>
+    <row r="210" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B210"/>
+      <c r="C210" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D210" s="212" t="str">
+        <v>74.71</v>
+      </c>
+      <c r="E210" s="212" t="str">
+        <v>71.4</v>
+      </c>
+      <c r="F210" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="G210" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="H210" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="I210" s="212" t="str">
+        <v>69.7</v>
+      </c>
+      <c r="J210" s="212" t="str">
+        <v>60.01</v>
+      </c>
+      <c r="K210" s="212" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="L210" s="212" t="str">
+        <v>53.07</v>
+      </c>
+      <c r="M210" s="219" t="str">
+        <v>90</v>
+      </c>
+      <c r="O210"/>
+    </row>
+    <row r="211" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B211"/>
+      <c r="C211" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D211" s="213" t="str">
+        <v>X=-1588108.78400993, Y=4653218.0046065</v>
+      </c>
+      <c r="E211" s="213" t="str">
+        <v>X=997429.291647658, Y=4946549.42959731</v>
+      </c>
+      <c r="F211" s="213" t="str">
+        <v>X=10065812.5662102, Y=7108107.30892012</v>
+      </c>
+      <c r="G211" s="213" t="str">
+        <v>X=10065812.5662102, Y=7108107.30892012</v>
+      </c>
+      <c r="H211" s="213" t="str">
+        <v>X=8492926.6648403, Y=7635942.58187141</v>
+      </c>
+      <c r="I211" s="213" t="str">
+        <v>X=3484722.01098932, Y=5966394.92755121</v>
+      </c>
+      <c r="J211" s="213" t="str">
+        <v>X=6396219.97160481, Y=2999807.81964541</v>
+      </c>
+      <c r="K211" s="213" t="str">
+        <v>X=-3872417.46753571, Y=1638056.1329905</v>
+      </c>
+      <c r="L211" s="213" t="str">
+        <v>X=-6512034.35982648, Y=2293627.08879407</v>
+      </c>
+      <c r="M211" s="220" t="str">
+        <v>X=30428.2699143998, Y=12753882.6489658</v>
+      </c>
+      <c r="O211"/>
+    </row>
+    <row r="212" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B212"/>
+      <c r="M212"/>
+      <c r="O212"/>
+    </row>
+    <row r="213" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B213"/>
+      <c r="M213"/>
+      <c r="O213"/>
+    </row>
+    <row r="214" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B214"/>
+      <c r="M214"/>
+      <c r="O214"/>
+    </row>
+    <row r="215" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B215"/>
+      <c r="M215"/>
+      <c r="O215"/>
+    </row>
+    <row r="216" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B216"/>
+      <c r="M216"/>
+      <c r="O216"/>
+    </row>
+    <row r="217" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B217"/>
+      <c r="M217"/>
+      <c r="O217"/>
+    </row>
+    <row r="218" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B218"/>
+      <c r="M218"/>
+      <c r="O218"/>
+    </row>
+    <row r="219" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B219"/>
+      <c r="C219" s="182" t="str" cm="1">
+        <f t="array" ref="C219:G221">_xll.PE.xfm.ListTransformPipelines($D$4,$D$5)</f>
+        <v>PipelineID</v>
+      </c>
+      <c r="D219" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="E219" s="183" t="str">
+        <v>Accuracy(m)</v>
+      </c>
+      <c r="F219" s="183" t="str">
+        <v>Grids</v>
+      </c>
+      <c r="G219" s="184" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="J219" t="s">
         <v>0</v>
       </c>
-      <c r="M131"/>
-    </row>
-    <row r="132" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C132" t="s">
-        <v>138</v>
-      </c>
-      <c r="D132" s="172" t="str" cm="1">
-        <f t="array" ref="D132">_xll.PE.crs.AsJsonString(D4)</f>
-        <v>{
-  "$schema": "https://proj.org/schemas/v0.7/projjson.schema.json",
-  "type": "ProjectedCRS",
-  "name": "Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)",
-  "base_crs": {
-    "name": "Albanian 1987",
-    "datum": {
-      "type": "GeodeticReferenceFrame",
-      "name": "Albanian 1987",
-      "ellipsoid": {
-        "name": "Krassowsky 1940",
-        "semi_major_axis": 6378245,
-        "inverse_flattening": 298.3
-      }
-    },
-    "coordinate_system": {
-      "subtype": "ellipsoidal",
-      "axis": [
-        {
-          "name": "Geodetic latitude",
-          "abbreviation": "Lat",
-          "direction": "north",
-          "unit": "degree"
-        },
-        {
-          "name": "Geodetic longitude",
-          "abbreviation": "Lon",
-          "direction": "east",
-          "unit": "degree"
-        }
-      ]
-    },
-    "id": {
-      "authority": "EPSG",
-      "code": 4191
-    }
-  },
-  "conversion": {
-    "name": "6-degree Gauss-Kruger zone 4",
-    "method": {
-      "name": "Transverse Mercator",
-      "id": {
-        "authority": "EPSG",
-        "code": 9807
-      }
-    },
-    "parameters": [
-      {
-        "name": "Latitude of natural origin",
-        "value": 0,
-        "unit": "degree",
-        "id": {
-          "authority": "EPSG",
-          "code": 8801
-        }
-      },
-      {
-        "name": "Longitude of natural origin",
-        "value": 21,
-        "unit": "degree",
-        "id": {
-          "authority": "EPSG",
-          "code": 8802
-        }
-      },
-      {
-        "name": "Scale factor at natural origin",
-        "value": 1,
-        "unit": "unity",
-        "id": {
-          "authority": "EPSG",
-          "code": 8805
-        }
-      },
-      {
-        "name": "False easting",
-        "value": 4500000,
-        "unit": "metre",
-        "id": {
-          "authority": "EPSG",
-          "code": 8806
-        }
-      },
-      {
-        "name": "False northing",
-        "value": 0,
-        "unit": "metre",
-        "id": {
-          "authority": "EPSG",
-          "code": 8807
-        }
-      }
-    ],
-    "id": {
-      "authority": "EPSG",
-      "code": 16204
-    }
-  },
-  "coordinate_system": {
-    "subtype": "Cartesian",
-    "axis": [
-      {
-        "name": "Easting",
-        "abbreviation": "Y",
-        "direction": "east",
-        "unit": "metre"
-      },
-      {
-        "name": "Northing",
-        "abbreviation": "X",
-        "direction": "north",
-        "unit": "metre"
-      }
-    ]
-  },
-  "scope": "Cadastre, engineering survey, topographic mapping.",
-  "area": "Albania - onshore.",
-  "bbox": {
-    "south_latitude": 39.64,
-    "west_longitude": 19.22,
-    "north_latitude": 42.67,
-    "east_longitude": 21.06
-  },
-  "remarks": "Axis order reversed compared to EPSG:2462"
-}</v>
-      </c>
-      <c r="M132"/>
-    </row>
-    <row r="133" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D133" s="172" t="str" cm="1">
-        <f t="array" ref="D133">_xll.PE.crs.AsProjString(D4)</f>
-        <v>+proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +units=m +no_defs +type=crs</v>
-      </c>
-      <c r="M133"/>
-    </row>
-    <row r="134" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D134" s="172" t="str" cm="1">
-        <f t="array" ref="D134">_xll.PE.crs.AsWktString(D4)</f>
-        <v>PROJCRS["Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)",
-    BASEGEOGCRS["Albanian 1987",
-        DATUM["Albanian 1987",
-            ELLIPSOID["Krassowsky 1940",6378245,298.3,
-                LENGTHUNIT["metre",1]]],
-        PRIMEM["Greenwich",0,
-            ANGLEUNIT["degree",0.0174532925199433]],
-        ID["EPSG",4191]],
-    CONVERSION["6-degree Gauss-Kruger zone 4",
-        METHOD["Transverse Mercator",
-            ID["EPSG",9807]],
-        PARAMETER["Latitude of natural origin",0,
-            ANGLEUNIT["degree",0.0174532925199433],
-            ID["EPSG",8801]],
-        PARAMETER["Longitude of natural origin",21,
-            ANGLEUNIT["degree",0.0174532925199433],
-            ID["EPSG",8802]],
-        PARAMETER["Scale factor at natural origin",1,
-            SCALEUNIT["unity",1],
-            ID["EPSG",8805]],
-        PARAMETER["False easting",4500000,
-            LENGTHUNIT["metre",1],
-            ID["EPSG",8806]],
-        PARAMETER["False northing",0,
-            LENGTHUNIT["metre",1],
-            ID["EPSG",8807]],
-        ID["EPSG",16204]],
-    CS[Cartesian,2],
-        AXIS["easting (Y)",east,
-            ORDER[1],
-            LENGTHUNIT["metre",1,
-                ID["EPSG",9001]]],
-        AXIS["northing (X)",north,
-            ORDER[2],
-            LENGTHUNIT["metre",1,
-                ID["EPSG",9001]]],
-    USAGE[
-        SCOPE["Cadastre, engineering survey, topographic mapping."],
-        AREA["Albania - onshore."],
-        BBOX[39.64,19.22,42.67,21.06]],
-    REMARK["Axis order reversed compared to EPSG:2462"]]</v>
-      </c>
-      <c r="M134"/>
-    </row>
-    <row r="135" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D135" s="174" t="str" cm="1">
-        <f t="array" ref="D135">_xll.PE.crs.Axis.Abbreviation(D4,0,TRUE)</f>
-        <v>Y</v>
-      </c>
-      <c r="M135"/>
-    </row>
-    <row r="136" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="D136" s="174" cm="1">
-        <f t="array" ref="D136">_xll.PE.crs.Axis.Count(D4,TRUE)</f>
+      <c r="K219" s="61"/>
+      <c r="M219"/>
+      <c r="O219"/>
+    </row>
+    <row r="220" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B220"/>
+      <c r="C220" s="198">
+        <v>1</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
+      </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" s="199" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="K220" s="61"/>
+      <c r="M220"/>
+      <c r="O220"/>
+    </row>
+    <row r="221" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B221"/>
+      <c r="C221" s="200">
         <v>2</v>
       </c>
-      <c r="M136"/>
-    </row>
-    <row r="137" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="M137"/>
-    </row>
-    <row r="139" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="M139"/>
-    </row>
-    <row r="140" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M140"/>
-    </row>
-    <row r="141" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C141" s="182" t="str" cm="1">
-        <f t="array" ref="C141:G143">_xll.PE.xfm.ListTransformPipelines($D$4,$D$5)</f>
-        <v>PipelineID</v>
-      </c>
-      <c r="D141" s="183" t="str">
+      <c r="D221" s="201" t="str">
+        <v>Albanian 1987 to WGS 84 (1)</v>
+      </c>
+      <c r="E221" s="201">
+        <v>1</v>
+      </c>
+      <c r="F221" s="201" t="str">
+        <v/>
+      </c>
+      <c r="G221" s="202" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="K221" s="61"/>
+      <c r="M221"/>
+      <c r="O221"/>
+    </row>
+    <row r="222" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B222"/>
+      <c r="K222" s="61"/>
+      <c r="M222"/>
+      <c r="O222"/>
+    </row>
+    <row r="223" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C223" s="182" t="str" cm="1">
+        <f t="array" ref="C223:L226">_xll.PE.trf.ListTransformOptions($D$4,$D$5)</f>
+        <v>CandidateIndex</v>
+      </c>
+      <c r="D223" s="183" t="str">
+        <v>DefaultSelection</v>
+      </c>
+      <c r="E223" s="183" t="str">
         <v>Name</v>
       </c>
-      <c r="E141" s="183" t="str">
-        <v>Accuracy(m)</v>
-      </c>
-      <c r="F141" s="183" t="str">
-        <v>Grids</v>
-      </c>
-      <c r="G141" s="184" t="str">
+      <c r="F223" s="183" t="str">
+        <v>Type</v>
+      </c>
+      <c r="G223" s="183" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="H223" s="183" t="str">
         <v>IsAvailable</v>
       </c>
-      <c r="J141" t="s">
+      <c r="I223" s="183" t="str">
+        <v>HasBallPark</v>
+      </c>
+      <c r="J223" s="183" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="K223" s="203" t="str">
+        <v>Pros</v>
+      </c>
+      <c r="L223" s="184" t="str">
+        <v>Cons</v>
+      </c>
+      <c r="M223"/>
+      <c r="O223"/>
+    </row>
+    <row r="224" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C224" s="198">
         <v>0</v>
       </c>
-      <c r="K141" s="61"/>
-      <c r="M141"/>
-    </row>
-    <row r="142" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C142" s="199">
+      <c r="D224" t="str">
+        <v>Only</v>
+      </c>
+      <c r="E224" t="str">
+        <v>Albanian 1987 to WGS 84 (1)</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Transformation</v>
+      </c>
+      <c r="G224">
         <v>1</v>
       </c>
-      <c r="D142" t="str">
+      <c r="H224" t="b">
+        <v>1</v>
+      </c>
+      <c r="I224" t="b">
+        <v>0</v>
+      </c>
+      <c r="J224" t="str">
+        <v>Albania - onshore.</v>
+      </c>
+      <c r="K224" s="61" t="str">
+        <v>Available; Non-ballpark; Accuracy=1; Has usage area; Default selection</v>
+      </c>
+      <c r="L224" s="199" t="str">
+        <v/>
+      </c>
+      <c r="M224"/>
+      <c r="O224"/>
+    </row>
+    <row r="225" spans="3:15" x14ac:dyDescent="0.35">
+      <c r="C225" s="198">
+        <v>1</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Only</v>
+      </c>
+      <c r="E225" t="str">
         <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
       </c>
-      <c r="E142" t="str">
+      <c r="F225" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225" t="b">
+        <v>1</v>
+      </c>
+      <c r="I225" t="b">
+        <v>0</v>
+      </c>
+      <c r="J225" t="str">
+        <v>Between 18°E and 24°E.</v>
+      </c>
+      <c r="K225" s="61" t="str">
+        <v>Available; Non-ballpark; Has usage area; Default selection</v>
+      </c>
+      <c r="L225" s="199" t="str">
+        <v>No reported accuracy</v>
+      </c>
+      <c r="M225"/>
+      <c r="O225"/>
+    </row>
+    <row r="226" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C226" s="200">
+        <v>2</v>
+      </c>
+      <c r="D226" s="201" t="str">
+        <v>Only</v>
+      </c>
+      <c r="E226" s="201" t="str">
+        <v>axis order change (2D)</v>
+      </c>
+      <c r="F226" s="201" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="G226" s="201">
+        <v>0</v>
+      </c>
+      <c r="H226" s="201" t="b">
+        <v>1</v>
+      </c>
+      <c r="I226" s="201" t="b">
+        <v>0</v>
+      </c>
+      <c r="J226" s="201" t="str">
         <v/>
       </c>
-      <c r="F142" t="str">
-        <v/>
-      </c>
-      <c r="G142" s="200" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="K142" s="61"/>
-      <c r="M142"/>
-    </row>
-    <row r="143" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C143" s="201">
-        <v>2</v>
-      </c>
-      <c r="D143" s="202" t="str">
-        <v>Albanian 1987 to WGS 84 (1)</v>
-      </c>
-      <c r="E143" s="202">
-        <v>1</v>
-      </c>
-      <c r="F143" s="202" t="str">
-        <v/>
-      </c>
-      <c r="G143" s="203" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="K143" s="61"/>
-      <c r="M143"/>
-    </row>
-    <row r="144" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K144" s="61"/>
-      <c r="M144"/>
-    </row>
-    <row r="145" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C145" s="182" t="str" cm="1">
-        <f t="array" ref="C145:L148">_xll.PE.trf.ListTransformOptions($D$4,$D$5)</f>
-        <v>CandidateIndex</v>
-      </c>
-      <c r="D145" s="183" t="str">
-        <v>DefaultSelection</v>
-      </c>
-      <c r="E145" s="183" t="str">
-        <v>Name</v>
-      </c>
-      <c r="F145" s="183" t="str">
-        <v>Type</v>
-      </c>
-      <c r="G145" s="183" t="str">
-        <v>Accuracy</v>
-      </c>
-      <c r="H145" s="183" t="str">
-        <v>IsAvailable</v>
-      </c>
-      <c r="I145" s="183" t="str">
-        <v>HasBallPark</v>
-      </c>
-      <c r="J145" s="183" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="K145" s="204" t="str">
-        <v>Pros</v>
-      </c>
-      <c r="L145" s="184" t="str">
-        <v>Cons</v>
-      </c>
-      <c r="M145"/>
-    </row>
-    <row r="146" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C146" s="199">
-        <v>0</v>
-      </c>
-      <c r="D146" t="str">
-        <v>Only</v>
-      </c>
-      <c r="E146" t="str">
-        <v>Albanian 1987 to WGS 84 (1)</v>
-      </c>
-      <c r="F146" t="str">
-        <v>Transformation</v>
-      </c>
-      <c r="G146">
-        <v>1</v>
-      </c>
-      <c r="H146" t="b">
-        <v>1</v>
-      </c>
-      <c r="I146" t="b">
-        <v>0</v>
-      </c>
-      <c r="J146" t="str">
-        <v>Albania - onshore.</v>
-      </c>
-      <c r="K146" s="61" t="str">
-        <v>Available; Non-ballpark; Accuracy=1; Has usage area; Default selection</v>
-      </c>
-      <c r="L146" s="200" t="str">
-        <v/>
-      </c>
-      <c r="M146"/>
-    </row>
-    <row r="147" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C147" s="199">
-        <v>1</v>
-      </c>
-      <c r="D147" t="str">
-        <v>Only</v>
-      </c>
-      <c r="E147" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
-      </c>
-      <c r="F147" t="str">
-        <v>Conversion</v>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147" t="b">
-        <v>1</v>
-      </c>
-      <c r="I147" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" t="str">
-        <v>Between 18°E and 24°E.</v>
-      </c>
-      <c r="K147" s="61" t="str">
-        <v>Available; Non-ballpark; Has usage area; Default selection</v>
-      </c>
-      <c r="L147" s="200" t="str">
+      <c r="K226" s="204" t="str">
+        <v>Available; Non-ballpark; Default selection</v>
+      </c>
+      <c r="L226" s="202" t="str">
         <v>No reported accuracy</v>
       </c>
-      <c r="M147"/>
-    </row>
-    <row r="148" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C148" s="201">
-        <v>2</v>
-      </c>
-      <c r="D148" s="202" t="str">
-        <v>Only</v>
-      </c>
-      <c r="E148" s="202" t="str">
-        <v>axis order change (2D)</v>
-      </c>
-      <c r="F148" s="202" t="str">
-        <v>Conversion</v>
-      </c>
-      <c r="G148" s="202">
-        <v>0</v>
-      </c>
-      <c r="H148" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="I148" s="202" t="b">
-        <v>0</v>
-      </c>
-      <c r="J148" s="202" t="str">
-        <v/>
-      </c>
-      <c r="K148" s="205" t="str">
-        <v>Available; Non-ballpark; Default selection</v>
-      </c>
-      <c r="L148" s="203" t="str">
-        <v>No reported accuracy</v>
-      </c>
-      <c r="M148"/>
-    </row>
-    <row r="149" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="K149" s="61"/>
-      <c r="M149"/>
-    </row>
-    <row r="150" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="K150" s="61"/>
-      <c r="M150"/>
-    </row>
-    <row r="151" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C151">
-        <v>2462</v>
-      </c>
-      <c r="K151" s="61"/>
-      <c r="M151"/>
-    </row>
-    <row r="152" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C152" s="217">
-        <v>4326</v>
-      </c>
-      <c r="D152" t="s">
-        <v>142</v>
-      </c>
-      <c r="K152" s="61"/>
-      <c r="M152"/>
-    </row>
-    <row r="153" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C153" s="217">
-        <v>3857</v>
-      </c>
-      <c r="D153" t="s">
-        <v>143</v>
-      </c>
-      <c r="K153" s="61"/>
-      <c r="M153"/>
-    </row>
-    <row r="154" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="K154" s="61"/>
-      <c r="M154"/>
-    </row>
-    <row r="155" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="M155"/>
-    </row>
-    <row r="156" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C156" s="172" t="str" cm="1">
-        <f t="array" ref="C156:D246">_xll.PE.trf.ListTransformInfo(C151,C152)</f>
-        <v>SourceCrs</v>
-      </c>
-      <c r="D156" t="str">
-        <v>2462</v>
-      </c>
-      <c r="M156"/>
-    </row>
-    <row r="157" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C157" s="172" t="str">
-        <v>DestinationCrs</v>
-      </c>
-      <c r="D157" t="str">
-        <v>4326</v>
-      </c>
-      <c r="M157"/>
-    </row>
-    <row r="158" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C158" s="172" t="str">
-        <v>Transform.Name</v>
-      </c>
-      <c r="D158" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4 + Albanian 1987 to WGS 84 (1) + axis order change (2D)</v>
-      </c>
-      <c r="M158"/>
-    </row>
-    <row r="159" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C159" s="172" t="str">
-        <v>Transform.Type</v>
-      </c>
-      <c r="D159" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="M159"/>
-    </row>
-    <row r="160" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C160" s="172" t="str">
-        <v>Transform.Identifier</v>
-      </c>
-      <c r="D160" t="str">
-        <v/>
-      </c>
-      <c r="M160"/>
-    </row>
-    <row r="161" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C161" s="172" t="str">
-        <v>Transform.Identifiers</v>
-      </c>
-      <c r="D161" t="str">
-        <v/>
-      </c>
-      <c r="M161"/>
-    </row>
-    <row r="162" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C162" s="172" t="str">
-        <v>Transform.Accuracy</v>
-      </c>
-      <c r="D162" t="str">
-        <v>1</v>
-      </c>
-      <c r="M162"/>
-    </row>
-    <row r="163" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C163" s="172" t="str">
-        <v>Transform.Count</v>
-      </c>
-      <c r="D163" t="str">
-        <v>3</v>
-      </c>
-      <c r="M163"/>
-    </row>
-    <row r="164" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C164" s="172" t="str">
-        <v>Transform.IsAvailable</v>
-      </c>
-      <c r="D164" t="str">
-        <v>True</v>
-      </c>
-      <c r="M164"/>
-    </row>
-    <row r="165" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C165" s="172" t="str">
-        <v>Transform.HasBallParkTransformation</v>
-      </c>
-      <c r="D165" t="str">
-        <v>False</v>
-      </c>
-      <c r="M165"/>
-    </row>
-    <row r="166" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C166" s="172" t="str">
-        <v>Transform.HasInverse</v>
-      </c>
-      <c r="D166" t="str">
-        <v>True</v>
-      </c>
-      <c r="M166"/>
-    </row>
-    <row r="167" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C167" s="172" t="str">
-        <v>Transform.MethodName</v>
-      </c>
-      <c r="D167" t="str">
-        <v/>
-      </c>
-      <c r="M167"/>
-    </row>
-    <row r="168" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C168" s="172" t="str">
-        <v>Transform.Scope</v>
-      </c>
-      <c r="D168" t="str">
-        <v/>
-      </c>
-      <c r="M168"/>
-    </row>
-    <row r="169" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C169" s="172" t="str">
-        <v>Transform.Remarks</v>
-      </c>
-      <c r="D169" t="str">
-        <v/>
-      </c>
-      <c r="M169"/>
-    </row>
-    <row r="170" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C170" s="172" t="str">
-        <v>Transform.GridUsages</v>
-      </c>
-      <c r="D170" t="str">
-        <v/>
-      </c>
-      <c r="M170"/>
-    </row>
-    <row r="171" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C171" s="172" t="str">
-        <v>Transform.Parameters</v>
-      </c>
-      <c r="D171" t="str">
-        <v/>
-      </c>
-      <c r="M171"/>
-    </row>
-    <row r="172" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C172" s="172" t="str">
-        <v>Transform.SourceCRS</v>
-      </c>
-      <c r="D172" t="str">
-        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
-      </c>
-      <c r="M172"/>
-    </row>
-    <row r="173" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C173" s="172" t="str">
-        <v>Transform.TargetCRS</v>
-      </c>
-      <c r="D173" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
-      <c r="M173"/>
-    </row>
-    <row r="174" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C174" s="172" t="str">
-        <v>Transform.Context</v>
-      </c>
-      <c r="D174" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="M174"/>
-    </row>
-    <row r="175" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C175" s="172" t="str">
-        <v>Transform.UsageArea</v>
-      </c>
-      <c r="D175" t="str">
-        <v>SharpProj.Proj.UsageArea</v>
-      </c>
-      <c r="M175"/>
-    </row>
-    <row r="176" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C176" s="172" t="str">
-        <v>Transform.UsageArea.Name</v>
-      </c>
-      <c r="D176" t="str">
-        <v>Albania - onshore.</v>
-      </c>
-      <c r="M176"/>
-    </row>
-    <row r="177" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C177" s="172" t="str">
-        <v>Transform.UsageArea.WestLongitude</v>
-      </c>
-      <c r="D177" t="str">
-        <v>19.22</v>
-      </c>
-      <c r="M177"/>
-    </row>
-    <row r="178" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C178" s="172" t="str">
-        <v>Transform.UsageArea.SouthLatitude</v>
-      </c>
-      <c r="D178" t="str">
-        <v>39.64</v>
-      </c>
-      <c r="M178"/>
-    </row>
-    <row r="179" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C179" s="172" t="str">
-        <v>Transform.UsageArea.EastLongitude</v>
-      </c>
-      <c r="D179" t="str">
-        <v>21.06</v>
-      </c>
-      <c r="M179"/>
-    </row>
-    <row r="180" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C180" s="172" t="str">
-        <v>Transform.UsageArea.NorthLatitude</v>
-      </c>
-      <c r="D180" t="str">
-        <v>42.67</v>
-      </c>
-      <c r="M180"/>
-    </row>
-    <row r="181" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C181" s="172" t="str">
-        <v>Transform.UsageArea.Center</v>
-      </c>
-      <c r="D181" t="str">
-        <v>X=4426173.53255827, Y=4558658.03284345</v>
-      </c>
-      <c r="M181"/>
-    </row>
-    <row r="182" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C182" s="172" t="str">
-        <v>Transform.EnumerableCount</v>
-      </c>
-      <c r="D182" t="str">
-        <v>3</v>
-      </c>
-      <c r="M182"/>
-    </row>
-    <row r="183" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C183" s="172" t="str">
-        <v>Transform.EnumerableItems</v>
-      </c>
-      <c r="D183" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4 | Albanian 1987 to WGS 84 (1) | axis order change (2D)</v>
-      </c>
-      <c r="H183" s="173" t="str" cm="1">
-        <f t="array" ref="H183:K206">_xll.PE.trf.TransformList(C151,C152)</f>
-        <v>TransformNo.</v>
-      </c>
-      <c r="I183" s="219">
-        <v>0</v>
-      </c>
-      <c r="J183" s="219">
-        <v>1</v>
-      </c>
-      <c r="K183" s="219">
-        <v>2</v>
-      </c>
-      <c r="M183"/>
-    </row>
-    <row r="184" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C184" s="206" t="str">
-        <v>Candidate[0].Name</v>
-      </c>
-      <c r="D184" t="str">
-        <v>Albanian 1987 to WGS 84 (1)</v>
-      </c>
-      <c r="H184" s="173" t="str">
-        <v>Name</v>
-      </c>
-      <c r="I184" s="218" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
-      </c>
-      <c r="J184" s="218" t="str">
-        <v>Albanian 1987 to WGS 84 (1)</v>
-      </c>
-      <c r="K184" s="218" t="str">
-        <v>axis order change (2D)</v>
-      </c>
-      <c r="M184"/>
-    </row>
-    <row r="185" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C185" s="206" t="str">
-        <v>Candidate[0].Type</v>
-      </c>
-      <c r="D185" t="str">
-        <v>Transformation</v>
-      </c>
-      <c r="H185" s="173" t="str">
-        <v>Type</v>
-      </c>
-      <c r="I185" s="218" t="str">
-        <v>Conversion</v>
-      </c>
-      <c r="J185" s="218" t="str">
-        <v>Transformation</v>
-      </c>
-      <c r="K185" s="218" t="str">
-        <v>Conversion</v>
-      </c>
-      <c r="M185"/>
-    </row>
-    <row r="186" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C186" s="206" t="str">
-        <v>Candidate[0].Identifier</v>
-      </c>
-      <c r="D186" t="str">
-        <v>DERIVED_FROM(EPSG):7834</v>
-      </c>
-      <c r="H186" s="173" t="str">
-        <v>Identifier</v>
-      </c>
-      <c r="I186" s="218" t="str">
-        <v>INVERSE(EPSG):16204</v>
-      </c>
-      <c r="J186" s="218" t="str">
-        <v>DERIVED_FROM(EPSG):7834</v>
-      </c>
-      <c r="K186" s="218" t="str">
-        <v>EPSG:15498</v>
-      </c>
-      <c r="M186"/>
-    </row>
-    <row r="187" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C187" s="206" t="str">
-        <v>Candidate[0].Identifiers</v>
-      </c>
-      <c r="D187" t="str">
-        <v>DERIVED_FROM(EPSG):7834</v>
-      </c>
-      <c r="H187" s="173" t="str">
-        <v>Identifiers</v>
-      </c>
-      <c r="I187" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="J187" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="K187" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M187"/>
-    </row>
-    <row r="188" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C188" s="206" t="str">
-        <v>Candidate[0].Accuracy</v>
-      </c>
-      <c r="D188" t="str">
-        <v>1</v>
-      </c>
-      <c r="H188" s="173" t="str">
-        <v>Accuracy</v>
-      </c>
-      <c r="I188" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="J188" s="218" t="str">
-        <v>1</v>
-      </c>
-      <c r="K188" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M188"/>
-    </row>
-    <row r="189" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C189" s="206" t="str">
-        <v>Candidate[0].IsAvailable</v>
-      </c>
-      <c r="D189" t="str">
-        <v>True</v>
-      </c>
-      <c r="H189" s="173" t="str">
-        <v>IsAvailable</v>
-      </c>
-      <c r="I189" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="J189" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="K189" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="M189"/>
-    </row>
-    <row r="190" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C190" s="206" t="str">
-        <v>Candidate[0].HasBallParkTransformation</v>
-      </c>
-      <c r="D190" t="str">
-        <v>False</v>
-      </c>
-      <c r="H190" s="173" t="str">
-        <v>HasBallParkTransformation</v>
-      </c>
-      <c r="I190" s="218" t="str">
-        <v>False</v>
-      </c>
-      <c r="J190" s="218" t="str">
-        <v>False</v>
-      </c>
-      <c r="K190" s="218" t="str">
-        <v>False</v>
-      </c>
-      <c r="M190"/>
-    </row>
-    <row r="191" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C191" s="206" t="str">
-        <v>Candidate[0].HasInverse</v>
-      </c>
-      <c r="D191" t="str">
-        <v>True</v>
-      </c>
-      <c r="H191" s="173" t="str">
-        <v>HasInverse</v>
-      </c>
-      <c r="I191" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="J191" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="K191" s="218" t="str">
-        <v>True</v>
-      </c>
-      <c r="M191"/>
-    </row>
-    <row r="192" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C192" s="206" t="str">
-        <v>Candidate[0].MethodName</v>
-      </c>
-      <c r="D192" t="str">
-        <v>Coordinate Frame rotation (geog2D domain)</v>
-      </c>
-      <c r="H192" s="173" t="str">
-        <v>MethodName</v>
-      </c>
-      <c r="I192" s="218" t="str">
-        <v>Inverse of Transverse Mercator</v>
-      </c>
-      <c r="J192" s="218" t="str">
-        <v>Coordinate Frame rotation (geog2D domain)</v>
-      </c>
-      <c r="K192" s="218" t="str">
-        <v>Axis Order Reversal (2D)</v>
-      </c>
-      <c r="M192"/>
-    </row>
-    <row r="193" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C193" s="206" t="str">
-        <v>Candidate[0].Scope</v>
-      </c>
-      <c r="D193" t="str">
-        <v>(null/copy) Approximation for medium and low accuracy applications assuming equality between plate-fixed static and earth-fixed dynamic CRSs, ignoring static/dynamic CRS differences.</v>
-      </c>
-      <c r="H193" s="173" t="str">
-        <v>Scope</v>
-      </c>
-      <c r="I193" s="218" t="str">
-        <v>Topographic mapping (medium scale).</v>
-      </c>
-      <c r="J193" s="218" t="str">
-        <v>(null/copy) Approximation for medium and low accuracy applications assuming equality between plate-fixed static and earth-fixed dynamic CRSs, ignoring static/dynamic CRS differences.</v>
-      </c>
-      <c r="K193" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M193"/>
-    </row>
-    <row r="194" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C194" s="206" t="str">
-        <v>Candidate[0].Remarks</v>
-      </c>
-      <c r="D194" t="str">
-        <v>Parameter values from Albanian 1987 to ETRS89 (1) (code 7833). Assumes ETRS89 and WGS 84 can be considered the same to within the accuracy of the transformation.</v>
-      </c>
-      <c r="H194" s="173" t="str">
-        <v>Remarks</v>
-      </c>
-      <c r="I194" s="218" t="str">
-        <v>Also found with zone truncated from false easting: see 6-degree Gauss-Kruger CM 21E (code 16304).</v>
-      </c>
-      <c r="J194" s="218" t="str">
-        <v>Parameter values from Albanian 1987 to ETRS89 (1) (code 7833). Assumes ETRS89 and WGS 84 can be considered the same to within the accuracy of the transformation.</v>
-      </c>
-      <c r="K194" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M194"/>
-    </row>
-    <row r="195" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C195" s="206" t="str">
-        <v>Candidate[0].GridUsages</v>
-      </c>
-      <c r="D195" t="str">
-        <v/>
-      </c>
-      <c r="H195" s="173" t="str">
-        <v>GridUsages</v>
-      </c>
-      <c r="I195" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="J195" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="K195" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M195"/>
-    </row>
-    <row r="196" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C196" s="206" t="str">
-        <v>Candidate[0].Parameters</v>
-      </c>
-      <c r="D196" t="str">
-        <v>UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-44.183; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-0.58; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-38.489; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.3867; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.7072; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=3.5196; UnitCategory=scale; UnitCode=9202; UnitAuthName=EPSG; UnitName=parts per million; UnitConversionFactor=1E-06; ValueString=-8.2703</v>
-      </c>
-      <c r="H196" s="173" t="str">
-        <v>Parameters</v>
-      </c>
-      <c r="I196" s="218" t="str">
-        <v>UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; Value=0; UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; ValueString=21; UnitCategory=scale; UnitCode=9201; UnitAuthName=EPSG; UnitName=unity; UnitConversionFactor=1; ValueString=1; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=4500000; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; Value=0</v>
-      </c>
-      <c r="J196" s="218" t="str">
-        <v>UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-44.183; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-0.58; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=-38.489; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.3867; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=-2.7072; UnitCategory=angular; UnitCode=9104; UnitAuthName=EPSG; UnitName=arc-second; UnitConversionFactor=4.84813681109536E-06; ValueString=3.5196; UnitCategory=scale; UnitCode=9202; UnitAuthName=EPSG; UnitName=parts per million; UnitConversionFactor=1E-06; ValueString=-8.2703</v>
-      </c>
-      <c r="K196" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M196"/>
-    </row>
-    <row r="197" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C197" s="206" t="str">
-        <v>Candidate[0].SourceCRS</v>
-      </c>
-      <c r="D197" t="str">
-        <v>Albanian 1987</v>
-      </c>
-      <c r="H197" s="173" t="str">
-        <v>SourceCRS</v>
-      </c>
-      <c r="I197" s="218" t="str">
-        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
-      </c>
-      <c r="J197" s="218" t="str">
-        <v>Albanian 1987</v>
-      </c>
-      <c r="K197" s="218" t="str">
-        <v>WGS 84</v>
-      </c>
-      <c r="M197"/>
-    </row>
-    <row r="198" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C198" s="206" t="str">
-        <v>Candidate[0].TargetCRS</v>
-      </c>
-      <c r="D198" t="str">
-        <v>WGS 84</v>
-      </c>
-      <c r="H198" s="173" t="str">
-        <v>TargetCRS</v>
-      </c>
-      <c r="I198" s="218" t="str">
-        <v>Albanian 1987</v>
-      </c>
-      <c r="J198" s="218" t="str">
-        <v>WGS 84</v>
-      </c>
-      <c r="K198" s="218" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
-      <c r="M198"/>
-    </row>
-    <row r="199" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C199" s="206" t="str">
-        <v>Candidate[0].Context</v>
-      </c>
-      <c r="D199" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="H199" s="173" t="str">
-        <v>Context</v>
-      </c>
-      <c r="I199" s="218" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="J199" s="218" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="K199" s="218" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="M199"/>
-    </row>
-    <row r="200" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C200" s="206" t="str">
-        <v>Candidate[0].UsageArea</v>
-      </c>
-      <c r="D200" t="str">
-        <v>SharpProj.Proj.UsageArea</v>
-      </c>
-      <c r="H200" s="173" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="I200" s="218" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="J200" s="218" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="K200" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M200"/>
-    </row>
-    <row r="201" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C201" s="206" t="str">
-        <v>Candidate[0].UsageArea.Name</v>
-      </c>
-      <c r="D201" t="str">
-        <v>Albania - onshore.</v>
-      </c>
-      <c r="H201" s="173" t="str">
-        <v>UsageArea.Name</v>
-      </c>
-      <c r="I201" s="218" t="str">
-        <v>Between 18°E and 24°E.</v>
-      </c>
-      <c r="J201" s="218" t="str">
-        <v>Albania - onshore.</v>
-      </c>
-      <c r="K201" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M201"/>
-    </row>
-    <row r="202" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C202" s="206" t="str">
-        <v>Candidate[0].UsageArea.WestLongitude</v>
-      </c>
-      <c r="D202" t="str">
-        <v>19.22</v>
-      </c>
-      <c r="H202" s="173" t="str">
-        <v>UsageArea.WestLongitude</v>
-      </c>
-      <c r="I202" s="218" t="str">
-        <v>18</v>
-      </c>
-      <c r="J202" s="218" t="str">
-        <v>19.22</v>
-      </c>
-      <c r="K202" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M202"/>
-    </row>
-    <row r="203" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C203" s="206" t="str">
-        <v>Candidate[0].UsageArea.SouthLatitude</v>
-      </c>
-      <c r="D203" t="str">
-        <v>39.64</v>
-      </c>
-      <c r="H203" s="173" t="str">
-        <v>UsageArea.SouthLatitude</v>
-      </c>
-      <c r="I203" s="218" t="str">
-        <v>-80</v>
-      </c>
-      <c r="J203" s="218" t="str">
-        <v>39.64</v>
-      </c>
-      <c r="K203" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M203"/>
-    </row>
-    <row r="204" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C204" s="206" t="str">
-        <v>Candidate[0].UsageArea.EastLongitude</v>
-      </c>
-      <c r="D204" t="str">
-        <v>21.06</v>
-      </c>
-      <c r="H204" s="173" t="str">
-        <v>UsageArea.EastLongitude</v>
-      </c>
-      <c r="I204" s="218" t="str">
-        <v>24</v>
-      </c>
-      <c r="J204" s="218" t="str">
-        <v>21.06</v>
-      </c>
-      <c r="K204" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M204"/>
-    </row>
-    <row r="205" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C205" s="206" t="str">
-        <v>Candidate[0].UsageArea.NorthLatitude</v>
-      </c>
-      <c r="D205" t="str">
-        <v>42.67</v>
-      </c>
-      <c r="H205" s="173" t="str">
-        <v>UsageArea.NorthLatitude</v>
-      </c>
-      <c r="I205" s="218" t="str">
-        <v>84</v>
-      </c>
-      <c r="J205" s="218" t="str">
-        <v>42.67</v>
-      </c>
-      <c r="K205" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M205"/>
-    </row>
-    <row r="206" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C206" s="206" t="str">
-        <v>Candidate[0].UsageArea.Center</v>
-      </c>
-      <c r="D206" t="str">
-        <v>X=41.155, Y=20.14</v>
-      </c>
-      <c r="H206" s="173" t="str">
-        <v>UsageArea.Center</v>
-      </c>
-      <c r="I206" s="218" t="str">
-        <v>X=4500000, Y=223053.008659147</v>
-      </c>
-      <c r="J206" s="218" t="str">
-        <v>X=41.155, Y=20.14</v>
-      </c>
-      <c r="K206" s="218" t="str">
-        <v>&lt;null&gt;</v>
-      </c>
-      <c r="M206"/>
-    </row>
-    <row r="207" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C207" s="172" t="str">
-        <v>Candidate[1].Name</v>
-      </c>
-      <c r="D207" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
-      </c>
-      <c r="M207"/>
-    </row>
-    <row r="208" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C208" s="172" t="str">
-        <v>Candidate[1].Type</v>
-      </c>
-      <c r="D208" t="str">
-        <v>Conversion</v>
-      </c>
-      <c r="M208"/>
-    </row>
-    <row r="209" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C209" s="172" t="str">
-        <v>Candidate[1].Identifier</v>
-      </c>
-      <c r="D209" t="str">
-        <v>INVERSE(EPSG):16204</v>
-      </c>
-      <c r="M209"/>
-    </row>
-    <row r="210" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C210" s="172" t="str">
-        <v>Candidate[1].Identifiers</v>
-      </c>
-      <c r="D210" t="str">
-        <v>INVERSE(EPSG):16204</v>
-      </c>
-      <c r="M210"/>
-    </row>
-    <row r="211" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C211" s="172" t="str">
-        <v>Candidate[1].Accuracy</v>
-      </c>
-      <c r="D211" t="str">
-        <v/>
-      </c>
-      <c r="M211"/>
-    </row>
-    <row r="212" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C212" s="172" t="str">
-        <v>Candidate[1].IsAvailable</v>
-      </c>
-      <c r="D212" t="str">
-        <v>True</v>
-      </c>
-      <c r="M212"/>
-    </row>
-    <row r="213" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C213" s="172" t="str">
-        <v>Candidate[1].HasBallParkTransformation</v>
-      </c>
-      <c r="D213" t="str">
-        <v>False</v>
-      </c>
-      <c r="M213"/>
-    </row>
-    <row r="214" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C214" s="172" t="str">
-        <v>Candidate[1].HasInverse</v>
-      </c>
-      <c r="D214" t="str">
-        <v>True</v>
-      </c>
-      <c r="M214"/>
-    </row>
-    <row r="215" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C215" s="172" t="str">
-        <v>Candidate[1].MethodName</v>
-      </c>
-      <c r="D215" t="str">
-        <v>Inverse of Transverse Mercator</v>
-      </c>
-      <c r="M215"/>
-    </row>
-    <row r="216" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C216" s="172" t="str">
-        <v>Candidate[1].Scope</v>
-      </c>
-      <c r="D216" t="str">
-        <v>Topographic mapping (medium scale).</v>
-      </c>
-      <c r="M216"/>
-    </row>
-    <row r="217" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C217" s="172" t="str">
-        <v>Candidate[1].Remarks</v>
-      </c>
-      <c r="D217" t="str">
-        <v>Also found with zone truncated from false easting: see 6-degree Gauss-Kruger CM 21E (code 16304).</v>
-      </c>
-      <c r="M217"/>
-    </row>
-    <row r="218" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C218" s="172" t="str">
-        <v>Candidate[1].GridUsages</v>
-      </c>
-      <c r="D218" t="str">
-        <v/>
-      </c>
-      <c r="M218"/>
-    </row>
-    <row r="219" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C219" s="172" t="str">
-        <v>Candidate[1].Parameters</v>
-      </c>
-      <c r="D219" t="str">
-        <v>UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; Value=0; UnitCategory=angular; UnitCode=9102; UnitAuthName=EPSG; UnitName=degree; UnitConversionFactor=0.0174532925199433; ValueString=21; UnitCategory=scale; UnitCode=9201; UnitAuthName=EPSG; UnitName=unity; UnitConversionFactor=1; ValueString=1; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; ValueString=4500000; UnitCategory=linear; UnitCode=9001; UnitAuthName=EPSG; UnitName=metre; UnitConversionFactor=1; Value=0</v>
-      </c>
-      <c r="M219"/>
-    </row>
-    <row r="220" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C220" s="172" t="str">
-        <v>Candidate[1].SourceCRS</v>
-      </c>
-      <c r="D220" t="str">
-        <v>Albanian 1987 / Gauss-Kruger zone 4 (with axis order normalized for visualization)</v>
-      </c>
-      <c r="M220"/>
-    </row>
-    <row r="221" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C221" s="172" t="str">
-        <v>Candidate[1].TargetCRS</v>
-      </c>
-      <c r="D221" t="str">
-        <v>Albanian 1987</v>
-      </c>
-      <c r="M221"/>
-    </row>
-    <row r="222" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C222" s="172" t="str">
-        <v>Candidate[1].Context</v>
-      </c>
-      <c r="D222" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="M222"/>
-    </row>
-    <row r="223" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C223" s="172" t="str">
-        <v>Candidate[1].UsageArea</v>
-      </c>
-      <c r="D223" t="str">
-        <v>SharpProj.Proj.UsageArea</v>
-      </c>
-      <c r="M223"/>
-    </row>
-    <row r="224" spans="3:13" x14ac:dyDescent="0.35">
-      <c r="C224" s="172" t="str">
-        <v>Candidate[1].UsageArea.Name</v>
-      </c>
-      <c r="D224" t="str">
-        <v>Between 18°E and 24°E.</v>
-      </c>
-      <c r="M224"/>
-    </row>
-    <row r="225" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C225" s="172" t="str">
-        <v>Candidate[1].UsageArea.WestLongitude</v>
-      </c>
-      <c r="D225" t="str">
-        <v>18</v>
-      </c>
-      <c r="M225"/>
-    </row>
-    <row r="226" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C226" s="172" t="str">
-        <v>Candidate[1].UsageArea.SouthLatitude</v>
-      </c>
-      <c r="D226" t="str">
-        <v>-80</v>
-      </c>
       <c r="M226"/>
+      <c r="O226"/>
     </row>
     <row r="227" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C227" s="172" t="str">
-        <v>Candidate[1].UsageArea.EastLongitude</v>
-      </c>
-      <c r="D227" t="str">
-        <v>24</v>
-      </c>
       <c r="M227"/>
+      <c r="O227"/>
     </row>
     <row r="228" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C228" s="172" t="str">
-        <v>Candidate[1].UsageArea.NorthLatitude</v>
-      </c>
-      <c r="D228" t="str">
-        <v>84</v>
-      </c>
       <c r="M228"/>
+      <c r="O228"/>
     </row>
     <row r="229" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C229" s="172" t="str">
-        <v>Candidate[1].UsageArea.Center</v>
-      </c>
-      <c r="D229" t="str">
-        <v>X=4500000, Y=223053.008659147</v>
-      </c>
       <c r="M229"/>
+      <c r="O229"/>
     </row>
     <row r="230" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C230" s="206" t="str">
-        <v>Candidate[2].Name</v>
-      </c>
-      <c r="D230" t="str">
-        <v>axis order change (2D)</v>
-      </c>
       <c r="M230"/>
       <c r="O230"/>
     </row>
     <row r="231" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C231" s="206" t="str">
-        <v>Candidate[2].Type</v>
-      </c>
-      <c r="D231" t="str">
-        <v>Conversion</v>
-      </c>
       <c r="M231"/>
       <c r="O231"/>
     </row>
     <row r="232" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C232" s="206" t="str">
-        <v>Candidate[2].Identifier</v>
-      </c>
-      <c r="D232" t="str">
-        <v>EPSG:15498</v>
-      </c>
       <c r="M232"/>
       <c r="O232"/>
     </row>
     <row r="233" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C233" s="206" t="str">
-        <v>Candidate[2].Identifiers</v>
-      </c>
-      <c r="D233" t="str">
-        <v>EPSG:15498</v>
-      </c>
       <c r="M233"/>
       <c r="O233"/>
     </row>
     <row r="234" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C234" s="206" t="str">
-        <v>Candidate[2].Accuracy</v>
-      </c>
-      <c r="D234" t="str">
-        <v/>
-      </c>
       <c r="M234"/>
       <c r="O234"/>
     </row>
     <row r="235" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C235" s="206" t="str">
-        <v>Candidate[2].IsAvailable</v>
-      </c>
-      <c r="D235" t="str">
-        <v>True</v>
-      </c>
       <c r="M235"/>
       <c r="O235"/>
     </row>
     <row r="236" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C236" s="206" t="str">
-        <v>Candidate[2].HasBallParkTransformation</v>
-      </c>
-      <c r="D236" t="str">
-        <v>False</v>
-      </c>
       <c r="M236"/>
       <c r="O236"/>
     </row>
     <row r="237" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C237" s="206" t="str">
-        <v>Candidate[2].HasInverse</v>
-      </c>
-      <c r="D237" t="str">
-        <v>True</v>
-      </c>
       <c r="M237"/>
       <c r="O237"/>
     </row>
     <row r="238" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C238" s="206" t="str">
-        <v>Candidate[2].MethodName</v>
-      </c>
-      <c r="D238" t="str">
-        <v>Axis Order Reversal (2D)</v>
-      </c>
       <c r="M238"/>
       <c r="O238"/>
     </row>
     <row r="239" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C239" s="206" t="str">
-        <v>Candidate[2].Scope</v>
-      </c>
-      <c r="D239" t="str">
-        <v/>
-      </c>
       <c r="M239"/>
       <c r="O239"/>
     </row>
     <row r="240" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C240" s="206" t="str">
-        <v>Candidate[2].Remarks</v>
-      </c>
-      <c r="D240" t="str">
-        <v/>
-      </c>
       <c r="M240"/>
       <c r="O240"/>
     </row>
-    <row r="241" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C241" s="206" t="str">
-        <v>Candidate[2].GridUsages</v>
-      </c>
-      <c r="D241" t="str">
-        <v/>
-      </c>
+    <row r="241" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M241"/>
       <c r="O241"/>
     </row>
-    <row r="242" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C242" s="206" t="str">
-        <v>Candidate[2].Parameters</v>
-      </c>
-      <c r="D242" t="str">
-        <v/>
-      </c>
+    <row r="242" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M242"/>
       <c r="O242"/>
     </row>
-    <row r="243" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C243" s="206" t="str">
-        <v>Candidate[2].SourceCRS</v>
-      </c>
-      <c r="D243" t="str">
-        <v>WGS 84</v>
-      </c>
+    <row r="243" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M243"/>
       <c r="O243"/>
     </row>
-    <row r="244" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C244" s="206" t="str">
-        <v>Candidate[2].TargetCRS</v>
-      </c>
-      <c r="D244" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
+    <row r="244" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M244"/>
       <c r="O244"/>
     </row>
-    <row r="245" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C245" s="206" t="str">
-        <v>Candidate[2].Context</v>
-      </c>
-      <c r="D245" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
+    <row r="245" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M245"/>
       <c r="O245"/>
     </row>
-    <row r="246" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C246" s="206" t="str">
-        <v>Candidate[2].UsageArea</v>
-      </c>
-      <c r="D246" t="str">
-        <v/>
-      </c>
+    <row r="246" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M246"/>
       <c r="O246"/>
     </row>
-    <row r="247" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="247" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M247"/>
       <c r="O247"/>
     </row>
-    <row r="248" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="248" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M248"/>
       <c r="O248"/>
     </row>
-    <row r="249" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="249" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M249"/>
       <c r="O249"/>
     </row>
-    <row r="250" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="250" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M250"/>
       <c r="O250"/>
     </row>
-    <row r="251" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="251" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M251"/>
       <c r="O251"/>
     </row>
-    <row r="252" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="252" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M252"/>
       <c r="O252"/>
     </row>
-    <row r="253" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="253" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M253"/>
       <c r="O253"/>
     </row>
-    <row r="254" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="254" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M254"/>
       <c r="O254"/>
     </row>
-    <row r="255" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="255" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M255"/>
       <c r="O255"/>
     </row>
-    <row r="256" spans="3:15" x14ac:dyDescent="0.35">
+    <row r="256" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M256"/>
       <c r="O256"/>
     </row>
@@ -47835,106 +48287,6 @@
     <row r="286" spans="13:15" x14ac:dyDescent="0.35">
       <c r="M286"/>
       <c r="O286"/>
-    </row>
-    <row r="287" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M287"/>
-      <c r="O287"/>
-    </row>
-    <row r="288" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M288"/>
-      <c r="O288"/>
-    </row>
-    <row r="289" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M289"/>
-      <c r="O289"/>
-    </row>
-    <row r="290" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M290"/>
-      <c r="O290"/>
-    </row>
-    <row r="291" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M291"/>
-      <c r="O291"/>
-    </row>
-    <row r="292" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M292"/>
-      <c r="O292"/>
-    </row>
-    <row r="293" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M293"/>
-      <c r="O293"/>
-    </row>
-    <row r="294" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M294"/>
-      <c r="O294"/>
-    </row>
-    <row r="295" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M295"/>
-      <c r="O295"/>
-    </row>
-    <row r="296" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M296"/>
-      <c r="O296"/>
-    </row>
-    <row r="297" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M297"/>
-      <c r="O297"/>
-    </row>
-    <row r="298" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M298"/>
-      <c r="O298"/>
-    </row>
-    <row r="299" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M299"/>
-      <c r="O299"/>
-    </row>
-    <row r="300" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M300"/>
-      <c r="O300"/>
-    </row>
-    <row r="301" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M301"/>
-      <c r="O301"/>
-    </row>
-    <row r="302" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M302"/>
-      <c r="O302"/>
-    </row>
-    <row r="303" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M303"/>
-      <c r="O303"/>
-    </row>
-    <row r="304" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M304"/>
-      <c r="O304"/>
-    </row>
-    <row r="305" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M305"/>
-      <c r="O305"/>
-    </row>
-    <row r="306" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M306"/>
-      <c r="O306"/>
-    </row>
-    <row r="307" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M307"/>
-      <c r="O307"/>
-    </row>
-    <row r="308" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M308"/>
-      <c r="O308"/>
-    </row>
-    <row r="309" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M309"/>
-      <c r="O309"/>
-    </row>
-    <row r="310" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M310"/>
-      <c r="O310"/>
-    </row>
-    <row r="311" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M311"/>
-      <c r="O311"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E954868-DF13-473D-9848-C4DD558A8D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EA1A1A-FD59-4683-9856-DBF7EDDD1A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1214,7 +1214,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1751,6 +1751,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="7" borderId="13" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -39512,7 +39515,9 @@
     <col min="24" max="24" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D2" s="1"/>
+    </row>
     <row r="3" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C3" s="59" t="s">
         <v>26</v>
@@ -39560,7 +39565,7 @@
       <c r="C5" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="232">
         <v>4326</v>
       </c>
       <c r="E5" s="208" t="b" cm="1">
@@ -39759,36 +39764,36 @@
         <f>E17-$D$7*COS(RADIANS(O17))</f>
         <v>4511477.2929155556</v>
       </c>
-      <c r="F16" s="135" cm="1">
-        <f t="array" ref="F16:G16">_xll.PE.trf.Transform($D$4,$D$5,D16,E16)</f>
-        <v>19.627501288698802</v>
-      </c>
-      <c r="G16" s="137">
-        <v>40.728657406572829</v>
+      <c r="F16" s="132" cm="1">
+        <f t="array" ref="F16:G21">_xll.PE.trf.Transform($D$4,$D$5,D16:D21,E16:E21)</f>
+        <v>39.590331698526754</v>
+      </c>
+      <c r="G16" s="134">
+        <v>21.13207859944475</v>
       </c>
       <c r="H16" s="135" t="str" cm="1">
         <f t="array" ref="H16">_xll.PE.deg.AsString(F16)</f>
-        <v>19 37 39</v>
+        <v>39 35 25</v>
       </c>
       <c r="I16" s="136" t="str" cm="1">
         <f t="array" ref="I16">_xll.PE.deg.AsString(G16)</f>
-        <v>40 43 43</v>
+        <v>21 07 55</v>
       </c>
       <c r="J16" s="135" cm="1">
         <f t="array" ref="J16">_xll.PE.deg.FromString(H16)</f>
-        <v>19.627500000000001</v>
+        <v>39.590277777777779</v>
       </c>
       <c r="K16" s="137" cm="1">
         <f t="array" ref="K16">_xll.PE.deg.FromString(I16)</f>
-        <v>40.728611111111114</v>
+        <v>21.131944444444446</v>
       </c>
       <c r="L16" s="83">
         <f t="shared" ref="L16:M21" si="0">F16-J16</f>
-        <v>1.2886988010052391E-6</v>
+        <v>5.3920748975144761E-5</v>
       </c>
       <c r="M16" s="79">
         <f t="shared" si="0"/>
-        <v>4.629546171486254E-5</v>
+        <v>1.341550003033376E-4</v>
       </c>
       <c r="N16" s="8">
         <f>SQRT((D17-D16)^2+(E17-E16)^2)</f>
@@ -39801,11 +39806,11 @@
       <c r="P16" s="89"/>
       <c r="Q16" s="44" t="str">
         <f t="shared" ref="Q16:Q21" si="1">CONCATENATE(TEXT(F16,"#.00000000"),",",TEXT(G16,"#.00000000"))</f>
-        <v>19.62750129,40.72865741</v>
+        <v>39.59033170,21.13207860</v>
       </c>
       <c r="R16" s="98" t="str">
         <f t="shared" ref="R16:R21" si="2">CONCATENATE("&lt;trkpt lon=""",TEXT(F16,"#.00000000"),""" lat=""",TEXT(G16,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B16,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.62750129" lat="40.72865741"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.59033170" lat="21.13207860"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39824,36 +39829,35 @@
         <f>E18-$D$8*COS(RADIANS(O18))</f>
         <v>4512035.3816660317</v>
       </c>
-      <c r="F17" s="135" cm="1">
-        <f t="array" ref="F17:G17">_xll.PE.trf.Transform($D$4,$D$5,D17,E17)</f>
-        <v>19.662282485406411</v>
+      <c r="F17" s="135">
+        <v>39.616872623603527</v>
       </c>
       <c r="G17" s="137">
-        <v>40.734091192706153</v>
+        <v>21.138628224456667</v>
       </c>
       <c r="H17" s="135" t="str" cm="1">
         <f t="array" ref="H17">_xll.PE.deg.AsString(F17)</f>
-        <v>19 39 44</v>
+        <v>39 37 01</v>
       </c>
       <c r="I17" s="136" t="str" cm="1">
         <f t="array" ref="I17">_xll.PE.deg.AsString(G17)</f>
-        <v>40 44 03</v>
+        <v>21 08 19</v>
       </c>
       <c r="J17" s="135" cm="1">
         <f t="array" ref="J17">_xll.PE.deg.FromString(H17)</f>
-        <v>19.662222222222219</v>
+        <v>39.616944444444442</v>
       </c>
       <c r="K17" s="137" cm="1">
         <f t="array" ref="K17">_xll.PE.deg.FromString(I17)</f>
-        <v>40.734166666666667</v>
+        <v>21.138611111111111</v>
       </c>
       <c r="L17" s="84">
         <f t="shared" si="0"/>
-        <v>6.0263184192166364E-5</v>
+        <v>-7.1820840915393092E-5</v>
       </c>
       <c r="M17" s="80">
         <f t="shared" si="0"/>
-        <v>-7.5473960514216287E-5</v>
+        <v>1.7113345556651893E-5</v>
       </c>
       <c r="N17" s="39">
         <f>SQRT((D18-D17)^2+(E18-E17)^2)</f>
@@ -39868,11 +39872,11 @@
       </c>
       <c r="Q17" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>19.66228249,40.73409119</v>
+        <v>39.61687262,21.13862822</v>
       </c>
       <c r="R17" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="19.66228249" lat="40.73409119"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.61687262" lat="21.13862822"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39889,36 +39893,35 @@
       <c r="E18" s="190">
         <v>4512779.5</v>
       </c>
-      <c r="F18" s="138" cm="1">
-        <f t="array" ref="F18:G18">_xll.PE.trf.Transform($D$4,$D$5,D18,E18)</f>
-        <v>19.708666633032713</v>
+      <c r="F18" s="138">
+        <v>39.652259745821347</v>
       </c>
       <c r="G18" s="140">
-        <v>40.741320058972271</v>
+        <v>21.147368889577873</v>
       </c>
       <c r="H18" s="138" t="str" cm="1">
         <f t="array" ref="H18">_xll.PE.deg.AsString(F18)</f>
-        <v>19 42 31</v>
+        <v>39 39 08</v>
       </c>
       <c r="I18" s="139" t="str" cm="1">
         <f t="array" ref="I18">_xll.PE.deg.AsString(G18)</f>
-        <v>40 44 29</v>
+        <v>21 08 51</v>
       </c>
       <c r="J18" s="138" cm="1">
         <f t="array" ref="J18">_xll.PE.deg.FromString(H18)</f>
-        <v>19.708611111111111</v>
+        <v>39.652222222222221</v>
       </c>
       <c r="K18" s="140" cm="1">
         <f t="array" ref="K18">_xll.PE.deg.FromString(I18)</f>
-        <v>40.741388888888892</v>
+        <v>21.147500000000001</v>
       </c>
       <c r="L18" s="85">
         <f t="shared" si="0"/>
-        <v>5.5521921602519342E-5</v>
+        <v>3.7523599125677265E-5</v>
       </c>
       <c r="M18" s="81">
         <f t="shared" si="0"/>
-        <v>-6.8829916621382381E-5</v>
+        <v>-1.3111042212798907E-4</v>
       </c>
       <c r="N18" s="10">
         <f>SQRT((D19-D18)^2+(E19-E18)^2)</f>
@@ -39934,11 +39937,11 @@
       </c>
       <c r="Q18" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>19.70866663,40.74132006</v>
+        <v>39.65225975,21.14736889</v>
       </c>
       <c r="R18" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="19.70866663" lat="40.74132006"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.65225975" lat="21.14736889"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39955,36 +39958,35 @@
       <c r="E19" s="190">
         <v>4516827</v>
       </c>
-      <c r="F19" s="138" cm="1">
-        <f t="array" ref="F19:G19">_xll.PE.trf.Transform($D$4,$D$5,D19,E19)</f>
-        <v>19.961147921469532</v>
+      <c r="F19" s="138">
+        <v>39.844726060354347</v>
       </c>
       <c r="G19" s="140">
-        <v>40.780315713923812</v>
+        <v>21.195069923134415</v>
       </c>
       <c r="H19" s="138" t="str" cm="1">
         <f t="array" ref="H19">_xll.PE.deg.AsString(F19)</f>
-        <v>19 57 40</v>
+        <v>39 50 41</v>
       </c>
       <c r="I19" s="139" t="str" cm="1">
         <f t="array" ref="I19">_xll.PE.deg.AsString(G19)</f>
-        <v>40 46 49</v>
+        <v>21 11 42</v>
       </c>
       <c r="J19" s="138" cm="1">
         <f t="array" ref="J19">_xll.PE.deg.FromString(H19)</f>
-        <v>19.961111111111112</v>
+        <v>39.844722222222224</v>
       </c>
       <c r="K19" s="140" cm="1">
         <f t="array" ref="K19">_xll.PE.deg.FromString(I19)</f>
-        <v>40.780277777777776</v>
+        <v>21.195</v>
       </c>
       <c r="L19" s="85">
         <f t="shared" si="0"/>
-        <v>3.6810358420069633E-5</v>
+        <v>3.8381321232350274E-6</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="0"/>
-        <v>3.7936146036088303E-5</v>
+        <v>6.9923134415006416E-5</v>
       </c>
       <c r="N19" s="39">
         <f>SQRT((D20-D19)^2+(E20-E19)^2)</f>
@@ -39997,11 +39999,11 @@
       <c r="P19" s="89"/>
       <c r="Q19" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>19.96114792,40.78031571</v>
+        <v>39.84472606,21.19506992</v>
       </c>
       <c r="R19" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="19.96114792" lat="40.78031571"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.84472606" lat="21.19506992"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40023,36 +40025,35 @@
         <f>E19+$D$8*COS(RADIANS(O18))</f>
         <v>4517571.1183339683</v>
       </c>
-      <c r="F20" s="135" cm="1">
-        <f t="array" ref="F20:G20">_xll.PE.trf.Transform($D$4,$D$5,D20,E20)</f>
-        <v>20.007599027220387</v>
+      <c r="F20" s="135">
+        <v>39.880107398901082</v>
       </c>
       <c r="G20" s="137">
-        <v>40.787425154590217</v>
+        <v>21.20386877320766</v>
       </c>
       <c r="H20" s="135" t="str" cm="1">
         <f t="array" ref="H20">_xll.PE.deg.AsString(F20)</f>
-        <v>20 00 27</v>
+        <v>39 52 48</v>
       </c>
       <c r="I20" s="136" t="str" cm="1">
         <f t="array" ref="I20">_xll.PE.deg.AsString(G20)</f>
-        <v>40 47 15</v>
+        <v>21 12 14</v>
       </c>
       <c r="J20" s="135" cm="1">
         <f t="array" ref="J20">_xll.PE.deg.FromString(H20)</f>
-        <v>20.0075</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="K20" s="137" cm="1">
         <f t="array" ref="K20">_xll.PE.deg.FromString(I20)</f>
-        <v>40.787500000000001</v>
+        <v>21.203888888888887</v>
       </c>
       <c r="L20" s="84">
         <f t="shared" si="0"/>
-        <v>9.9027220386460613E-5</v>
+        <v>1.0739890107913652E-4</v>
       </c>
       <c r="M20" s="80">
         <f t="shared" si="0"/>
-        <v>-7.4845409784529693E-5</v>
+        <v>-2.0115681227395044E-5</v>
       </c>
       <c r="N20" s="39">
         <f>SQRT((D21-D20)^2+(E21-E20)^2)</f>
@@ -40067,11 +40068,11 @@
       </c>
       <c r="Q20" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>20.00759903,40.78742515</v>
+        <v>39.88010740,21.20386877</v>
       </c>
       <c r="R20" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="20.00759903" lat="40.78742515"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.88010740" lat="21.20386877"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40090,36 +40091,35 @@
         <f>E20+$D$7*COS(RADIANS(O19))</f>
         <v>4518129.2070844444</v>
       </c>
-      <c r="F21" s="141" cm="1">
-        <f t="array" ref="F21:G21">_xll.PE.trf.Transform($D$4,$D$5,D21,E21)</f>
-        <v>20.042444089865263</v>
+      <c r="F21" s="141">
+        <v>39.906642807333341</v>
       </c>
       <c r="G21" s="143">
-        <v>40.792745029791639</v>
+        <v>21.210473896913385</v>
       </c>
       <c r="H21" s="141" t="str" cm="1">
         <f t="array" ref="H21">_xll.PE.deg.AsString(F21)</f>
-        <v>20 02 33</v>
+        <v>39 54 24</v>
       </c>
       <c r="I21" s="142" t="str" cm="1">
         <f t="array" ref="I21">_xll.PE.deg.AsString(G21)</f>
-        <v>40 47 34</v>
+        <v>21 12 38</v>
       </c>
       <c r="J21" s="141" cm="1">
         <f t="array" ref="J21">_xll.PE.deg.FromString(H21)</f>
-        <v>20.0425</v>
+        <v>39.906666666666666</v>
       </c>
       <c r="K21" s="143" cm="1">
         <f t="array" ref="K21">_xll.PE.deg.FromString(I21)</f>
-        <v>40.792777777777779</v>
+        <v>21.210555555555555</v>
       </c>
       <c r="L21" s="86">
         <f t="shared" si="0"/>
-        <v>-5.5910134737047201E-5</v>
+        <v>-2.3859333325049192E-5</v>
       </c>
       <c r="M21" s="82">
         <f t="shared" si="0"/>
-        <v>-3.2747986139725072E-5</v>
+        <v>-8.165864216991281E-5</v>
       </c>
       <c r="N21" s="34">
         <f>SUM(N17:N19)</f>
@@ -40130,15 +40130,15 @@
       </c>
       <c r="P21" s="90" cm="1">
         <f t="array" ref="P21">_xll.PE.crs.GeodesicDistance($D$5,J17:K20)</f>
-        <v>29750.260289015008</v>
+        <v>28258.642477159934</v>
       </c>
       <c r="Q21" s="44" t="str">
         <f t="shared" si="1"/>
-        <v>20.04244409,40.79274503</v>
+        <v>39.90664281,21.21047390</v>
       </c>
       <c r="R21" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>&lt;trkpt lon="20.04244409" lat="40.79274503"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.90664281" lat="21.21047390"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40216,35 +40216,35 @@
         <v>4509248.2137425337</v>
       </c>
       <c r="F24" s="132" cm="1">
-        <f t="array" ref="F24:G24">_xll.PE.trf.Transform($D$4,$D$5,D24,E24)</f>
-        <v>19.667912708680866</v>
+        <f t="array" ref="F24:G30">_xll.PE.trf.Transform($D$4,$D$5,D24:D30,E24:E30)</f>
+        <v>39.62081072677514</v>
       </c>
       <c r="G24" s="134">
-        <v>40.7090588923271</v>
+        <v>21.106176217606961</v>
       </c>
       <c r="H24" s="132" t="str" cm="1">
         <f t="array" ref="H24">_xll.PE.deg.AsString(F24)</f>
-        <v>19 40 04</v>
+        <v>39 37 15</v>
       </c>
       <c r="I24" s="133" t="str" cm="1">
         <f t="array" ref="I24">_xll.PE.deg.AsString(G24)</f>
-        <v>40 42 33</v>
+        <v>21 06 22</v>
       </c>
       <c r="J24" s="132" cm="1">
         <f t="array" ref="J24">_xll.PE.deg.FromString(H24)</f>
-        <v>19.667777777777779</v>
+        <v>39.620833333333337</v>
       </c>
       <c r="K24" s="134" cm="1">
         <f t="array" ref="K24">_xll.PE.deg.FromString(I24)</f>
-        <v>40.709166666666668</v>
+        <v>21.106111111111112</v>
       </c>
       <c r="L24" s="71">
         <f t="shared" ref="L24:M30" si="3">F24-J24</f>
-        <v>1.3493090308713818E-4</v>
+        <v>-2.2606558196969218E-5</v>
       </c>
       <c r="M24" s="72">
         <f t="shared" si="3"/>
-        <v>-1.0777433956832283E-4</v>
+        <v>6.5106495849676094E-5</v>
       </c>
       <c r="N24" s="8">
         <f t="shared" ref="N24:N29" si="4">SQRT((D25-D24)^2+(E25-E24)^2)</f>
@@ -40257,11 +40257,11 @@
       <c r="P24" s="89"/>
       <c r="Q24" s="44" t="str">
         <f t="shared" ref="Q24:Q30" si="6">CONCATENATE(TEXT(F24,"#.00000000"),",",TEXT(G24,"#.00000000"))</f>
-        <v>19.66791271,40.70905889</v>
+        <v>39.62081073,21.10617622</v>
       </c>
       <c r="R24" s="98" t="str">
         <f t="shared" ref="R24:R30" si="7">CONCATENATE("&lt;trkpt lon=""",TEXT(F24,"#.00000000"),""" lat=""",TEXT(G24,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B24,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.66791271" lat="40.70905889"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.62081073" lat="21.10617622"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40280,36 +40280,35 @@
         <f>E26-$D$8*COS(RADIANS(O26))</f>
         <v>4509971.1221385906</v>
       </c>
-      <c r="F25" s="135" cm="1">
-        <f t="array" ref="F25:G25">_xll.PE.trf.Transform($D$4,$D$5,D25,E25)</f>
-        <v>19.702232192676256</v>
+      <c r="F25" s="135">
+        <v>39.647026556284445</v>
       </c>
       <c r="G25" s="137">
-        <v>40.715959438348861</v>
+        <v>21.114638567764665</v>
       </c>
       <c r="H25" s="135" t="str" cm="1">
         <f t="array" ref="H25">_xll.PE.deg.AsString(F25)</f>
-        <v>19 42 08</v>
+        <v>39 38 49</v>
       </c>
       <c r="I25" s="136" t="str" cm="1">
         <f t="array" ref="I25">_xll.PE.deg.AsString(G25)</f>
-        <v>40 42 57</v>
+        <v>21 06 53</v>
       </c>
       <c r="J25" s="135" cm="1">
         <f t="array" ref="J25">_xll.PE.deg.FromString(H25)</f>
-        <v>19.702222222222222</v>
+        <v>39.646944444444443</v>
       </c>
       <c r="K25" s="137" cm="1">
         <f t="array" ref="K25">_xll.PE.deg.FromString(I25)</f>
-        <v>40.715833333333336</v>
+        <v>21.114722222222223</v>
       </c>
       <c r="L25" s="73">
         <f t="shared" si="3"/>
-        <v>9.9704540339473624E-6</v>
+        <v>8.2111840001175551E-5</v>
       </c>
       <c r="M25" s="74">
         <f t="shared" si="3"/>
-        <v>1.2610501552501319E-4</v>
+        <v>-8.3654457558424156E-5</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="4"/>
@@ -40322,11 +40321,11 @@
       <c r="P25" s="89"/>
       <c r="Q25" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>19.70223219,40.71595944</v>
+        <v>39.64702656,21.11463857</v>
       </c>
       <c r="R25" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="19.70223219" lat="40.71595944"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.64702656" lat="21.11463857"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40343,36 +40342,35 @@
       <c r="E26" s="190">
         <v>4510935</v>
       </c>
-      <c r="F26" s="138" cm="1">
-        <f t="array" ref="F26:G26">_xll.PE.trf.Transform($D$4,$D$5,D26,E26)</f>
-        <v>19.748002911094968</v>
+      <c r="F26" s="138">
+        <v>39.681979836465864</v>
       </c>
       <c r="G26" s="140">
-        <v>40.725144440548164</v>
+        <v>21.12593168483744</v>
       </c>
       <c r="H26" s="138" t="str" cm="1">
         <f t="array" ref="H26">_xll.PE.deg.AsString(F26)</f>
-        <v>19 44 53</v>
+        <v>39 40 55</v>
       </c>
       <c r="I26" s="139" t="str" cm="1">
         <f t="array" ref="I26">_xll.PE.deg.AsString(G26)</f>
-        <v>40 43 31</v>
+        <v>21 07 33</v>
       </c>
       <c r="J26" s="138" cm="1">
         <f t="array" ref="J26">_xll.PE.deg.FromString(H26)</f>
-        <v>19.748055555555556</v>
+        <v>39.68194444444444</v>
       </c>
       <c r="K26" s="140" cm="1">
         <f t="array" ref="K26">_xll.PE.deg.FromString(I26)</f>
-        <v>40.725277777777777</v>
+        <v>21.125833333333333</v>
       </c>
       <c r="L26" s="75">
         <f t="shared" si="3"/>
-        <v>-5.2644460588169295E-5</v>
+        <v>3.5392021423774622E-5</v>
       </c>
       <c r="M26" s="76">
         <f t="shared" si="3"/>
-        <v>-1.3333722961306194E-4</v>
+        <v>9.835150410708593E-5</v>
       </c>
       <c r="N26" s="10">
         <f t="shared" si="4"/>
@@ -40387,11 +40385,11 @@
       </c>
       <c r="Q26" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>19.74800291,40.72514444</v>
+        <v>39.68197984,21.12593168</v>
       </c>
       <c r="R26" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="19.74800291" lat="40.72514444"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.68197984" lat="21.12593168"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40408,36 +40406,35 @@
       <c r="E27" s="190">
         <v>4513180</v>
       </c>
-      <c r="F27" s="138" cm="1">
-        <f t="array" ref="F27:G27">_xll.PE.trf.Transform($D$4,$D$5,D27,E27)</f>
-        <v>19.854659382414237</v>
+      <c r="F27" s="138">
+        <v>39.763385526637173</v>
       </c>
       <c r="G27" s="140">
-        <v>40.74646776162173</v>
+        <v>21.152279249110322</v>
       </c>
       <c r="H27" s="138" t="str" cm="1">
         <f t="array" ref="H27">_xll.PE.deg.AsString(F27)</f>
-        <v>19 51 17</v>
+        <v>39 45 48</v>
       </c>
       <c r="I27" s="139" t="str" cm="1">
         <f t="array" ref="I27">_xll.PE.deg.AsString(G27)</f>
-        <v>40 44 47</v>
+        <v>21 09 08</v>
       </c>
       <c r="J27" s="138" cm="1">
         <f t="array" ref="J27">_xll.PE.deg.FromString(H27)</f>
-        <v>19.854722222222225</v>
+        <v>39.763333333333335</v>
       </c>
       <c r="K27" s="140" cm="1">
         <f t="array" ref="K27">_xll.PE.deg.FromString(I27)</f>
-        <v>40.746388888888887</v>
+        <v>21.152222222222221</v>
       </c>
       <c r="L27" s="75">
         <f t="shared" si="3"/>
-        <v>-6.2839807988268603E-5</v>
+        <v>5.2193303837100302E-5</v>
       </c>
       <c r="M27" s="76">
         <f t="shared" si="3"/>
-        <v>7.8872732842683035E-5</v>
+        <v>5.702688810060863E-5</v>
       </c>
       <c r="N27" s="10">
         <f t="shared" si="4"/>
@@ -40453,11 +40450,11 @@
       </c>
       <c r="Q27" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>19.85465938,40.74646776</v>
+        <v>39.76338553,21.15227925</v>
       </c>
       <c r="R27" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="19.85465938" lat="40.74646776"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.76338553" lat="21.15227925"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40474,36 +40471,35 @@
       <c r="E28" s="190">
         <v>4518740</v>
       </c>
-      <c r="F28" s="138" cm="1">
-        <f t="array" ref="F28:G28">_xll.PE.trf.Transform($D$4,$D$5,D28,E28)</f>
-        <v>20.099124970644958</v>
+      <c r="F28" s="138">
+        <v>39.949775411026479</v>
       </c>
       <c r="G28" s="140">
-        <v>40.798701544598003</v>
+        <v>21.217753331295434</v>
       </c>
       <c r="H28" s="138" t="str" cm="1">
         <f t="array" ref="H28">_xll.PE.deg.AsString(F28)</f>
-        <v>20 05 57</v>
+        <v>39 56 59</v>
       </c>
       <c r="I28" s="139" t="str" cm="1">
         <f t="array" ref="I28">_xll.PE.deg.AsString(G28)</f>
-        <v>40 47 55</v>
+        <v>21 13 04</v>
       </c>
       <c r="J28" s="138" cm="1">
         <f t="array" ref="J28">_xll.PE.deg.FromString(H28)</f>
-        <v>20.099166666666665</v>
+        <v>39.949722222222221</v>
       </c>
       <c r="K28" s="140" cm="1">
         <f t="array" ref="K28">_xll.PE.deg.FromString(I28)</f>
-        <v>40.798611111111107</v>
+        <v>21.217777777777776</v>
       </c>
       <c r="L28" s="75">
         <f t="shared" si="3"/>
-        <v>-4.1696021707338105E-5</v>
+        <v>5.3188804258752498E-5</v>
       </c>
       <c r="M28" s="76">
         <f t="shared" si="3"/>
-        <v>9.0433486896301929E-5</v>
+        <v>-2.4446482342455056E-5</v>
       </c>
       <c r="N28" s="39">
         <f t="shared" si="4"/>
@@ -40516,11 +40512,11 @@
       <c r="P28" s="89"/>
       <c r="Q28" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>20.09912497,40.79870154</v>
+        <v>39.94977541,21.21775333</v>
       </c>
       <c r="R28" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="20.09912497" lat="40.79870154"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.94977541" lat="21.21775333"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40542,36 +40538,35 @@
         <f>E28+$D$8*COS(RADIANS(O27))</f>
         <v>4519777.2910376322</v>
       </c>
-      <c r="F29" s="135" cm="1">
-        <f t="array" ref="F29:G29">_xll.PE.trf.Transform($D$4,$D$5,D29,E29)</f>
-        <v>20.144776595350073</v>
+      <c r="F29" s="135">
+        <v>39.984544027985052</v>
       </c>
       <c r="G29" s="137">
-        <v>40.808389494859469</v>
+        <v>21.230007913744046</v>
       </c>
       <c r="H29" s="135" t="str" cm="1">
         <f t="array" ref="H29">_xll.PE.deg.AsString(F29)</f>
-        <v>20 08 41</v>
+        <v>39 59 04</v>
       </c>
       <c r="I29" s="136" t="str" cm="1">
         <f t="array" ref="I29">_xll.PE.deg.AsString(G29)</f>
-        <v>40 48 30</v>
+        <v>21 13 48</v>
       </c>
       <c r="J29" s="135" cm="1">
         <f t="array" ref="J29">_xll.PE.deg.FromString(H29)</f>
-        <v>20.144722222222221</v>
+        <v>39.984444444444442</v>
       </c>
       <c r="K29" s="137" cm="1">
         <f t="array" ref="K29">_xll.PE.deg.FromString(I29)</f>
-        <v>40.80833333333333</v>
+        <v>21.229999999999997</v>
       </c>
       <c r="L29" s="73">
         <f t="shared" si="3"/>
-        <v>5.4373127852613834E-5</v>
+        <v>9.958354061012642E-5</v>
       </c>
       <c r="M29" s="74">
         <f t="shared" si="3"/>
-        <v>5.6161526138964746E-5</v>
+        <v>7.9137440494037037E-6</v>
       </c>
       <c r="N29" s="39">
         <f t="shared" si="4"/>
@@ -40586,11 +40581,11 @@
       </c>
       <c r="Q29" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>20.14477660,40.80838949</v>
+        <v>39.98454403,21.23000791</v>
       </c>
       <c r="R29" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="20.14477660" lat="40.80838949"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.98454403" lat="21.23000791"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40609,36 +40604,35 @@
         <f>E29+$D$7*COS(RADIANS(O28))</f>
         <v>4520555.2593158567</v>
       </c>
-      <c r="F30" s="141" cm="1">
-        <f t="array" ref="F30:G30">_xll.PE.trf.Transform($D$4,$D$5,D30,E30)</f>
-        <v>20.17902421260742</v>
+      <c r="F30" s="141">
+        <v>40.010619479406813</v>
       </c>
       <c r="G30" s="143">
-        <v>40.815643676429772</v>
+        <v>21.239207057687711</v>
       </c>
       <c r="H30" s="141" t="str" cm="1">
         <f t="array" ref="H30">_xll.PE.deg.AsString(F30)</f>
-        <v>20 10 44</v>
+        <v>40 00 38</v>
       </c>
       <c r="I30" s="142" t="str" cm="1">
         <f t="array" ref="I30">_xll.PE.deg.AsString(G30)</f>
-        <v>40 48 56</v>
+        <v>21 14 21</v>
       </c>
       <c r="J30" s="141" cm="1">
         <f t="array" ref="J30">_xll.PE.deg.FromString(H30)</f>
-        <v>20.178888888888888</v>
+        <v>40.010555555555555</v>
       </c>
       <c r="K30" s="143" cm="1">
         <f t="array" ref="K30">_xll.PE.deg.FromString(I30)</f>
-        <v>40.815555555555555</v>
+        <v>21.239166666666666</v>
       </c>
       <c r="L30" s="77">
         <f t="shared" si="3"/>
-        <v>1.3532371853131053E-4</v>
+        <v>6.3923851257641218E-5</v>
       </c>
       <c r="M30" s="78">
         <f t="shared" si="3"/>
-        <v>8.8120874217167966E-5</v>
+        <v>4.0391021045138586E-5</v>
       </c>
       <c r="N30" s="34">
         <f>SUM(N25:N28)</f>
@@ -40649,15 +40643,15 @@
       </c>
       <c r="P30" s="90" cm="1">
         <f t="array" ref="P30">_xll.PE.crs.GeodesicDistance($D$5,J25:K29)</f>
-        <v>38751.296513615664</v>
+        <v>37304.794441425118</v>
       </c>
       <c r="Q30" s="44" t="str">
         <f t="shared" si="6"/>
-        <v>20.17902421,40.81564368</v>
+        <v>40.01061948,21.23920706</v>
       </c>
       <c r="R30" s="98" t="str">
         <f t="shared" si="7"/>
-        <v>&lt;trkpt lon="20.17902421" lat="40.81564368"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.01061948" lat="21.23920706"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40735,35 +40729,35 @@
         <v>4525483.832561858</v>
       </c>
       <c r="F33" s="132" cm="1">
-        <f t="array" ref="F33:G33">_xll.PE.trf.Transform($D$4,$D$5,D33,E33)</f>
-        <v>19.701095294756342</v>
+        <f t="array" ref="F33:G39">_xll.PE.trf.Transform($D$4,$D$5,D33:D39,E33:E39)</f>
+        <v>39.647911791234314</v>
       </c>
       <c r="G33" s="134">
-        <v>40.855631732298527</v>
+        <v>21.295374193543232</v>
       </c>
       <c r="H33" s="132" t="str" cm="1">
         <f t="array" ref="H33">_xll.PE.deg.AsString(F33)</f>
-        <v>19 42 04</v>
+        <v>39 38 52</v>
       </c>
       <c r="I33" s="133" t="str" cm="1">
         <f t="array" ref="I33">_xll.PE.deg.AsString(G33)</f>
-        <v>40 51 20</v>
+        <v>21 17 43</v>
       </c>
       <c r="J33" s="132" cm="1">
         <f t="array" ref="J33">_xll.PE.deg.FromString(H33)</f>
-        <v>19.701111111111111</v>
+        <v>39.647777777777776</v>
       </c>
       <c r="K33" s="134" cm="1">
         <f t="array" ref="K33">_xll.PE.deg.FromString(I33)</f>
-        <v>40.855555555555554</v>
+        <v>21.29527777777778</v>
       </c>
       <c r="L33" s="71">
         <f t="shared" ref="L33:M39" si="8">F33-J33</f>
-        <v>-1.5816354768105612E-5</v>
+        <v>1.3401345653818453E-4</v>
       </c>
       <c r="M33" s="72">
         <f t="shared" si="8"/>
-        <v>7.6176742972222655E-5</v>
+        <v>9.6415765451496327E-5</v>
       </c>
       <c r="N33" s="8">
         <f t="shared" ref="N33:N38" si="9">SQRT((D34-D33)^2+(E34-E33)^2)</f>
@@ -40776,11 +40770,11 @@
       <c r="P33" s="89"/>
       <c r="Q33" s="44" t="str">
         <f t="shared" ref="Q33:Q39" si="11">CONCATENATE(TEXT(F33,"#.00000000"),",",TEXT(G33,"#.00000000"))</f>
-        <v>19.70109529,40.85563173</v>
+        <v>39.64791179,21.29537419</v>
       </c>
       <c r="R33" s="98" t="str">
         <f t="shared" ref="R33:R39" si="12">CONCATENATE("&lt;trkpt lon=""",TEXT(F33,"#.00000000"),""" lat=""",TEXT(G33,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B33,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.70109529" lat="40.85563173"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.64791179" lat="21.29537419"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40799,36 +40793,35 @@
         <f>E35-$D$8*COS(RADIANS(O35))</f>
         <v>4524196.0807782048</v>
       </c>
-      <c r="F34" s="135" cm="1">
-        <f t="array" ref="F34:G34">_xll.PE.trf.Transform($D$4,$D$5,D34,E34)</f>
-        <v>19.733442649612513</v>
+      <c r="F34" s="135">
+        <v>39.672352702801376</v>
       </c>
       <c r="G34" s="137">
-        <v>40.844395968057178</v>
+        <v>21.280469724769016</v>
       </c>
       <c r="H34" s="135" t="str" cm="1">
         <f t="array" ref="H34">_xll.PE.deg.AsString(F34)</f>
-        <v>19 44 00</v>
+        <v>39 40 20</v>
       </c>
       <c r="I34" s="136" t="str" cm="1">
         <f t="array" ref="I34">_xll.PE.deg.AsString(G34)</f>
-        <v>40 50 40</v>
+        <v>21 16 50</v>
       </c>
       <c r="J34" s="135" cm="1">
         <f t="array" ref="J34">_xll.PE.deg.FromString(H34)</f>
-        <v>19.733333333333334</v>
+        <v>39.672222222222217</v>
       </c>
       <c r="K34" s="137" cm="1">
         <f t="array" ref="K34">_xll.PE.deg.FromString(I34)</f>
-        <v>40.844444444444449</v>
+        <v>21.280555555555555</v>
       </c>
       <c r="L34" s="73">
         <f t="shared" si="8"/>
-        <v>1.0931627917898368E-4</v>
+        <v>1.3048057915909794E-4</v>
       </c>
       <c r="M34" s="74">
         <f t="shared" si="8"/>
-        <v>-4.8476387270568466E-5</v>
+        <v>-8.5830786538565462E-5</v>
       </c>
       <c r="N34" s="39">
         <f t="shared" si="9"/>
@@ -40841,11 +40834,11 @@
       <c r="P34" s="89"/>
       <c r="Q34" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>19.73344265,40.84439597</v>
+        <v>39.67235270,21.28046972</v>
       </c>
       <c r="R34" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="19.73344265" lat="40.84439597"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.67235270" lat="21.28046972"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40862,36 +40855,35 @@
       <c r="E35" s="195">
         <v>4522479.0784</v>
       </c>
-      <c r="F35" s="138" cm="1">
-        <f t="array" ref="F35:G35">_xll.PE.trf.Transform($D$4,$D$5,D35,E35)</f>
-        <v>19.776555734991796</v>
+      <c r="F35" s="138">
+        <v>39.704937504201723</v>
       </c>
       <c r="G35" s="140">
-        <v>40.829400558913271</v>
+        <v>21.260580812886403</v>
       </c>
       <c r="H35" s="138" t="str" cm="1">
         <f t="array" ref="H35">_xll.PE.deg.AsString(F35)</f>
-        <v>19 46 36</v>
+        <v>39 42 18</v>
       </c>
       <c r="I35" s="139" t="str" cm="1">
         <f t="array" ref="I35">_xll.PE.deg.AsString(G35)</f>
-        <v>40 49 46</v>
+        <v>21 15 38</v>
       </c>
       <c r="J35" s="138" cm="1">
         <f t="array" ref="J35">_xll.PE.deg.FromString(H35)</f>
-        <v>19.776666666666667</v>
+        <v>39.705000000000005</v>
       </c>
       <c r="K35" s="140" cm="1">
         <f t="array" ref="K35">_xll.PE.deg.FromString(I35)</f>
-        <v>40.829444444444448</v>
+        <v>21.260555555555555</v>
       </c>
       <c r="L35" s="75">
         <f t="shared" si="8"/>
-        <v>-1.1093167487175037E-4</v>
+        <v>-6.2495798282213855E-5</v>
       </c>
       <c r="M35" s="76">
         <f t="shared" si="8"/>
-        <v>-4.388553117706806E-5</v>
+        <v>2.5257330847239245E-5</v>
       </c>
       <c r="N35" s="10">
         <f t="shared" si="9"/>
@@ -40906,11 +40898,11 @@
       </c>
       <c r="Q35" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>19.77655573,40.82940056</v>
+        <v>39.70493750,21.26058081</v>
       </c>
       <c r="R35" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="19.77655573" lat="40.82940056"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.70493750" lat="21.26058081"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40927,36 +40919,35 @@
       <c r="E36" s="195">
         <v>4517866.0075000003</v>
       </c>
-      <c r="F36" s="138" cm="1">
-        <f t="array" ref="F36:G36">_xll.PE.trf.Transform($D$4,$D$5,D36,E36)</f>
-        <v>19.892292936682402</v>
+      <c r="F36" s="138">
+        <v>39.792465578440506</v>
       </c>
       <c r="G36" s="140">
-        <v>40.78903112296662</v>
+        <v>21.207052772857299</v>
       </c>
       <c r="H36" s="138" t="str" cm="1">
         <f t="array" ref="H36">_xll.PE.deg.AsString(F36)</f>
-        <v>19 53 32</v>
+        <v>39 47 33</v>
       </c>
       <c r="I36" s="139" t="str" cm="1">
         <f t="array" ref="I36">_xll.PE.deg.AsString(G36)</f>
-        <v>40 47 21</v>
+        <v>21 12 25</v>
       </c>
       <c r="J36" s="138" cm="1">
         <f t="array" ref="J36">_xll.PE.deg.FromString(H36)</f>
-        <v>19.892222222222223</v>
+        <v>39.792499999999997</v>
       </c>
       <c r="K36" s="140" cm="1">
         <f t="array" ref="K36">_xll.PE.deg.FromString(I36)</f>
-        <v>40.789166666666667</v>
+        <v>21.206944444444442</v>
       </c>
       <c r="L36" s="75">
         <f t="shared" si="8"/>
-        <v>7.0714460179033267E-5</v>
+        <v>-3.4421559490738218E-5</v>
       </c>
       <c r="M36" s="76">
         <f t="shared" si="8"/>
-        <v>-1.3554370004698058E-4</v>
+        <v>1.083284128569062E-4</v>
       </c>
       <c r="N36" s="10">
         <f t="shared" si="9"/>
@@ -40972,11 +40963,11 @@
       </c>
       <c r="Q36" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>19.89229294,40.78903112</v>
+        <v>39.79246558,21.20705277</v>
       </c>
       <c r="R36" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="19.89229294" lat="40.78903112"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.79246558" lat="21.20705277"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40993,36 +40984,35 @@
       <c r="E37" s="195">
         <v>4514669.1546</v>
       </c>
-      <c r="F37" s="138" cm="1">
-        <f t="array" ref="F37:G37">_xll.PE.trf.Transform($D$4,$D$5,D37,E37)</f>
-        <v>19.965689392996619</v>
+      <c r="F37" s="138">
+        <v>39.847989843091248</v>
       </c>
       <c r="G37" s="140">
-        <v>40.760925753185163</v>
+        <v>21.169865879923282</v>
       </c>
       <c r="H37" s="138" t="str" cm="1">
         <f t="array" ref="H37">_xll.PE.deg.AsString(F37)</f>
-        <v>19 57 56</v>
+        <v>39 50 53</v>
       </c>
       <c r="I37" s="139" t="str" cm="1">
         <f t="array" ref="I37">_xll.PE.deg.AsString(G37)</f>
-        <v>40 45 39</v>
+        <v>21 10 12</v>
       </c>
       <c r="J37" s="138" cm="1">
         <f t="array" ref="J37">_xll.PE.deg.FromString(H37)</f>
-        <v>19.965555555555554</v>
+        <v>39.848055555555561</v>
       </c>
       <c r="K37" s="140" cm="1">
         <f t="array" ref="K37">_xll.PE.deg.FromString(I37)</f>
-        <v>40.760833333333331</v>
+        <v>21.17</v>
       </c>
       <c r="L37" s="75">
         <f t="shared" si="8"/>
-        <v>1.3383744106576501E-4</v>
+        <v>-6.571246431263944E-5</v>
       </c>
       <c r="M37" s="76">
         <f t="shared" si="8"/>
-        <v>9.2419851831948563E-5</v>
+        <v>-1.3412007671931292E-4</v>
       </c>
       <c r="N37" s="39">
         <f t="shared" si="9"/>
@@ -41035,11 +41025,11 @@
       <c r="P37" s="89"/>
       <c r="Q37" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>19.96568939,40.76092575</v>
+        <v>39.84798984,21.16986588</v>
       </c>
       <c r="R37" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="19.96568939" lat="40.76092575"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.84798984" lat="21.16986588"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41061,36 +41051,35 @@
         <f>E37+$D$8*COS(RADIANS(O36))</f>
         <v>4512826.2181084193</v>
       </c>
-      <c r="F38" s="135" cm="1">
-        <f t="array" ref="F38:G38">_xll.PE.trf.Transform($D$4,$D$5,D38,E38)</f>
-        <v>20.007973540197661</v>
+      <c r="F38" s="135">
+        <v>39.879993122120752</v>
       </c>
       <c r="G38" s="137">
-        <v>40.744701833348564</v>
+        <v>21.148401031869863</v>
       </c>
       <c r="H38" s="135" t="str" cm="1">
         <f t="array" ref="H38">_xll.PE.deg.AsString(F38)</f>
-        <v>20 00 29</v>
+        <v>39 52 48</v>
       </c>
       <c r="I38" s="136" t="str" cm="1">
         <f t="array" ref="I38">_xll.PE.deg.AsString(G38)</f>
-        <v>40 44 41</v>
+        <v>21 08 54</v>
       </c>
       <c r="J38" s="135" cm="1">
         <f t="array" ref="J38">_xll.PE.deg.FromString(H38)</f>
-        <v>20.008055555555554</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="K38" s="137" cm="1">
         <f t="array" ref="K38">_xll.PE.deg.FromString(I38)</f>
-        <v>40.744722222222222</v>
+        <v>21.148333333333333</v>
       </c>
       <c r="L38" s="73">
         <f t="shared" si="8"/>
-        <v>-8.2015357893538976E-5</v>
+        <v>-6.8778792510215681E-6</v>
       </c>
       <c r="M38" s="74">
         <f t="shared" si="8"/>
-        <v>-2.0388873657850581E-5</v>
+        <v>6.7698536529547937E-5</v>
       </c>
       <c r="N38" s="39">
         <f t="shared" si="9"/>
@@ -41105,11 +41094,11 @@
       </c>
       <c r="Q38" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>20.00797354,40.74470183</v>
+        <v>39.87999312,21.14840103</v>
       </c>
       <c r="R38" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="20.00797354" lat="40.74470183"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.87999312" lat="21.14840103"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41128,36 +41117,35 @@
         <f>E38+$D$7*COS(RADIANS(O37))</f>
         <v>4511444.0157397343</v>
       </c>
-      <c r="F39" s="141" cm="1">
-        <f t="array" ref="F39:G39">_xll.PE.trf.Transform($D$4,$D$5,D39,E39)</f>
-        <v>20.039673311207402</v>
+      <c r="F39" s="141">
+        <v>39.903992881029595</v>
       </c>
       <c r="G39" s="143">
-        <v>40.732523543254402</v>
+        <v>21.132289319182163</v>
       </c>
       <c r="H39" s="141" t="str" cm="1">
         <f t="array" ref="H39">_xll.PE.deg.AsString(F39)</f>
-        <v>20 02 23</v>
+        <v>39 54 14</v>
       </c>
       <c r="I39" s="142" t="str" cm="1">
         <f t="array" ref="I39">_xll.PE.deg.AsString(G39)</f>
-        <v>40 43 57</v>
+        <v>21 07 56</v>
       </c>
       <c r="J39" s="141" cm="1">
         <f t="array" ref="J39">_xll.PE.deg.FromString(H39)</f>
-        <v>20.039722222222224</v>
+        <v>39.903888888888886</v>
       </c>
       <c r="K39" s="143" cm="1">
         <f t="array" ref="K39">_xll.PE.deg.FromString(I39)</f>
-        <v>40.732500000000002</v>
+        <v>21.132222222222222</v>
       </c>
       <c r="L39" s="77">
         <f t="shared" si="8"/>
-        <v>-4.8911014822294874E-5</v>
+        <v>1.0399214070844209E-4</v>
       </c>
       <c r="M39" s="78">
         <f t="shared" si="8"/>
-        <v>2.3543254400237856E-5</v>
+        <v>6.7096959941892464E-5</v>
       </c>
       <c r="N39" s="34">
         <f>SUM(N34:N37)</f>
@@ -41168,15 +41156,15 @@
       </c>
       <c r="P39" s="90" cm="1">
         <f t="array" ref="P39">_xll.PE.crs.GeodesicDistance($D$5,J34:K38)</f>
-        <v>25698.595848817353</v>
+        <v>26075.765539000367</v>
       </c>
       <c r="Q39" s="44" t="str">
         <f t="shared" si="11"/>
-        <v>20.03967331,40.73252354</v>
+        <v>39.90399288,21.13228932</v>
       </c>
       <c r="R39" s="98" t="str">
         <f t="shared" si="12"/>
-        <v>&lt;trkpt lon="20.03967331" lat="40.73252354"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.90399288" lat="21.13228932"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41254,35 +41242,35 @@
         <v>4466849.4596596127</v>
       </c>
       <c r="F42" s="132" cm="1">
-        <f t="array" ref="F42:G42">_xll.PE.trf.Transform($D$4,$D$5,D42,E42)</f>
-        <v>19.873652457410753</v>
+        <f t="array" ref="F42:G47">_xll.PE.trf.Transform($D$4,$D$5,D42:D47,E42:E47)</f>
+        <v>39.771952595497545</v>
       </c>
       <c r="G42" s="134">
-        <v>40.329447526505525</v>
+        <v>20.611546495957494</v>
       </c>
       <c r="H42" s="132" t="str" cm="1">
         <f t="array" ref="H42">_xll.PE.deg.AsString(F42)</f>
-        <v>19 52 25</v>
+        <v>39 46 19</v>
       </c>
       <c r="I42" s="133" t="str" cm="1">
         <f t="array" ref="I42">_xll.PE.deg.AsString(G42)</f>
-        <v>40 19 46</v>
+        <v>20 36 42</v>
       </c>
       <c r="J42" s="132" cm="1">
         <f t="array" ref="J42">_xll.PE.deg.FromString(H42)</f>
-        <v>19.87361111111111</v>
+        <v>39.771944444444443</v>
       </c>
       <c r="K42" s="134" cm="1">
         <f t="array" ref="K42">_xll.PE.deg.FromString(I42)</f>
-        <v>40.329444444444448</v>
+        <v>20.611666666666668</v>
       </c>
       <c r="L42" s="83">
         <f t="shared" ref="L42:M47" si="13">F42-J42</f>
-        <v>4.1346299642697204E-5</v>
+        <v>8.1510531018125221E-6</v>
       </c>
       <c r="M42" s="79">
         <f t="shared" si="13"/>
-        <v>3.0820610774640045E-6</v>
+        <v>-1.2017070917380579E-4</v>
       </c>
       <c r="N42" s="8">
         <f>SQRT((D43-D42)^2+(E43-E42)^2)</f>
@@ -41295,11 +41283,11 @@
       <c r="P42" s="89"/>
       <c r="Q42" s="44" t="str">
         <f t="shared" ref="Q42:Q47" si="14">CONCATENATE(TEXT(F42,"#.00000000"),",",TEXT(G42,"#.00000000"))</f>
-        <v>19.87365246,40.32944753</v>
+        <v>39.77195260,20.61154650</v>
       </c>
       <c r="R42" s="98" t="str">
         <f t="shared" ref="R42:R47" si="15">CONCATENATE("&lt;trkpt lon=""",TEXT(F42,"#.00000000"),""" lat=""",TEXT(G42,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B42,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.87365246" lat="40.32944753"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.77195260" lat="20.61154650"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41318,36 +41306,35 @@
         <f>E44-$D$8*COS(RADIANS(O44))</f>
         <v>4467896.6912340643</v>
       </c>
-      <c r="F43" s="135" cm="1">
-        <f t="array" ref="F43:G43">_xll.PE.trf.Transform($D$4,$D$5,D43,E43)</f>
-        <v>19.906574728018438</v>
+      <c r="F43" s="135">
+        <v>39.797312024085414</v>
       </c>
       <c r="G43" s="137">
-        <v>40.339194134416083</v>
+        <v>20.623631154478261</v>
       </c>
       <c r="H43" s="135" t="str" cm="1">
         <f t="array" ref="H43">_xll.PE.deg.AsString(F43)</f>
-        <v>19 54 24</v>
+        <v>39 47 50</v>
       </c>
       <c r="I43" s="136" t="str" cm="1">
         <f t="array" ref="I43">_xll.PE.deg.AsString(G43)</f>
-        <v>40 20 21</v>
+        <v>20 37 25</v>
       </c>
       <c r="J43" s="135" cm="1">
         <f t="array" ref="J43">_xll.PE.deg.FromString(H43)</f>
-        <v>19.906666666666666</v>
+        <v>39.797222222222217</v>
       </c>
       <c r="K43" s="137" cm="1">
         <f t="array" ref="K43">_xll.PE.deg.FromString(I43)</f>
-        <v>40.339166666666671</v>
+        <v>20.62361111111111</v>
       </c>
       <c r="L43" s="84">
         <f t="shared" si="13"/>
-        <v>-9.1938648228762077E-5</v>
+        <v>8.9801863197180865E-5</v>
       </c>
       <c r="M43" s="80">
         <f t="shared" si="13"/>
-        <v>2.7467749411869136E-5</v>
+        <v>2.004336715089039E-5</v>
       </c>
       <c r="N43" s="39">
         <f>SQRT((D44-D43)^2+(E44-E43)^2)</f>
@@ -41362,11 +41349,11 @@
       </c>
       <c r="Q43" s="44" t="str">
         <f t="shared" si="14"/>
-        <v>19.90657473,40.33919413</v>
+        <v>39.79731202,20.62363115</v>
       </c>
       <c r="R43" s="98" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;trkpt lon="19.90657473" lat="40.33919413"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.79731202" lat="20.62363115"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41383,36 +41370,35 @@
       <c r="E44" s="195">
         <v>4469293</v>
       </c>
-      <c r="F44" s="138" cm="1">
-        <f t="array" ref="F44:G44">_xll.PE.trf.Transform($D$4,$D$5,D44,E44)</f>
-        <v>19.950486102913491</v>
+      <c r="F44" s="138">
+        <v>39.831122527841188</v>
       </c>
       <c r="G44" s="140">
-        <v>40.352175195042321</v>
+        <v>20.639757750080758</v>
       </c>
       <c r="H44" s="138" t="str" cm="1">
         <f t="array" ref="H44">_xll.PE.deg.AsString(F44)</f>
-        <v>19 57 02</v>
+        <v>39 49 52</v>
       </c>
       <c r="I44" s="139" t="str" cm="1">
         <f t="array" ref="I44">_xll.PE.deg.AsString(G44)</f>
-        <v>40 21 08</v>
+        <v>20 38 23</v>
       </c>
       <c r="J44" s="138" cm="1">
         <f t="array" ref="J44">_xll.PE.deg.FromString(H44)</f>
-        <v>19.950555555555553</v>
+        <v>39.831111111111113</v>
       </c>
       <c r="K44" s="140" cm="1">
         <f t="array" ref="K44">_xll.PE.deg.FromString(I44)</f>
-        <v>40.352222222222224</v>
+        <v>20.639722222222222</v>
       </c>
       <c r="L44" s="85">
         <f t="shared" si="13"/>
-        <v>-6.9452642062373116E-5</v>
+        <v>1.1416730075097803E-5</v>
       </c>
       <c r="M44" s="81">
         <f t="shared" si="13"/>
-        <v>-4.7027179903125216E-5</v>
+        <v>3.5527858535999712E-5</v>
       </c>
       <c r="N44" s="10">
         <f>SQRT((D45-D44)^2+(E45-E44)^2)</f>
@@ -41428,11 +41414,11 @@
       </c>
       <c r="Q44" s="44" t="str">
         <f t="shared" si="14"/>
-        <v>19.95048610,40.35217520</v>
+        <v>39.83112253,20.63975775</v>
       </c>
       <c r="R44" s="98" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;trkpt lon="19.95048610" lat="40.35217520"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.83112253" lat="20.63975775"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41449,36 +41435,35 @@
       <c r="E45" s="195">
         <v>4479111.9987000003</v>
       </c>
-      <c r="F45" s="138" cm="1">
-        <f t="array" ref="F45:G45">_xll.PE.trf.Transform($D$4,$D$5,D45,E45)</f>
-        <v>20.259758719416958</v>
+      <c r="F45" s="138">
+        <v>40.068814349444395</v>
       </c>
       <c r="G45" s="140">
-        <v>40.442992245042944</v>
+        <v>20.753607675556793</v>
       </c>
       <c r="H45" s="138" t="str" cm="1">
         <f t="array" ref="H45">_xll.PE.deg.AsString(F45)</f>
-        <v>20 15 35</v>
+        <v>40 04 08</v>
       </c>
       <c r="I45" s="139" t="str" cm="1">
         <f t="array" ref="I45">_xll.PE.deg.AsString(G45)</f>
-        <v>40 26 35</v>
+        <v>20 45 13</v>
       </c>
       <c r="J45" s="138" cm="1">
         <f t="array" ref="J45">_xll.PE.deg.FromString(H45)</f>
-        <v>20.259722222222223</v>
+        <v>40.068888888888893</v>
       </c>
       <c r="K45" s="140" cm="1">
         <f t="array" ref="K45">_xll.PE.deg.FromString(I45)</f>
-        <v>40.443055555555553</v>
+        <v>20.753611111111113</v>
       </c>
       <c r="L45" s="85">
         <f t="shared" si="13"/>
-        <v>3.6497194734863569E-5</v>
+        <v>-7.4539444497645491E-5</v>
       </c>
       <c r="M45" s="81">
         <f t="shared" si="13"/>
-        <v>-6.3310512608438785E-5</v>
+        <v>-3.4355543192532423E-6</v>
       </c>
       <c r="N45" s="39">
         <f>SQRT((D46-D45)^2+(E46-E45)^2)</f>
@@ -41491,11 +41476,11 @@
       <c r="P45" s="89"/>
       <c r="Q45" s="44" t="str">
         <f t="shared" si="14"/>
-        <v>20.25975872,40.44299225</v>
+        <v>40.06881435,20.75360768</v>
       </c>
       <c r="R45" s="98" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;trkpt lon="20.25975872" lat="40.44299225"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.06881435" lat="20.75360768"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41517,36 +41502,35 @@
         <f>E45+$D$8*COS(RADIANS(O44))</f>
         <v>4480508.3074659361</v>
       </c>
-      <c r="F46" s="135" cm="1">
-        <f t="array" ref="F46:G46">_xll.PE.trf.Transform($D$4,$D$5,D46,E46)</f>
-        <v>20.303807202490884</v>
+      <c r="F46" s="135">
+        <v>40.102605584338633</v>
       </c>
       <c r="G46" s="137">
-        <v>40.455840147522494</v>
+        <v>20.769861557446394</v>
       </c>
       <c r="H46" s="135" t="str" cm="1">
         <f t="array" ref="H46">_xll.PE.deg.AsString(F46)</f>
-        <v>20 18 14</v>
+        <v>40 06 09</v>
       </c>
       <c r="I46" s="136" t="str" cm="1">
         <f t="array" ref="I46">_xll.PE.deg.AsString(G46)</f>
-        <v>40 27 21</v>
+        <v>20 46 12</v>
       </c>
       <c r="J46" s="135" cm="1">
         <f t="array" ref="J46">_xll.PE.deg.FromString(H46)</f>
-        <v>20.303888888888888</v>
+        <v>40.102499999999999</v>
       </c>
       <c r="K46" s="137" cm="1">
         <f t="array" ref="K46">_xll.PE.deg.FromString(I46)</f>
-        <v>40.455833333333338</v>
+        <v>20.77</v>
       </c>
       <c r="L46" s="84">
         <f t="shared" si="13"/>
-        <v>-8.1686398004876537E-5</v>
+        <v>1.0558433863394612E-4</v>
       </c>
       <c r="M46" s="80">
         <f t="shared" si="13"/>
-        <v>6.8141891560458134E-6</v>
+        <v>-1.3844255360595525E-4</v>
       </c>
       <c r="N46" s="39">
         <f>SQRT((D47-D46)^2+(E47-E46)^2)</f>
@@ -41561,11 +41545,11 @@
       </c>
       <c r="Q46" s="44" t="str">
         <f t="shared" si="14"/>
-        <v>20.30380720,40.45584015</v>
+        <v>40.10260558,20.76986156</v>
       </c>
       <c r="R46" s="98" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;trkpt lon="20.30380720" lat="40.45584015"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.10260558" lat="20.76986156"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41584,36 +41568,35 @@
         <f>E46+$D$7*COS(RADIANS(O45))</f>
         <v>4481555.5390403876</v>
       </c>
-      <c r="F47" s="141" cm="1">
-        <f t="array" ref="F47:G47">_xll.PE.trf.Transform($D$4,$D$5,D47,E47)</f>
-        <v>20.336854707752281</v>
+      <c r="F47" s="141">
+        <v>40.127947412484311</v>
       </c>
       <c r="G47" s="143">
-        <v>40.465465128118076</v>
+        <v>20.782062480924413</v>
       </c>
       <c r="H47" s="141" t="str" cm="1">
         <f t="array" ref="H47">_xll.PE.deg.AsString(F47)</f>
-        <v>20 20 13</v>
+        <v>40 07 41</v>
       </c>
       <c r="I47" s="142" t="str" cm="1">
         <f t="array" ref="I47">_xll.PE.deg.AsString(G47)</f>
-        <v>40 27 56</v>
+        <v>20 46 55</v>
       </c>
       <c r="J47" s="141" cm="1">
         <f t="array" ref="J47">_xll.PE.deg.FromString(H47)</f>
-        <v>20.336944444444445</v>
+        <v>40.128055555555555</v>
       </c>
       <c r="K47" s="143" cm="1">
         <f t="array" ref="K47">_xll.PE.deg.FromString(I47)</f>
-        <v>40.465555555555561</v>
+        <v>20.781944444444445</v>
       </c>
       <c r="L47" s="86">
         <f t="shared" si="13"/>
-        <v>-8.9736692164166243E-5</v>
+        <v>-1.081430712446263E-4</v>
       </c>
       <c r="M47" s="82">
         <f t="shared" si="13"/>
-        <v>-9.0427437484663642E-5</v>
+        <v>1.1803647996799782E-4</v>
       </c>
       <c r="N47" s="34">
         <f>SUM(N43:N45)</f>
@@ -41624,15 +41607,15 @@
       </c>
       <c r="P47" s="90" cm="1">
         <f t="array" ref="P47">_xll.PE.crs.GeodesicDistance($D$5,J42:K46)</f>
-        <v>39134.832653386409</v>
+        <v>38643.191914328607</v>
       </c>
       <c r="Q47" s="44" t="str">
         <f t="shared" si="14"/>
-        <v>20.33685471,40.46546513</v>
+        <v>40.12794741,20.78206248</v>
       </c>
       <c r="R47" s="98" t="str">
         <f t="shared" si="15"/>
-        <v>&lt;trkpt lon="20.33685471" lat="40.46546513"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.12794741" lat="20.78206248"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41710,35 +41693,35 @@
         <v>4464929.1109348536</v>
       </c>
       <c r="F50" s="132" cm="1">
-        <f t="array" ref="F50:G50">_xll.PE.trf.Transform($D$4,$D$5,D50,E50)</f>
-        <v>19.900207757522892</v>
+        <f t="array" ref="F50:G55">_xll.PE.trf.Transform($D$4,$D$5,D50:D55,E50:E55)</f>
+        <v>39.791989095864032</v>
       </c>
       <c r="G50" s="134">
-        <v>40.312409673182536</v>
+        <v>20.589013819347606</v>
       </c>
       <c r="H50" s="132" t="str" cm="1">
         <f t="array" ref="H50">_xll.PE.deg.AsString(F50)</f>
-        <v>19 54 01</v>
+        <v>39 47 31</v>
       </c>
       <c r="I50" s="133" t="str" cm="1">
         <f t="array" ref="I50">_xll.PE.deg.AsString(G50)</f>
-        <v>40 18 45</v>
+        <v>20 35 20</v>
       </c>
       <c r="J50" s="132" cm="1">
         <f t="array" ref="J50">_xll.PE.deg.FromString(H50)</f>
-        <v>19.900277777777777</v>
+        <v>39.791944444444439</v>
       </c>
       <c r="K50" s="134" cm="1">
         <f t="array" ref="K50">_xll.PE.deg.FromString(I50)</f>
-        <v>40.3125</v>
+        <v>20.588888888888889</v>
       </c>
       <c r="L50" s="83">
         <f t="shared" ref="L50:M55" si="16">F50-J50</f>
-        <v>-7.0020254884894939E-5</v>
+        <v>4.4651419592867114E-5</v>
       </c>
       <c r="M50" s="79">
         <f t="shared" si="16"/>
-        <v>-9.0326817463903808E-5</v>
+        <v>1.2493045871764252E-4</v>
       </c>
       <c r="N50" s="8">
         <f>SQRT((D51-D50)^2+(E51-E50)^2)</f>
@@ -41751,11 +41734,11 @@
       <c r="P50" s="89"/>
       <c r="Q50" s="44" t="str">
         <f t="shared" ref="Q50:Q55" si="17">CONCATENATE(TEXT(F50,"#.00000000"),",",TEXT(G50,"#.00000000"))</f>
-        <v>19.90020776,40.31240967</v>
+        <v>39.79198910,20.58901382</v>
       </c>
       <c r="R50" s="98" t="str">
         <f t="shared" ref="R50:R55" si="18">CONCATENATE("&lt;trkpt lon=""",TEXT(F50,"#.00000000"),""" lat=""",TEXT(G50,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B50,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.90020776" lat="40.31240967"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.79198910" lat="20.58901382"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41774,36 +41757,35 @@
         <f>E52-$D$8*COS(RADIANS(O52))</f>
         <v>4465879.6348627731</v>
       </c>
-      <c r="F51" s="135" cm="1">
-        <f t="array" ref="F51:G51">_xll.PE.trf.Transform($D$4,$D$5,D51,E51)</f>
-        <v>19.933541273379543</v>
+      <c r="F51" s="135">
+        <v>39.817654465781466</v>
       </c>
       <c r="G51" s="137">
-        <v>40.321281636115572</v>
+        <v>20.599962394933218</v>
       </c>
       <c r="H51" s="135" t="str" cm="1">
         <f t="array" ref="H51">_xll.PE.deg.AsString(F51)</f>
-        <v>19 56 01</v>
+        <v>39 49 04</v>
       </c>
       <c r="I51" s="136" t="str" cm="1">
         <f t="array" ref="I51">_xll.PE.deg.AsString(G51)</f>
-        <v>40 19 17</v>
+        <v>20 35 60</v>
       </c>
       <c r="J51" s="135" cm="1">
         <f t="array" ref="J51">_xll.PE.deg.FromString(H51)</f>
-        <v>19.933611111111112</v>
+        <v>39.817777777777778</v>
       </c>
       <c r="K51" s="137" cm="1">
         <f t="array" ref="K51">_xll.PE.deg.FromString(I51)</f>
-        <v>40.32138888888889</v>
+        <v>20.599999999999998</v>
       </c>
       <c r="L51" s="84">
         <f t="shared" si="16"/>
-        <v>-6.9837731569322159E-5</v>
+        <v>-1.2331199631177014E-4</v>
       </c>
       <c r="M51" s="80">
         <f t="shared" si="16"/>
-        <v>-1.0725277331857797E-4</v>
+        <v>-3.7605066779633489E-5</v>
       </c>
       <c r="N51" s="39">
         <f>SQRT((D52-D51)^2+(E52-E51)^2)</f>
@@ -41818,11 +41800,11 @@
       </c>
       <c r="Q51" s="44" t="str">
         <f t="shared" si="17"/>
-        <v>19.93354127,40.32128164</v>
+        <v>39.81765447,20.59996239</v>
       </c>
       <c r="R51" s="98" t="str">
         <f t="shared" si="18"/>
-        <v>&lt;trkpt lon="19.93354127" lat="40.32128164"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.81765447" lat="20.59996239"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41839,36 +41821,35 @@
       <c r="E52" s="195">
         <v>4467147.0000999998</v>
       </c>
-      <c r="F52" s="138" cm="1">
-        <f t="array" ref="F52:G52">_xll.PE.trf.Transform($D$4,$D$5,D52,E52)</f>
-        <v>19.97799981976652</v>
+      <c r="F52" s="138">
+        <v>39.851873236395171</v>
       </c>
       <c r="G52" s="140">
-        <v>40.333096123789161</v>
+        <v>20.61457306275846</v>
       </c>
       <c r="H52" s="138" t="str" cm="1">
         <f t="array" ref="H52">_xll.PE.deg.AsString(F52)</f>
-        <v>19 58 41</v>
+        <v>39 51 07</v>
       </c>
       <c r="I52" s="139" t="str" cm="1">
         <f t="array" ref="I52">_xll.PE.deg.AsString(G52)</f>
-        <v>40 19 59</v>
+        <v>20 36 52</v>
       </c>
       <c r="J52" s="138" cm="1">
         <f t="array" ref="J52">_xll.PE.deg.FromString(H52)</f>
-        <v>19.978055555555553</v>
+        <v>39.851944444444449</v>
       </c>
       <c r="K52" s="140" cm="1">
         <f t="array" ref="K52">_xll.PE.deg.FromString(I52)</f>
-        <v>40.333055555555561</v>
+        <v>20.614444444444445</v>
       </c>
       <c r="L52" s="85">
         <f t="shared" si="16"/>
-        <v>-5.5735789032951288E-5</v>
+        <v>-7.1208049277515784E-5</v>
       </c>
       <c r="M52" s="81">
         <f t="shared" si="16"/>
-        <v>4.0568233600879466E-5</v>
+        <v>1.286183140152275E-4</v>
       </c>
       <c r="N52" s="10">
         <f>SQRT((D53-D52)^2+(E53-E52)^2)</f>
@@ -41884,11 +41865,11 @@
       </c>
       <c r="Q52" s="44" t="str">
         <f t="shared" si="17"/>
-        <v>19.97799982,40.33309612</v>
+        <v>39.85187324,20.61457306</v>
       </c>
       <c r="R52" s="98" t="str">
         <f t="shared" si="18"/>
-        <v>&lt;trkpt lon="19.97799982" lat="40.33309612"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.85187324" lat="20.61457306"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41905,36 +41886,35 @@
       <c r="E53" s="195">
         <v>4475048.0003000004</v>
       </c>
-      <c r="F53" s="138" cm="1">
-        <f t="array" ref="F53:G53">_xll.PE.trf.Transform($D$4,$D$5,D53,E53)</f>
-        <v>20.255518710888996</v>
+      <c r="F53" s="138">
+        <v>40.065154878750747</v>
       </c>
       <c r="G53" s="140">
-        <v>40.406367319968865</v>
+        <v>20.705984811064706</v>
       </c>
       <c r="H53" s="138" t="str" cm="1">
         <f t="array" ref="H53">_xll.PE.deg.AsString(F53)</f>
-        <v>20 15 20</v>
+        <v>40 03 55</v>
       </c>
       <c r="I53" s="139" t="str" cm="1">
         <f t="array" ref="I53">_xll.PE.deg.AsString(G53)</f>
-        <v>40 24 23</v>
+        <v>20 42 22</v>
       </c>
       <c r="J53" s="138" cm="1">
         <f t="array" ref="J53">_xll.PE.deg.FromString(H53)</f>
-        <v>20.255555555555556</v>
+        <v>40.065277777777773</v>
       </c>
       <c r="K53" s="140" cm="1">
         <f t="array" ref="K53">_xll.PE.deg.FromString(I53)</f>
-        <v>40.406388888888884</v>
+        <v>20.70611111111111</v>
       </c>
       <c r="L53" s="85">
         <f t="shared" si="16"/>
-        <v>-3.6844666560398309E-5</v>
+        <v>-1.2289902702633526E-4</v>
       </c>
       <c r="M53" s="81">
         <f t="shared" si="16"/>
-        <v>-2.1568920018921744E-5</v>
+        <v>-1.2630004640357129E-4</v>
       </c>
       <c r="N53" s="39">
         <f>SQRT((D54-D53)^2+(E54-E53)^2)</f>
@@ -41947,11 +41927,11 @@
       <c r="P53" s="89"/>
       <c r="Q53" s="44" t="str">
         <f t="shared" si="17"/>
-        <v>20.25551871,40.40636732</v>
+        <v>40.06515488,20.70598481</v>
       </c>
       <c r="R53" s="98" t="str">
         <f t="shared" si="18"/>
-        <v>&lt;trkpt lon="20.25551871" lat="40.40636732"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.06515488" lat="20.70598481"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -41973,36 +41953,35 @@
         <f>E53+$D$8*COS(RADIANS(O52))</f>
         <v>4476315.3655372271</v>
       </c>
-      <c r="F54" s="135" cm="1">
-        <f t="array" ref="F54:G54">_xll.PE.trf.Transform($D$4,$D$5,D54,E54)</f>
-        <v>20.300091131624491</v>
+      <c r="F54" s="135">
+        <v>40.099359210936228</v>
       </c>
       <c r="G54" s="137">
-        <v>40.418058849922616</v>
+        <v>20.720700426564282</v>
       </c>
       <c r="H54" s="135" t="str" cm="1">
         <f t="array" ref="H54">_xll.PE.deg.AsString(F54)</f>
-        <v>20 18 00</v>
+        <v>40 05 58</v>
       </c>
       <c r="I54" s="136" t="str" cm="1">
         <f t="array" ref="I54">_xll.PE.deg.AsString(G54)</f>
-        <v>40 25 05</v>
+        <v>20 43 15</v>
       </c>
       <c r="J54" s="135" cm="1">
         <f t="array" ref="J54">_xll.PE.deg.FromString(H54)</f>
-        <v>20.3</v>
+        <v>40.099444444444444</v>
       </c>
       <c r="K54" s="137" cm="1">
         <f t="array" ref="K54">_xll.PE.deg.FromString(I54)</f>
-        <v>40.418055555555554</v>
+        <v>20.720833333333331</v>
       </c>
       <c r="L54" s="84">
         <f t="shared" si="16"/>
-        <v>9.1131624490259355E-5</v>
+        <v>-8.5233508215765141E-5</v>
       </c>
       <c r="M54" s="80">
         <f t="shared" si="16"/>
-        <v>3.2943670618124088E-6</v>
+        <v>-1.3290676904986753E-4</v>
       </c>
       <c r="N54" s="39">
         <f>SQRT((D55-D54)^2+(E55-E54)^2)</f>
@@ -42017,11 +41996,11 @@
       </c>
       <c r="Q54" s="44" t="str">
         <f t="shared" si="17"/>
-        <v>20.30009113,40.41805885</v>
+        <v>40.09935921,20.72070043</v>
       </c>
       <c r="R54" s="98" t="str">
         <f t="shared" si="18"/>
-        <v>&lt;trkpt lon="20.30009113" lat="40.41805885"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.09935921" lat="20.72070043"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42040,36 +42019,35 @@
         <f>E54+$D$7*COS(RADIANS(O53))</f>
         <v>4477265.8894651467</v>
       </c>
-      <c r="F55" s="141" cm="1">
-        <f t="array" ref="F55:G55">_xll.PE.trf.Transform($D$4,$D$5,D55,E55)</f>
-        <v>20.333530712767278</v>
+      <c r="F55" s="141">
+        <v>40.125011132371569</v>
       </c>
       <c r="G55" s="143">
-        <v>40.426816286558491</v>
+        <v>20.731746754230969</v>
       </c>
       <c r="H55" s="141" t="str" cm="1">
         <f t="array" ref="H55">_xll.PE.deg.AsString(F55)</f>
-        <v>20 20 01</v>
+        <v>40 07 30</v>
       </c>
       <c r="I55" s="142" t="str" cm="1">
         <f t="array" ref="I55">_xll.PE.deg.AsString(G55)</f>
-        <v>40 25 37</v>
+        <v>20 43 54</v>
       </c>
       <c r="J55" s="141" cm="1">
         <f t="array" ref="J55">_xll.PE.deg.FromString(H55)</f>
-        <v>20.333611111111111</v>
+        <v>40.125</v>
       </c>
       <c r="K55" s="143" cm="1">
         <f t="array" ref="K55">_xll.PE.deg.FromString(I55)</f>
-        <v>40.426944444444445</v>
+        <v>20.731666666666666</v>
       </c>
       <c r="L55" s="86">
         <f t="shared" si="16"/>
-        <v>-8.0398343833110175E-5</v>
+        <v>1.1132371568578492E-5</v>
       </c>
       <c r="M55" s="82">
         <f t="shared" si="16"/>
-        <v>-1.2815788595332833E-4</v>
+        <v>8.0087564302999681E-5</v>
       </c>
       <c r="N55" s="34">
         <f>SUM(N51:N53)</f>
@@ -42080,15 +42058,15 @@
       </c>
       <c r="P55" s="90" cm="1">
         <f t="array" ref="P55">_xll.PE.crs.GeodesicDistance($D$5,J51:K54)</f>
-        <v>32917.277057803265</v>
+        <v>32255.779849783452</v>
       </c>
       <c r="Q55" s="44" t="str">
         <f t="shared" si="17"/>
-        <v>20.33353071,40.42681629</v>
+        <v>40.12501113,20.73174675</v>
       </c>
       <c r="R55" s="98" t="str">
         <f t="shared" si="18"/>
-        <v>&lt;trkpt lon="20.33353071" lat="40.42681629"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.12501113" lat="20.73174675"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42166,35 +42144,35 @@
         <v>4463055.1312818611</v>
       </c>
       <c r="F58" s="132" cm="1">
-        <f t="array" ref="F58:G58">_xll.PE.trf.Transform($D$4,$D$5,D58,E58)</f>
-        <v>19.925860955743484</v>
+        <f t="array" ref="F58:G63">_xll.PE.trf.Transform($D$4,$D$5,D58:D63,E58:E63)</f>
+        <v>39.811347452975021</v>
       </c>
       <c r="G58" s="134">
-        <v>40.295774822822679</v>
+        <v>20.56701379367782</v>
       </c>
       <c r="H58" s="132" t="str" cm="1">
         <f t="array" ref="H58">_xll.PE.deg.AsString(F58)</f>
-        <v>19 55 33</v>
+        <v>39 48 41</v>
       </c>
       <c r="I58" s="133" t="str" cm="1">
         <f t="array" ref="I58">_xll.PE.deg.AsString(G58)</f>
-        <v>40 17 45</v>
+        <v>20 34 01</v>
       </c>
       <c r="J58" s="132" cm="1">
         <f t="array" ref="J58">_xll.PE.deg.FromString(H58)</f>
-        <v>19.925833333333333</v>
+        <v>39.811388888888885</v>
       </c>
       <c r="K58" s="134" cm="1">
         <f t="array" ref="K58">_xll.PE.deg.FromString(I58)</f>
-        <v>40.295833333333334</v>
+        <v>20.566944444444445</v>
       </c>
       <c r="L58" s="83">
         <f t="shared" ref="L58:M63" si="19">F58-J58</f>
-        <v>2.7622410151195709E-5</v>
+        <v>-4.143591386451817E-5</v>
       </c>
       <c r="M58" s="79">
         <f t="shared" si="19"/>
-        <v>-5.8510510655196413E-5</v>
+        <v>6.9349233374538244E-5</v>
       </c>
       <c r="N58" s="8">
         <f>SQRT((D59-D58)^2+(E59-E58)^2)</f>
@@ -42207,11 +42185,11 @@
       <c r="P58" s="89"/>
       <c r="Q58" s="44" t="str">
         <f t="shared" ref="Q58:Q63" si="20">CONCATENATE(TEXT(F58,"#.00000000"),",",TEXT(G58,"#.00000000"))</f>
-        <v>19.92586096,40.29577482</v>
+        <v>39.81134745,20.56701379</v>
       </c>
       <c r="R58" s="98" t="str">
         <f t="shared" ref="R58:R63" si="21">CONCATENATE("&lt;trkpt lon=""",TEXT(F58,"#.00000000"),""" lat=""",TEXT(G58,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B58,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.92586096" lat="40.29577482"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.81134745" lat="20.56701379"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42230,36 +42208,35 @@
         <f>E60-$D$8*COS(RADIANS(O60))</f>
         <v>4463865.0748896347</v>
       </c>
-      <c r="F59" s="135" cm="1">
-        <f t="array" ref="F59:G59">_xll.PE.trf.Transform($D$4,$D$5,D59,E59)</f>
-        <v>19.959716888540239</v>
+      <c r="F59" s="135">
+        <v>39.837397513721442</v>
       </c>
       <c r="G59" s="137">
-        <v>40.303378114903786</v>
+        <v>20.576312484881818</v>
       </c>
       <c r="H59" s="135" t="str" cm="1">
         <f t="array" ref="H59">_xll.PE.deg.AsString(F59)</f>
-        <v>19 57 35</v>
+        <v>39 50 15</v>
       </c>
       <c r="I59" s="136" t="str" cm="1">
         <f t="array" ref="I59">_xll.PE.deg.AsString(G59)</f>
-        <v>40 18 12</v>
+        <v>20 34 35</v>
       </c>
       <c r="J59" s="135" cm="1">
         <f t="array" ref="J59">_xll.PE.deg.FromString(H59)</f>
-        <v>19.959722222222222</v>
+        <v>39.837500000000006</v>
       </c>
       <c r="K59" s="137" cm="1">
         <f t="array" ref="K59">_xll.PE.deg.FromString(I59)</f>
-        <v>40.303333333333327</v>
+        <v>20.576388888888889</v>
       </c>
       <c r="L59" s="84">
         <f t="shared" si="19"/>
-        <v>-5.3336819831883986E-6</v>
+        <v>-1.0248627856412895E-4</v>
       </c>
       <c r="M59" s="80">
         <f t="shared" si="19"/>
-        <v>4.4781570458951592E-5</v>
+        <v>-7.6404007071317892E-5</v>
       </c>
       <c r="N59" s="39">
         <f>SQRT((D60-D59)^2+(E60-E59)^2)</f>
@@ -42274,11 +42251,11 @@
       </c>
       <c r="Q59" s="44" t="str">
         <f t="shared" si="20"/>
-        <v>19.95971689,40.30337811</v>
+        <v>39.83739751,20.57631248</v>
       </c>
       <c r="R59" s="98" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;trkpt lon="19.95971689" lat="40.30337811"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.83739751" lat="20.57631248"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42295,36 +42272,35 @@
       <c r="E60" s="195">
         <v>4464944.9996999996</v>
       </c>
-      <c r="F60" s="138" cm="1">
-        <f t="array" ref="F60:G60">_xll.PE.trf.Transform($D$4,$D$5,D60,E60)</f>
-        <v>20.00487023617189</v>
+      <c r="F60" s="138">
+        <v>39.872129642809206</v>
       </c>
       <c r="G60" s="140">
-        <v>40.313500551006001</v>
+        <v>20.58872155124104</v>
       </c>
       <c r="H60" s="138" t="str" cm="1">
         <f t="array" ref="H60">_xll.PE.deg.AsString(F60)</f>
-        <v>20 00 18</v>
+        <v>39 52 20</v>
       </c>
       <c r="I60" s="139" t="str" cm="1">
         <f t="array" ref="I60">_xll.PE.deg.AsString(G60)</f>
-        <v>40 18 49</v>
+        <v>20 35 19</v>
       </c>
       <c r="J60" s="138" cm="1">
         <f t="array" ref="J60">_xll.PE.deg.FromString(H60)</f>
-        <v>20.004999999999999</v>
+        <v>39.87222222222222</v>
       </c>
       <c r="K60" s="140" cm="1">
         <f t="array" ref="K60">_xll.PE.deg.FromString(I60)</f>
-        <v>40.313611111111108</v>
+        <v>20.58861111111111</v>
       </c>
       <c r="L60" s="85">
         <f t="shared" si="19"/>
-        <v>-1.2976382810947484E-4</v>
+        <v>-9.2579413013993417E-5</v>
       </c>
       <c r="M60" s="81">
         <f t="shared" si="19"/>
-        <v>-1.1056010510657188E-4</v>
+        <v>1.1044012993011165E-4</v>
       </c>
       <c r="N60" s="10">
         <f>SQRT((D61-D60)^2+(E61-E60)^2)</f>
@@ -42340,11 +42316,11 @@
       </c>
       <c r="Q60" s="44" t="str">
         <f t="shared" si="20"/>
-        <v>20.00487024,40.31350055</v>
+        <v>39.87212964,20.58872155</v>
       </c>
       <c r="R60" s="98" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;trkpt lon="20.00487024" lat="40.31350055"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.87212964" lat="20.58872155"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42361,36 +42337,35 @@
       <c r="E61" s="195">
         <v>4470817.0005000001</v>
       </c>
-      <c r="F61" s="138" cm="1">
-        <f t="array" ref="F61:G61">_xll.PE.trf.Transform($D$4,$D$5,D61,E61)</f>
-        <v>20.250628652514411</v>
+      <c r="F61" s="138">
+        <v>40.06095677482832</v>
       </c>
       <c r="G61" s="140">
-        <v>40.368233892392162</v>
+        <v>20.656412386573372</v>
       </c>
       <c r="H61" s="138" t="str" cm="1">
         <f t="array" ref="H61">_xll.PE.deg.AsString(F61)</f>
-        <v>20 15 02</v>
+        <v>40 03 39</v>
       </c>
       <c r="I61" s="139" t="str" cm="1">
         <f t="array" ref="I61">_xll.PE.deg.AsString(G61)</f>
-        <v>40 22 06</v>
+        <v>20 39 23</v>
       </c>
       <c r="J61" s="138" cm="1">
         <f t="array" ref="J61">_xll.PE.deg.FromString(H61)</f>
-        <v>20.250555555555554</v>
+        <v>40.060833333333328</v>
       </c>
       <c r="K61" s="140" cm="1">
         <f t="array" ref="K61">_xll.PE.deg.FromString(I61)</f>
-        <v>40.368333333333332</v>
+        <v>20.656388888888888</v>
       </c>
       <c r="L61" s="85">
         <f t="shared" si="19"/>
-        <v>7.3096958857377103E-5</v>
+        <v>1.2344149499199375E-4</v>
       </c>
       <c r="M61" s="81">
         <f t="shared" si="19"/>
-        <v>-9.9440941170314545E-5</v>
+        <v>2.3497684484397041E-5</v>
       </c>
       <c r="N61" s="39">
         <f>SQRT((D62-D61)^2+(E62-E61)^2)</f>
@@ -42403,11 +42378,11 @@
       <c r="P61" s="89"/>
       <c r="Q61" s="44" t="str">
         <f t="shared" si="20"/>
-        <v>20.25062865,40.36823389</v>
+        <v>40.06095677,20.65641239</v>
       </c>
       <c r="R61" s="98" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;trkpt lon="20.25062865" lat="40.36823389"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.06095677" lat="20.65641239"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42429,36 +42404,35 @@
         <f>E61+$D$8*COS(RADIANS(O60))</f>
         <v>4471896.9253103649</v>
       </c>
-      <c r="F62" s="135" cm="1">
-        <f t="array" ref="F62:G62">_xll.PE.trf.Transform($D$4,$D$5,D62,E62)</f>
-        <v>20.295870360336661</v>
+      <c r="F62" s="135">
+        <v>40.095679332694765</v>
       </c>
       <c r="G62" s="137">
-        <v>40.378243418278601</v>
+        <v>20.66890173600618</v>
       </c>
       <c r="H62" s="135" t="str" cm="1">
         <f t="array" ref="H62">_xll.PE.deg.AsString(F62)</f>
-        <v>20 17 45</v>
+        <v>40 05 44</v>
       </c>
       <c r="I62" s="136" t="str" cm="1">
         <f t="array" ref="I62">_xll.PE.deg.AsString(G62)</f>
-        <v>40 22 42</v>
+        <v>20 40 08</v>
       </c>
       <c r="J62" s="135" cm="1">
         <f t="array" ref="J62">_xll.PE.deg.FromString(H62)</f>
-        <v>20.295833333333334</v>
+        <v>40.095555555555556</v>
       </c>
       <c r="K62" s="137" cm="1">
         <f t="array" ref="K62">_xll.PE.deg.FromString(I62)</f>
-        <v>40.37833333333333</v>
+        <v>20.66888888888889</v>
       </c>
       <c r="L62" s="84">
         <f t="shared" si="19"/>
-        <v>3.7027003326528529E-5</v>
+        <v>1.2377713920841416E-4</v>
       </c>
       <c r="M62" s="80">
         <f t="shared" si="19"/>
-        <v>-8.9915054729772237E-5</v>
+        <v>1.2847117289993548E-5</v>
       </c>
       <c r="N62" s="39">
         <f>SQRT((D63-D62)^2+(E63-E62)^2)</f>
@@ -42473,11 +42447,11 @@
       </c>
       <c r="Q62" s="44" t="str">
         <f t="shared" si="20"/>
-        <v>20.29587036,40.37824342</v>
+        <v>40.09567933,20.66890174</v>
       </c>
       <c r="R62" s="98" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;trkpt lon="20.29587036" lat="40.37824342"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.09567933" lat="20.66890174"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42496,36 +42470,35 @@
         <f>E62+$D$7*COS(RADIANS(O61))</f>
         <v>4472706.8689181386</v>
       </c>
-      <c r="F63" s="141" cm="1">
-        <f t="array" ref="F63:G63">_xll.PE.trf.Transform($D$4,$D$5,D63,E63)</f>
-        <v>20.32981057815698</v>
+      <c r="F63" s="141">
+        <v>40.121720263527173</v>
       </c>
       <c r="G63" s="143">
-        <v>40.385739007087452</v>
+        <v>20.678277008623301</v>
       </c>
       <c r="H63" s="141" t="str" cm="1">
         <f t="array" ref="H63">_xll.PE.deg.AsString(F63)</f>
-        <v>20 19 47</v>
+        <v>40 07 18</v>
       </c>
       <c r="I63" s="142" t="str" cm="1">
         <f t="array" ref="I63">_xll.PE.deg.AsString(G63)</f>
-        <v>40 23 09</v>
+        <v>20 40 42</v>
       </c>
       <c r="J63" s="141" cm="1">
         <f t="array" ref="J63">_xll.PE.deg.FromString(H63)</f>
-        <v>20.329722222222223</v>
+        <v>40.12166666666667</v>
       </c>
       <c r="K63" s="143" cm="1">
         <f t="array" ref="K63">_xll.PE.deg.FromString(I63)</f>
-        <v>40.385833333333331</v>
+        <v>20.678333333333335</v>
       </c>
       <c r="L63" s="86">
         <f t="shared" si="19"/>
-        <v>8.8355934757089472E-5</v>
+        <v>5.3596860503546395E-5</v>
       </c>
       <c r="M63" s="82">
         <f t="shared" si="19"/>
-        <v>-9.4326245879017279E-5</v>
+        <v>-5.6324710033806014E-5</v>
       </c>
       <c r="N63" s="34">
         <f>SUM(N59:N61)</f>
@@ -42536,15 +42509,15 @@
       </c>
       <c r="P63" s="90" cm="1">
         <f t="array" ref="P63">_xll.PE.crs.GeodesicDistance($D$5,J59:K62)</f>
-        <v>29748.130977686935</v>
+        <v>28780.714983765094</v>
       </c>
       <c r="Q63" s="44" t="str">
         <f t="shared" si="20"/>
-        <v>20.32981058,40.38573901</v>
+        <v>40.12172026,20.67827701</v>
       </c>
       <c r="R63" s="98" t="str">
         <f t="shared" si="21"/>
-        <v>&lt;trkpt lon="20.32981058" lat="40.38573901"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.12172026" lat="20.67827701"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42618,35 +42591,35 @@
         <v>4450574.3227219004</v>
       </c>
       <c r="F66" s="132" cm="1">
-        <f t="array" ref="F66:G66">_xll.PE.trf.Transform($D$4,$D$5,D66,E66)</f>
-        <v>19.99171711359562</v>
+        <f t="array" ref="F66:G72">_xll.PE.trf.Transform($D$4,$D$5,D66:D72,E66:E72)</f>
+        <v>39.859869961259648</v>
       </c>
       <c r="G66" s="134">
-        <v>40.183971418221908</v>
+        <v>20.420853047265258</v>
       </c>
       <c r="H66" s="132" t="str" cm="1">
         <f t="array" ref="H66">_xll.PE.deg.AsString(F66)</f>
-        <v>19 59 30</v>
+        <v>39 51 36</v>
       </c>
       <c r="I66" s="133" t="str" cm="1">
         <f t="array" ref="I66">_xll.PE.deg.AsString(G66)</f>
-        <v>40 11 02</v>
+        <v>20 25 15</v>
       </c>
       <c r="J66" s="132" cm="1">
         <f t="array" ref="J66">_xll.PE.deg.FromString(H66)</f>
-        <v>19.991666666666667</v>
+        <v>39.86</v>
       </c>
       <c r="K66" s="134" cm="1">
         <f t="array" ref="K66">_xll.PE.deg.FromString(I66)</f>
-        <v>40.183888888888887</v>
+        <v>20.420833333333334</v>
       </c>
       <c r="L66" s="71">
         <f t="shared" ref="L66:M72" si="22">F66-J66</f>
-        <v>5.0446928952396775E-5</v>
+        <v>-1.3003874035177887E-4</v>
       </c>
       <c r="M66" s="72">
         <f t="shared" si="22"/>
-        <v>8.2529333020886497E-5</v>
+        <v>1.9713931923348582E-5</v>
       </c>
       <c r="N66" s="8">
         <f t="shared" ref="N66:N71" si="23">SQRT((D67-D66)^2+(E67-E66)^2)</f>
@@ -42659,11 +42632,11 @@
       <c r="P66" s="89"/>
       <c r="Q66" s="44" t="str">
         <f t="shared" ref="Q66:Q72" si="25">CONCATENATE(TEXT(F66,"#.00000000"),",",TEXT(G66,"#.00000000"))</f>
-        <v>19.99171711,40.18397142</v>
+        <v>39.85986996,20.42085305</v>
       </c>
       <c r="R66" s="98" t="str">
         <f t="shared" ref="R66:R72" si="26">CONCATENATE("&lt;trkpt lon=""",TEXT(F66,"#.00000000"),""" lat=""",TEXT(G66,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B66,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.99171711" lat="40.18397142"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.85986996" lat="20.42085305"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42682,36 +42655,35 @@
         <f>E68-$D$8*COS(RADIANS(O68))</f>
         <v>4452180.0220553717</v>
       </c>
-      <c r="F67" s="135" cm="1">
-        <f t="array" ref="F67:G67">_xll.PE.trf.Transform($D$4,$D$5,D67,E67)</f>
-        <v>20.021260198241439</v>
+      <c r="F67" s="135">
+        <v>39.882784099687193</v>
       </c>
       <c r="G67" s="137">
-        <v>40.198685281102414</v>
+        <v>20.439431357297501</v>
       </c>
       <c r="H67" s="135" t="str" cm="1">
         <f t="array" ref="H67">_xll.PE.deg.AsString(F67)</f>
-        <v>20 01 17</v>
+        <v>39 52 58</v>
       </c>
       <c r="I67" s="136" t="str" cm="1">
         <f t="array" ref="I67">_xll.PE.deg.AsString(G67)</f>
-        <v>40 11 55</v>
+        <v>20 26 22</v>
       </c>
       <c r="J67" s="135" cm="1">
         <f t="array" ref="J67">_xll.PE.deg.FromString(H67)</f>
-        <v>20.02138888888889</v>
+        <v>39.882777777777775</v>
       </c>
       <c r="K67" s="137" cm="1">
         <f t="array" ref="K67">_xll.PE.deg.FromString(I67)</f>
-        <v>40.198611111111106</v>
+        <v>20.439444444444444</v>
       </c>
       <c r="L67" s="73">
         <f t="shared" si="22"/>
-        <v>-1.2869064745046899E-4</v>
+        <v>6.3219094172950463E-6</v>
       </c>
       <c r="M67" s="74">
         <f t="shared" si="22"/>
-        <v>7.4169991307826422E-5</v>
+        <v>-1.3087146943036032E-5</v>
       </c>
       <c r="N67" s="39">
         <f t="shared" si="23"/>
@@ -42724,11 +42696,11 @@
       <c r="P67" s="89"/>
       <c r="Q67" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.02126020,40.19868528</v>
+        <v>39.88278410,20.43943136</v>
       </c>
       <c r="R67" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.02126020" lat="40.19868528"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.88278410" lat="20.43943136"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42745,36 +42717,35 @@
       <c r="E68" s="197">
         <v>4454320.9545</v>
       </c>
-      <c r="F68" s="138" cm="1">
-        <f t="array" ref="F68:G68">_xll.PE.trf.Transform($D$4,$D$5,D68,E68)</f>
-        <v>20.06067098541865</v>
+      <c r="F68" s="138">
+        <v>39.913331643298172</v>
       </c>
       <c r="G68" s="140">
-        <v>40.218292206114242</v>
+        <v>20.464221601734241</v>
       </c>
       <c r="H68" s="138" t="str" cm="1">
         <f t="array" ref="H68">_xll.PE.deg.AsString(F68)</f>
-        <v>20 03 38</v>
+        <v>39 54 48</v>
       </c>
       <c r="I68" s="139" t="str" cm="1">
         <f t="array" ref="I68">_xll.PE.deg.AsString(G68)</f>
-        <v>40 13 06</v>
+        <v>20 27 51</v>
       </c>
       <c r="J68" s="138" cm="1">
         <f t="array" ref="J68">_xll.PE.deg.FromString(H68)</f>
-        <v>20.060555555555556</v>
+        <v>39.913333333333334</v>
       </c>
       <c r="K68" s="140" cm="1">
         <f t="array" ref="K68">_xll.PE.deg.FromString(I68)</f>
-        <v>40.218333333333334</v>
+        <v>20.464166666666667</v>
       </c>
       <c r="L68" s="75">
         <f t="shared" si="22"/>
-        <v>1.1542986309365233E-4</v>
+        <v>-1.6900351624826726E-6</v>
       </c>
       <c r="M68" s="76">
         <f t="shared" si="22"/>
-        <v>-4.1127219091663392E-5</v>
+        <v>5.4935067574035656E-5</v>
       </c>
       <c r="N68" s="10">
         <f t="shared" si="23"/>
@@ -42789,11 +42760,11 @@
       </c>
       <c r="Q68" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.06067099,40.21829221</v>
+        <v>39.91333164,20.46422160</v>
       </c>
       <c r="R68" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.06067099" lat="40.21829221"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.91333164" lat="20.46422160"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42810,36 +42781,35 @@
       <c r="E69" s="197">
         <v>4459903.6739999996</v>
       </c>
-      <c r="F69" s="138" cm="1">
-        <f t="array" ref="F69:G69">_xll.PE.trf.Transform($D$4,$D$5,D69,E69)</f>
-        <v>20.163546599470713</v>
+      <c r="F69" s="138">
+        <v>39.992962696070656</v>
       </c>
       <c r="G69" s="140">
-        <v>40.269357117836726</v>
+        <v>20.528968240985812</v>
       </c>
       <c r="H69" s="138" t="str" cm="1">
         <f t="array" ref="H69">_xll.PE.deg.AsString(F69)</f>
-        <v>20 09 49</v>
+        <v>39 59 35</v>
       </c>
       <c r="I69" s="139" t="str" cm="1">
         <f t="array" ref="I69">_xll.PE.deg.AsString(G69)</f>
-        <v>40 16 10</v>
+        <v>20 31 44</v>
       </c>
       <c r="J69" s="138" cm="1">
         <f t="array" ref="J69">_xll.PE.deg.FromString(H69)</f>
-        <v>20.163611111111109</v>
+        <v>39.993055555555557</v>
       </c>
       <c r="K69" s="140" cm="1">
         <f t="array" ref="K69">_xll.PE.deg.FromString(I69)</f>
-        <v>40.269444444444446</v>
+        <v>20.528888888888886</v>
       </c>
       <c r="L69" s="75">
         <f t="shared" si="22"/>
-        <v>-6.45116403958923E-5</v>
+        <v>-9.2859484901453015E-5</v>
       </c>
       <c r="M69" s="76">
         <f t="shared" si="22"/>
-        <v>-8.7326607719262483E-5</v>
+        <v>7.9352096925333626E-5</v>
       </c>
       <c r="N69" s="10">
         <f t="shared" si="23"/>
@@ -42855,11 +42825,11 @@
       </c>
       <c r="Q69" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.16354660,40.26935712</v>
+        <v>39.99296270,20.52896824</v>
       </c>
       <c r="R69" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.16354660" lat="40.26935712"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.99296270" lat="20.52896824"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42876,36 +42846,35 @@
       <c r="E70" s="197">
         <v>4465830.3525</v>
       </c>
-      <c r="F70" s="138" cm="1">
-        <f t="array" ref="F70:G70">_xll.PE.trf.Transform($D$4,$D$5,D70,E70)</f>
-        <v>20.236972394273813</v>
+      <c r="F70" s="138">
+        <v>40.049934818884374</v>
       </c>
       <c r="G70" s="140">
-        <v>40.323237545161852</v>
+        <v>20.598029983950802</v>
       </c>
       <c r="H70" s="138" t="str" cm="1">
         <f t="array" ref="H70">_xll.PE.deg.AsString(F70)</f>
-        <v>20 14 13</v>
+        <v>40 02 60</v>
       </c>
       <c r="I70" s="139" t="str" cm="1">
         <f t="array" ref="I70">_xll.PE.deg.AsString(G70)</f>
-        <v>40 19 24</v>
+        <v>20 35 53</v>
       </c>
       <c r="J70" s="138" cm="1">
         <f t="array" ref="J70">_xll.PE.deg.FromString(H70)</f>
-        <v>20.236944444444447</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="K70" s="140" cm="1">
         <f t="array" ref="K70">_xll.PE.deg.FromString(I70)</f>
-        <v>40.323333333333338</v>
+        <v>20.598055555555554</v>
       </c>
       <c r="L70" s="75">
         <f t="shared" si="22"/>
-        <v>2.7949829366491485E-5</v>
+        <v>-6.5181115623147434E-5</v>
       </c>
       <c r="M70" s="76">
         <f t="shared" si="22"/>
-        <v>-9.5788171485367002E-5</v>
+        <v>-2.5571604751917221E-5</v>
       </c>
       <c r="N70" s="39">
         <f t="shared" si="23"/>
@@ -42918,11 +42887,11 @@
       <c r="P70" s="89"/>
       <c r="Q70" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.23697239,40.32323755</v>
+        <v>40.04993482,20.59802998</v>
       </c>
       <c r="R70" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.23697239" lat="40.32323755"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.04993482" lat="20.59802998"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -42944,36 +42913,35 @@
         <f>E70+$D$8*COS(RADIANS(O69))</f>
         <v>4468571.8112974633</v>
       </c>
-      <c r="F71" s="135" cm="1">
-        <f t="array" ref="F71:G71">_xll.PE.trf.Transform($D$4,$D$5,D71,E71)</f>
-        <v>20.270975922742149</v>
+      <c r="F71" s="135">
+        <v>40.076274051053659</v>
       </c>
       <c r="G71" s="137">
-        <v>40.348145024869751</v>
+        <v>20.630014230828383</v>
       </c>
       <c r="H71" s="135" t="str" cm="1">
         <f t="array" ref="H71">_xll.PE.deg.AsString(F71)</f>
-        <v>20 16 16</v>
+        <v>40 04 35</v>
       </c>
       <c r="I71" s="136" t="str" cm="1">
         <f t="array" ref="I71">_xll.PE.deg.AsString(G71)</f>
-        <v>40 20 53</v>
+        <v>20 37 48</v>
       </c>
       <c r="J71" s="135" cm="1">
         <f t="array" ref="J71">_xll.PE.deg.FromString(H71)</f>
-        <v>20.271111111111111</v>
+        <v>40.076388888888893</v>
       </c>
       <c r="K71" s="137" cm="1">
         <f t="array" ref="K71">_xll.PE.deg.FromString(I71)</f>
-        <v>40.348055555555561</v>
+        <v>20.63</v>
       </c>
       <c r="L71" s="73">
         <f t="shared" si="22"/>
-        <v>-1.351883689615363E-4</v>
+        <v>-1.1483783523402735E-4</v>
       </c>
       <c r="M71" s="74">
         <f t="shared" si="22"/>
-        <v>8.9469314190182558E-5</v>
+        <v>1.4230828384143024E-5</v>
       </c>
       <c r="N71" s="39">
         <f t="shared" si="23"/>
@@ -42988,11 +42956,11 @@
       </c>
       <c r="Q71" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.27097592,40.34814502</v>
+        <v>40.07627405,20.63001423</v>
       </c>
       <c r="R71" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.27097592" lat="40.34814502"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.07627405" lat="20.63001423"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43011,36 +42979,35 @@
         <f>E71+$D$7*COS(RADIANS(O70))</f>
         <v>4470627.9053955609</v>
       </c>
-      <c r="F72" s="141" cm="1">
-        <f t="array" ref="F72:G72">_xll.PE.trf.Transform($D$4,$D$5,D72,E72)</f>
-        <v>20.296494997345555</v>
+      <c r="F72" s="141">
+        <v>40.096022671207621</v>
       </c>
       <c r="G72" s="143">
-        <v>40.366819144150845</v>
+        <v>20.654018584538754</v>
       </c>
       <c r="H72" s="141" t="str" cm="1">
         <f t="array" ref="H72">_xll.PE.deg.AsString(F72)</f>
-        <v>20 17 47</v>
+        <v>40 05 46</v>
       </c>
       <c r="I72" s="142" t="str" cm="1">
         <f t="array" ref="I72">_xll.PE.deg.AsString(G72)</f>
-        <v>40 22 01</v>
+        <v>20 39 14</v>
       </c>
       <c r="J72" s="141" cm="1">
         <f t="array" ref="J72">_xll.PE.deg.FromString(H72)</f>
-        <v>20.296388888888892</v>
+        <v>40.096111111111114</v>
       </c>
       <c r="K72" s="143" cm="1">
         <f t="array" ref="K72">_xll.PE.deg.FromString(I72)</f>
-        <v>40.366944444444442</v>
+        <v>20.653888888888886</v>
       </c>
       <c r="L72" s="77">
         <f t="shared" si="22"/>
-        <v>1.0610845666292334E-4</v>
+        <v>-8.8439903493053862E-5</v>
       </c>
       <c r="M72" s="78">
         <f t="shared" si="22"/>
-        <v>-1.2530029359680839E-4</v>
+        <v>1.2969564986775595E-4</v>
       </c>
       <c r="N72" s="34">
         <f>SUM(N67:N70)</f>
@@ -43051,15 +43018,15 @@
       </c>
       <c r="P72" s="90" cm="1">
         <f t="array" ref="P72">_xll.PE.crs.GeodesicDistance($D$5,J67:K71)</f>
-        <v>27072.023467884705</v>
+        <v>29349.578484452715</v>
       </c>
       <c r="Q72" s="44" t="str">
         <f t="shared" si="25"/>
-        <v>20.29649500,40.36681914</v>
+        <v>40.09602267,20.65401858</v>
       </c>
       <c r="R72" s="98" t="str">
         <f t="shared" si="26"/>
-        <v>&lt;trkpt lon="20.29649500" lat="40.36681914"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.09602267" lat="20.65401858"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43137,35 +43104,35 @@
         <v>4441250.3036329644</v>
       </c>
       <c r="F75" s="132" cm="1">
-        <f t="array" ref="F75:G75">_xll.PE.trf.Transform($D$4,$D$5,D75,E75)</f>
-        <v>20.009021806680682</v>
+        <f t="array" ref="F75:G81">_xll.PE.trf.Transform($D$4,$D$5,D75:D81,E75:E81)</f>
+        <v>39.871612409855402</v>
       </c>
       <c r="G75" s="134">
-        <v>40.100151765718145</v>
+        <v>20.311771800973467</v>
       </c>
       <c r="H75" s="132" t="str" cm="1">
         <f t="array" ref="H75">_xll.PE.deg.AsString(F75)</f>
-        <v>20 00 32</v>
+        <v>39 52 18</v>
       </c>
       <c r="I75" s="133" t="str" cm="1">
         <f t="array" ref="I75">_xll.PE.deg.AsString(G75)</f>
-        <v>40 06 01</v>
+        <v>20 18 42</v>
       </c>
       <c r="J75" s="132" cm="1">
         <f t="array" ref="J75">_xll.PE.deg.FromString(H75)</f>
-        <v>20.00888888888889</v>
+        <v>39.87166666666667</v>
       </c>
       <c r="K75" s="134" cm="1">
         <f t="array" ref="K75">_xll.PE.deg.FromString(I75)</f>
-        <v>40.100277777777777</v>
+        <v>20.311666666666667</v>
       </c>
       <c r="L75" s="71">
         <f t="shared" ref="L75:M81" si="27">F75-J75</f>
-        <v>1.3291779179169794E-4</v>
+        <v>-5.425681126780546E-5</v>
       </c>
       <c r="M75" s="72">
         <f t="shared" si="27"/>
-        <v>-1.2601205963136408E-4</v>
+        <v>1.0513430679992553E-4</v>
       </c>
       <c r="N75" s="8">
         <f t="shared" ref="N75:N80" si="28">SQRT((D76-D75)^2+(E76-E75)^2)</f>
@@ -43178,11 +43145,11 @@
       <c r="P75" s="89"/>
       <c r="Q75" s="44" t="str">
         <f t="shared" ref="Q75:Q81" si="30">CONCATENATE(TEXT(F75,"#.00000000"),",",TEXT(G75,"#.00000000"))</f>
-        <v>20.00902181,40.10015177</v>
+        <v>39.87161241,20.31177180</v>
       </c>
       <c r="R75" s="98" t="str">
         <f t="shared" ref="R75:R81" si="31">CONCATENATE("&lt;trkpt lon=""",TEXT(F75,"#.00000000"),""" lat=""",TEXT(G75,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B75,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.00902181" lat="40.10015177"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.87161241" lat="20.31177180"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43201,36 +43168,35 @@
         <f>E77-$D$8*COS(RADIANS(O77))</f>
         <v>4442758.5208331225</v>
       </c>
-      <c r="F76" s="135" cm="1">
-        <f t="array" ref="F76:G76">_xll.PE.trf.Transform($D$4,$D$5,D76,E76)</f>
-        <v>20.039239468543986</v>
+      <c r="F76" s="135">
+        <v>39.895070267248819</v>
       </c>
       <c r="G76" s="137">
-        <v>40.113989007241472</v>
+        <v>20.329171758346739</v>
       </c>
       <c r="H76" s="135" t="str" cm="1">
         <f t="array" ref="H76">_xll.PE.deg.AsString(F76)</f>
-        <v>20 02 21</v>
+        <v>39 53 42</v>
       </c>
       <c r="I76" s="136" t="str" cm="1">
         <f t="array" ref="I76">_xll.PE.deg.AsString(G76)</f>
-        <v>40 06 50</v>
+        <v>20 19 45</v>
       </c>
       <c r="J76" s="135" cm="1">
         <f t="array" ref="J76">_xll.PE.deg.FromString(H76)</f>
-        <v>20.039166666666667</v>
+        <v>39.894999999999996</v>
       </c>
       <c r="K76" s="137" cm="1">
         <f t="array" ref="K76">_xll.PE.deg.FromString(I76)</f>
-        <v>40.113888888888887</v>
+        <v>20.329166666666666</v>
       </c>
       <c r="L76" s="73">
         <f t="shared" si="27"/>
-        <v>7.2801877319506048E-5</v>
+        <v>7.0267248823085993E-5</v>
       </c>
       <c r="M76" s="74">
         <f t="shared" si="27"/>
-        <v>1.001183525843885E-4</v>
+        <v>5.0916800731215517E-6</v>
       </c>
       <c r="N76" s="39">
         <f t="shared" si="28"/>
@@ -43243,11 +43209,11 @@
       <c r="P76" s="89"/>
       <c r="Q76" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.03923947,40.11398901</v>
+        <v>39.89507027,20.32917176</v>
       </c>
       <c r="R76" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.03923947" lat="40.11398901"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.89507027" lat="20.32917176"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43264,36 +43230,35 @@
       <c r="E77" s="197">
         <v>4444769.4770999998</v>
       </c>
-      <c r="F77" s="138" cm="1">
-        <f t="array" ref="F77:G77">_xll.PE.trf.Transform($D$4,$D$5,D77,E77)</f>
-        <v>20.079548896305266</v>
+      <c r="F77" s="138">
+        <v>39.926343351359669</v>
       </c>
       <c r="G77" s="140">
-        <v>40.132426562297368</v>
+        <v>20.352390049197279</v>
       </c>
       <c r="H77" s="138" t="str" cm="1">
         <f t="array" ref="H77">_xll.PE.deg.AsString(F77)</f>
-        <v>20 04 46</v>
+        <v>39 55 35</v>
       </c>
       <c r="I77" s="139" t="str" cm="1">
         <f t="array" ref="I77">_xll.PE.deg.AsString(G77)</f>
-        <v>40 07 57</v>
+        <v>20 21 09</v>
       </c>
       <c r="J77" s="138" cm="1">
         <f t="array" ref="J77">_xll.PE.deg.FromString(H77)</f>
-        <v>20.079444444444444</v>
+        <v>39.926388888888887</v>
       </c>
       <c r="K77" s="140" cm="1">
         <f t="array" ref="K77">_xll.PE.deg.FromString(I77)</f>
-        <v>40.1325</v>
+        <v>20.352500000000003</v>
       </c>
       <c r="L77" s="75">
         <f t="shared" si="27"/>
-        <v>1.0445186082108648E-4</v>
+        <v>-4.5537529217654082E-5</v>
       </c>
       <c r="M77" s="76">
         <f t="shared" si="27"/>
-        <v>-7.3437702631906632E-5</v>
+        <v>-1.0995080272380164E-4</v>
       </c>
       <c r="N77" s="10">
         <f t="shared" si="28"/>
@@ -43308,11 +43273,11 @@
       </c>
       <c r="Q77" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.07954890,40.13242656</v>
+        <v>39.92634335,20.35239005</v>
       </c>
       <c r="R77" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.07954890" lat="40.13242656"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.92634335" lat="20.35239005"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43329,36 +43294,35 @@
       <c r="E78" s="197">
         <v>4450616.7803999996</v>
       </c>
-      <c r="F78" s="138" cm="1">
-        <f t="array" ref="F78:G78">_xll.PE.trf.Transform($D$4,$D$5,D78,E78)</f>
-        <v>20.196882297215772</v>
+      <c r="F78" s="138">
+        <v>40.017250318280254</v>
       </c>
       <c r="G78" s="140">
-        <v>40.185959052012649</v>
+        <v>20.42002192077608</v>
       </c>
       <c r="H78" s="138" t="str" cm="1">
         <f t="array" ref="H78">_xll.PE.deg.AsString(F78)</f>
-        <v>20 11 49</v>
+        <v>40 01 02</v>
       </c>
       <c r="I78" s="139" t="str" cm="1">
         <f t="array" ref="I78">_xll.PE.deg.AsString(G78)</f>
-        <v>40 11 09</v>
+        <v>20 25 12</v>
       </c>
       <c r="J78" s="138" cm="1">
         <f t="array" ref="J78">_xll.PE.deg.FromString(H78)</f>
-        <v>20.196944444444444</v>
+        <v>40.017222222222223</v>
       </c>
       <c r="K78" s="140" cm="1">
         <f t="array" ref="K78">_xll.PE.deg.FromString(I78)</f>
-        <v>40.185833333333328</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="L78" s="75">
         <f t="shared" si="27"/>
-        <v>-6.2147228671705079E-5</v>
+        <v>2.8096058031223947E-5</v>
       </c>
       <c r="M78" s="76">
         <f t="shared" si="27"/>
-        <v>1.2571867932109626E-4</v>
+        <v>2.1920776077877235E-5</v>
       </c>
       <c r="N78" s="10">
         <f t="shared" si="28"/>
@@ -43374,11 +43338,11 @@
       </c>
       <c r="Q78" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.19688230,40.18595905</v>
+        <v>40.01725032,20.42002192</v>
       </c>
       <c r="R78" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.19688230" lat="40.18595905"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.01725032" lat="20.42002192"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43395,36 +43359,35 @@
       <c r="E79" s="197">
         <v>4459612.6317999996</v>
       </c>
-      <c r="F79" s="138" cm="1">
-        <f t="array" ref="F79:G79">_xll.PE.trf.Transform($D$4,$D$5,D79,E79)</f>
-        <v>20.333399268047305</v>
+      <c r="F79" s="138">
+        <v>40.123048019061969</v>
       </c>
       <c r="G79" s="140">
-        <v>40.267839383536206</v>
+        <v>20.524657219495193</v>
       </c>
       <c r="H79" s="138" t="str" cm="1">
         <f t="array" ref="H79">_xll.PE.deg.AsString(F79)</f>
-        <v>20 20 00</v>
+        <v>40 07 23</v>
       </c>
       <c r="I79" s="139" t="str" cm="1">
         <f t="array" ref="I79">_xll.PE.deg.AsString(G79)</f>
-        <v>40 16 04</v>
+        <v>20 31 29</v>
       </c>
       <c r="J79" s="138" cm="1">
         <f t="array" ref="J79">_xll.PE.deg.FromString(H79)</f>
-        <v>20.333333333333332</v>
+        <v>40.123055555555553</v>
       </c>
       <c r="K79" s="140" cm="1">
         <f t="array" ref="K79">_xll.PE.deg.FromString(I79)</f>
-        <v>40.267777777777773</v>
+        <v>20.52472222222222</v>
       </c>
       <c r="L79" s="75">
         <f t="shared" si="27"/>
-        <v>6.5934713973092585E-5</v>
+        <v>-7.5364935838706515E-6</v>
       </c>
       <c r="M79" s="76">
         <f t="shared" si="27"/>
-        <v>6.1605758432392577E-5</v>
+        <v>-6.5002727026808316E-5</v>
       </c>
       <c r="N79" s="39">
         <f t="shared" si="28"/>
@@ -43437,11 +43400,11 @@
       <c r="P79" s="89"/>
       <c r="Q79" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.33339927,40.26783938</v>
+        <v>40.12304802,20.52465722</v>
       </c>
       <c r="R79" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.33339927" lat="40.26783938"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.12304802" lat="20.52465722"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43463,36 +43426,35 @@
         <f>E79+$D$8*COS(RADIANS(O78))</f>
         <v>4462051.4748460185</v>
       </c>
-      <c r="F80" s="135" cm="1">
-        <f t="array" ref="F80:G80">_xll.PE.trf.Transform($D$4,$D$5,D80,E80)</f>
-        <v>20.370466902167522</v>
+      <c r="F80" s="135">
+        <v>40.151714267945763</v>
       </c>
       <c r="G80" s="137">
-        <v>40.290010254686557</v>
+        <v>20.553080389326706</v>
       </c>
       <c r="H80" s="135" t="str" cm="1">
         <f t="array" ref="H80">_xll.PE.deg.AsString(F80)</f>
-        <v>20 22 14</v>
+        <v>40 09 06</v>
       </c>
       <c r="I80" s="136" t="str" cm="1">
         <f t="array" ref="I80">_xll.PE.deg.AsString(G80)</f>
-        <v>40 17 24</v>
+        <v>20 33 11</v>
       </c>
       <c r="J80" s="135" cm="1">
         <f t="array" ref="J80">_xll.PE.deg.FromString(H80)</f>
-        <v>20.370555555555555</v>
+        <v>40.151666666666664</v>
       </c>
       <c r="K80" s="137" cm="1">
         <f t="array" ref="K80">_xll.PE.deg.FromString(I80)</f>
-        <v>40.29</v>
+        <v>20.553055555555556</v>
       </c>
       <c r="L80" s="73">
         <f t="shared" si="27"/>
-        <v>-8.8653388033321789E-5</v>
+        <v>4.7601279099751537E-5</v>
       </c>
       <c r="M80" s="74">
         <f t="shared" si="27"/>
-        <v>1.025468655768691E-5</v>
+        <v>2.4833771149701533E-5</v>
       </c>
       <c r="N80" s="39">
         <f t="shared" si="28"/>
@@ -43507,11 +43469,11 @@
       </c>
       <c r="Q80" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.37046690,40.29001025</v>
+        <v>40.15171427,20.55308039</v>
       </c>
       <c r="R80" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.37046690" lat="40.29001025"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.15171427" lat="20.55308039"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43530,36 +43492,35 @@
         <f>E80+$D$7*COS(RADIANS(O79))</f>
         <v>4463880.6071305331</v>
       </c>
-      <c r="F81" s="141" cm="1">
-        <f t="array" ref="F81:G81">_xll.PE.trf.Transform($D$4,$D$5,D81,E81)</f>
-        <v>20.398283565718462</v>
+      <c r="F81" s="141">
+        <v>40.173209365271106</v>
       </c>
       <c r="G81" s="143">
-        <v>40.306630675756253</v>
+        <v>20.574413423198564</v>
       </c>
       <c r="H81" s="141" t="str" cm="1">
         <f t="array" ref="H81">_xll.PE.deg.AsString(F81)</f>
-        <v>20 23 54</v>
+        <v>40 10 24</v>
       </c>
       <c r="I81" s="142" t="str" cm="1">
         <f t="array" ref="I81">_xll.PE.deg.AsString(G81)</f>
-        <v>40 18 24</v>
+        <v>20 34 28</v>
       </c>
       <c r="J81" s="141" cm="1">
         <f t="array" ref="J81">_xll.PE.deg.FromString(H81)</f>
-        <v>20.398333333333333</v>
+        <v>40.173333333333332</v>
       </c>
       <c r="K81" s="143" cm="1">
         <f t="array" ref="K81">_xll.PE.deg.FromString(I81)</f>
-        <v>40.306666666666665</v>
+        <v>20.574444444444445</v>
       </c>
       <c r="L81" s="77">
         <f t="shared" si="27"/>
-        <v>-4.9767614871853993E-5</v>
+        <v>-1.2396806222625401E-4</v>
       </c>
       <c r="M81" s="78">
         <f t="shared" si="27"/>
-        <v>-3.5990910411953791E-5</v>
+        <v>-3.1021245881390769E-5</v>
       </c>
       <c r="N81" s="34">
         <f>SUM(N76:N79)</f>
@@ -43570,15 +43531,15 @@
       </c>
       <c r="P81" s="90" cm="1">
         <f t="array" ref="P81">_xll.PE.crs.GeodesicDistance($D$5,J76:K80)</f>
-        <v>34401.169697441554</v>
+        <v>36585.798312003411</v>
       </c>
       <c r="Q81" s="44" t="str">
         <f t="shared" si="30"/>
-        <v>20.39828357,40.30663068</v>
+        <v>40.17320937,20.57441342</v>
       </c>
       <c r="R81" s="98" t="str">
         <f t="shared" si="31"/>
-        <v>&lt;trkpt lon="20.39828357" lat="40.30663068"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.17320937" lat="20.57441342"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43656,35 +43617,35 @@
         <v>4429507.8151147934</v>
       </c>
       <c r="F84" s="132" cm="1">
-        <f t="array" ref="F84:G84">_xll.PE.trf.Transform($D$4,$D$5,D84,E84)</f>
-        <v>20.069993444467798</v>
+        <f t="array" ref="F84:G90">_xll.PE.trf.Transform($D$4,$D$5,D84:D90,E84:E90)</f>
+        <v>39.916437725442194</v>
       </c>
       <c r="G84" s="134">
-        <v>39.994906393702017</v>
+        <v>20.17398400945514</v>
       </c>
       <c r="H84" s="132" t="str" cm="1">
         <f t="array" ref="H84">_xll.PE.deg.AsString(F84)</f>
-        <v>20 04 12</v>
+        <v>39 54 59</v>
       </c>
       <c r="I84" s="133" t="str" cm="1">
         <f t="array" ref="I84">_xll.PE.deg.AsString(G84)</f>
-        <v>39 59 42</v>
+        <v>20 10 26</v>
       </c>
       <c r="J84" s="132" cm="1">
         <f t="array" ref="J84">_xll.PE.deg.FromString(H84)</f>
-        <v>20.07</v>
+        <v>39.916388888888889</v>
       </c>
       <c r="K84" s="134" cm="1">
         <f t="array" ref="K84">_xll.PE.deg.FromString(I84)</f>
-        <v>39.994999999999997</v>
+        <v>20.173888888888889</v>
       </c>
       <c r="L84" s="71">
         <f t="shared" ref="L84:M90" si="32">F84-J84</f>
-        <v>-6.5555322024124507E-6</v>
+        <v>4.8836553304454355E-5</v>
       </c>
       <c r="M84" s="72">
         <f t="shared" si="32"/>
-        <v>-9.3606297980386444E-5</v>
+        <v>9.5120566250272987E-5</v>
       </c>
       <c r="N84" s="8">
         <f t="shared" ref="N84:N89" si="33">SQRT((D85-D84)^2+(E85-E84)^2)</f>
@@ -43697,11 +43658,11 @@
       <c r="P84" s="89"/>
       <c r="Q84" s="44" t="str">
         <f t="shared" ref="Q84:Q90" si="35">CONCATENATE(TEXT(F84,"#.00000000"),",",TEXT(G84,"#.00000000"))</f>
-        <v>20.06999344,39.99490639</v>
+        <v>39.91643773,20.17398401</v>
       </c>
       <c r="R84" s="98" t="str">
         <f t="shared" ref="R84:R90" si="36">CONCATENATE("&lt;trkpt lon=""",TEXT(F84,"#.00000000"),""" lat=""",TEXT(G84,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B84,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.06999344" lat="39.99490639"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.91643773" lat="20.17398401"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43720,36 +43681,35 @@
         <f>E86-$D$8*COS(RADIANS(O86))</f>
         <v>4431013.8744655959</v>
       </c>
-      <c r="F85" s="135" cm="1">
-        <f t="array" ref="F85:G85">_xll.PE.trf.Transform($D$4,$D$5,D85,E85)</f>
-        <v>20.100192626928944</v>
+      <c r="F85" s="135">
+        <v>39.939926844134114</v>
       </c>
       <c r="G85" s="137">
-        <v>40.00870828034725</v>
+        <v>20.191322337739035</v>
       </c>
       <c r="H85" s="135" t="str" cm="1">
         <f t="array" ref="H85">_xll.PE.deg.AsString(F85)</f>
-        <v>20 06 01</v>
+        <v>39 56 24</v>
       </c>
       <c r="I85" s="136" t="str" cm="1">
         <f t="array" ref="I85">_xll.PE.deg.AsString(G85)</f>
-        <v>40 00 31</v>
+        <v>20 11 29</v>
       </c>
       <c r="J85" s="135" cm="1">
         <f t="array" ref="J85">_xll.PE.deg.FromString(H85)</f>
-        <v>20.10027777777778</v>
+        <v>39.94</v>
       </c>
       <c r="K85" s="137" cm="1">
         <f t="array" ref="K85">_xll.PE.deg.FromString(I85)</f>
-        <v>40.008611111111108</v>
+        <v>20.191388888888888</v>
       </c>
       <c r="L85" s="73">
         <f t="shared" si="32"/>
-        <v>-8.5150848835979787E-5</v>
+        <v>-7.3155865884189097E-5</v>
       </c>
       <c r="M85" s="74">
         <f t="shared" si="32"/>
-        <v>9.7169236141780857E-5</v>
+        <v>-6.65511498532112E-5</v>
       </c>
       <c r="N85" s="39">
         <f t="shared" si="33"/>
@@ -43762,11 +43722,11 @@
       <c r="P85" s="89"/>
       <c r="Q85" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.10019263,40.00870828</v>
+        <v>39.93992684,20.19132234</v>
       </c>
       <c r="R85" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.10019263" lat="40.00870828"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.93992684" lat="20.19132234"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43783,36 +43743,35 @@
       <c r="E86" s="197">
         <v>4433021.9535999997</v>
       </c>
-      <c r="F86" s="138" cm="1">
-        <f t="array" ref="F86:G86">_xll.PE.trf.Transform($D$4,$D$5,D86,E86)</f>
-        <v>20.140477274654241</v>
+      <c r="F86" s="138">
+        <v>39.971241668349471</v>
       </c>
       <c r="G86" s="140">
-        <v>40.027098704556671</v>
+        <v>20.21445842049598</v>
       </c>
       <c r="H86" s="138" t="str" cm="1">
         <f t="array" ref="H86">_xll.PE.deg.AsString(F86)</f>
-        <v>20 08 26</v>
+        <v>39 58 16</v>
       </c>
       <c r="I86" s="139" t="str" cm="1">
         <f t="array" ref="I86">_xll.PE.deg.AsString(G86)</f>
-        <v>40 01 38</v>
+        <v>20 12 52</v>
       </c>
       <c r="J86" s="138" cm="1">
         <f t="array" ref="J86">_xll.PE.deg.FromString(H86)</f>
-        <v>20.140555555555554</v>
+        <v>39.971111111111114</v>
       </c>
       <c r="K86" s="140" cm="1">
         <f t="array" ref="K86">_xll.PE.deg.FromString(I86)</f>
-        <v>40.027222222222221</v>
+        <v>20.214444444444442</v>
       </c>
       <c r="L86" s="75">
         <f t="shared" si="32"/>
-        <v>-7.8280901313121376E-5</v>
+        <v>1.3055723835719846E-4</v>
       </c>
       <c r="M86" s="76">
         <f t="shared" si="32"/>
-        <v>-1.2351766554985488E-4</v>
+        <v>1.3976051537412104E-5</v>
       </c>
       <c r="N86" s="10">
         <f t="shared" si="33"/>
@@ -43827,11 +43786,11 @@
       </c>
       <c r="Q86" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.14047727,40.02709870</v>
+        <v>39.97124167,20.21445842</v>
       </c>
       <c r="R86" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.14047727" lat="40.02709870"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.97124167" lat="20.21445842"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43848,36 +43807,35 @@
       <c r="E87" s="197">
         <v>4439871.5713</v>
       </c>
-      <c r="F87" s="138" cm="1">
-        <f t="array" ref="F87:G87">_xll.PE.trf.Transform($D$4,$D$5,D87,E87)</f>
-        <v>20.278053401830466</v>
+      <c r="F87" s="138">
+        <v>40.07802286972867</v>
       </c>
       <c r="G87" s="140">
-        <v>40.089724675701291</v>
+        <v>20.293534300438793</v>
       </c>
       <c r="H87" s="138" t="str" cm="1">
         <f t="array" ref="H87">_xll.PE.deg.AsString(F87)</f>
-        <v>20 16 41</v>
+        <v>40 04 41</v>
       </c>
       <c r="I87" s="139" t="str" cm="1">
         <f t="array" ref="I87">_xll.PE.deg.AsString(G87)</f>
-        <v>40 05 23</v>
+        <v>20 17 37</v>
       </c>
       <c r="J87" s="138" cm="1">
         <f t="array" ref="J87">_xll.PE.deg.FromString(H87)</f>
-        <v>20.278055555555554</v>
+        <v>40.078055555555558</v>
       </c>
       <c r="K87" s="140" cm="1">
         <f t="array" ref="K87">_xll.PE.deg.FromString(I87)</f>
-        <v>40.089722222222221</v>
+        <v>20.293611111111112</v>
       </c>
       <c r="L87" s="75">
         <f t="shared" si="32"/>
-        <v>-2.1537250880498959E-6</v>
+        <v>-3.268582688775723E-5</v>
       </c>
       <c r="M87" s="76">
         <f t="shared" si="32"/>
-        <v>2.4534790696861819E-6</v>
+        <v>-7.6810672318572415E-5</v>
       </c>
       <c r="N87" s="10">
         <f t="shared" si="33"/>
@@ -43893,11 +43851,11 @@
       </c>
       <c r="Q87" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.27805340,40.08972468</v>
+        <v>40.07802287,20.29353430</v>
       </c>
       <c r="R87" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.27805340" lat="40.08972468"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.07802287" lat="20.29353430"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43914,36 +43872,35 @@
       <c r="E88" s="197">
         <v>4450775.5307999998</v>
       </c>
-      <c r="F88" s="138" cm="1">
-        <f t="array" ref="F88:G88">_xll.PE.trf.Transform($D$4,$D$5,D88,E88)</f>
-        <v>20.472740821899968</v>
+      <c r="F88" s="138">
+        <v>40.228843636231794</v>
       </c>
       <c r="G88" s="140">
-        <v>40.188973955050109</v>
+        <v>20.420086075465704</v>
       </c>
       <c r="H88" s="138" t="str" cm="1">
         <f t="array" ref="H88">_xll.PE.deg.AsString(F88)</f>
-        <v>20 28 22</v>
+        <v>40 13 44</v>
       </c>
       <c r="I88" s="139" t="str" cm="1">
         <f t="array" ref="I88">_xll.PE.deg.AsString(G88)</f>
-        <v>40 11 20</v>
+        <v>20 25 12</v>
       </c>
       <c r="J88" s="138" cm="1">
         <f t="array" ref="J88">_xll.PE.deg.FromString(H88)</f>
-        <v>20.472777777777775</v>
+        <v>40.228888888888889</v>
       </c>
       <c r="K88" s="140" cm="1">
         <f t="array" ref="K88">_xll.PE.deg.FromString(I88)</f>
-        <v>40.188888888888883</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="L88" s="75">
         <f t="shared" si="32"/>
-        <v>-3.6955877806832405E-5</v>
+        <v>-4.5252657095318227E-5</v>
       </c>
       <c r="M88" s="76">
         <f t="shared" si="32"/>
-        <v>8.5066161226166059E-5</v>
+        <v>8.607546570260638E-5</v>
       </c>
       <c r="N88" s="39">
         <f t="shared" si="33"/>
@@ -43956,11 +43913,11 @@
       <c r="P88" s="89"/>
       <c r="Q88" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.47274082,40.18897396</v>
+        <v>40.22884364,20.42008608</v>
       </c>
       <c r="R88" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.47274082" lat="40.18897396"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.22884364" lat="20.42008608"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -43982,36 +43939,35 @@
         <f>E88+$D$8*COS(RADIANS(O87))</f>
         <v>4452965.229134731</v>
       </c>
-      <c r="F89" s="135" cm="1">
-        <f t="array" ref="F89:G89">_xll.PE.trf.Transform($D$4,$D$5,D89,E89)</f>
-        <v>20.511905954708112</v>
+      <c r="F89" s="135">
+        <v>40.259114296852644</v>
       </c>
       <c r="G89" s="137">
-        <v>40.208865629399845</v>
+        <v>20.445567152973528</v>
       </c>
       <c r="H89" s="135" t="str" cm="1">
         <f t="array" ref="H89">_xll.PE.deg.AsString(F89)</f>
-        <v>20 30 43</v>
+        <v>40 15 33</v>
       </c>
       <c r="I89" s="136" t="str" cm="1">
         <f t="array" ref="I89">_xll.PE.deg.AsString(G89)</f>
-        <v>40 12 32</v>
+        <v>20 26 44</v>
       </c>
       <c r="J89" s="135" cm="1">
         <f t="array" ref="J89">_xll.PE.deg.FromString(H89)</f>
-        <v>20.511944444444445</v>
+        <v>40.259166666666665</v>
       </c>
       <c r="K89" s="137" cm="1">
         <f t="array" ref="K89">_xll.PE.deg.FromString(I89)</f>
-        <v>40.208888888888893</v>
+        <v>20.445555555555554</v>
       </c>
       <c r="L89" s="73">
         <f t="shared" si="32"/>
-        <v>-3.8489736333247038E-5</v>
+        <v>-5.2369814021346883E-5</v>
       </c>
       <c r="M89" s="74">
         <f t="shared" si="32"/>
-        <v>-2.325948904768893E-5</v>
+        <v>1.1597417973518986E-5</v>
       </c>
       <c r="N89" s="9">
         <f t="shared" si="33"/>
@@ -44026,11 +43982,11 @@
       </c>
       <c r="Q89" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.51190595,40.20886563</v>
+        <v>40.25911430,20.44556715</v>
       </c>
       <c r="R89" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.51190595" lat="40.20886563"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.25911430" lat="20.44556715"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44049,36 +44005,35 @@
         <f>E89+$D$7*COS(RADIANS(O88))</f>
         <v>4454607.5028857794</v>
       </c>
-      <c r="F90" s="141" cm="1">
-        <f t="array" ref="F90:G90">_xll.PE.trf.Transform($D$4,$D$5,D90,E90)</f>
-        <v>20.541294879939993</v>
+      <c r="F90" s="141">
+        <v>40.281813603818456</v>
       </c>
       <c r="G90" s="143">
-        <v>40.223775729147633</v>
+        <v>20.46469281026986</v>
       </c>
       <c r="H90" s="141" t="str" cm="1">
         <f t="array" ref="H90">_xll.PE.deg.AsString(F90)</f>
-        <v>20 32 29</v>
+        <v>40 16 55</v>
       </c>
       <c r="I90" s="142" t="str" cm="1">
         <f t="array" ref="I90">_xll.PE.deg.AsString(G90)</f>
-        <v>40 13 26</v>
+        <v>20 27 53</v>
       </c>
       <c r="J90" s="141" cm="1">
         <f t="array" ref="J90">_xll.PE.deg.FromString(H90)</f>
-        <v>20.541388888888889</v>
+        <v>40.281944444444441</v>
       </c>
       <c r="K90" s="143" cm="1">
         <f t="array" ref="K90">_xll.PE.deg.FromString(I90)</f>
-        <v>40.223888888888894</v>
+        <v>20.464722222222221</v>
       </c>
       <c r="L90" s="77">
         <f t="shared" si="32"/>
-        <v>-9.4008948895663025E-5</v>
+        <v>-1.3084062598522905E-4</v>
       </c>
       <c r="M90" s="78">
         <f t="shared" si="32"/>
-        <v>-1.1315974126091533E-4</v>
+        <v>-2.9411952361613203E-5</v>
       </c>
       <c r="N90" s="34">
         <f>SUM(N85:N88)</f>
@@ -44089,15 +44044,15 @@
       </c>
       <c r="P90" s="90" cm="1">
         <f t="array" ref="P90">_xll.PE.crs.GeodesicDistance($D$5,J85:K89)</f>
-        <v>41564.1105254254</v>
+        <v>43642.071284427591</v>
       </c>
       <c r="Q90" s="44" t="str">
         <f t="shared" si="35"/>
-        <v>20.54129488,40.22377573</v>
+        <v>40.28181360,20.46469281</v>
       </c>
       <c r="R90" s="98" t="str">
         <f t="shared" si="36"/>
-        <v>&lt;trkpt lon="20.54129488" lat="40.22377573"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.28181360" lat="20.46469281"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44175,35 +44130,35 @@
         <v>4468581.3680245327</v>
       </c>
       <c r="F93" s="132" cm="1">
-        <f t="array" ref="F93:G93">_xll.PE.trf.Transform($D$4,$D$5,D93,E93)</f>
-        <v>20.041822842787745</v>
+        <f t="array" ref="F93:G99">_xll.PE.trf.Transform($D$4,$D$5,D93:D99,E93:E99)</f>
+        <v>39.900920025054823</v>
       </c>
       <c r="G93" s="134">
-        <v>40.346559530862841</v>
+        <v>20.631071018111275</v>
       </c>
       <c r="H93" s="132" t="str" cm="1">
         <f t="array" ref="H93">_xll.PE.deg.AsString(F93)</f>
-        <v>20 02 31</v>
+        <v>39 54 03</v>
       </c>
       <c r="I93" s="133" t="str" cm="1">
         <f t="array" ref="I93">_xll.PE.deg.AsString(G93)</f>
-        <v>40 20 48</v>
+        <v>20 37 52</v>
       </c>
       <c r="J93" s="132" cm="1">
         <f t="array" ref="J93">_xll.PE.deg.FromString(H93)</f>
-        <v>20.041944444444447</v>
+        <v>39.900833333333331</v>
       </c>
       <c r="K93" s="134" cm="1">
         <f t="array" ref="K93">_xll.PE.deg.FromString(I93)</f>
-        <v>40.346666666666671</v>
+        <v>20.63111111111111</v>
       </c>
       <c r="L93" s="71">
         <f t="shared" ref="L93:M99" si="37">F93-J93</f>
-        <v>-1.2160165670138667E-4</v>
+        <v>8.6691721492115903E-5</v>
       </c>
       <c r="M93" s="72">
         <f t="shared" si="37"/>
-        <v>-1.0713580383026056E-4</v>
+        <v>-4.0092999835650289E-5</v>
       </c>
       <c r="N93" s="8">
         <f t="shared" ref="N93:N98" si="38">SQRT((D94-D93)^2+(E94-E93)^2)</f>
@@ -44216,11 +44171,11 @@
       <c r="P93" s="89"/>
       <c r="Q93" s="44" t="str">
         <f t="shared" ref="Q93:Q99" si="40">CONCATENATE(TEXT(F93,"#.00000000"),",",TEXT(G93,"#.00000000"))</f>
-        <v>20.04182284,40.34655953</v>
+        <v>39.90092003,20.63107102</v>
       </c>
       <c r="R93" s="98" t="str">
         <f t="shared" ref="R93:R99" si="41">CONCATENATE("&lt;trkpt lon=""",TEXT(F93,"#.00000000"),""" lat=""",TEXT(G93,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B93,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.04182284" lat="40.34655953"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.90092003" lat="20.63107102"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44239,36 +44194,35 @@
         <f>E95-$D$8*COS(RADIANS(O95))</f>
         <v>4466546.5277140187</v>
       </c>
-      <c r="F94" s="135" cm="1">
-        <f t="array" ref="F94:G94">_xll.PE.trf.Transform($D$4,$D$5,D94,E94)</f>
-        <v>20.068017585449915</v>
+      <c r="F94" s="135">
+        <v>39.920694908365022</v>
       </c>
       <c r="G94" s="137">
-        <v>40.328449033346601</v>
+        <v>20.607163806598347</v>
       </c>
       <c r="H94" s="135" t="str" cm="1">
         <f t="array" ref="H94">_xll.PE.deg.AsString(F94)</f>
-        <v>20 04 05</v>
+        <v>39 55 15</v>
       </c>
       <c r="I94" s="136" t="str" cm="1">
         <f t="array" ref="I94">_xll.PE.deg.AsString(G94)</f>
-        <v>40 19 42</v>
+        <v>20 36 26</v>
       </c>
       <c r="J94" s="135" cm="1">
         <f t="array" ref="J94">_xll.PE.deg.FromString(H94)</f>
-        <v>20.068055555555556</v>
+        <v>39.920833333333334</v>
       </c>
       <c r="K94" s="137" cm="1">
         <f t="array" ref="K94">_xll.PE.deg.FromString(I94)</f>
-        <v>40.328333333333333</v>
+        <v>20.607222222222223</v>
       </c>
       <c r="L94" s="73">
         <f t="shared" si="37"/>
-        <v>-3.7970105640994234E-5</v>
+        <v>-1.3842496831273365E-4</v>
       </c>
       <c r="M94" s="74">
         <f t="shared" si="37"/>
-        <v>1.1570001326788315E-4</v>
+        <v>-5.8415623875873735E-5</v>
       </c>
       <c r="N94" s="39">
         <f t="shared" si="38"/>
@@ -44281,11 +44235,11 @@
       <c r="P94" s="89"/>
       <c r="Q94" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.06801759,40.32844903</v>
+        <v>39.92069491,20.60716381</v>
       </c>
       <c r="R94" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.06801759" lat="40.32844903"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.92069491" lat="20.60716381"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44302,36 +44256,35 @@
       <c r="E95" s="197">
         <v>4463833.4073000001</v>
       </c>
-      <c r="F95" s="138" cm="1">
-        <f t="array" ref="F95:G95">_xll.PE.trf.Transform($D$4,$D$5,D95,E95)</f>
-        <v>20.102922159653534</v>
+      <c r="F95" s="138">
+        <v>39.947053537214863</v>
       </c>
       <c r="G95" s="140">
-        <v>40.304292150475973</v>
+        <v>20.575266113602552</v>
       </c>
       <c r="H95" s="138" t="str" cm="1">
         <f t="array" ref="H95">_xll.PE.deg.AsString(F95)</f>
-        <v>20 06 11</v>
+        <v>39 56 49</v>
       </c>
       <c r="I95" s="139" t="str" cm="1">
         <f t="array" ref="I95">_xll.PE.deg.AsString(G95)</f>
-        <v>40 18 15</v>
+        <v>20 34 31</v>
       </c>
       <c r="J95" s="138" cm="1">
         <f t="array" ref="J95">_xll.PE.deg.FromString(H95)</f>
-        <v>20.103055555555557</v>
+        <v>39.946944444444441</v>
       </c>
       <c r="K95" s="140" cm="1">
         <f t="array" ref="K95">_xll.PE.deg.FromString(I95)</f>
-        <v>40.304166666666667</v>
+        <v>20.575277777777778</v>
       </c>
       <c r="L95" s="75">
         <f t="shared" si="37"/>
-        <v>-1.333959020222153E-4</v>
+        <v>1.0909277042259191E-4</v>
       </c>
       <c r="M95" s="76">
         <f t="shared" si="37"/>
-        <v>1.2548380930610392E-4</v>
+        <v>-1.1664175225689632E-5</v>
       </c>
       <c r="N95" s="10">
         <f t="shared" si="38"/>
@@ -44346,11 +44299,11 @@
       </c>
       <c r="Q95" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.10292216,40.30429215</v>
+        <v>39.94705354,20.57526611</v>
       </c>
       <c r="R95" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.10292216" lat="40.30429215"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.94705354" lat="20.57526611"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44367,36 +44320,35 @@
       <c r="E96" s="197">
         <v>4452879.6354</v>
       </c>
-      <c r="F96" s="138" cm="1">
-        <f t="array" ref="F96:G96">_xll.PE.trf.Transform($D$4,$D$5,D96,E96)</f>
-        <v>20.243591327481912</v>
+      <c r="F96" s="138">
+        <v>40.053380030351782</v>
       </c>
       <c r="G96" s="140">
-        <v>40.206652264856999</v>
+        <v>20.446234992650606</v>
       </c>
       <c r="H96" s="138" t="str" cm="1">
         <f t="array" ref="H96">_xll.PE.deg.AsString(F96)</f>
-        <v>20 14 37</v>
+        <v>40 03 12</v>
       </c>
       <c r="I96" s="139" t="str" cm="1">
         <f t="array" ref="I96">_xll.PE.deg.AsString(G96)</f>
-        <v>40 12 24</v>
+        <v>20 26 46</v>
       </c>
       <c r="J96" s="138" cm="1">
         <f t="array" ref="J96">_xll.PE.deg.FromString(H96)</f>
-        <v>20.243611111111111</v>
+        <v>40.053333333333327</v>
       </c>
       <c r="K96" s="140" cm="1">
         <f t="array" ref="K96">_xll.PE.deg.FromString(I96)</f>
-        <v>40.206666666666671</v>
+        <v>20.446111111111112</v>
       </c>
       <c r="L96" s="75">
         <f t="shared" si="37"/>
-        <v>-1.9783629198855124E-5</v>
+        <v>4.6697018454722183E-5</v>
       </c>
       <c r="M96" s="76">
         <f t="shared" si="37"/>
-        <v>-1.4401809671937826E-5</v>
+        <v>1.2388153949416392E-4</v>
       </c>
       <c r="N96" s="10">
         <f t="shared" si="38"/>
@@ -44412,11 +44364,11 @@
       </c>
       <c r="Q96" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.24359133,40.20665226</v>
+        <v>40.05338003,20.44623499</v>
       </c>
       <c r="R96" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.24359133" lat="40.20665226"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.05338003" lat="20.44623499"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44433,36 +44385,35 @@
       <c r="E97" s="197">
         <v>4437480.8546000002</v>
       </c>
-      <c r="F97" s="138" cm="1">
-        <f t="array" ref="F97:G97">_xll.PE.trf.Transform($D$4,$D$5,D97,E97)</f>
-        <v>20.435390220595277</v>
+      <c r="F97" s="138">
+        <v>40.198551077836655</v>
       </c>
       <c r="G97" s="140">
-        <v>40.069067928851965</v>
+        <v>20.264207532733924</v>
       </c>
       <c r="H97" s="138" t="str" cm="1">
         <f t="array" ref="H97">_xll.PE.deg.AsString(F97)</f>
-        <v>20 26 07</v>
+        <v>40 11 55</v>
       </c>
       <c r="I97" s="139" t="str" cm="1">
         <f t="array" ref="I97">_xll.PE.deg.AsString(G97)</f>
-        <v>40 04 09</v>
+        <v>20 15 51</v>
       </c>
       <c r="J97" s="138" cm="1">
         <f t="array" ref="J97">_xll.PE.deg.FromString(H97)</f>
-        <v>20.435277777777777</v>
+        <v>40.198611111111106</v>
       </c>
       <c r="K97" s="140" cm="1">
         <f t="array" ref="K97">_xll.PE.deg.FromString(I97)</f>
-        <v>40.069166666666668</v>
+        <v>20.264166666666668</v>
       </c>
       <c r="L97" s="75">
         <f t="shared" si="37"/>
-        <v>1.1244281749966945E-4</v>
+        <v>-6.003327445114337E-5</v>
       </c>
       <c r="M97" s="76">
         <f t="shared" si="37"/>
-        <v>-9.8737814703042659E-5</v>
+        <v>4.0866067255507232E-5</v>
       </c>
       <c r="N97" s="39">
         <f t="shared" si="38"/>
@@ -44475,11 +44426,11 @@
       <c r="P97" s="89"/>
       <c r="Q97" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.43539022,40.06906793</v>
+        <v>40.19855108,20.26420753</v>
       </c>
       <c r="R97" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.43539022" lat="40.06906793"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.19855108" lat="20.26420753"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44501,36 +44452,35 @@
         <f>E97+$D$8*COS(RADIANS(O96))</f>
         <v>4434727.9086254323</v>
       </c>
-      <c r="F98" s="135" cm="1">
-        <f t="array" ref="F98:G98">_xll.PE.trf.Transform($D$4,$D$5,D98,E98)</f>
-        <v>20.469598076487333</v>
+      <c r="F98" s="135">
+        <v>40.224473029917014</v>
       </c>
       <c r="G98" s="137">
-        <v>40.044436668263572</v>
+        <v>20.231583456880998</v>
       </c>
       <c r="H98" s="135" t="str" cm="1">
         <f t="array" ref="H98">_xll.PE.deg.AsString(F98)</f>
-        <v>20 28 11</v>
+        <v>40 13 28</v>
       </c>
       <c r="I98" s="136" t="str" cm="1">
         <f t="array" ref="I98">_xll.PE.deg.AsString(G98)</f>
-        <v>40 02 40</v>
+        <v>20 13 54</v>
       </c>
       <c r="J98" s="135" cm="1">
         <f t="array" ref="J98">_xll.PE.deg.FromString(H98)</f>
-        <v>20.46972222222222</v>
+        <v>40.224444444444444</v>
       </c>
       <c r="K98" s="137" cm="1">
         <f t="array" ref="K98">_xll.PE.deg.FromString(I98)</f>
-        <v>40.044444444444444</v>
+        <v>20.231666666666666</v>
       </c>
       <c r="L98" s="73">
         <f t="shared" si="37"/>
-        <v>-1.24145734886838E-4</v>
+        <v>2.8585472570341608E-5</v>
       </c>
       <c r="M98" s="74">
         <f t="shared" si="37"/>
-        <v>-7.7761808725540504E-6</v>
+        <v>-8.3209785668003633E-5</v>
       </c>
       <c r="N98" s="9">
         <f t="shared" si="38"/>
@@ -44545,11 +44495,11 @@
       </c>
       <c r="Q98" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.46959808,40.04443667</v>
+        <v>40.22447303,20.23158346</v>
       </c>
       <c r="R98" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.46959808" lat="40.04443667"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.22447303" lat="20.23158346"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44568,36 +44518,35 @@
         <f>E98+$D$7*COS(RADIANS(O97))</f>
         <v>4432663.1991445068</v>
       </c>
-      <c r="F99" s="141" cm="1">
-        <f t="array" ref="F99:G99">_xll.PE.trf.Transform($D$4,$D$5,D99,E99)</f>
-        <v>20.495237819768231</v>
+      <c r="F99" s="141">
+        <v>40.243908228260693</v>
       </c>
       <c r="G99" s="143">
-        <v>40.02595642488258</v>
+        <v>20.207099068873791</v>
       </c>
       <c r="H99" s="141" t="str" cm="1">
         <f t="array" ref="H99">_xll.PE.deg.AsString(F99)</f>
-        <v>20 29 43</v>
+        <v>40 14 38</v>
       </c>
       <c r="I99" s="142" t="str" cm="1">
         <f t="array" ref="I99">_xll.PE.deg.AsString(G99)</f>
-        <v>40 01 33</v>
+        <v>20 12 26</v>
       </c>
       <c r="J99" s="141" cm="1">
         <f t="array" ref="J99">_xll.PE.deg.FromString(H99)</f>
-        <v>20.49527777777778</v>
+        <v>40.24388888888889</v>
       </c>
       <c r="K99" s="143" cm="1">
         <f t="array" ref="K99">_xll.PE.deg.FromString(I99)</f>
-        <v>40.025833333333331</v>
+        <v>20.207222222222221</v>
       </c>
       <c r="L99" s="77">
         <f t="shared" si="37"/>
-        <v>-3.9958009548257678E-5</v>
+        <v>1.9339371803539507E-5</v>
       </c>
       <c r="M99" s="78">
         <f t="shared" si="37"/>
-        <v>1.2309154924849963E-4</v>
+        <v>-1.2315334842938341E-4</v>
       </c>
       <c r="N99" s="14">
         <f>SUM(N94:N97)</f>
@@ -44608,15 +44557,15 @@
       </c>
       <c r="P99" s="90" cm="1">
         <f t="array" ref="P99">_xll.PE.crs.GeodesicDistance($D$5,J94:K98)</f>
-        <v>46517.121930830108</v>
+        <v>52276.91780357869</v>
       </c>
       <c r="Q99" s="44" t="str">
         <f t="shared" si="40"/>
-        <v>20.49523782,40.02595642</v>
+        <v>40.24390823,20.20709907</v>
       </c>
       <c r="R99" s="98" t="str">
         <f t="shared" si="41"/>
-        <v>&lt;trkpt lon="20.49523782" lat="40.02595642"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.24390823" lat="20.20709907"&gt;&lt;name&gt;S07&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44694,35 +44643,35 @@
         <v>4468437.1458815532</v>
       </c>
       <c r="F102" s="132" cm="1">
-        <f t="array" ref="F102:G102">_xll.PE.trf.Transform($D$4,$D$5,D102,E102)</f>
-        <v>20.122614090696832</v>
+        <f t="array" ref="F102:G107">_xll.PE.trf.Transform($D$4,$D$5,D102:D107,E102:E107)</f>
+        <v>39.962728047740342</v>
       </c>
       <c r="G102" s="134">
-        <v>40.345901906338121</v>
+        <v>20.629050994247372</v>
       </c>
       <c r="H102" s="132" t="str" cm="1">
         <f t="array" ref="H102">_xll.PE.deg.AsString(F102)</f>
-        <v>20 07 21</v>
+        <v>39 57 46</v>
       </c>
       <c r="I102" s="133" t="str" cm="1">
         <f t="array" ref="I102">_xll.PE.deg.AsString(G102)</f>
-        <v>40 20 45</v>
+        <v>20 37 45</v>
       </c>
       <c r="J102" s="132" cm="1">
         <f t="array" ref="J102">_xll.PE.deg.FromString(H102)</f>
-        <v>20.122499999999999</v>
+        <v>39.962777777777781</v>
       </c>
       <c r="K102" s="134" cm="1">
         <f t="array" ref="K102">_xll.PE.deg.FromString(I102)</f>
-        <v>40.345833333333339</v>
+        <v>20.629166666666666</v>
       </c>
       <c r="L102" s="83">
         <f t="shared" ref="L102:M107" si="42">F102-J102</f>
-        <v>1.1409069683310236E-4</v>
+        <v>-4.9730037439132957E-5</v>
       </c>
       <c r="M102" s="79">
         <f t="shared" si="42"/>
-        <v>6.8573004782024327E-5</v>
+        <v>-1.1567241929455463E-4</v>
       </c>
       <c r="N102" s="8">
         <f>SQRT((D103-D102)^2+(E103-E102)^2)</f>
@@ -44735,11 +44684,11 @@
       <c r="P102" s="94"/>
       <c r="Q102" s="44" t="str">
         <f t="shared" ref="Q102:Q107" si="43">CONCATENATE(TEXT(F102,"#.00000000"),",",TEXT(G102,"#.00000000"))</f>
-        <v>20.12261409,40.34590191</v>
+        <v>39.96272805,20.62905099</v>
       </c>
       <c r="R102" s="98" t="str">
         <f t="shared" ref="R102:R107" si="44">CONCATENATE("&lt;trkpt lon=""",TEXT(F102,"#.00000000"),""" lat=""",TEXT(G102,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B102,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.12261409" lat="40.34590191"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.96272805" lat="20.62905099"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44758,36 +44707,35 @@
         <f>E104-$D$8*COS(RADIANS(O104))</f>
         <v>4466599.7976466017</v>
       </c>
-      <c r="F103" s="135" cm="1">
-        <f t="array" ref="F103:G103">_xll.PE.trf.Transform($D$4,$D$5,D103,E103)</f>
-        <v>20.150731246325268</v>
+      <c r="F103" s="135">
+        <v>39.98401511625643</v>
       </c>
       <c r="G103" s="137">
-        <v>40.329565676373818</v>
+        <v>20.607424980318356</v>
       </c>
       <c r="H103" s="135" t="str" cm="1">
         <f t="array" ref="H103">_xll.PE.deg.AsString(F103)</f>
-        <v>20 09 03</v>
+        <v>39 59 02</v>
       </c>
       <c r="I103" s="136" t="str" cm="1">
         <f t="array" ref="I103">_xll.PE.deg.AsString(G103)</f>
-        <v>40 19 46</v>
+        <v>20 36 27</v>
       </c>
       <c r="J103" s="135" cm="1">
         <f t="array" ref="J103">_xll.PE.deg.FromString(H103)</f>
-        <v>20.150833333333331</v>
+        <v>39.983888888888892</v>
       </c>
       <c r="K103" s="137" cm="1">
         <f t="array" ref="K103">_xll.PE.deg.FromString(I103)</f>
-        <v>40.329444444444448</v>
+        <v>20.607500000000002</v>
       </c>
       <c r="L103" s="84">
         <f t="shared" si="42"/>
-        <v>-1.0208700806302318E-4</v>
+        <v>1.2622736753797881E-4</v>
       </c>
       <c r="M103" s="80">
         <f t="shared" si="42"/>
-        <v>1.2123192936996929E-4</v>
+        <v>-7.5019681645471792E-5</v>
       </c>
       <c r="N103" s="39">
         <f>SQRT((D104-D103)^2+(E104-E103)^2)</f>
@@ -44802,11 +44750,11 @@
       </c>
       <c r="Q103" s="44" t="str">
         <f t="shared" si="43"/>
-        <v>20.15073125,40.32956568</v>
+        <v>39.98401512,20.60742498</v>
       </c>
       <c r="R103" s="98" t="str">
         <f t="shared" si="44"/>
-        <v>&lt;trkpt lon="20.15073125" lat="40.32956568"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.98401512" lat="20.60742498"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44823,36 +44771,35 @@
       <c r="E104" s="197">
         <v>4464150</v>
       </c>
-      <c r="F104" s="138" cm="1">
-        <f t="array" ref="F104:G104">_xll.PE.trf.Transform($D$4,$D$5,D104,E104)</f>
-        <v>20.188199773372965</v>
+      <c r="F104" s="138">
+        <v>40.012391370043247</v>
       </c>
       <c r="G104" s="140">
-        <v>40.307773124662731</v>
+        <v>20.578569374278874</v>
       </c>
       <c r="H104" s="138" t="str" cm="1">
         <f t="array" ref="H104">_xll.PE.deg.AsString(F104)</f>
-        <v>20 11 18</v>
+        <v>40 00 45</v>
       </c>
       <c r="I104" s="139" t="str" cm="1">
         <f t="array" ref="I104">_xll.PE.deg.AsString(G104)</f>
-        <v>40 18 28</v>
+        <v>20 34 43</v>
       </c>
       <c r="J104" s="138" cm="1">
         <f t="array" ref="J104">_xll.PE.deg.FromString(H104)</f>
-        <v>20.188333333333333</v>
+        <v>40.012500000000003</v>
       </c>
       <c r="K104" s="140" cm="1">
         <f t="array" ref="K104">_xll.PE.deg.FromString(I104)</f>
-        <v>40.307777777777773</v>
+        <v>20.578611111111112</v>
       </c>
       <c r="L104" s="85">
         <f t="shared" si="42"/>
-        <v>-1.3355996036779061E-4</v>
+        <v>-1.0862995675609E-4</v>
       </c>
       <c r="M104" s="81">
         <f t="shared" si="42"/>
-        <v>-4.6531150417195022E-6</v>
+        <v>-4.1736832237404542E-5</v>
       </c>
       <c r="N104" s="10">
         <f>SQRT((D105-D104)^2+(E105-E104)^2)</f>
@@ -44868,11 +44815,11 @@
       </c>
       <c r="Q104" s="44" t="str">
         <f t="shared" si="43"/>
-        <v>20.18819977,40.30777312</v>
+        <v>40.01239137,20.57856937</v>
       </c>
       <c r="R104" s="98" t="str">
         <f t="shared" si="44"/>
-        <v>&lt;trkpt lon="20.18819977" lat="40.30777312"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.01239137" lat="20.57856937"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44889,36 +44836,35 @@
       <c r="E105" s="197">
         <v>4445370</v>
       </c>
-      <c r="F105" s="138" cm="1">
-        <f t="array" ref="F105:G105">_xll.PE.trf.Transform($D$4,$D$5,D105,E105)</f>
-        <v>20.474635225434131</v>
+      <c r="F105" s="138">
+        <v>40.229672848998348</v>
       </c>
       <c r="G105" s="140">
-        <v>40.140301411599609</v>
+        <v>20.356565648785285</v>
       </c>
       <c r="H105" s="138" t="str" cm="1">
         <f t="array" ref="H105">_xll.PE.deg.AsString(F105)</f>
-        <v>20 28 29</v>
+        <v>40 13 47</v>
       </c>
       <c r="I105" s="139" t="str" cm="1">
         <f t="array" ref="I105">_xll.PE.deg.AsString(G105)</f>
-        <v>40 08 25</v>
+        <v>20 21 24</v>
       </c>
       <c r="J105" s="138" cm="1">
         <f t="array" ref="J105">_xll.PE.deg.FromString(H105)</f>
-        <v>20.474722222222219</v>
+        <v>40.229722222222222</v>
       </c>
       <c r="K105" s="140" cm="1">
         <f t="array" ref="K105">_xll.PE.deg.FromString(I105)</f>
-        <v>40.140277777777776</v>
+        <v>20.356666666666669</v>
       </c>
       <c r="L105" s="85">
         <f t="shared" si="42"/>
-        <v>-8.6996788088100629E-5</v>
+        <v>-4.9373223873772076E-5</v>
       </c>
       <c r="M105" s="81">
         <f t="shared" si="42"/>
-        <v>2.3633821832902413E-5</v>
+        <v>-1.0101788138427992E-4</v>
       </c>
       <c r="N105" s="39">
         <f>SQRT((D106-D105)^2+(E106-E105)^2)</f>
@@ -44931,11 +44877,11 @@
       <c r="P105" s="89"/>
       <c r="Q105" s="44" t="str">
         <f t="shared" si="43"/>
-        <v>20.47463523,40.14030141</v>
+        <v>40.22967285,20.35656565</v>
       </c>
       <c r="R105" s="98" t="str">
         <f t="shared" si="44"/>
-        <v>&lt;trkpt lon="20.47463523" lat="40.14030141"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.22967285" lat="20.35656565"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -44957,36 +44903,35 @@
         <f>E105+$D$8*COS(RADIANS(O104))</f>
         <v>4442920.2023533983</v>
       </c>
-      <c r="F106" s="135" cm="1">
-        <f t="array" ref="F106:G106">_xll.PE.trf.Transform($D$4,$D$5,D106,E106)</f>
-        <v>20.511896311461349</v>
+      <c r="F106" s="135">
+        <v>40.257983796295008</v>
       </c>
       <c r="G106" s="137">
-        <v>40.118401931638644</v>
+        <v>20.327501177994407</v>
       </c>
       <c r="H106" s="135" t="str" cm="1">
         <f t="array" ref="H106">_xll.PE.deg.AsString(F106)</f>
-        <v>20 30 43</v>
+        <v>40 15 29</v>
       </c>
       <c r="I106" s="136" t="str" cm="1">
         <f t="array" ref="I106">_xll.PE.deg.AsString(G106)</f>
-        <v>40 07 06</v>
+        <v>20 19 39</v>
       </c>
       <c r="J106" s="135" cm="1">
         <f t="array" ref="J106">_xll.PE.deg.FromString(H106)</f>
-        <v>20.511944444444445</v>
+        <v>40.258055555555558</v>
       </c>
       <c r="K106" s="137" cm="1">
         <f t="array" ref="K106">_xll.PE.deg.FromString(I106)</f>
-        <v>40.118333333333332</v>
+        <v>20.327500000000001</v>
       </c>
       <c r="L106" s="84">
         <f t="shared" si="42"/>
-        <v>-4.813298309613856E-5</v>
+        <v>-7.1759260549697501E-5</v>
       </c>
       <c r="M106" s="80">
         <f t="shared" si="42"/>
-        <v>6.859830531169564E-5</v>
+        <v>1.1779944060208436E-6</v>
       </c>
       <c r="N106" s="9">
         <f>SQRT((D107-D106)^2+(E107-E106)^2)</f>
@@ -45001,11 +44946,11 @@
       </c>
       <c r="Q106" s="44" t="str">
         <f t="shared" si="43"/>
-        <v>20.51189631,40.11840193</v>
+        <v>40.25798380,20.32750118</v>
       </c>
       <c r="R106" s="98" t="str">
         <f t="shared" si="44"/>
-        <v>&lt;trkpt lon="20.51189631" lat="40.11840193"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.25798380" lat="20.32750118"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45024,36 +44969,35 @@
         <f>E106+$D$7*COS(RADIANS(O105))</f>
         <v>4441082.8541184468</v>
       </c>
-      <c r="F107" s="141" cm="1">
-        <f t="array" ref="F107:G107">_xll.PE.trf.Transform($D$4,$D$5,D107,E107)</f>
-        <v>20.53982646884727</v>
+      <c r="F107" s="141">
+        <v>40.279211993651224</v>
       </c>
       <c r="G107" s="143">
-        <v>40.101969310522684</v>
+        <v>20.305686881448619</v>
       </c>
       <c r="H107" s="141" t="str" cm="1">
         <f t="array" ref="H107">_xll.PE.deg.AsString(F107)</f>
-        <v>20 32 23</v>
+        <v>40 16 45</v>
       </c>
       <c r="I107" s="142" t="str" cm="1">
         <f t="array" ref="I107">_xll.PE.deg.AsString(G107)</f>
-        <v>40 06 07</v>
+        <v>20 18 20</v>
       </c>
       <c r="J107" s="141" cm="1">
         <f t="array" ref="J107">_xll.PE.deg.FromString(H107)</f>
-        <v>20.539722222222224</v>
+        <v>40.279166666666669</v>
       </c>
       <c r="K107" s="143" cm="1">
         <f t="array" ref="K107">_xll.PE.deg.FromString(I107)</f>
-        <v>40.101944444444449</v>
+        <v>20.305555555555557</v>
       </c>
       <c r="L107" s="86">
         <f t="shared" si="42"/>
-        <v>1.0424662504604498E-4</v>
+        <v>4.532698455506079E-5</v>
       </c>
       <c r="M107" s="82">
         <f t="shared" si="42"/>
-        <v>2.4866078234708766E-5</v>
+        <v>1.3132589306152909E-4</v>
       </c>
       <c r="N107" s="14">
         <f>SUM(N103:N105)</f>
@@ -45064,15 +45008,15 @@
       </c>
       <c r="P107" s="87" cm="1">
         <f t="array" ref="P107">_xll.PE.crs.GeodesicDistance($D$5,J103:K106)</f>
-        <v>38654.733582932749</v>
+        <v>42180.359798878162</v>
       </c>
       <c r="Q107" s="44" t="str">
         <f t="shared" si="43"/>
-        <v>20.53982647,40.10196931</v>
+        <v>40.27921199,20.30568688</v>
       </c>
       <c r="R107" s="98" t="str">
         <f t="shared" si="44"/>
-        <v>&lt;trkpt lon="20.53982647" lat="40.10196931"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.27921199" lat="20.30568688"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="108" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45150,35 +45094,35 @@
         <v>4456901.3573793834</v>
       </c>
       <c r="F110" s="132" cm="1">
-        <f t="array" ref="F110:G110">_xll.PE.trf.Transform($D$4,$D$5,D110,E110)</f>
-        <v>19.980295097411723</v>
+        <f t="array" ref="F110:G115">_xll.PE.trf.Transform($D$4,$D$5,D110:D115,E110:E115)</f>
+        <v>39.852108440023834</v>
       </c>
       <c r="G110" s="134">
-        <v>40.240849828416813</v>
+        <v>20.494850230147918</v>
       </c>
       <c r="H110" s="132" t="str" cm="1">
         <f t="array" ref="H110">_xll.PE.deg.AsString(F110)</f>
-        <v>19 58 49</v>
+        <v>39 51 08</v>
       </c>
       <c r="I110" s="133" t="str" cm="1">
         <f t="array" ref="I110">_xll.PE.deg.AsString(G110)</f>
-        <v>40 14 27</v>
+        <v>20 29 41</v>
       </c>
       <c r="J110" s="132" cm="1">
         <f t="array" ref="J110">_xll.PE.deg.FromString(H110)</f>
-        <v>19.980277777777776</v>
+        <v>39.852222222222224</v>
       </c>
       <c r="K110" s="134" cm="1">
         <f t="array" ref="K110">_xll.PE.deg.FromString(I110)</f>
-        <v>40.240833333333335</v>
+        <v>20.494722222222222</v>
       </c>
       <c r="L110" s="83">
         <f t="shared" ref="L110:M115" si="45">F110-J110</f>
-        <v>1.7319633947465718E-5</v>
+        <v>-1.137821983903109E-4</v>
       </c>
       <c r="M110" s="79">
         <f t="shared" si="45"/>
-        <v>1.6495083478673678E-5</v>
+        <v>1.2800792569578334E-4</v>
       </c>
       <c r="N110" s="8">
         <f>SQRT((D111-D110)^2+(E111-E110)^2)</f>
@@ -45191,11 +45135,11 @@
       <c r="P110" s="89"/>
       <c r="Q110" s="44" t="str">
         <f t="shared" ref="Q110:Q115" si="46">CONCATENATE(TEXT(F110,"#.00000000"),",",TEXT(G110,"#.00000000"))</f>
-        <v>19.98029510,40.24084983</v>
+        <v>39.85210844,20.49485023</v>
       </c>
       <c r="R110" s="98" t="str">
         <f t="shared" ref="R110:R115" si="47">CONCATENATE("&lt;trkpt lon=""",TEXT(F110,"#.00000000"),""" lat=""",TEXT(G110,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B110,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="19.98029510" lat="40.24084983"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.85210844" lat="20.49485023"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="111" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45214,36 +45158,35 @@
         <f>E112-$D$8*COS(RADIANS(O112))</f>
         <v>4454655.0613596477</v>
       </c>
-      <c r="F111" s="135" cm="1">
-        <f t="array" ref="F111:G111">_xll.PE.trf.Transform($D$4,$D$5,D111,E111)</f>
-        <v>20.003956316830397</v>
+      <c r="F111" s="135">
+        <v>39.869899544283378</v>
       </c>
       <c r="G111" s="137">
-        <v>40.220826808208159</v>
+        <v>20.468464776658756</v>
       </c>
       <c r="H111" s="135" t="str" cm="1">
         <f t="array" ref="H111">_xll.PE.deg.AsString(F111)</f>
-        <v>20 00 14</v>
+        <v>39 52 12</v>
       </c>
       <c r="I111" s="136" t="str" cm="1">
         <f t="array" ref="I111">_xll.PE.deg.AsString(G111)</f>
-        <v>40 13 15</v>
+        <v>20 28 06</v>
       </c>
       <c r="J111" s="135" cm="1">
         <f t="array" ref="J111">_xll.PE.deg.FromString(H111)</f>
-        <v>20.003888888888888</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="K111" s="137" cm="1">
         <f t="array" ref="K111">_xll.PE.deg.FromString(I111)</f>
-        <v>40.220833333333339</v>
+        <v>20.46833333333333</v>
       </c>
       <c r="L111" s="84">
         <f t="shared" si="45"/>
-        <v>6.7427941509379252E-5</v>
+        <v>-1.0045571661976282E-4</v>
       </c>
       <c r="M111" s="80">
         <f t="shared" si="45"/>
-        <v>-6.5251251797349141E-6</v>
+        <v>1.3144332542580628E-4</v>
       </c>
       <c r="N111" s="39">
         <f>SQRT((D112-D111)^2+(E112-E111)^2)</f>
@@ -45258,11 +45201,11 @@
       </c>
       <c r="Q111" s="44" t="str">
         <f t="shared" si="46"/>
-        <v>20.00395632,40.22082681</v>
+        <v>39.86989954,20.46846478</v>
       </c>
       <c r="R111" s="98" t="str">
         <f t="shared" si="47"/>
-        <v>&lt;trkpt lon="20.00395632" lat="40.22082681"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.86989954" lat="20.46846478"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="112" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45279,36 +45222,35 @@
       <c r="E112" s="197">
         <v>4451660</v>
       </c>
-      <c r="F112" s="138" cm="1">
-        <f t="array" ref="F112:G112">_xll.PE.trf.Transform($D$4,$D$5,D112,E112)</f>
-        <v>20.035482907483946</v>
+      <c r="F112" s="138">
+        <v>39.893611448779389</v>
       </c>
       <c r="G112" s="140">
-        <v>40.194121561226794</v>
+        <v>20.433262986097112</v>
       </c>
       <c r="H112" s="138" t="str" cm="1">
         <f t="array" ref="H112">_xll.PE.deg.AsString(F112)</f>
-        <v>20 02 08</v>
+        <v>39 53 37</v>
       </c>
       <c r="I112" s="139" t="str" cm="1">
         <f t="array" ref="I112">_xll.PE.deg.AsString(G112)</f>
-        <v>40 11 39</v>
+        <v>20 25 60</v>
       </c>
       <c r="J112" s="138" cm="1">
         <f t="array" ref="J112">_xll.PE.deg.FromString(H112)</f>
-        <v>20.035555555555558</v>
+        <v>39.893611111111113</v>
       </c>
       <c r="K112" s="140" cm="1">
         <f t="array" ref="K112">_xll.PE.deg.FromString(I112)</f>
-        <v>40.194166666666661</v>
+        <v>20.433333333333334</v>
       </c>
       <c r="L112" s="85">
         <f t="shared" si="45"/>
-        <v>-7.2648071611780551E-5</v>
+        <v>3.3766827556291901E-7</v>
       </c>
       <c r="M112" s="81">
         <f t="shared" si="45"/>
-        <v>-4.5105439866688357E-5</v>
+        <v>-7.0347236221124376E-5</v>
       </c>
       <c r="N112" s="10">
         <f>SQRT((D113-D112)^2+(E113-E112)^2)</f>
@@ -45324,11 +45266,11 @@
       </c>
       <c r="Q112" s="44" t="str">
         <f t="shared" si="46"/>
-        <v>20.03548291,40.19412156</v>
+        <v>39.89361145,20.43326299</v>
       </c>
       <c r="R112" s="98" t="str">
         <f t="shared" si="47"/>
-        <v>&lt;trkpt lon="20.03548291" lat="40.19412156"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.89361145" lat="20.43326299"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="113" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45345,36 +45287,35 @@
       <c r="E113" s="197">
         <v>4430146</v>
       </c>
-      <c r="F113" s="138" cm="1">
-        <f t="array" ref="F113:G113">_xll.PE.trf.Transform($D$4,$D$5,D113,E113)</f>
-        <v>20.261217584877354</v>
+      <c r="F113" s="138">
+        <v>40.063614096843054</v>
       </c>
       <c r="G113" s="140">
-        <v>40.002030742739421</v>
+        <v>20.17968922866179</v>
       </c>
       <c r="H113" s="138" t="str" cm="1">
         <f t="array" ref="H113">_xll.PE.deg.AsString(F113)</f>
-        <v>20 15 40</v>
+        <v>40 03 49</v>
       </c>
       <c r="I113" s="139" t="str" cm="1">
         <f t="array" ref="I113">_xll.PE.deg.AsString(G113)</f>
-        <v>40 00 07</v>
+        <v>20 10 47</v>
       </c>
       <c r="J113" s="138" cm="1">
         <f t="array" ref="J113">_xll.PE.deg.FromString(H113)</f>
-        <v>20.261111111111113</v>
+        <v>40.063611111111108</v>
       </c>
       <c r="K113" s="140" cm="1">
         <f t="array" ref="K113">_xll.PE.deg.FromString(I113)</f>
-        <v>40.001944444444447</v>
+        <v>20.179722222222225</v>
       </c>
       <c r="L113" s="85">
         <f t="shared" si="45"/>
-        <v>1.0647376624106641E-4</v>
+        <v>2.9857319461257248E-6</v>
       </c>
       <c r="M113" s="81">
         <f t="shared" si="45"/>
-        <v>8.6298294974085366E-5</v>
+        <v>-3.2993560434846358E-5</v>
       </c>
       <c r="N113" s="39">
         <f>SQRT((D114-D113)^2+(E114-E113)^2)</f>
@@ -45387,11 +45328,11 @@
       <c r="P113" s="89"/>
       <c r="Q113" s="44" t="str">
         <f t="shared" si="46"/>
-        <v>20.26121758,40.00203074</v>
+        <v>40.06361410,20.17968923</v>
       </c>
       <c r="R113" s="98" t="str">
         <f t="shared" si="47"/>
-        <v>&lt;trkpt lon="20.26121758" lat="40.00203074"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.06361410" lat="20.17968923"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="114" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45413,36 +45354,35 @@
         <f>E113+$D$8*COS(RADIANS(O112))</f>
         <v>4427150.9386403523</v>
       </c>
-      <c r="F114" s="135" cm="1">
-        <f t="array" ref="F114:G114">_xll.PE.trf.Transform($D$4,$D$5,D114,E114)</f>
-        <v>20.292542535155217</v>
+      <c r="F114" s="135">
+        <v>40.087235533593649</v>
       </c>
       <c r="G114" s="137">
-        <v>39.975252625030251</v>
+        <v>20.144288416569839</v>
       </c>
       <c r="H114" s="135" t="str" cm="1">
         <f t="array" ref="H114">_xll.PE.deg.AsString(F114)</f>
-        <v>20 17 33</v>
+        <v>40 05 14</v>
       </c>
       <c r="I114" s="136" t="str" cm="1">
         <f t="array" ref="I114">_xll.PE.deg.AsString(G114)</f>
-        <v>39 58 31</v>
+        <v>20 08 39</v>
       </c>
       <c r="J114" s="135" cm="1">
         <f t="array" ref="J114">_xll.PE.deg.FromString(H114)</f>
-        <v>20.2925</v>
+        <v>40.087222222222223</v>
       </c>
       <c r="K114" s="137" cm="1">
         <f t="array" ref="K114">_xll.PE.deg.FromString(I114)</f>
-        <v>39.975277777777777</v>
+        <v>20.144166666666667</v>
       </c>
       <c r="L114" s="84">
         <f t="shared" si="45"/>
-        <v>4.2535155216683052E-5</v>
+        <v>1.3311371425572815E-5</v>
       </c>
       <c r="M114" s="80">
         <f t="shared" si="45"/>
-        <v>-2.5152747525680752E-5</v>
+        <v>1.2174990317248557E-4</v>
       </c>
       <c r="N114" s="9">
         <f>SQRT((D115-D114)^2+(E115-E114)^2)</f>
@@ -45457,11 +45397,11 @@
       </c>
       <c r="Q114" s="44" t="str">
         <f t="shared" si="46"/>
-        <v>20.29254254,39.97525263</v>
+        <v>40.08723553,20.14428842</v>
       </c>
       <c r="R114" s="98" t="str">
         <f t="shared" si="47"/>
-        <v>&lt;trkpt lon="20.29254254" lat="39.97525263"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.08723553" lat="20.14428842"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="115" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45480,36 +45420,35 @@
         <f>E114+$D$7*COS(RADIANS(O113))</f>
         <v>4424904.6426206166</v>
       </c>
-      <c r="F115" s="141" cm="1">
-        <f t="array" ref="F115:G115">_xll.PE.trf.Transform($D$4,$D$5,D115,E115)</f>
-        <v>20.316020182948577</v>
+      <c r="F115" s="141">
+        <v>40.104944276700735</v>
       </c>
       <c r="G115" s="143">
-        <v>39.955163263756695</v>
+        <v>20.117721776035467</v>
       </c>
       <c r="H115" s="141" t="str" cm="1">
         <f t="array" ref="H115">_xll.PE.deg.AsString(F115)</f>
-        <v>20 18 58</v>
+        <v>40 06 18</v>
       </c>
       <c r="I115" s="142" t="str" cm="1">
         <f t="array" ref="I115">_xll.PE.deg.AsString(G115)</f>
-        <v>39 57 19</v>
+        <v>20 07 04</v>
       </c>
       <c r="J115" s="141" cm="1">
         <f t="array" ref="J115">_xll.PE.deg.FromString(H115)</f>
-        <v>20.316111111111113</v>
+        <v>40.105000000000004</v>
       </c>
       <c r="K115" s="143" cm="1">
         <f t="array" ref="K115">_xll.PE.deg.FromString(I115)</f>
-        <v>39.955277777777781</v>
+        <v>20.117777777777778</v>
       </c>
       <c r="L115" s="86">
         <f t="shared" si="45"/>
-        <v>-9.0928162535419688E-5</v>
+        <v>-5.5723299269061499E-5</v>
       </c>
       <c r="M115" s="82">
         <f t="shared" si="45"/>
-        <v>-1.1451402108519915E-4</v>
+        <v>-5.6001742311906355E-5</v>
       </c>
       <c r="N115" s="14">
         <f>SUM(N111:N113)</f>
@@ -45520,15 +45459,15 @@
       </c>
       <c r="P115" s="90" cm="1">
         <f t="array" ref="P115">_xll.PE.crs.GeodesicDistance($D$5,J111:K114)</f>
-        <v>36729.862302124151</v>
+        <v>42457.728641102956</v>
       </c>
       <c r="Q115" s="44" t="str">
         <f t="shared" si="46"/>
-        <v>20.31602018,39.95516326</v>
+        <v>40.10494428,20.11772178</v>
       </c>
       <c r="R115" s="98" t="str">
         <f t="shared" si="47"/>
-        <v>&lt;trkpt lon="20.31602018" lat="39.95516326"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.10494428" lat="20.11772178"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="116" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45605,36 +45544,36 @@
         <f>E119-$D$7*COS(RADIANS(O119))</f>
         <v>4452852.3097855086</v>
       </c>
-      <c r="F118" s="135" cm="1">
-        <f t="array" ref="F118:G118">_xll.PE.trf.Transform($D$4,$D$5,D118,E118)</f>
-        <v>20.155244386653319</v>
-      </c>
-      <c r="G118" s="137">
-        <v>40.205795085677487</v>
+      <c r="F118" s="132" cm="1">
+        <f t="array" ref="F118:G123">_xll.PE.trf.Transform($D$4,$D$5,D118:D123,E118:E123)</f>
+        <v>39.985632552543962</v>
+      </c>
+      <c r="G118" s="134">
+        <v>20.446462537542015</v>
       </c>
       <c r="H118" s="132" t="str" cm="1">
         <f t="array" ref="H118">_xll.PE.deg.AsString(F118)</f>
-        <v>20 09 19</v>
+        <v>39 59 08</v>
       </c>
       <c r="I118" s="133" t="str" cm="1">
         <f t="array" ref="I118">_xll.PE.deg.AsString(G118)</f>
-        <v>40 12 21</v>
+        <v>20 26 47</v>
       </c>
       <c r="J118" s="132" cm="1">
         <f t="array" ref="J118">_xll.PE.deg.FromString(H118)</f>
-        <v>20.155277777777776</v>
+        <v>39.985555555555557</v>
       </c>
       <c r="K118" s="134" cm="1">
         <f t="array" ref="K118">_xll.PE.deg.FromString(I118)</f>
-        <v>40.205833333333338</v>
+        <v>20.44638888888889</v>
       </c>
       <c r="L118" s="83">
         <f t="shared" ref="L118:M123" si="48">F118-J118</f>
-        <v>-3.3391124457438082E-5</v>
+        <v>7.6996988404687272E-5</v>
       </c>
       <c r="M118" s="79">
         <f t="shared" si="48"/>
-        <v>-3.824765585136447E-5</v>
+        <v>7.3648653124536168E-5</v>
       </c>
       <c r="N118" s="8">
         <f>SQRT((D119-D118)^2+(E119-E118)^2)</f>
@@ -45647,11 +45586,11 @@
       <c r="P118" s="94"/>
       <c r="Q118" s="44" t="str">
         <f t="shared" ref="Q118:Q123" si="49">CONCATENATE(TEXT(F118,"#.00000000"),",",TEXT(G118,"#.00000000"))</f>
-        <v>20.15524439,40.20579509</v>
+        <v>39.98563255,20.44646254</v>
       </c>
       <c r="R118" s="98" t="str">
         <f t="shared" ref="R118:R123" si="50">CONCATENATE("&lt;trkpt lon=""",TEXT(F118,"#.00000000"),""" lat=""",TEXT(G118,"#.00000000"),"""","&gt;&lt;name&gt;S",TEXT(B118,"00"),"&lt;/name&gt;&lt;/trkpt&gt;")</f>
-        <v>&lt;trkpt lon="20.15524439" lat="40.20579509"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="39.98563255" lat="20.44646254"&gt;&lt;name&gt;S01&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="119" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45670,36 +45609,35 @@
         <f>E120-$D$8*COS(RADIANS(O120))</f>
         <v>4454594.5170202907</v>
       </c>
-      <c r="F119" s="135" cm="1">
-        <f t="array" ref="F119:G119">_xll.PE.trf.Transform($D$4,$D$5,D119,E119)</f>
-        <v>20.183739389448178</v>
+      <c r="F119" s="135">
+        <v>40.007722687679916</v>
       </c>
       <c r="G119" s="137">
-        <v>40.22168924313722</v>
+        <v>20.466688121706184</v>
       </c>
       <c r="H119" s="135" t="str" cm="1">
         <f t="array" ref="H119">_xll.PE.deg.AsString(F119)</f>
-        <v>20 11 01</v>
+        <v>40 00 28</v>
       </c>
       <c r="I119" s="136" t="str" cm="1">
         <f t="array" ref="I119">_xll.PE.deg.AsString(G119)</f>
-        <v>40 13 18</v>
+        <v>20 28 00</v>
       </c>
       <c r="J119" s="135" cm="1">
         <f t="array" ref="J119">_xll.PE.deg.FromString(H119)</f>
-        <v>20.183611111111112</v>
+        <v>40.007777777777775</v>
       </c>
       <c r="K119" s="137" cm="1">
         <f t="array" ref="K119">_xll.PE.deg.FromString(I119)</f>
-        <v>40.221666666666671</v>
+        <v>20.466666666666665</v>
       </c>
       <c r="L119" s="84">
         <f t="shared" si="48"/>
-        <v>1.2827833706552383E-4</v>
+        <v>-5.5090097859533671E-5</v>
       </c>
       <c r="M119" s="80">
         <f t="shared" si="48"/>
-        <v>2.257647054904055E-5</v>
+        <v>2.1455039519224783E-5</v>
       </c>
       <c r="N119" s="39">
         <f>SQRT((D120-D119)^2+(E120-E119)^2)</f>
@@ -45714,11 +45652,11 @@
       </c>
       <c r="Q119" s="44" t="str">
         <f t="shared" si="49"/>
-        <v>20.18373939,40.22168924</v>
+        <v>40.00772269,20.46668812</v>
       </c>
       <c r="R119" s="98" t="str">
         <f t="shared" si="50"/>
-        <v>&lt;trkpt lon="20.18373939" lat="40.22168924"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.00772269" lat="20.46668812"&gt;&lt;name&gt;S02&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="120" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45735,36 +45673,35 @@
       <c r="E120" s="197">
         <v>4456917.46</v>
       </c>
-      <c r="F120" s="138" cm="1">
-        <f t="array" ref="F120:G120">_xll.PE.trf.Transform($D$4,$D$5,D120,E120)</f>
-        <v>20.22175353346173</v>
+      <c r="F120" s="138">
+        <v>40.037170707152626</v>
       </c>
       <c r="G120" s="140">
-        <v>40.2428706698594</v>
+        <v>20.493675796644851</v>
       </c>
       <c r="H120" s="138" t="str" cm="1">
         <f t="array" ref="H120">_xll.PE.deg.AsString(F120)</f>
-        <v>20 13 18</v>
+        <v>40 02 14</v>
       </c>
       <c r="I120" s="139" t="str" cm="1">
         <f t="array" ref="I120">_xll.PE.deg.AsString(G120)</f>
-        <v>40 14 34</v>
+        <v>20 29 37</v>
       </c>
       <c r="J120" s="138" cm="1">
         <f t="array" ref="J120">_xll.PE.deg.FromString(H120)</f>
-        <v>20.221666666666664</v>
+        <v>40.037222222222219</v>
       </c>
       <c r="K120" s="140" cm="1">
         <f t="array" ref="K120">_xll.PE.deg.FromString(I120)</f>
-        <v>40.242777777777782</v>
+        <v>20.493611111111111</v>
       </c>
       <c r="L120" s="85">
         <f t="shared" si="48"/>
-        <v>8.6866795065532187E-5</v>
+        <v>-5.1515069593222051E-5</v>
       </c>
       <c r="M120" s="81">
         <f t="shared" si="48"/>
-        <v>9.2892081617890199E-5</v>
+        <v>6.4685533740060919E-5</v>
       </c>
       <c r="N120" s="10">
         <f>SQRT((D121-D120)^2+(E121-E120)^2)</f>
@@ -45780,11 +45717,11 @@
       </c>
       <c r="Q120" s="44" t="str">
         <f t="shared" si="49"/>
-        <v>20.22175353,40.24287067</v>
+        <v>40.03717071,20.49367580</v>
       </c>
       <c r="R120" s="98" t="str">
         <f t="shared" si="50"/>
-        <v>&lt;trkpt lon="20.22175353" lat="40.24287067"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.03717071" lat="20.49367580"&gt;&lt;name&gt;S03&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="121" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45801,36 +45738,35 @@
       <c r="E121" s="197">
         <v>4461819.1283</v>
       </c>
-      <c r="F121" s="138" cm="1">
-        <f t="array" ref="F121:G121">_xll.PE.trf.Transform($D$4,$D$5,D121,E121)</f>
-        <v>20.302045697642804</v>
+      <c r="F121" s="138">
+        <v>40.099288620615951</v>
       </c>
       <c r="G121" s="140">
-        <v>40.287525281732698</v>
+        <v>20.550698838423028</v>
       </c>
       <c r="H121" s="138" t="str" cm="1">
         <f t="array" ref="H121">_xll.PE.deg.AsString(F121)</f>
-        <v>20 18 07</v>
+        <v>40 05 57</v>
       </c>
       <c r="I121" s="139" t="str" cm="1">
         <f t="array" ref="I121">_xll.PE.deg.AsString(G121)</f>
-        <v>40 17 15</v>
+        <v>20 33 03</v>
       </c>
       <c r="J121" s="138" cm="1">
         <f t="array" ref="J121">_xll.PE.deg.FromString(H121)</f>
-        <v>20.301944444444445</v>
+        <v>40.099166666666669</v>
       </c>
       <c r="K121" s="140" cm="1">
         <f t="array" ref="K121">_xll.PE.deg.FromString(I121)</f>
-        <v>40.287500000000001</v>
+        <v>20.550833333333333</v>
       </c>
       <c r="L121" s="85">
         <f t="shared" si="48"/>
-        <v>1.0125319835907476E-4</v>
+        <v>1.2195394928227188E-4</v>
       </c>
       <c r="M121" s="81">
         <f t="shared" si="48"/>
-        <v>2.5281732696669224E-5</v>
+        <v>-1.3449491030570471E-4</v>
       </c>
       <c r="N121" s="39">
         <f>SQRT((D122-D121)^2+(E122-E121)^2)</f>
@@ -45843,11 +45779,11 @@
       <c r="P121" s="89"/>
       <c r="Q121" s="44" t="str">
         <f t="shared" si="49"/>
-        <v>20.30204570,40.28752528</v>
+        <v>40.09928862,20.55069884</v>
       </c>
       <c r="R121" s="98" t="str">
         <f t="shared" si="50"/>
-        <v>&lt;trkpt lon="20.30204570" lat="40.28752528"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.09928862" lat="20.55069884"&gt;&lt;name&gt;S04&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="122" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45869,36 +45805,35 @@
         <f>E121+$D$8*COS(RADIANS(O120))</f>
         <v>4464142.0712797092</v>
       </c>
-      <c r="F122" s="135" cm="1">
-        <f t="array" ref="F122:G122">_xll.PE.trf.Transform($D$4,$D$5,D122,E122)</f>
-        <v>20.340133885134307</v>
+      <c r="F122" s="135">
+        <v>40.128716991604712</v>
       </c>
       <c r="G122" s="137">
-        <v>40.308668208385107</v>
+        <v>20.57775867974599</v>
       </c>
       <c r="H122" s="135" t="str" cm="1">
         <f t="array" ref="H122">_xll.PE.deg.AsString(F122)</f>
-        <v>20 20 24</v>
+        <v>40 07 43</v>
       </c>
       <c r="I122" s="136" t="str" cm="1">
         <f t="array" ref="I122">_xll.PE.deg.AsString(G122)</f>
-        <v>40 18 31</v>
+        <v>20 34 40</v>
       </c>
       <c r="J122" s="135" cm="1">
         <f t="array" ref="J122">_xll.PE.deg.FromString(H122)</f>
-        <v>20.34</v>
+        <v>40.128611111111113</v>
       </c>
       <c r="K122" s="137" cm="1">
         <f t="array" ref="K122">_xll.PE.deg.FromString(I122)</f>
-        <v>40.308611111111105</v>
+        <v>20.577777777777779</v>
       </c>
       <c r="L122" s="84">
         <f t="shared" si="48"/>
-        <v>1.3388513430712123E-4</v>
+        <v>1.0588049359938623E-4</v>
       </c>
       <c r="M122" s="80">
         <f t="shared" si="48"/>
-        <v>5.7097274002160248E-5</v>
+        <v>-1.9098031788900016E-5</v>
       </c>
       <c r="N122" s="9">
         <f>SQRT((D123-D122)^2+(E123-E122)^2)</f>
@@ -45913,11 +45848,11 @@
       </c>
       <c r="Q122" s="44" t="str">
         <f t="shared" si="49"/>
-        <v>20.34013389,40.30866821</v>
+        <v>40.12871699,20.57775868</v>
       </c>
       <c r="R122" s="98" t="str">
         <f t="shared" si="50"/>
-        <v>&lt;trkpt lon="20.34013389" lat="40.30866821"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.12871699" lat="20.57775868"&gt;&lt;name&gt;S05&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="123" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45936,36 +45871,35 @@
         <f>E122+$D$7*COS(RADIANS(O121))</f>
         <v>4465884.2785144914</v>
       </c>
-      <c r="F123" s="141" cm="1">
-        <f t="array" ref="F123:G123">_xll.PE.trf.Transform($D$4,$D$5,D123,E123)</f>
-        <v>20.3687156675634</v>
+      <c r="F123" s="141">
+        <v>40.150784098452753</v>
       </c>
       <c r="G123" s="143">
-        <v>40.324517243329709</v>
+        <v>20.598068843796192</v>
       </c>
       <c r="H123" s="141" t="str" cm="1">
         <f t="array" ref="H123">_xll.PE.deg.AsString(F123)</f>
-        <v>20 22 07</v>
+        <v>40 09 03</v>
       </c>
       <c r="I123" s="142" t="str" cm="1">
         <f t="array" ref="I123">_xll.PE.deg.AsString(G123)</f>
-        <v>40 19 28</v>
+        <v>20 35 53</v>
       </c>
       <c r="J123" s="141" cm="1">
         <f t="array" ref="J123">_xll.PE.deg.FromString(H123)</f>
-        <v>20.368611111111111</v>
+        <v>40.150833333333331</v>
       </c>
       <c r="K123" s="143" cm="1">
         <f t="array" ref="K123">_xll.PE.deg.FromString(I123)</f>
-        <v>40.324444444444445</v>
+        <v>20.598055555555554</v>
       </c>
       <c r="L123" s="86">
         <f t="shared" si="48"/>
-        <v>1.0455645228901744E-4</v>
+        <v>-4.9234880577841977E-5</v>
       </c>
       <c r="M123" s="82">
         <f t="shared" si="48"/>
-        <v>7.2798885263125612E-5</v>
+        <v>1.3288240637621129E-5</v>
       </c>
       <c r="N123" s="14">
         <f>SUM(N119:N121)</f>
@@ -45976,15 +45910,15 @@
       </c>
       <c r="P123" s="87" cm="1">
         <f t="array" ref="P123">_xll.PE.crs.GeodesicDistance($D$5,J119:K122)</f>
-        <v>16436.893372856532</v>
+        <v>17611.012861982512</v>
       </c>
       <c r="Q123" s="44" t="str">
         <f t="shared" si="49"/>
-        <v>20.36871567,40.32451724</v>
+        <v>40.15078410,20.59806884</v>
       </c>
       <c r="R123" s="98" t="str">
         <f t="shared" si="50"/>
-        <v>&lt;trkpt lon="20.36871567" lat="40.32451724"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
+        <v>&lt;trkpt lon="40.15078410" lat="20.59806884"&gt;&lt;name&gt;S06&lt;/name&gt;&lt;/trkpt&gt;</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.35">
@@ -46083,6 +46017,10 @@
       <c r="D131" s="216" t="str">
         <v>Inverse of 6-degree Gauss-Kruger zone 4 + Ballpark geographic offset from Albanian 1987 to WGS 84 (with axis order normalized for visualization)</v>
       </c>
+      <c r="M131" s="1" t="e" cm="1">
+        <f t="array" ref="M131">PE.trf.</f>
+        <v>#NAME?</v>
+      </c>
     </row>
     <row r="132" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C132" s="12" t="str">
@@ -48290,8 +48228,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" display="EPSG:4326" xr:uid="{3AAF80B1-BF36-4D61-AD61-AF82F1F13DDB}"/>
-    <hyperlink ref="D4" r:id="rId2" display="EPSG:2462" xr:uid="{5EFF38E2-4195-4146-A2EC-6EE672032DC8}"/>
+    <hyperlink ref="D5" r:id="rId1" display="EPSG:4326" xr:uid="{66D20308-4A92-4E7F-BCF3-ABBE83B04144}"/>
+    <hyperlink ref="D4" r:id="rId2" display="EPSG:2462" xr:uid="{85968B81-EC1A-4D4D-9D7C-8F089AB13728}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41775AD1-BAE3-449E-9417-F5B3F442DEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766B9A21-4C8C-4160-A61A-707E5903CDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="146">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1214,7 +1214,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="259">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1754,17 +1754,12 @@
     <xf numFmtId="1" fontId="10" fillId="7" borderId="13" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1779,7 +1774,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1792,8 +1786,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1801,11 +1793,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -39545,7 +39559,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E55C8259-B2F0-4599-98D4-024E12781605}">
-  <dimension ref="A2:T313"/>
+  <dimension ref="A2:T396"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -39687,7 +39701,7 @@
         <v>File version</v>
       </c>
       <c r="E11" s="179" t="str">
-        <v>1.0.261020.1050</v>
+        <v>1.0.261020.1245</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -39696,7 +39710,7 @@
         <v>Info version</v>
       </c>
       <c r="E12" s="181" t="str">
-        <v>1.0.261020.1050</v>
+        <v>1.0.261020.1245</v>
       </c>
       <c r="Q12" s="100" t="s">
         <v>44</v>
@@ -45913,7 +45927,7 @@
         <v>UsageArea.Name</v>
       </c>
       <c r="D147" s="216" t="str">
-        <v>UsageArea</v>
+        <v>World</v>
       </c>
     </row>
     <row r="148" spans="3:15" x14ac:dyDescent="0.35">
@@ -45921,7 +45935,7 @@
         <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D148" s="216" t="str">
-        <v>World</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="149" spans="3:15" x14ac:dyDescent="0.35">
@@ -45929,7 +45943,7 @@
         <v>UsageArea.SouthLatitude</v>
       </c>
       <c r="D149" s="216" t="str">
-        <v>-180</v>
+        <v>-90</v>
       </c>
       <c r="F149" t="str">
         <f>C149</f>
@@ -45941,7 +45955,7 @@
         <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D150" s="216" t="str">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="151" spans="3:15" x14ac:dyDescent="0.35">
@@ -45949,7 +45963,7 @@
         <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D151" s="216" t="str">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="152" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -45957,7 +45971,7 @@
         <v>UsageArea.Center</v>
       </c>
       <c r="D152" s="217" t="str">
-        <v>90</v>
+        <v>0, 0</v>
       </c>
       <c r="M152"/>
     </row>
@@ -45965,15 +45979,15 @@
       <c r="M153"/>
     </row>
     <row r="154" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C154" s="237" t="str" cm="1">
-        <f t="array" ref="C154:E167">_xll.PE.trf.TransformSteps(D127,D128,C129,"proj")</f>
-        <v>Transform Identifiers</v>
-      </c>
-      <c r="D154" s="233" t="str">
-        <v>INVERSE(EPSG)</v>
-      </c>
-      <c r="E154" s="234">
+      <c r="C154" s="251" t="str" cm="1">
+        <f t="array" ref="C154:E168">_xll.PE.trf.TransformSteps(D127,D128,C129,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D154" s="215">
         <v>0</v>
+      </c>
+      <c r="E154" s="5">
+        <v>1</v>
       </c>
       <c r="G154" s="182" t="str" cm="1">
         <f t="array" ref="G154:K156">_xll.PE.xfm.ListTransformPipelines(D127,D128)</f>
@@ -45996,14 +46010,14 @@
       <c r="O154"/>
     </row>
     <row r="155" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C155" s="238" t="str">
-        <v>Transform Name</v>
+      <c r="C155" s="235" t="str">
+        <v>Step Identifiers</v>
       </c>
       <c r="D155" s="172" t="str">
-        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
-      </c>
-      <c r="E155" s="235" t="str">
-        <v>Ballpark geographic offset from Albanian 1987 to WGS 84</v>
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E155" s="233">
+        <v>0</v>
       </c>
       <c r="G155" s="198">
         <v>1</v>
@@ -46025,14 +46039,14 @@
       <c r="O155"/>
     </row>
     <row r="156" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C156" s="238" t="str">
-        <v>Accuracy [m]</v>
-      </c>
-      <c r="D156" s="172">
-        <v>0</v>
-      </c>
-      <c r="E156" s="235">
-        <v>0</v>
+      <c r="C156" s="235" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="D156" s="172" t="str">
+        <v>Inverse of 6-degree Gauss-Kruger zone 4</v>
+      </c>
+      <c r="E156" s="233" t="str">
+        <v>Ballpark geographic offset from Albanian 1987 to WGS 84</v>
       </c>
       <c r="G156" s="200">
         <v>2</v>
@@ -46054,14 +46068,14 @@
       <c r="O156"/>
     </row>
     <row r="157" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C157" s="238" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="D157" s="172" t="str">
-        <v>Between 18°E and 24°E.</v>
-      </c>
-      <c r="E157" s="235" t="str">
-        <v>World</v>
+      <c r="C157" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D157" s="172">
+        <v>0</v>
+      </c>
+      <c r="E157" s="233">
+        <v>0</v>
       </c>
       <c r="H157" t="str">
         <f>H155</f>
@@ -46072,14 +46086,14 @@
       <c r="O157"/>
     </row>
     <row r="158" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C158" s="238" t="str">
-        <v>Scope</v>
+      <c r="C158" s="235" t="str">
+        <v>UsageArea</v>
       </c>
       <c r="D158" s="172" t="str">
-        <v>Topographic mapping (medium scale).</v>
-      </c>
-      <c r="E158" s="235" t="str">
-        <v>Unknown</v>
+        <v>Between 18°E and 24°E.</v>
+      </c>
+      <c r="E158" s="233" t="str">
+        <v>World</v>
       </c>
       <c r="H158" t="str">
         <f>H156</f>
@@ -46090,14 +46104,14 @@
       <c r="O158"/>
     </row>
     <row r="159" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="C159" s="238" t="str">
-        <v>Remarks</v>
+      <c r="C159" s="235" t="str">
+        <v>Scope</v>
       </c>
       <c r="D159" s="172" t="str">
-        <v>Also found with zone truncated from false easting: see 6-degree Gauss-Kruger CM 21E (code 16304).</v>
-      </c>
-      <c r="E159" s="235" t="str">
-        <v>None</v>
+        <v>Topographic mapping (medium scale).</v>
+      </c>
+      <c r="E159" s="233" t="str">
+        <v>Unknown</v>
       </c>
       <c r="L159" s="1"/>
       <c r="M159"/>
@@ -46105,29 +46119,29 @@
       <c r="O159"/>
     </row>
     <row r="160" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C160" s="238" t="str">
-        <v>UsageArea.WestLongitude</v>
-      </c>
-      <c r="D160" s="172">
-        <v>18</v>
-      </c>
-      <c r="E160" s="235">
-        <v>-180</v>
+      <c r="C160" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D160" s="172" t="str">
+        <v>Also found with zone truncated from false easting: see 6-degree Gauss-Kruger CM 21E (code 16304).</v>
+      </c>
+      <c r="E160" s="233" t="str">
+        <v>None</v>
       </c>
       <c r="L160" s="1"/>
       <c r="M160"/>
       <c r="N160" s="61"/>
       <c r="O160"/>
     </row>
-    <row r="161" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C161" s="238" t="str">
-        <v>UsageArea.SouthLatitude</v>
+    <row r="161" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C161" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D161" s="172">
-        <v>24</v>
-      </c>
-      <c r="E161" s="235">
-        <v>180</v>
+        <v>18</v>
+      </c>
+      <c r="E161" s="233">
+        <v>-180</v>
       </c>
       <c r="G161" s="182" t="str" cm="1">
         <f t="array" ref="G161:P164">_xll.PE.trf.ListTransformOptions(D127,D128)</f>
@@ -46161,15 +46175,15 @@
         <v>Cons</v>
       </c>
     </row>
-    <row r="162" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C162" s="238" t="str">
-        <v>UsageArea.EastLongitude</v>
+    <row r="162" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C162" s="235" t="str">
+        <v>UsageArea.SouthLatitude</v>
       </c>
       <c r="D162" s="172">
-        <v>-80</v>
-      </c>
-      <c r="E162" s="235">
-        <v>-90</v>
+        <v>24</v>
+      </c>
+      <c r="E162" s="233">
+        <v>180</v>
       </c>
       <c r="G162" s="198">
         <v>0</v>
@@ -46195,22 +46209,22 @@
       <c r="N162" t="str">
         <v>Albania - onshore.</v>
       </c>
-      <c r="O162" s="240" t="str">
+      <c r="O162" s="237" t="str">
         <v>Available; Non-ballpark; Accuracy=1; Has usage area; Default selection</v>
       </c>
-      <c r="P162" s="241" t="str">
+      <c r="P162" s="238" t="str">
         <v/>
       </c>
     </row>
-    <row r="163" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C163" s="238" t="str">
-        <v>UsageArea.NorthLatitude</v>
+    <row r="163" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C163" s="235" t="str">
+        <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D163" s="172">
-        <v>84</v>
-      </c>
-      <c r="E163" s="235">
-        <v>90</v>
+        <v>-80</v>
+      </c>
+      <c r="E163" s="233">
+        <v>-90</v>
       </c>
       <c r="G163" s="198">
         <v>1</v>
@@ -46236,22 +46250,22 @@
       <c r="N163" t="str">
         <v>Between 18°E and 24°E.</v>
       </c>
-      <c r="O163" s="240" t="str">
+      <c r="O163" s="237" t="str">
         <v>Available; Non-ballpark; Has usage area; Default selection</v>
       </c>
-      <c r="P163" s="241" t="str">
+      <c r="P163" s="238" t="str">
         <v>No reported accuracy</v>
       </c>
     </row>
-    <row r="164" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C164" s="238" t="str">
-        <v>Nr grids</v>
+    <row r="164" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C164" s="235" t="str">
+        <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D164" s="172">
-        <v>0</v>
-      </c>
-      <c r="E164" s="235">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="E164" s="233">
+        <v>90</v>
       </c>
       <c r="G164" s="200">
         <v>2</v>
@@ -46277,22 +46291,22 @@
       <c r="N164" s="201" t="str">
         <v/>
       </c>
-      <c r="O164" s="242" t="str">
+      <c r="O164" s="239" t="str">
         <v>Available; Non-ballpark; Default selection</v>
       </c>
-      <c r="P164" s="243" t="str">
+      <c r="P164" s="240" t="str">
         <v>No reported accuracy</v>
       </c>
     </row>
-    <row r="165" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C165" s="238" t="str">
-        <v>1st grid</v>
-      </c>
-      <c r="D165" s="172" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="E165" s="235" t="str">
-        <v>N.A.</v>
+    <row r="165" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C165" s="235" t="str">
+        <v>Nr grids</v>
+      </c>
+      <c r="D165" s="172">
+        <v>0</v>
+      </c>
+      <c r="E165" s="233">
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>I162</f>
@@ -46302,14 +46316,14 @@
       <c r="M165"/>
       <c r="O165"/>
     </row>
-    <row r="166" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C166" s="238" t="str">
-        <v>2nd grid</v>
+    <row r="166" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C166" s="235" t="str">
+        <v>1st grid</v>
       </c>
       <c r="D166" s="172" t="str">
         <v>N.A.</v>
       </c>
-      <c r="E166" s="235" t="str">
+      <c r="E166" s="233" t="str">
         <v>N.A.</v>
       </c>
       <c r="I166" t="str">
@@ -46318,15 +46332,15 @@
       </c>
       <c r="M166"/>
     </row>
-    <row r="167" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C167" s="239" t="str">
-        <v>Transform PROJ string</v>
-      </c>
-      <c r="D167" s="214" t="str">
-        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +inv +proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
-      </c>
-      <c r="E167" s="236" t="str">
-        <v>+proj=noop</v>
+    <row r="167" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C167" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D167" s="172" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E167" s="233" t="str">
+        <v>N.A.</v>
       </c>
       <c r="I167" t="str">
         <f>I164</f>
@@ -46334,151 +46348,141 @@
       </c>
       <c r="M167"/>
     </row>
-    <row r="168" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C168" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D168" s="214" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +inv +proj=tmerc +lat_0=0 +lon_0=21 +k=1 +x_0=4500000 +y_0=0 +ellps=krass +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E168" s="234" t="str">
+        <v>+proj=noop</v>
+      </c>
       <c r="M168"/>
     </row>
-    <row r="169" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B169"/>
       <c r="M169"/>
-    </row>
-    <row r="170" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C170" s="41" t="s">
+      <c r="O169"/>
+    </row>
+    <row r="170" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M170"/>
+    </row>
+    <row r="171" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C171" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="D170" s="210">
+      <c r="D171" s="210">
         <v>3857</v>
-      </c>
-      <c r="K170" s="61"/>
-      <c r="M170"/>
-    </row>
-    <row r="171" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C171" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D171" s="211">
-        <v>23095</v>
       </c>
       <c r="K171" s="61"/>
       <c r="M171"/>
     </row>
-    <row r="172" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C172" s="182" t="str" cm="1">
-        <f t="array" ref="C172">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,3,)</f>
-        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=3; AllowDeprecatedCrs=False</v>
-      </c>
-      <c r="D172" s="183"/>
-      <c r="E172" s="183"/>
-      <c r="F172" s="183"/>
-      <c r="G172" s="183"/>
-      <c r="H172" s="183"/>
-      <c r="I172" s="183"/>
-      <c r="J172" s="183"/>
-      <c r="K172" s="183"/>
-      <c r="L172" s="183"/>
-      <c r="M172" s="183"/>
-      <c r="N172" s="183"/>
-      <c r="O172" s="184"/>
-      <c r="P172" s="184"/>
-    </row>
-    <row r="173" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C173" s="223" t="str" cm="1">
-        <f t="array" ref="C173:I195">_xll.PE.trf.TransformList(D170,D171,C172,"")</f>
+    <row r="172" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C172" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D172" s="211">
+        <v>23095</v>
+      </c>
+      <c r="K172" s="61"/>
+      <c r="M172"/>
+    </row>
+    <row r="173" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C173" s="182" t="str" cm="1">
+        <f t="array" ref="C173">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D173" s="183"/>
+      <c r="E173" s="183"/>
+      <c r="F173" s="183"/>
+      <c r="G173" s="183"/>
+      <c r="H173" s="183"/>
+      <c r="I173" s="183"/>
+      <c r="J173" s="183"/>
+      <c r="K173" s="183"/>
+      <c r="L173" s="183"/>
+      <c r="M173" s="183"/>
+      <c r="N173" s="183"/>
+      <c r="O173" s="184"/>
+      <c r="P173" s="184"/>
+    </row>
+    <row r="174" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C174" s="223" t="str" cm="1">
+        <f t="array" ref="C174:I196">_xll.PE.trf.TransformList(D171,D172,C173,"")</f>
         <v>Transform Number</v>
       </c>
-      <c r="D173" s="215">
+      <c r="D174" s="215">
         <v>0</v>
       </c>
-      <c r="E173" s="215">
+      <c r="E174" s="215">
         <v>1</v>
       </c>
-      <c r="F173" s="215">
+      <c r="F174" s="215">
         <v>2</v>
       </c>
-      <c r="G173" s="215">
+      <c r="G174" s="215">
         <v>3</v>
       </c>
-      <c r="H173" s="215">
+      <c r="H174" s="215">
         <v>4</v>
       </c>
-      <c r="I173" s="5">
+      <c r="I174" s="5">
         <v>5</v>
       </c>
-      <c r="M173"/>
-    </row>
-    <row r="174" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C174" s="12" t="str">
+      <c r="M174"/>
+    </row>
+    <row r="175" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C175" s="12" t="str">
         <v>Transform Name</v>
       </c>
-      <c r="D174" s="212" t="str">
+      <c r="D175" s="212" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (18) + TM 5 NE</v>
       </c>
-      <c r="E174" s="212" t="str">
+      <c r="E175" s="212" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (32) + TM 5 NE</v>
       </c>
-      <c r="F174" s="212" t="str">
+      <c r="F175" s="212" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
       </c>
-      <c r="G174" s="172" t="str">
+      <c r="G175" s="172" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (1) + TM 5 NE</v>
       </c>
-      <c r="H174" s="172" t="str">
+      <c r="H175" s="172" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
       </c>
-      <c r="I174" s="179" t="str">
+      <c r="I175" s="179" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
       </c>
-      <c r="M174"/>
-    </row>
-    <row r="175" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C175" s="12" t="str">
+      <c r="M175"/>
+    </row>
+    <row r="176" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="C176" s="12" t="str">
         <v>Transform Type</v>
       </c>
-      <c r="D175" s="212" t="str">
+      <c r="D176" s="212" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="E175" s="212" t="str">
+      <c r="E176" s="212" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="F175" s="212" t="str">
+      <c r="F176" s="212" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="G175" s="172" t="str">
+      <c r="G176" s="172" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="H175" s="172" t="str">
+      <c r="H176" s="172" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="I175" s="179" t="str">
+      <c r="I176" s="179" t="str">
         <v>ConcatenatedOperation</v>
-      </c>
-      <c r="M175"/>
-    </row>
-    <row r="176" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C176" s="12" t="str">
-        <v>Identifier</v>
-      </c>
-      <c r="D176" s="212" t="str">
-        <v/>
-      </c>
-      <c r="E176" s="212" t="str">
-        <v/>
-      </c>
-      <c r="F176" s="212" t="str">
-        <v/>
-      </c>
-      <c r="G176" s="172" t="str">
-        <v/>
-      </c>
-      <c r="H176" s="172" t="str">
-        <v/>
-      </c>
-      <c r="I176" s="179" t="str">
-        <v/>
       </c>
       <c r="M176"/>
     </row>
     <row r="177" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C177" s="12" t="str">
-        <v>Identifiers</v>
+        <v>Identifier</v>
       </c>
       <c r="D177" s="212" t="str">
         <v/>
@@ -46502,127 +46506,127 @@
     </row>
     <row r="178" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C178" s="12" t="str">
-        <v>Accuracy</v>
+        <v>Identifiers</v>
       </c>
       <c r="D178" s="212" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="E178" s="212" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="F178" s="212" t="str">
-        <v>6</v>
+        <v/>
       </c>
       <c r="G178" s="172" t="str">
-        <v>10</v>
+        <v/>
       </c>
       <c r="H178" s="172" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="I178" s="179" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="M178"/>
     </row>
     <row r="179" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C179" s="12" t="str">
-        <v>IsAvailable</v>
+        <v>Accuracy</v>
       </c>
       <c r="D179" s="212" t="str">
-        <v>True</v>
+        <v>1</v>
       </c>
       <c r="E179" s="212" t="str">
-        <v>True</v>
+        <v>5</v>
       </c>
       <c r="F179" s="212" t="str">
-        <v>True</v>
+        <v>6</v>
       </c>
       <c r="G179" s="172" t="str">
-        <v>True</v>
+        <v>10</v>
       </c>
       <c r="H179" s="172" t="str">
-        <v>True</v>
+        <v>1</v>
       </c>
       <c r="I179" s="179" t="str">
-        <v>True</v>
+        <v>2</v>
       </c>
       <c r="M179"/>
     </row>
     <row r="180" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C180" s="12" t="str">
-        <v>HasBallParkTransformation</v>
+        <v>IsAvailable</v>
       </c>
       <c r="D180" s="212" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="E180" s="212" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="F180" s="212" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="G180" s="172" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="H180" s="172" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="I180" s="179" t="str">
-        <v>False</v>
+        <v>True</v>
       </c>
       <c r="M180"/>
     </row>
     <row r="181" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C181" s="12" t="str">
-        <v>HasInverse</v>
+        <v>HasBallParkTransformation</v>
       </c>
       <c r="D181" s="212" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="E181" s="212" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="F181" s="212" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="G181" s="172" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="H181" s="172" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="I181" s="179" t="str">
-        <v>True</v>
+        <v>False</v>
       </c>
       <c r="M181"/>
     </row>
     <row r="182" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C182" s="12" t="str">
-        <v>MethodName</v>
+        <v>HasInverse</v>
       </c>
       <c r="D182" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="E182" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="F182" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="G182" s="172" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="H182" s="172" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="I182" s="179" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="M182"/>
     </row>
     <row r="183" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C183" s="12" t="str">
-        <v>Scope</v>
+        <v>MethodName</v>
       </c>
       <c r="D183" s="212" t="str">
         <v/>
@@ -46646,7 +46650,7 @@
     </row>
     <row r="184" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C184" s="12" t="str">
-        <v>Remarks</v>
+        <v>Scope</v>
       </c>
       <c r="D184" s="212" t="str">
         <v/>
@@ -46670,7 +46674,7 @@
     </row>
     <row r="185" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C185" s="12" t="str">
-        <v>GridUsages</v>
+        <v>Remarks</v>
       </c>
       <c r="D185" s="212" t="str">
         <v/>
@@ -46694,7 +46698,7 @@
     </row>
     <row r="186" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C186" s="12" t="str">
-        <v>Parameters</v>
+        <v>GridUsages</v>
       </c>
       <c r="D186" s="212" t="str">
         <v/>
@@ -46718,103 +46722,103 @@
     </row>
     <row r="187" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C187" s="12" t="str">
-        <v>SourceCRS</v>
+        <v>Parameters</v>
       </c>
       <c r="D187" s="212" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="E187" s="212" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="F187" s="212" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="G187" s="172" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="H187" s="172" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="I187" s="179" t="str">
-        <v>WGS 84 / Pseudo-Mercator</v>
+        <v/>
       </c>
       <c r="M187"/>
     </row>
     <row r="188" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C188" s="12" t="str">
-        <v>TargetCRS</v>
+        <v>SourceCRS</v>
       </c>
       <c r="D188" s="212" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="E188" s="212" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="F188" s="212" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="G188" s="172" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="H188" s="172" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="I188" s="179" t="str">
-        <v>ED50 / TM 5 NE</v>
+        <v>WGS 84 / Pseudo-Mercator</v>
       </c>
       <c r="M188"/>
     </row>
     <row r="189" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C189" s="12" t="str">
-        <v>Context</v>
+        <v>TargetCRS</v>
       </c>
       <c r="D189" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="E189" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="F189" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="G189" s="172" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="H189" s="172" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="I189" s="179" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>ED50 / TM 5 NE</v>
       </c>
       <c r="M189"/>
     </row>
     <row r="190" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C190" s="12" t="str">
-        <v>UsageArea.Name</v>
+        <v>Context</v>
       </c>
       <c r="D190" s="212" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="E190" s="212" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="F190" s="212" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="G190" s="172" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="H190" s="172" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="I190" s="179" t="str">
-        <v>UsageArea</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="M190"/>
     </row>
     <row r="191" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C191" s="12" t="str">
-        <v>UsageArea.WestLongitude</v>
+        <v>UsageArea.Name</v>
       </c>
       <c r="D191" s="212" t="str">
         <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
@@ -46838,7 +46842,7 @@
     </row>
     <row r="192" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C192" s="12" t="str">
-        <v>UsageArea.SouthLatitude</v>
+        <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D192" s="212" t="str">
         <v>-16.1</v>
@@ -46862,7 +46866,7 @@
     </row>
     <row r="193" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C193" s="12" t="str">
-        <v>UsageArea.EastLongitude</v>
+        <v>UsageArea.SouthLatitude</v>
       </c>
       <c r="D193" s="212" t="str">
         <v>47.42</v>
@@ -46886,7 +46890,7 @@
     </row>
     <row r="194" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C194" s="12" t="str">
-        <v>UsageArea.NorthLatitude</v>
+        <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D194" s="212" t="str">
         <v>10.86</v>
@@ -46908,160 +46912,139 @@
       </c>
       <c r="M194"/>
     </row>
-    <row r="195" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C195" s="13" t="str">
+    <row r="195" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C195" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D195" s="212" t="str">
+        <v>63.89</v>
+      </c>
+      <c r="E195" s="212" t="str">
+        <v>55.77</v>
+      </c>
+      <c r="F195" s="212" t="str">
+        <v>57.8</v>
+      </c>
+      <c r="G195" s="172" t="str">
+        <v>71.24</v>
+      </c>
+      <c r="H195" s="172" t="str">
+        <v>55.92</v>
+      </c>
+      <c r="I195" s="179" t="str">
+        <v>51.56</v>
+      </c>
+      <c r="M195"/>
+    </row>
+    <row r="196" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C196" s="13" t="str">
         <v>UsageArea.Center</v>
       </c>
-      <c r="D195" s="213" t="str">
-        <v>63.89</v>
-      </c>
-      <c r="E195" s="213" t="str">
-        <v>55.77</v>
-      </c>
-      <c r="F195" s="213" t="str">
-        <v>57.8</v>
-      </c>
-      <c r="G195" s="214" t="str">
-        <v>71.24</v>
-      </c>
-      <c r="H195" s="214" t="str">
-        <v>55.92</v>
-      </c>
-      <c r="I195" s="181" t="str">
-        <v>51.56</v>
-      </c>
-      <c r="M195"/>
-    </row>
-    <row r="196" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D196" s="213" t="str">
+        <v>-2.62, 55.655</v>
+      </c>
+      <c r="E196" s="213" t="str">
+        <v>4.45, 53.605</v>
+      </c>
+      <c r="F196" s="213" t="str">
+        <v>6.15, 50.065</v>
+      </c>
+      <c r="G196" s="214" t="str">
+        <v>11.015, 53.06</v>
+      </c>
+      <c r="H196" s="214" t="str">
+        <v>6.11, 54.75</v>
+      </c>
+      <c r="I196" s="181" t="str">
+        <v>0.260000000000001, 46.355</v>
+      </c>
       <c r="M196"/>
     </row>
     <row r="197" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C197" s="237" t="str" cm="1">
-        <f t="array" ref="C197:F210">_xll.PE.trf.TransformSteps(D170,D171,C172,"proj")</f>
-        <v>Transform Identifiers</v>
-      </c>
-      <c r="D197" s="176" t="str">
-        <v>INVERSE(EPSG)</v>
-      </c>
-      <c r="E197" s="233" t="str">
-        <v>INVERSE(EPSG)</v>
-      </c>
-      <c r="F197" s="233" t="str">
-        <v>EPSG</v>
-      </c>
-      <c r="G197" s="233"/>
-      <c r="H197" s="233"/>
-      <c r="I197" s="177"/>
-      <c r="K197" s="182" t="str" cm="1">
-        <f t="array" ref="K197:O203">_xll.PE.xfm.ListTransformPipelines(D170,D171)</f>
+      <c r="M197"/>
+    </row>
+    <row r="198" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C198" s="251" t="str" cm="1">
+        <f t="array" ref="C198:D212">_xll.PE.trf.TransformSteps(D171,D172,C173,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D198" s="4">
+        <v>0</v>
+      </c>
+      <c r="E198" s="215"/>
+      <c r="F198" s="215"/>
+      <c r="G198" s="215"/>
+      <c r="H198" s="215"/>
+      <c r="I198" s="5"/>
+      <c r="K198" s="182" t="str" cm="1">
+        <f t="array" ref="K198:O204">_xll.PE.xfm.ListTransformPipelines(D171,D172)</f>
         <v>PipelineID</v>
       </c>
-      <c r="L197" s="183" t="str">
+      <c r="L198" s="183" t="str">
         <v>Name</v>
       </c>
-      <c r="M197" s="183" t="str">
+      <c r="M198" s="183" t="str">
         <v>Accuracy(m)</v>
       </c>
-      <c r="N197" s="183" t="str">
+      <c r="N198" s="183" t="str">
         <v>Grids</v>
       </c>
-      <c r="O197" s="184" t="str">
+      <c r="O198" s="184" t="str">
         <v>IsAvailable</v>
       </c>
-      <c r="R197" s="61"/>
-    </row>
-    <row r="198" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C198" s="238" t="str">
-        <v>Transform Name</v>
-      </c>
-      <c r="D198" s="178" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator</v>
-      </c>
-      <c r="E198" s="244" t="str">
-        <v>Inverse of ED50 to WGS 84 (1)</v>
-      </c>
-      <c r="F198" s="244" t="str">
-        <v>TM 5 NE</v>
-      </c>
-      <c r="G198" s="244"/>
-      <c r="H198" s="244"/>
-      <c r="I198" s="179"/>
-      <c r="K198" s="248">
+      <c r="R198" s="61"/>
+    </row>
+    <row r="199" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C199" s="235" t="str">
+        <v>Step Identifiers</v>
+      </c>
+      <c r="D199" s="178">
+        <v>0</v>
+      </c>
+      <c r="E199" s="172"/>
+      <c r="F199" s="172"/>
+      <c r="G199" s="172"/>
+      <c r="H199" s="172"/>
+      <c r="I199" s="179"/>
+      <c r="K199" s="244">
         <v>1</v>
       </c>
-      <c r="L198" s="249" t="str">
+      <c r="L199" s="245" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (18) + TM 5 NE</v>
       </c>
-      <c r="M198" s="249">
+      <c r="M199" s="245">
         <v>1</v>
       </c>
-      <c r="N198" s="249" t="str">
+      <c r="N199" s="245" t="str">
         <v/>
       </c>
-      <c r="O198" s="257" t="str">
+      <c r="O199" s="250" t="str">
         <v>TRUE</v>
       </c>
-      <c r="R198" s="61"/>
-    </row>
-    <row r="199" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C199" s="238" t="str">
-        <v>Accuracy [m]</v>
-      </c>
-      <c r="D199" s="178">
-        <v>55</v>
-      </c>
-      <c r="E199" s="244">
-        <v>55</v>
-      </c>
-      <c r="F199" s="244">
-        <v>55</v>
-      </c>
-      <c r="G199" s="244"/>
-      <c r="H199" s="244"/>
-      <c r="I199" s="179"/>
-      <c r="K199" s="198">
-        <v>2</v>
-      </c>
-      <c r="L199" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (32) + TM 5 NE</v>
-      </c>
-      <c r="M199" s="251">
-        <v>5</v>
-      </c>
-      <c r="N199" s="251" t="str">
-        <v/>
-      </c>
-      <c r="O199" s="199" t="str">
-        <v>TRUE</v>
-      </c>
       <c r="R199" s="61"/>
     </row>
     <row r="200" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C200" s="238" t="str">
-        <v>UsageArea</v>
+      <c r="C200" s="235" t="str">
+        <v>Step Name</v>
       </c>
       <c r="D200" s="178" t="str">
-        <v>World.</v>
-      </c>
-      <c r="E200" s="244" t="str">
-        <v>Austria; Belgium; Denmark; Finland; Faroe islands; France; Germany (west); Gibraltar; Greece; Italy; Luxembourg; Netherlands; Norway; Portugal; Spain; Sweden; Switzerland.</v>
-      </c>
-      <c r="F200" s="244" t="str">
-        <v>Netherlands - offshore North Sea.</v>
-      </c>
-      <c r="G200" s="244"/>
-      <c r="H200" s="244"/>
+        <v>&lt;choose-coordinate-transform&gt;</v>
+      </c>
+      <c r="E200" s="172"/>
+      <c r="F200" s="172"/>
+      <c r="G200" s="172"/>
+      <c r="H200" s="172"/>
       <c r="I200" s="179"/>
       <c r="K200" s="198">
-        <v>3</v>
-      </c>
-      <c r="L200" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
-      </c>
-      <c r="M200" s="251">
-        <v>6</v>
-      </c>
-      <c r="N200" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (32) + TM 5 NE</v>
+      </c>
+      <c r="M200">
+        <v>5</v>
+      </c>
+      <c r="N200" t="str">
         <v/>
       </c>
       <c r="O200" s="199" t="str">
@@ -47070,31 +47053,27 @@
       <c r="R200" s="61"/>
     </row>
     <row r="201" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C201" s="238" t="str">
-        <v>Scope</v>
-      </c>
-      <c r="D201" s="178" t="str">
-        <v>Web mapping and visualisation.</v>
-      </c>
-      <c r="E201" s="244" t="str">
-        <v>Military survey.</v>
-      </c>
-      <c r="F201" s="244" t="str">
-        <v>Oil and gas exploration and production.</v>
-      </c>
-      <c r="G201" s="244"/>
-      <c r="H201" s="244"/>
+      <c r="C201" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D201" s="178">
+        <v>55</v>
+      </c>
+      <c r="E201" s="172"/>
+      <c r="F201" s="172"/>
+      <c r="G201" s="172"/>
+      <c r="H201" s="172"/>
       <c r="I201" s="179"/>
       <c r="K201" s="198">
-        <v>4</v>
-      </c>
-      <c r="L201" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (1) + TM 5 NE</v>
-      </c>
-      <c r="M201" s="251">
-        <v>10</v>
-      </c>
-      <c r="N201" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
+      </c>
+      <c r="M201">
+        <v>6</v>
+      </c>
+      <c r="N201" t="str">
         <v/>
       </c>
       <c r="O201" s="199" t="str">
@@ -47103,663 +47082,606 @@
       <c r="R201" s="61"/>
     </row>
     <row r="202" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C202" s="238" t="str">
-        <v>Remarks</v>
+      <c r="C202" s="235" t="str">
+        <v>UsageArea</v>
       </c>
       <c r="D202" s="178" t="str">
-        <v>None</v>
-      </c>
-      <c r="E202" s="244" t="str">
-        <v>Derived at 85 stations. Accuracy 3m, 8m and 5m in X, Y and Z axes. In Germany will be accepted by LBA for minerals management purposes as alternative to tfm 1052 or 1998.</v>
-      </c>
-      <c r="F202" s="244" t="str">
-        <v>None</v>
-      </c>
-      <c r="G202" s="244"/>
-      <c r="H202" s="244"/>
+        <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
+      </c>
+      <c r="E202" s="172"/>
+      <c r="F202" s="172"/>
+      <c r="G202" s="172"/>
+      <c r="H202" s="172"/>
       <c r="I202" s="179"/>
       <c r="K202" s="198">
-        <v>5</v>
-      </c>
-      <c r="L202" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
-      </c>
-      <c r="M202" s="251">
-        <v>1</v>
-      </c>
-      <c r="N202" s="251" t="str">
+        <v>4</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (1) + TM 5 NE</v>
+      </c>
+      <c r="M202">
+        <v>10</v>
+      </c>
+      <c r="N202" t="str">
         <v/>
       </c>
       <c r="O202" s="199" t="str">
         <v>TRUE</v>
       </c>
-      <c r="P202" s="1"/>
       <c r="R202" s="61"/>
     </row>
-    <row r="203" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C203" s="238" t="str">
-        <v>UsageArea.WestLongitude</v>
-      </c>
-      <c r="D203" s="178">
-        <v>-180</v>
-      </c>
-      <c r="E203" s="244">
-        <v>-9.56</v>
-      </c>
-      <c r="F203" s="244">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="G203" s="244"/>
-      <c r="H203" s="244"/>
+    <row r="203" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C203" s="235" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D203" s="178" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E203" s="172"/>
+      <c r="F203" s="172"/>
+      <c r="G203" s="172"/>
+      <c r="H203" s="172"/>
       <c r="I203" s="179"/>
-      <c r="K203" s="200">
-        <v>6</v>
-      </c>
-      <c r="L203" s="201" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
-      </c>
-      <c r="M203" s="201">
-        <v>2</v>
-      </c>
-      <c r="N203" s="201" t="str">
+      <c r="K203" s="198">
+        <v>5</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
+      </c>
+      <c r="M203">
+        <v>1</v>
+      </c>
+      <c r="N203" t="str">
         <v/>
       </c>
-      <c r="O203" s="202" t="str">
+      <c r="O203" s="199" t="str">
         <v>TRUE</v>
       </c>
       <c r="P203" s="1"/>
       <c r="R203" s="61"/>
     </row>
     <row r="204" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C204" s="238" t="str">
+      <c r="C204" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D204" s="178" t="str">
+        <v>None</v>
+      </c>
+      <c r="E204" s="172"/>
+      <c r="F204" s="172"/>
+      <c r="G204" s="172"/>
+      <c r="H204" s="172"/>
+      <c r="I204" s="179"/>
+      <c r="K204" s="200">
+        <v>6</v>
+      </c>
+      <c r="L204" s="201" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
+      </c>
+      <c r="M204" s="201">
+        <v>2</v>
+      </c>
+      <c r="N204" s="201" t="str">
+        <v/>
+      </c>
+      <c r="O204" s="202" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P204" s="1"/>
+      <c r="R204" s="61"/>
+    </row>
+    <row r="205" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C205" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D205" s="178">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="E205" s="172"/>
+      <c r="F205" s="172"/>
+      <c r="G205" s="172"/>
+      <c r="H205" s="172"/>
+      <c r="I205" s="179"/>
+    </row>
+    <row r="206" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C206" s="235" t="str">
         <v>UsageArea.SouthLatitude</v>
       </c>
-      <c r="D204" s="178">
-        <v>180</v>
-      </c>
-      <c r="E204" s="244">
-        <v>31.59</v>
-      </c>
-      <c r="F204" s="244">
-        <v>6.37</v>
-      </c>
-      <c r="G204" s="244"/>
-      <c r="H204" s="244"/>
-      <c r="I204" s="179"/>
-    </row>
-    <row r="205" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C205" s="238" t="str">
+      <c r="D206" s="178">
+        <v>10.86</v>
+      </c>
+      <c r="E206" s="172"/>
+      <c r="F206" s="172"/>
+      <c r="G206" s="172"/>
+      <c r="H206" s="172"/>
+      <c r="I206" s="179"/>
+      <c r="K206" s="182" t="str" cm="1">
+        <f t="array" ref="K206:T212">_xll.PE.trf.ListTransformOptions(D171,D172)</f>
+        <v>CandidateIndex</v>
+      </c>
+      <c r="L206" s="183" t="str">
+        <v>DefaultSelection</v>
+      </c>
+      <c r="M206" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="N206" s="183" t="str">
+        <v>Type</v>
+      </c>
+      <c r="O206" s="183" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="P206" s="183" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="Q206" s="183" t="str">
+        <v>HasBallPark</v>
+      </c>
+      <c r="R206" s="183" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="S206" s="203" t="str">
+        <v>Pros</v>
+      </c>
+      <c r="T206" s="184" t="str">
+        <v>Cons</v>
+      </c>
+    </row>
+    <row r="207" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C207" s="235" t="str">
         <v>UsageArea.EastLongitude</v>
       </c>
-      <c r="D205" s="178">
-        <v>-90</v>
-      </c>
-      <c r="E205" s="244">
-        <v>34.880000000000003</v>
-      </c>
-      <c r="F205" s="244">
-        <v>51.44</v>
-      </c>
-      <c r="G205" s="244"/>
-      <c r="H205" s="244"/>
-      <c r="I205" s="179"/>
-      <c r="K205" s="182" t="str" cm="1">
-        <f t="array" ref="K205:T211">_xll.PE.trf.ListTransformOptions(D170,D171)</f>
-        <v>CandidateIndex</v>
-      </c>
-      <c r="L205" s="183" t="str">
-        <v>DefaultSelection</v>
-      </c>
-      <c r="M205" s="183" t="str">
-        <v>Name</v>
-      </c>
-      <c r="N205" s="183" t="str">
-        <v>Type</v>
-      </c>
-      <c r="O205" s="183" t="str">
-        <v>Accuracy</v>
-      </c>
-      <c r="P205" s="183" t="str">
-        <v>IsAvailable</v>
-      </c>
-      <c r="Q205" s="183" t="str">
-        <v>HasBallPark</v>
-      </c>
-      <c r="R205" s="183" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="S205" s="203" t="str">
-        <v>Pros</v>
-      </c>
-      <c r="T205" s="184" t="str">
-        <v>Cons</v>
-      </c>
-    </row>
-    <row r="206" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C206" s="238" t="str">
+      <c r="D207" s="178">
+        <v>47.42</v>
+      </c>
+      <c r="E207" s="172"/>
+      <c r="F207" s="172"/>
+      <c r="G207" s="172"/>
+      <c r="H207" s="172"/>
+      <c r="I207" s="179"/>
+      <c r="K207" s="244">
+        <v>0</v>
+      </c>
+      <c r="L207" s="245" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M207" s="245" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (18) + TM 5 NE</v>
+      </c>
+      <c r="N207" s="245" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O207" s="245">
+        <v>1</v>
+      </c>
+      <c r="P207" s="245" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q207" s="245" t="b">
+        <v>0</v>
+      </c>
+      <c r="R207" s="245" t="str">
+        <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
+      </c>
+      <c r="S207" s="248" t="str">
+        <v>Available; Non-ballpark; Accuracy=1; Has usage area; Default selection</v>
+      </c>
+      <c r="T207" s="249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C208" s="235" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D206" s="178">
-        <v>90</v>
-      </c>
-      <c r="E206" s="244">
-        <v>71.239999999999995</v>
-      </c>
-      <c r="F206" s="244">
-        <v>55.77</v>
-      </c>
-      <c r="G206" s="244"/>
-      <c r="H206" s="244"/>
-      <c r="I206" s="179"/>
-      <c r="K206" s="248">
-        <v>0</v>
-      </c>
-      <c r="L206" s="249" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="M206" s="249" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (18) + TM 5 NE</v>
-      </c>
-      <c r="N206" s="249" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O206" s="249">
-        <v>1</v>
-      </c>
-      <c r="P206" s="249" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q206" s="249" t="b">
-        <v>0</v>
-      </c>
-      <c r="R206" s="249" t="str">
-        <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
-      </c>
-      <c r="S206" s="254" t="str">
-        <v>Available; Non-ballpark; Accuracy=1; Has usage area; Default selection</v>
-      </c>
-      <c r="T206" s="255" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C207" s="238" t="str">
-        <v>Nr grids</v>
-      </c>
-      <c r="D207" s="178">
-        <v>0</v>
-      </c>
-      <c r="E207" s="244">
-        <v>0</v>
-      </c>
-      <c r="F207" s="244">
-        <v>0</v>
-      </c>
-      <c r="G207" s="244"/>
-      <c r="H207" s="244"/>
-      <c r="I207" s="179"/>
-      <c r="K207" s="198">
-        <v>1</v>
-      </c>
-      <c r="L207" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M207" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
-      </c>
-      <c r="N207" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O207" s="251">
-        <v>1</v>
-      </c>
-      <c r="P207" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q207" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R207" s="251" t="str">
-        <v>Germany - offshore North Sea.</v>
-      </c>
-      <c r="S207" s="256" t="str">
-        <v>Available; Non-ballpark; Accuracy=1; Has usage area</v>
-      </c>
-      <c r="T207" s="241" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="208" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C208" s="238" t="str">
-        <v>1st grid</v>
-      </c>
-      <c r="D208" s="178" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="E208" s="244" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="F208" s="244" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="G208" s="244"/>
-      <c r="H208" s="244"/>
+      <c r="D208" s="178">
+        <v>63.89</v>
+      </c>
+      <c r="E208" s="172"/>
+      <c r="F208" s="172"/>
+      <c r="G208" s="172"/>
+      <c r="H208" s="172"/>
       <c r="I208" s="179"/>
       <c r="K208" s="198">
-        <v>2</v>
-      </c>
-      <c r="L208" s="251" t="str">
+        <v>1</v>
+      </c>
+      <c r="L208" t="str">
         <v>No</v>
       </c>
-      <c r="M208" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
-      </c>
-      <c r="N208" s="251" t="str">
+      <c r="M208" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (36) + TM 5 NE</v>
+      </c>
+      <c r="N208" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O208" s="251">
-        <v>2</v>
-      </c>
-      <c r="P208" s="251" t="b">
+      <c r="O208">
         <v>1</v>
       </c>
-      <c r="Q208" s="251" t="b">
+      <c r="P208" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q208" t="b">
         <v>0</v>
       </c>
-      <c r="R208" s="251" t="str">
-        <v>France - onshore and offshore, mainland and Corsica (France métropolitaine including Corsica).</v>
-      </c>
-      <c r="S208" s="256" t="str">
-        <v>Available; Non-ballpark; Accuracy=2; Has usage area</v>
-      </c>
-      <c r="T208" s="241" t="str">
+      <c r="R208" t="str">
+        <v>Germany - offshore North Sea.</v>
+      </c>
+      <c r="S208" s="237" t="str">
+        <v>Available; Non-ballpark; Accuracy=1; Has usage area</v>
+      </c>
+      <c r="T208" s="238" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
     <row r="209" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C209" s="238" t="str">
-        <v>2nd grid</v>
-      </c>
-      <c r="D209" s="178" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="E209" s="244" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="F209" s="244" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="G209" s="244"/>
-      <c r="H209" s="244"/>
+      <c r="C209" s="235" t="str">
+        <v>Nr grids</v>
+      </c>
+      <c r="D209" s="178">
+        <v>0</v>
+      </c>
+      <c r="E209" s="172"/>
+      <c r="F209" s="172"/>
+      <c r="G209" s="172"/>
+      <c r="H209" s="172"/>
       <c r="I209" s="179"/>
       <c r="K209" s="198">
+        <v>2</v>
+      </c>
+      <c r="L209" t="str">
+        <v>No</v>
+      </c>
+      <c r="M209" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (17) + TM 5 NE</v>
+      </c>
+      <c r="N209" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O209">
+        <v>2</v>
+      </c>
+      <c r="P209" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q209" t="b">
+        <v>0</v>
+      </c>
+      <c r="R209" t="str">
+        <v>France - onshore and offshore, mainland and Corsica (France métropolitaine including Corsica).</v>
+      </c>
+      <c r="S209" s="237" t="str">
+        <v>Available; Non-ballpark; Accuracy=2; Has usage area</v>
+      </c>
+      <c r="T209" s="238" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="210" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C210" s="235" t="str">
+        <v>1st grid</v>
+      </c>
+      <c r="D210" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E210" s="172"/>
+      <c r="F210" s="172"/>
+      <c r="G210" s="172"/>
+      <c r="H210" s="172"/>
+      <c r="I210" s="179"/>
+      <c r="K210" s="198">
         <v>3</v>
       </c>
-      <c r="L209" s="251" t="str">
+      <c r="L210" t="str">
         <v>No</v>
       </c>
-      <c r="M209" s="251" t="str">
+      <c r="M210" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (32) + TM 5 NE</v>
       </c>
-      <c r="N209" s="251" t="str">
+      <c r="N210" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O209" s="258">
+      <c r="O210" s="61">
         <v>5</v>
       </c>
-      <c r="P209" s="251" t="b">
+      <c r="P210" t="b">
         <v>1</v>
       </c>
-      <c r="Q209" s="251" t="b">
+      <c r="Q210" t="b">
         <v>0</v>
       </c>
-      <c r="R209" s="251" t="str">
+      <c r="R210" t="str">
         <v>Netherlands - offshore North Sea.</v>
       </c>
-      <c r="S209" s="251" t="str">
+      <c r="S210" t="str">
         <v>Available; Non-ballpark; Accuracy=5; Has usage area</v>
-      </c>
-      <c r="T209" s="199" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="210" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C210" s="239" t="str">
-        <v>Transform PROJ string</v>
-      </c>
-      <c r="D210" s="180" t="str">
-        <v>+proj=pipeline +step +inv +proj=webmerc +lat_0=0 +lon_0=0 +x_0=0 +y_0=0 +ellps=WGS84 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
-      </c>
-      <c r="E210" s="214" t="str">
-        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=push +v_3 +step +proj=cart +ellps=WGS84 +step +proj=helmert +x=87 +y=98 +z=121 +step +inv +proj=cart +ellps=intl +step +proj=pop +v_3 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
-      </c>
-      <c r="F210" s="214" t="str">
-        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=tmerc +lat_0=0 +lon_0=5 +k=0.9996 +x_0=500000 +y_0=0 +ellps=intl</v>
-      </c>
-      <c r="G210" s="214"/>
-      <c r="H210" s="214"/>
-      <c r="I210" s="181"/>
-      <c r="K210" s="198">
-        <v>4</v>
-      </c>
-      <c r="L210" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M210" s="251" t="str">
-        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
-      </c>
-      <c r="N210" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O210" s="258">
-        <v>6</v>
-      </c>
-      <c r="P210" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q210" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R210" s="251" t="str">
-        <v>Austria; Denmark; France; Germany (west); Netherlands; Switzerland.</v>
-      </c>
-      <c r="S210" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=6; Has usage area</v>
       </c>
       <c r="T210" s="199" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="211" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K211" s="200">
+    <row r="211" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C211" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D211" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E211" s="172"/>
+      <c r="F211" s="172"/>
+      <c r="G211" s="172"/>
+      <c r="H211" s="172"/>
+      <c r="I211" s="179"/>
+      <c r="K211" s="198">
+        <v>4</v>
+      </c>
+      <c r="L211" t="str">
+        <v>No</v>
+      </c>
+      <c r="M211" t="str">
+        <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (2) + TM 5 NE</v>
+      </c>
+      <c r="N211" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O211" s="61">
+        <v>6</v>
+      </c>
+      <c r="P211" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q211" t="b">
+        <v>0</v>
+      </c>
+      <c r="R211" t="str">
+        <v>Austria; Denmark; France; Germany (west); Netherlands; Switzerland.</v>
+      </c>
+      <c r="S211" t="str">
+        <v>Available; Non-ballpark; Accuracy=6; Has usage area</v>
+      </c>
+      <c r="T211" s="199" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="212" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C212" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D212" s="180">
+        <v>0</v>
+      </c>
+      <c r="E212" s="214"/>
+      <c r="F212" s="214"/>
+      <c r="G212" s="214"/>
+      <c r="H212" s="214"/>
+      <c r="I212" s="181"/>
+      <c r="K212" s="200">
         <v>5</v>
       </c>
-      <c r="L211" s="201" t="str">
+      <c r="L212" s="201" t="str">
         <v>No</v>
       </c>
-      <c r="M211" s="201" t="str">
+      <c r="M212" s="201" t="str">
         <v>Inverse of Popular Visualisation Pseudo-Mercator + Inverse of ED50 to WGS 84 (1) + TM 5 NE</v>
       </c>
-      <c r="N211" s="201" t="str">
+      <c r="N212" s="201" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O211" s="204">
+      <c r="O212" s="204">
         <v>10</v>
       </c>
-      <c r="P211" s="201" t="b">
+      <c r="P212" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q211" s="201" t="b">
+      <c r="Q212" s="201" t="b">
         <v>0</v>
       </c>
-      <c r="R211" s="201" t="str">
+      <c r="R212" s="201" t="str">
         <v>Austria; Belgium; Denmark; Finland; Faroe islands; France; Germany (west); Gibraltar; Greece; Italy; Luxembourg; Netherlands; Norway; Portugal; Spain; Sweden; Switzerland.</v>
       </c>
-      <c r="S211" s="201" t="str">
+      <c r="S212" s="201" t="str">
         <v>Available; Non-ballpark; Accuracy=10; Has usage area</v>
       </c>
-      <c r="T211" s="202" t="str">
+      <c r="T212" s="202" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="212" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="M212"/>
-    </row>
     <row r="213" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="C213" s="41" t="s">
+      <c r="L213" s="253"/>
+      <c r="M213" s="253"/>
+      <c r="N213" s="253"/>
+      <c r="O213" s="254"/>
+      <c r="P213" s="253"/>
+      <c r="Q213" s="253"/>
+      <c r="R213" s="253"/>
+      <c r="S213" s="253"/>
+      <c r="T213" s="253"/>
+    </row>
+    <row r="214" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M214"/>
+    </row>
+    <row r="215" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C215" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="D213" s="210">
+      <c r="D215" s="210">
         <v>2964</v>
       </c>
-      <c r="E213" s="222" t="s">
+      <c r="E215" s="222" t="s">
         <v>144</v>
       </c>
-      <c r="M213"/>
-    </row>
-    <row r="214" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C214" s="12" t="s">
+      <c r="M215"/>
+    </row>
+    <row r="216" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C216" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D214" s="221">
+      <c r="D216" s="221">
         <v>4326</v>
       </c>
-      <c r="E214" s="222" t="s">
+      <c r="E216" s="222" t="s">
         <v>145</v>
       </c>
-      <c r="M214"/>
-    </row>
-    <row r="215" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C215" s="182" t="str" cm="1">
-        <f t="array" ref="C215">_xll.PE.trf.Options(,,,,,,,,,,,,0,,,)</f>
+      <c r="M216"/>
+    </row>
+    <row r="217" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C217" s="182" t="str" cm="1">
+        <f t="array" ref="C217">_xll.PE.trf.Options(,,,,,,,,,,,,0,,,)</f>
         <v>Authority=EPSG; Area=; Accuracy=; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Auto; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
       </c>
-      <c r="D215" s="183"/>
-      <c r="E215" s="183"/>
-      <c r="F215" s="183"/>
-      <c r="G215" s="183"/>
-      <c r="H215" s="183"/>
-      <c r="I215" s="183"/>
-      <c r="J215" s="183"/>
-      <c r="K215" s="183"/>
-      <c r="L215" s="183"/>
-      <c r="M215" s="183"/>
-      <c r="N215" s="183"/>
-      <c r="O215" s="184"/>
-      <c r="P215" s="184"/>
-    </row>
-    <row r="216" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B216"/>
-      <c r="C216" s="223" t="str" cm="1">
-        <f t="array" ref="C216:M238">_xll.PE.trf.TransformList(D213,D214,C215, "")</f>
+      <c r="D217" s="183"/>
+      <c r="E217" s="183"/>
+      <c r="F217" s="183"/>
+      <c r="G217" s="183"/>
+      <c r="H217" s="183"/>
+      <c r="I217" s="183"/>
+      <c r="J217" s="183"/>
+      <c r="K217" s="183"/>
+      <c r="L217" s="183"/>
+      <c r="M217" s="183"/>
+      <c r="N217" s="183"/>
+      <c r="O217" s="184"/>
+      <c r="P217" s="184"/>
+    </row>
+    <row r="218" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B218"/>
+      <c r="C218" s="223" t="str" cm="1">
+        <f t="array" ref="C218:M240">_xll.PE.trf.TransformList(D215,D216,C217, "")</f>
         <v>Transform Number</v>
       </c>
-      <c r="D216" s="215">
+      <c r="D218" s="215">
         <v>0</v>
       </c>
-      <c r="E216" s="215">
+      <c r="E218" s="215">
         <v>1</v>
       </c>
-      <c r="F216" s="215">
+      <c r="F218" s="215">
         <v>2</v>
       </c>
-      <c r="G216" s="215">
+      <c r="G218" s="215">
         <v>3</v>
       </c>
-      <c r="H216" s="215">
+      <c r="H218" s="215">
         <v>4</v>
       </c>
-      <c r="I216" s="215">
+      <c r="I218" s="215">
         <v>5</v>
       </c>
-      <c r="J216" s="215">
+      <c r="J218" s="215">
         <v>6</v>
       </c>
-      <c r="K216" s="215">
+      <c r="K218" s="215">
         <v>7</v>
       </c>
-      <c r="L216" s="215">
+      <c r="L218" s="215">
         <v>8</v>
       </c>
-      <c r="M216" s="5">
+      <c r="M218" s="5">
         <v>9</v>
-      </c>
-    </row>
-    <row r="217" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B217"/>
-      <c r="C217" s="12" t="str">
-        <v>Transform Name</v>
-      </c>
-      <c r="D217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
-      </c>
-      <c r="E217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
-      </c>
-      <c r="F217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
-      </c>
-      <c r="G217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
-      </c>
-      <c r="H217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
-      </c>
-      <c r="I217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
-      </c>
-      <c r="J217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
-      </c>
-      <c r="K217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
-      </c>
-      <c r="L217" s="212" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
-      </c>
-      <c r="M217" s="219" t="str">
-        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
-      </c>
-    </row>
-    <row r="218" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B218"/>
-      <c r="C218" s="12" t="str">
-        <v>Transform Type</v>
-      </c>
-      <c r="D218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="E218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="F218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="G218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="H218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="I218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="J218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="K218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="L218" s="212" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="M218" s="219" t="str">
-        <v>ConcatenatedOperation</v>
       </c>
     </row>
     <row r="219" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B219"/>
       <c r="C219" s="12" t="str">
-        <v>Identifier</v>
+        <v>Transform Name</v>
       </c>
       <c r="D219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
       </c>
       <c r="E219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
       </c>
       <c r="F219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
       </c>
       <c r="G219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
       </c>
       <c r="H219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
       </c>
       <c r="I219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
       </c>
       <c r="J219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
       </c>
       <c r="K219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
       </c>
       <c r="L219" s="212" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
       </c>
       <c r="M219" s="219" t="str">
-        <v/>
+        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
       </c>
     </row>
     <row r="220" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B220"/>
       <c r="C220" s="12" t="str">
-        <v>Identifiers</v>
+        <v>Transform Type</v>
       </c>
       <c r="D220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="E220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="F220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="G220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="H220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="I220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="J220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="K220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="L220" s="212" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
       <c r="M220" s="219" t="str">
-        <v/>
+        <v>ConcatenatedOperation</v>
       </c>
     </row>
     <row r="221" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B221"/>
       <c r="C221" s="12" t="str">
-        <v>Accuracy</v>
+        <v>Identifier</v>
       </c>
       <c r="D221" s="212" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="E221" s="212" t="str">
-        <v>12</v>
+        <v/>
       </c>
       <c r="F221" s="212" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="G221" s="212" t="str">
-        <v>20</v>
+        <v/>
       </c>
       <c r="H221" s="212" t="str">
-        <v>8</v>
+        <v/>
       </c>
       <c r="I221" s="212" t="str">
-        <v>10</v>
+        <v/>
       </c>
       <c r="J221" s="212" t="str">
-        <v>13</v>
+        <v/>
       </c>
       <c r="K221" s="212" t="str">
-        <v>15</v>
+        <v/>
       </c>
       <c r="L221" s="212" t="str">
-        <v>18</v>
+        <v/>
       </c>
       <c r="M221" s="219" t="str">
         <v/>
@@ -47768,79 +47690,79 @@
     <row r="222" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B222"/>
       <c r="C222" s="12" t="str">
-        <v>IsAvailable</v>
+        <v>Identifiers</v>
       </c>
       <c r="D222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="E222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="F222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="G222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="H222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="I222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="J222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="K222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="L222" s="212" t="str">
-        <v>True</v>
+        <v/>
       </c>
       <c r="M222" s="219" t="str">
-        <v>True</v>
+        <v/>
       </c>
     </row>
     <row r="223" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B223"/>
       <c r="C223" s="12" t="str">
-        <v>HasBallParkTransformation</v>
+        <v>Accuracy</v>
       </c>
       <c r="D223" s="212" t="str">
-        <v>False</v>
+        <v>5</v>
       </c>
       <c r="E223" s="212" t="str">
-        <v>False</v>
+        <v>12</v>
       </c>
       <c r="F223" s="212" t="str">
-        <v>False</v>
+        <v>2</v>
       </c>
       <c r="G223" s="212" t="str">
-        <v>False</v>
+        <v>20</v>
       </c>
       <c r="H223" s="212" t="str">
-        <v>False</v>
+        <v>8</v>
       </c>
       <c r="I223" s="212" t="str">
-        <v>False</v>
+        <v>10</v>
       </c>
       <c r="J223" s="212" t="str">
-        <v>False</v>
+        <v>13</v>
       </c>
       <c r="K223" s="212" t="str">
-        <v>False</v>
+        <v>15</v>
       </c>
       <c r="L223" s="212" t="str">
-        <v>False</v>
+        <v>18</v>
       </c>
       <c r="M223" s="219" t="str">
-        <v>True</v>
+        <v/>
       </c>
     </row>
     <row r="224" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B224"/>
       <c r="C224" s="12" t="str">
-        <v>HasInverse</v>
+        <v>IsAvailable</v>
       </c>
       <c r="D224" s="212" t="str">
         <v>True</v>
@@ -47873,82 +47795,82 @@
         <v>True</v>
       </c>
     </row>
-    <row r="225" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B225"/>
       <c r="C225" s="12" t="str">
-        <v>MethodName</v>
+        <v>HasBallParkTransformation</v>
       </c>
       <c r="D225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="E225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="F225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="G225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="H225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="I225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="J225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="K225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="L225" s="212" t="str">
-        <v/>
+        <v>False</v>
       </c>
       <c r="M225" s="219" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="2:18" x14ac:dyDescent="0.35">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="226" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B226"/>
       <c r="C226" s="12" t="str">
-        <v>Scope</v>
+        <v>HasInverse</v>
       </c>
       <c r="D226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="E226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="F226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="G226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="H226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="I226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="J226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="K226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="L226" s="212" t="str">
-        <v/>
+        <v>True</v>
       </c>
       <c r="M226" s="219" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="2:18" x14ac:dyDescent="0.35">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="227" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B227"/>
       <c r="C227" s="12" t="str">
-        <v>Remarks</v>
+        <v>MethodName</v>
       </c>
       <c r="D227" s="212" t="str">
         <v/>
@@ -47981,10 +47903,10 @@
         <v/>
       </c>
     </row>
-    <row r="228" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B228"/>
       <c r="C228" s="12" t="str">
-        <v>GridUsages</v>
+        <v>Scope</v>
       </c>
       <c r="D228" s="212" t="str">
         <v/>
@@ -48017,10 +47939,10 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B229"/>
       <c r="C229" s="12" t="str">
-        <v>Parameters</v>
+        <v>Remarks</v>
       </c>
       <c r="D229" s="212" t="str">
         <v/>
@@ -48053,1195 +47975,3370 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B230"/>
       <c r="C230" s="12" t="str">
-        <v>SourceCRS</v>
+        <v>GridUsages</v>
       </c>
       <c r="D230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="E230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="F230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="G230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="H230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="I230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="J230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="K230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="L230" s="212" t="str">
-        <v>NAD27 / Alaska Albers</v>
+        <v/>
       </c>
       <c r="M230" s="219" t="str">
-        <v>NAD27 / Alaska Albers</v>
-      </c>
-    </row>
-    <row r="231" spans="2:18" x14ac:dyDescent="0.35">
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B231"/>
       <c r="C231" s="12" t="str">
-        <v>TargetCRS</v>
+        <v>Parameters</v>
       </c>
       <c r="D231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="E231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="F231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="G231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="H231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="I231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="J231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="K231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="L231" s="212" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
+        <v/>
       </c>
       <c r="M231" s="219" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
-    </row>
-    <row r="232" spans="2:18" x14ac:dyDescent="0.35">
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B232"/>
       <c r="C232" s="12" t="str">
-        <v>Context</v>
+        <v>SourceCRS</v>
       </c>
       <c r="D232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="E232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="F232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="G232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="H232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="I232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="J232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="K232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="L232" s="212" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+        <v>NAD27 / Alaska Albers</v>
       </c>
       <c r="M232" s="219" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-    </row>
-    <row r="233" spans="2:18" x14ac:dyDescent="0.35">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+    </row>
+    <row r="233" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B233"/>
       <c r="C233" s="12" t="str">
-        <v>UsageArea.Name</v>
+        <v>TargetCRS</v>
       </c>
       <c r="D233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="E233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="F233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="G233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="H233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="I233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="J233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="K233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="L233" s="212" t="str">
-        <v>UsageArea</v>
+        <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
       <c r="M233" s="219" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="O233"/>
-    </row>
-    <row r="234" spans="2:18" x14ac:dyDescent="0.35">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="234" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B234"/>
       <c r="C234" s="12" t="str">
-        <v>UsageArea.WestLongitude</v>
+        <v>Context</v>
       </c>
       <c r="D234" s="212" t="str">
-        <v>United States (USA) - Alaska including EEZ.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="E234" s="212" t="str">
-        <v>United States (USA) - Alaska mainland.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="F234" s="212" t="str">
-        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="G234" s="212" t="str">
-        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="H234" s="212" t="str">
-        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="I234" s="212" t="str">
-        <v>Canada - Yukon.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="J234" s="212" t="str">
-        <v>Canada - Alberta; British Columbia.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="K234" s="212" t="str">
-        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="L234" s="212" t="str">
-        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="M234" s="219" t="str">
-        <v>World</v>
-      </c>
-      <c r="O234"/>
-    </row>
-    <row r="235" spans="2:18" x14ac:dyDescent="0.35">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+    </row>
+    <row r="235" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B235"/>
       <c r="C235" s="12" t="str">
-        <v>UsageArea.SouthLatitude</v>
+        <v>UsageArea.Name</v>
       </c>
       <c r="D235" s="212" t="str">
-        <v>167.65</v>
+        <v>United States (USA) - Alaska including EEZ.</v>
       </c>
       <c r="E235" s="212" t="str">
-        <v>-168.26</v>
+        <v>United States (USA) - Alaska mainland.</v>
       </c>
       <c r="F235" s="212" t="str">
-        <v>-141.01</v>
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
       </c>
       <c r="G235" s="212" t="str">
-        <v>-141.01</v>
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
       </c>
       <c r="H235" s="212" t="str">
-        <v>-136.46</v>
+        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
       </c>
       <c r="I235" s="212" t="str">
-        <v>-141.01</v>
+        <v>Canada - Yukon.</v>
       </c>
       <c r="J235" s="212" t="str">
-        <v>-139.04</v>
+        <v>Canada - Alberta; British Columbia.</v>
       </c>
       <c r="K235" s="212" t="str">
-        <v>-178.3</v>
+        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
       </c>
       <c r="L235" s="212" t="str">
-        <v>172.42</v>
+        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
       </c>
       <c r="M235" s="219" t="str">
-        <v>-180</v>
+        <v>World</v>
       </c>
       <c r="O235"/>
     </row>
-    <row r="236" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B236"/>
       <c r="C236" s="12" t="str">
-        <v>UsageArea.EastLongitude</v>
+        <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D236" s="212" t="str">
-        <v>47.88</v>
+        <v>167.65</v>
       </c>
       <c r="E236" s="212" t="str">
-        <v>54.34</v>
+        <v>-168.26</v>
       </c>
       <c r="F236" s="212" t="str">
-        <v>40</v>
+        <v>-141.01</v>
       </c>
       <c r="G236" s="212" t="str">
-        <v>40</v>
+        <v>-141.01</v>
       </c>
       <c r="H236" s="212" t="str">
-        <v>49</v>
+        <v>-136.46</v>
       </c>
       <c r="I236" s="212" t="str">
-        <v>59.99</v>
+        <v>-141.01</v>
       </c>
       <c r="J236" s="212" t="str">
-        <v>48.25</v>
+        <v>-139.04</v>
       </c>
       <c r="K236" s="212" t="str">
-        <v>51.54</v>
+        <v>-178.3</v>
       </c>
       <c r="L236" s="212" t="str">
-        <v>51.3</v>
+        <v>172.42</v>
       </c>
       <c r="M236" s="219" t="str">
-        <v>-90</v>
+        <v>-180</v>
       </c>
       <c r="O236"/>
     </row>
-    <row r="237" spans="2:18" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B237"/>
       <c r="C237" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D237" s="212" t="str">
+        <v>47.88</v>
+      </c>
+      <c r="E237" s="212" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="F237" s="212" t="str">
+        <v>40</v>
+      </c>
+      <c r="G237" s="212" t="str">
+        <v>40</v>
+      </c>
+      <c r="H237" s="212" t="str">
+        <v>49</v>
+      </c>
+      <c r="I237" s="212" t="str">
+        <v>59.99</v>
+      </c>
+      <c r="J237" s="212" t="str">
+        <v>48.25</v>
+      </c>
+      <c r="K237" s="212" t="str">
+        <v>51.54</v>
+      </c>
+      <c r="L237" s="212" t="str">
+        <v>51.3</v>
+      </c>
+      <c r="M237" s="219" t="str">
+        <v>-90</v>
+      </c>
+      <c r="O237"/>
+    </row>
+    <row r="238" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B238"/>
+      <c r="C238" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D238" s="212" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="E238" s="212" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="F238" s="212" t="str">
+        <v>-44</v>
+      </c>
+      <c r="G238" s="212" t="str">
+        <v>-44</v>
+      </c>
+      <c r="H238" s="212" t="str">
+        <v>-60.72</v>
+      </c>
+      <c r="I238" s="212" t="str">
+        <v>-123.91</v>
+      </c>
+      <c r="J238" s="212" t="str">
+        <v>-109.98</v>
+      </c>
+      <c r="K238" s="212" t="str">
+        <v>-164.84</v>
+      </c>
+      <c r="L238" s="212" t="str">
+        <v>179.86</v>
+      </c>
+      <c r="M238" s="219" t="str">
+        <v>180</v>
+      </c>
+      <c r="O238"/>
+    </row>
+    <row r="239" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B239"/>
+      <c r="C239" s="12" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D237" s="212" t="str">
-        <v>-129.99</v>
-      </c>
-      <c r="E237" s="212" t="str">
-        <v>-129.99</v>
-      </c>
-      <c r="F237" s="212" t="str">
-        <v>-44</v>
-      </c>
-      <c r="G237" s="212" t="str">
-        <v>-44</v>
-      </c>
-      <c r="H237" s="212" t="str">
-        <v>-60.72</v>
-      </c>
-      <c r="I237" s="212" t="str">
-        <v>-123.91</v>
-      </c>
-      <c r="J237" s="212" t="str">
-        <v>-109.98</v>
-      </c>
-      <c r="K237" s="212" t="str">
-        <v>-164.84</v>
-      </c>
-      <c r="L237" s="212" t="str">
-        <v>179.86</v>
-      </c>
-      <c r="M237" s="219" t="str">
-        <v>180</v>
-      </c>
-      <c r="O237"/>
-    </row>
-    <row r="238" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B238"/>
-      <c r="C238" s="13" t="str">
+      <c r="D239" s="212" t="str">
+        <v>74.71</v>
+      </c>
+      <c r="E239" s="212" t="str">
+        <v>71.4</v>
+      </c>
+      <c r="F239" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="G239" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="H239" s="212" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="I239" s="212" t="str">
+        <v>69.7</v>
+      </c>
+      <c r="J239" s="212" t="str">
+        <v>60.01</v>
+      </c>
+      <c r="K239" s="212" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="L239" s="212" t="str">
+        <v>53.07</v>
+      </c>
+      <c r="M239" s="219" t="str">
+        <v>90</v>
+      </c>
+      <c r="O239"/>
+    </row>
+    <row r="240" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B240"/>
+      <c r="C240" s="13" t="str">
         <v>UsageArea.Center</v>
       </c>
-      <c r="D238" s="213" t="str">
-        <v>74.71</v>
-      </c>
-      <c r="E238" s="213" t="str">
-        <v>71.4</v>
-      </c>
-      <c r="F238" s="213" t="str">
-        <v>83.17</v>
-      </c>
-      <c r="G238" s="213" t="str">
-        <v>83.17</v>
-      </c>
-      <c r="H238" s="213" t="str">
-        <v>83.17</v>
-      </c>
-      <c r="I238" s="213" t="str">
-        <v>69.7</v>
-      </c>
-      <c r="J238" s="213" t="str">
-        <v>60.01</v>
-      </c>
-      <c r="K238" s="213" t="str">
-        <v>54.34</v>
-      </c>
-      <c r="L238" s="213" t="str">
-        <v>53.07</v>
-      </c>
-      <c r="M238" s="220" t="str">
-        <v>90</v>
-      </c>
-      <c r="O238"/>
-    </row>
-    <row r="239" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B239"/>
-      <c r="M239"/>
-      <c r="O239"/>
-    </row>
-    <row r="240" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B240"/>
-      <c r="C240" s="237" t="str" cm="1">
-        <f t="array" ref="C240:D253">_xll.PE.trf.TransformSteps(D213,D214,C215,"proj")</f>
-        <v>Transform Identifiers</v>
-      </c>
-      <c r="D240" s="177">
+      <c r="D240" s="213" t="str">
+        <v>18.83, 61.295</v>
+      </c>
+      <c r="E240" s="213" t="str">
+        <v>-149.125, 62.87</v>
+      </c>
+      <c r="F240" s="213" t="str">
+        <v>-92.505, 61.585</v>
+      </c>
+      <c r="G240" s="213" t="str">
+        <v>-92.505, 61.585</v>
+      </c>
+      <c r="H240" s="213" t="str">
+        <v>-98.59, 66.085</v>
+      </c>
+      <c r="I240" s="213" t="str">
+        <v>-132.46, 64.845</v>
+      </c>
+      <c r="J240" s="213" t="str">
+        <v>-124.51, 54.13</v>
+      </c>
+      <c r="K240" s="213" t="str">
+        <v>-171.57, 52.94</v>
+      </c>
+      <c r="L240" s="213" t="str">
+        <v>176.14, 52.185</v>
+      </c>
+      <c r="M240" s="220" t="str">
+        <v>0, 0</v>
+      </c>
+      <c r="O240"/>
+    </row>
+    <row r="241" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B241"/>
+      <c r="M241"/>
+      <c r="O241"/>
+    </row>
+    <row r="242" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B242"/>
+      <c r="C242" s="251" t="str" cm="1">
+        <f t="array" ref="C242:D256">_xll.PE.trf.TransformSteps(D215,D216,C217,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D242" s="5">
         <v>0</v>
       </c>
-      <c r="F240" t="str">
-        <f>D217</f>
+      <c r="F242" t="str">
+        <f>D219</f>
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
       </c>
-      <c r="K240" s="182" t="str" cm="1">
-        <f t="array" ref="K240:O250">_xll.PE.xfm.ListTransformPipelines(D213,D214)</f>
+      <c r="K242" s="182" t="str" cm="1">
+        <f t="array" ref="K242:O252">_xll.PE.xfm.ListTransformPipelines(D215,D216)</f>
         <v>PipelineID</v>
       </c>
-      <c r="L240" s="183" t="str">
+      <c r="L242" s="183" t="str">
         <v>Name</v>
       </c>
-      <c r="M240" s="183" t="str">
+      <c r="M242" s="183" t="str">
         <v>Accuracy(m)</v>
       </c>
-      <c r="N240" s="183" t="str">
+      <c r="N242" s="183" t="str">
         <v>Grids</v>
       </c>
-      <c r="O240" s="184" t="str">
+      <c r="O242" s="184" t="str">
         <v>IsAvailable</v>
-      </c>
-      <c r="R240" s="61"/>
-    </row>
-    <row r="241" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B241"/>
-      <c r="C241" s="238" t="str">
-        <v>Transform Name</v>
-      </c>
-      <c r="D241" s="179" t="str">
-        <v>&lt;choose-coordinate-transform&gt;</v>
-      </c>
-      <c r="F241" t="str">
-        <f>E217</f>
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
-      </c>
-      <c r="K241" s="248">
-        <v>1</v>
-      </c>
-      <c r="L241" s="249" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85)</v>
-      </c>
-      <c r="M241" s="249">
-        <v>5</v>
-      </c>
-      <c r="N241" s="249" t="str">
-        <v/>
-      </c>
-      <c r="O241" s="250" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="R241" s="61"/>
-    </row>
-    <row r="242" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B242"/>
-      <c r="C242" s="238" t="str">
-        <v>Accuracy [m]</v>
-      </c>
-      <c r="D242" s="179">
-        <v>0</v>
-      </c>
-      <c r="F242" t="str">
-        <f>F217</f>
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
-      </c>
-      <c r="K242" s="198">
-        <v>2</v>
-      </c>
-      <c r="L242" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7)</v>
-      </c>
-      <c r="M242" s="251">
-        <v>12</v>
-      </c>
-      <c r="N242" s="251" t="str">
-        <v/>
-      </c>
-      <c r="O242" s="245" t="str">
-        <v>TRUE</v>
       </c>
       <c r="R242" s="61"/>
     </row>
     <row r="243" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B243"/>
-      <c r="C243" s="238" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="D243" s="179" t="str">
-        <v>United States (USA) - Alaska including EEZ.</v>
+      <c r="C243" s="235" t="str">
+        <v>Step Identifiers</v>
+      </c>
+      <c r="D243" s="179">
+        <v>0</v>
       </c>
       <c r="F243" t="str">
-        <f>G217</f>
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
-      </c>
-      <c r="K243" s="198">
-        <v>3</v>
-      </c>
-      <c r="L243" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33)</v>
-      </c>
-      <c r="M243" s="251">
-        <v>2</v>
-      </c>
-      <c r="N243" s="251" t="str">
+        <f>E219</f>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
+      </c>
+      <c r="K243" s="244">
+        <v>1</v>
+      </c>
+      <c r="L243" s="245" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85)</v>
+      </c>
+      <c r="M243" s="245">
+        <v>5</v>
+      </c>
+      <c r="N243" s="245" t="str">
         <v/>
       </c>
-      <c r="O243" s="245" t="str">
+      <c r="O243" s="246" t="str">
         <v>TRUE</v>
       </c>
       <c r="R243" s="61"/>
     </row>
     <row r="244" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B244"/>
-      <c r="C244" s="238" t="str">
-        <v>Scope</v>
+      <c r="C244" s="235" t="str">
+        <v>Step Name</v>
       </c>
       <c r="D244" s="179" t="str">
-        <v>Unknown</v>
+        <v>&lt;choose-coordinate-transform&gt;</v>
       </c>
       <c r="F244" t="str">
-        <f>H217</f>
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
+        <f>F219</f>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
       </c>
       <c r="K244" s="198">
-        <v>4</v>
-      </c>
-      <c r="L244" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3)</v>
-      </c>
-      <c r="M244" s="251">
-        <v>20</v>
-      </c>
-      <c r="N244" s="251" t="str">
+        <v>2</v>
+      </c>
+      <c r="L244" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7)</v>
+      </c>
+      <c r="M244">
+        <v>12</v>
+      </c>
+      <c r="N244" t="str">
         <v/>
       </c>
-      <c r="O244" s="245" t="str">
+      <c r="O244" s="241" t="str">
         <v>TRUE</v>
       </c>
       <c r="R244" s="61"/>
     </row>
     <row r="245" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B245"/>
-      <c r="C245" s="238" t="str">
-        <v>Remarks</v>
-      </c>
-      <c r="D245" s="179" t="str">
-        <v>None</v>
+      <c r="C245" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D245" s="179">
+        <v>0</v>
+      </c>
+      <c r="F245" t="str">
+        <f>G219</f>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
       </c>
       <c r="K245" s="198">
-        <v>5</v>
-      </c>
-      <c r="L245" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13)</v>
-      </c>
-      <c r="M245" s="251">
-        <v>8</v>
-      </c>
-      <c r="N245" s="251" t="str">
+        <v>3</v>
+      </c>
+      <c r="L245" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33)</v>
+      </c>
+      <c r="M245">
+        <v>2</v>
+      </c>
+      <c r="N245" t="str">
         <v/>
       </c>
-      <c r="O245" s="245" t="str">
+      <c r="O245" s="241" t="str">
         <v>TRUE</v>
       </c>
-      <c r="P245" s="1"/>
       <c r="R245" s="61"/>
     </row>
     <row r="246" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B246"/>
-      <c r="C246" s="238" t="str">
-        <v>UsageArea.WestLongitude</v>
-      </c>
-      <c r="D246" s="179">
-        <v>167.65</v>
+      <c r="C246" s="235" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D246" s="179" t="str">
+        <v>United States (USA) - Alaska including EEZ.</v>
+      </c>
+      <c r="F246" t="str">
+        <f>H219</f>
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
       </c>
       <c r="K246" s="198">
-        <v>6</v>
-      </c>
-      <c r="L246" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14)</v>
-      </c>
-      <c r="M246" s="251">
-        <v>10</v>
-      </c>
-      <c r="N246" s="251" t="str">
+        <v>4</v>
+      </c>
+      <c r="L246" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3)</v>
+      </c>
+      <c r="M246">
+        <v>20</v>
+      </c>
+      <c r="N246" t="str">
         <v/>
       </c>
-      <c r="O246" s="245" t="str">
+      <c r="O246" s="241" t="str">
         <v>TRUE</v>
       </c>
-      <c r="P246" s="1"/>
       <c r="R246" s="61"/>
     </row>
     <row r="247" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B247"/>
-      <c r="C247" s="238" t="str">
-        <v>UsageArea.SouthLatitude</v>
-      </c>
-      <c r="D247" s="179">
-        <v>-129.99</v>
+      <c r="C247" s="235" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D247" s="179" t="str">
+        <v>Unknown</v>
       </c>
       <c r="K247" s="198">
-        <v>7</v>
-      </c>
-      <c r="L247" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10)</v>
-      </c>
-      <c r="M247" s="252">
-        <v>13</v>
-      </c>
-      <c r="N247" s="251" t="str">
+        <v>5</v>
+      </c>
+      <c r="L247" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13)</v>
+      </c>
+      <c r="M247">
+        <v>8</v>
+      </c>
+      <c r="N247" t="str">
         <v/>
       </c>
-      <c r="O247" s="245" t="str">
+      <c r="O247" s="241" t="str">
         <v>TRUE</v>
       </c>
+      <c r="P247" s="1"/>
+      <c r="R247" s="61"/>
     </row>
     <row r="248" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B248"/>
-      <c r="C248" s="238" t="str">
-        <v>UsageArea.EastLongitude</v>
-      </c>
-      <c r="D248" s="179">
-        <v>47.88</v>
+      <c r="C248" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D248" s="179" t="str">
+        <v>None</v>
       </c>
       <c r="K248" s="198">
-        <v>8</v>
-      </c>
-      <c r="L248" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21)</v>
-      </c>
-      <c r="M248" s="252">
-        <v>15</v>
-      </c>
-      <c r="N248" s="251" t="str">
+        <v>6</v>
+      </c>
+      <c r="L248" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14)</v>
+      </c>
+      <c r="M248">
+        <v>10</v>
+      </c>
+      <c r="N248" t="str">
         <v/>
       </c>
-      <c r="O248" s="245" t="str">
+      <c r="O248" s="241" t="str">
         <v>TRUE</v>
       </c>
+      <c r="P248" s="1"/>
+      <c r="R248" s="61"/>
     </row>
     <row r="249" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B249"/>
-      <c r="C249" s="238" t="str">
+      <c r="C249" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D249" s="179">
+        <v>167.65</v>
+      </c>
+      <c r="K249" s="198">
+        <v>7</v>
+      </c>
+      <c r="L249" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10)</v>
+      </c>
+      <c r="M249" s="1">
+        <v>13</v>
+      </c>
+      <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" s="241" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="250" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B250"/>
+      <c r="C250" s="235" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D250" s="179">
+        <v>-129.99</v>
+      </c>
+      <c r="K250" s="198">
+        <v>8</v>
+      </c>
+      <c r="L250" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21)</v>
+      </c>
+      <c r="M250" s="1">
+        <v>15</v>
+      </c>
+      <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" s="241" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="251" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B251"/>
+      <c r="C251" s="235" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D251" s="179">
+        <v>47.88</v>
+      </c>
+      <c r="K251" s="198">
+        <v>9</v>
+      </c>
+      <c r="L251" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22)</v>
+      </c>
+      <c r="M251" s="1">
+        <v>18</v>
+      </c>
+      <c r="N251" t="str">
+        <v/>
+      </c>
+      <c r="O251" s="241" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="252" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C252" s="235" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D249" s="179">
+      <c r="D252" s="179">
         <v>74.709999999999994</v>
       </c>
-      <c r="K249" s="198">
-        <v>9</v>
-      </c>
-      <c r="L249" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22)</v>
-      </c>
-      <c r="M249" s="252">
-        <v>18</v>
-      </c>
-      <c r="N249" s="251" t="str">
+      <c r="K252" s="200">
+        <v>10</v>
+      </c>
+      <c r="L252" s="201" t="str">
+        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84</v>
+      </c>
+      <c r="M252" s="243" t="str">
         <v/>
       </c>
-      <c r="O249" s="245" t="str">
+      <c r="N252" s="201" t="str">
+        <v/>
+      </c>
+      <c r="O252" s="242" t="str">
         <v>TRUE</v>
       </c>
     </row>
-    <row r="250" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C250" s="238" t="str">
+    <row r="253" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C253" s="235" t="str">
         <v>Nr grids</v>
       </c>
-      <c r="D250" s="179">
+      <c r="D253" s="179">
         <v>1</v>
       </c>
-      <c r="K250" s="200">
+    </row>
+    <row r="254" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C254" s="235" t="str">
+        <v>1st grid</v>
+      </c>
+      <c r="D254" s="179" t="str">
+        <v/>
+      </c>
+      <c r="K254" s="182" t="str" cm="1">
+        <f t="array" ref="K254:T264">_xll.PE.trf.ListTransformOptions(D215,D216)</f>
+        <v>CandidateIndex</v>
+      </c>
+      <c r="L254" s="183" t="str">
+        <v>DefaultSelection</v>
+      </c>
+      <c r="M254" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="N254" s="183" t="str">
+        <v>Type</v>
+      </c>
+      <c r="O254" s="183" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="P254" s="183" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="Q254" s="183" t="str">
+        <v>HasBallPark</v>
+      </c>
+      <c r="R254" s="183" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="S254" s="203" t="str">
+        <v>Pros</v>
+      </c>
+      <c r="T254" s="184" t="str">
+        <v>Cons</v>
+      </c>
+    </row>
+    <row r="255" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C255" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D255" s="179" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="K255" s="244">
+        <v>0</v>
+      </c>
+      <c r="L255" s="245" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M255" s="245" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
+      </c>
+      <c r="N255" s="245" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O255" s="247">
+        <v>2</v>
+      </c>
+      <c r="P255" s="245" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q255" s="245" t="b">
+        <v>0</v>
+      </c>
+      <c r="R255" s="245" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="S255" s="248" t="str">
+        <v>Available; Non-ballpark; Accuracy=2; Has usage area; Default selection</v>
+      </c>
+      <c r="T255" s="249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C256" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D256" s="181">
+        <v>0</v>
+      </c>
+      <c r="K256" s="198">
+        <v>1</v>
+      </c>
+      <c r="L256" t="str">
+        <v>No</v>
+      </c>
+      <c r="M256" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
+      </c>
+      <c r="N256" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O256" s="1">
+        <v>5</v>
+      </c>
+      <c r="P256" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q256" t="b">
+        <v>0</v>
+      </c>
+      <c r="R256" t="str">
+        <v>United States (USA) - Alaska including EEZ.</v>
+      </c>
+      <c r="S256" s="237" t="str">
+        <v>Available; Non-ballpark; Accuracy=5; Has usage area</v>
+      </c>
+      <c r="T256" s="238" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="257" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K257" s="198">
+        <v>2</v>
+      </c>
+      <c r="L257" t="str">
+        <v>No</v>
+      </c>
+      <c r="M257" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
+      </c>
+      <c r="N257" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O257" s="1">
+        <v>8</v>
+      </c>
+      <c r="P257" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q257" t="b">
+        <v>0</v>
+      </c>
+      <c r="R257" t="str">
+        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
+      </c>
+      <c r="S257" s="237" t="str">
+        <v>Available; Non-ballpark; Accuracy=8; Has usage area</v>
+      </c>
+      <c r="T257" s="238" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="258" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K258" s="198">
+        <v>3</v>
+      </c>
+      <c r="L258" t="str">
+        <v>No</v>
+      </c>
+      <c r="M258" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
+      </c>
+      <c r="N258" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O258" s="1">
         <v>10</v>
       </c>
-      <c r="L250" s="201" t="str">
-        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84</v>
-      </c>
-      <c r="M250" s="247" t="str">
-        <v/>
-      </c>
-      <c r="N250" s="201" t="str">
-        <v/>
-      </c>
-      <c r="O250" s="246" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="251" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C251" s="238" t="str">
-        <v>1st grid</v>
-      </c>
-      <c r="D251" s="179" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C252" s="238" t="str">
-        <v>2nd grid</v>
-      </c>
-      <c r="D252" s="179" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="K252" s="182" t="str" cm="1">
-        <f t="array" ref="K252:T262">_xll.PE.trf.ListTransformOptions(D213,D214)</f>
-        <v>CandidateIndex</v>
-      </c>
-      <c r="L252" s="183" t="str">
-        <v>DefaultSelection</v>
-      </c>
-      <c r="M252" s="183" t="str">
-        <v>Name</v>
-      </c>
-      <c r="N252" s="183" t="str">
-        <v>Type</v>
-      </c>
-      <c r="O252" s="183" t="str">
-        <v>Accuracy</v>
-      </c>
-      <c r="P252" s="183" t="str">
-        <v>IsAvailable</v>
-      </c>
-      <c r="Q252" s="183" t="str">
-        <v>HasBallPark</v>
-      </c>
-      <c r="R252" s="183" t="str">
-        <v>UsageArea</v>
-      </c>
-      <c r="S252" s="203" t="str">
-        <v>Pros</v>
-      </c>
-      <c r="T252" s="184" t="str">
-        <v>Cons</v>
-      </c>
-    </row>
-    <row r="253" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C253" s="239" t="str">
-        <v>Transform PROJ string</v>
-      </c>
-      <c r="D253" s="181">
+      <c r="P258" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q258" t="b">
         <v>0</v>
       </c>
-      <c r="K253" s="248">
-        <v>0</v>
-      </c>
-      <c r="L253" s="249" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="M253" s="249" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
-      </c>
-      <c r="N253" s="249" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O253" s="253">
-        <v>2</v>
-      </c>
-      <c r="P253" s="249" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q253" s="249" t="b">
-        <v>0</v>
-      </c>
-      <c r="R253" s="249" t="str">
-        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
-      </c>
-      <c r="S253" s="254" t="str">
-        <v>Available; Non-ballpark; Accuracy=2; Has usage area; Default selection</v>
-      </c>
-      <c r="T253" s="255" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="K254" s="198">
-        <v>1</v>
-      </c>
-      <c r="L254" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M254" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
-      </c>
-      <c r="N254" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O254" s="252">
-        <v>5</v>
-      </c>
-      <c r="P254" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q254" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R254" s="251" t="str">
-        <v>United States (USA) - Alaska including EEZ.</v>
-      </c>
-      <c r="S254" s="256" t="str">
-        <v>Available; Non-ballpark; Accuracy=5; Has usage area</v>
-      </c>
-      <c r="T254" s="241" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="255" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="K255" s="198">
-        <v>2</v>
-      </c>
-      <c r="L255" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M255" s="251" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
-      </c>
-      <c r="N255" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O255" s="252">
-        <v>8</v>
-      </c>
-      <c r="P255" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q255" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R255" s="251" t="str">
-        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
-      </c>
-      <c r="S255" s="256" t="str">
-        <v>Available; Non-ballpark; Accuracy=8; Has usage area</v>
-      </c>
-      <c r="T255" s="241" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="256" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="K256" s="198">
-        <v>3</v>
-      </c>
-      <c r="L256" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M256" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
-      </c>
-      <c r="N256" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O256" s="252">
-        <v>10</v>
-      </c>
-      <c r="P256" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q256" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R256" s="251" t="str">
+      <c r="R258" t="str">
         <v>Canada - Yukon.</v>
       </c>
-      <c r="S256" s="251" t="str">
+      <c r="S258" t="str">
         <v>Available; Non-ballpark; Accuracy=10; Has usage area</v>
-      </c>
-      <c r="T256" s="199" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="257" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="K257" s="198">
-        <v>4</v>
-      </c>
-      <c r="L257" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M257" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
-      </c>
-      <c r="N257" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O257" s="252">
-        <v>12</v>
-      </c>
-      <c r="P257" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q257" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R257" s="251" t="str">
-        <v>United States (USA) - Alaska mainland.</v>
-      </c>
-      <c r="S257" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=12; Has usage area</v>
-      </c>
-      <c r="T257" s="199" t="str">
-        <v>Alternate candidate</v>
-      </c>
-    </row>
-    <row r="258" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="K258" s="198">
-        <v>5</v>
-      </c>
-      <c r="L258" s="251" t="str">
-        <v>No</v>
-      </c>
-      <c r="M258" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
-      </c>
-      <c r="N258" s="251" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="O258" s="252">
-        <v>13</v>
-      </c>
-      <c r="P258" s="251" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q258" s="251" t="b">
-        <v>0</v>
-      </c>
-      <c r="R258" s="251" t="str">
-        <v>Canada - Alberta; British Columbia.</v>
-      </c>
-      <c r="S258" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=13; Has usage area</v>
       </c>
       <c r="T258" s="199" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="259" spans="10:20" x14ac:dyDescent="0.35">
+    <row r="259" spans="3:20" x14ac:dyDescent="0.35">
       <c r="K259" s="198">
-        <v>6</v>
-      </c>
-      <c r="L259" s="251" t="str">
+        <v>4</v>
+      </c>
+      <c r="L259" t="str">
         <v>No</v>
       </c>
-      <c r="M259" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
-      </c>
-      <c r="N259" s="251" t="str">
+      <c r="M259" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
+      </c>
+      <c r="N259" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O259" s="252">
-        <v>15</v>
-      </c>
-      <c r="P259" s="251" t="b">
+      <c r="O259" s="1">
+        <v>12</v>
+      </c>
+      <c r="P259" t="b">
         <v>1</v>
       </c>
-      <c r="Q259" s="251" t="b">
+      <c r="Q259" t="b">
         <v>0</v>
       </c>
-      <c r="R259" s="251" t="str">
-        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
-      </c>
-      <c r="S259" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=15; Has usage area</v>
+      <c r="R259" t="str">
+        <v>United States (USA) - Alaska mainland.</v>
+      </c>
+      <c r="S259" t="str">
+        <v>Available; Non-ballpark; Accuracy=12; Has usage area</v>
       </c>
       <c r="T259" s="199" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="260" spans="10:20" x14ac:dyDescent="0.35">
+    <row r="260" spans="3:20" x14ac:dyDescent="0.35">
       <c r="K260" s="198">
-        <v>7</v>
-      </c>
-      <c r="L260" s="251" t="str">
+        <v>5</v>
+      </c>
+      <c r="L260" t="str">
         <v>No</v>
       </c>
-      <c r="M260" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
-      </c>
-      <c r="N260" s="251" t="str">
+      <c r="M260" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
+      </c>
+      <c r="N260" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O260" s="252">
-        <v>18</v>
-      </c>
-      <c r="P260" s="251" t="b">
+      <c r="O260" s="1">
+        <v>13</v>
+      </c>
+      <c r="P260" t="b">
         <v>1</v>
       </c>
-      <c r="Q260" s="251" t="b">
+      <c r="Q260" t="b">
         <v>0</v>
       </c>
-      <c r="R260" s="251" t="str">
-        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
-      </c>
-      <c r="S260" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=18; Has usage area</v>
+      <c r="R260" t="str">
+        <v>Canada - Alberta; British Columbia.</v>
+      </c>
+      <c r="S260" t="str">
+        <v>Available; Non-ballpark; Accuracy=13; Has usage area</v>
       </c>
       <c r="T260" s="199" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="261" spans="10:20" x14ac:dyDescent="0.35">
+    <row r="261" spans="3:20" x14ac:dyDescent="0.35">
       <c r="K261" s="198">
-        <v>8</v>
-      </c>
-      <c r="L261" s="251" t="str">
+        <v>6</v>
+      </c>
+      <c r="L261" t="str">
         <v>No</v>
       </c>
-      <c r="M261" s="252" t="str">
-        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
-      </c>
-      <c r="N261" s="251" t="str">
+      <c r="M261" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
+      </c>
+      <c r="N261" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O261" s="252">
-        <v>20</v>
-      </c>
-      <c r="P261" s="251" t="b">
+      <c r="O261" s="1">
+        <v>15</v>
+      </c>
+      <c r="P261" t="b">
         <v>1</v>
       </c>
-      <c r="Q261" s="251" t="b">
+      <c r="Q261" t="b">
         <v>0</v>
       </c>
-      <c r="R261" s="251" t="str">
-        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
-      </c>
-      <c r="S261" s="251" t="str">
-        <v>Available; Non-ballpark; Accuracy=20; Has usage area</v>
+      <c r="R261" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
+      </c>
+      <c r="S261" t="str">
+        <v>Available; Non-ballpark; Accuracy=15; Has usage area</v>
       </c>
       <c r="T261" s="199" t="str">
         <v>Alternate candidate</v>
       </c>
     </row>
-    <row r="262" spans="10:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J262" t="s">
+    <row r="262" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K262" s="198">
+        <v>7</v>
+      </c>
+      <c r="L262" t="str">
+        <v>No</v>
+      </c>
+      <c r="M262" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
+      </c>
+      <c r="N262" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O262" s="1">
+        <v>18</v>
+      </c>
+      <c r="P262" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q262" t="b">
         <v>0</v>
       </c>
-      <c r="K262" s="200">
+      <c r="R262" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
+      </c>
+      <c r="S262" t="str">
+        <v>Available; Non-ballpark; Accuracy=18; Has usage area</v>
+      </c>
+      <c r="T262" s="199" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="263" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="K263" s="198">
+        <v>8</v>
+      </c>
+      <c r="L263" t="str">
+        <v>No</v>
+      </c>
+      <c r="M263" s="1" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
+      </c>
+      <c r="N263" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="O263" s="1">
+        <v>20</v>
+      </c>
+      <c r="P263" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q263" t="b">
+        <v>0</v>
+      </c>
+      <c r="R263" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="S263" t="str">
+        <v>Available; Non-ballpark; Accuracy=20; Has usage area</v>
+      </c>
+      <c r="T263" s="199" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="264" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J264" t="s">
+        <v>0</v>
+      </c>
+      <c r="K264" s="200">
         <v>9</v>
       </c>
-      <c r="L262" s="201" t="str">
+      <c r="L264" s="201" t="str">
         <v>No</v>
       </c>
-      <c r="M262" s="247" t="str">
+      <c r="M264" s="243" t="str">
         <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="N262" s="201" t="str">
+      <c r="N264" s="201" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="O262" s="247">
+      <c r="O264" s="243">
         <v>0</v>
       </c>
-      <c r="P262" s="201" t="b">
+      <c r="P264" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q262" s="201" t="b">
+      <c r="Q264" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="R262" s="201" t="str">
+      <c r="R264" s="201" t="str">
         <v>World</v>
       </c>
-      <c r="S262" s="201" t="str">
+      <c r="S264" s="201" t="str">
         <v>Available; Has usage area</v>
       </c>
-      <c r="T262" s="202" t="str">
+      <c r="T264" s="202" t="str">
         <v>Ballpark transformation; No reported accuracy; Alternate candidate</v>
       </c>
     </row>
-    <row r="267" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="O267"/>
-    </row>
-    <row r="268" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="O268"/>
-    </row>
-    <row r="269" spans="10:20" x14ac:dyDescent="0.35">
-      <c r="O269"/>
-    </row>
-    <row r="270" spans="10:20" x14ac:dyDescent="0.35">
+    <row r="266" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="267" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C267" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D267" s="210">
+        <v>25832</v>
+      </c>
+      <c r="K267" s="61"/>
+      <c r="M267"/>
+    </row>
+    <row r="268" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C268" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D268" s="211">
+        <v>25833</v>
+      </c>
+      <c r="K268" s="61"/>
+      <c r="M268"/>
+    </row>
+    <row r="269" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C269" s="182" t="str" cm="1">
+        <f t="array" ref="C269">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D269" s="183"/>
+      <c r="E269" s="183"/>
+      <c r="F269" s="183"/>
+      <c r="G269" s="183"/>
+      <c r="H269" s="183"/>
+      <c r="I269" s="183"/>
+      <c r="J269" s="183"/>
+      <c r="K269" s="183"/>
+      <c r="L269" s="183"/>
+      <c r="M269" s="183"/>
+      <c r="N269" s="183"/>
+      <c r="O269" s="184"/>
+      <c r="P269" s="184"/>
+    </row>
+    <row r="270" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C270" s="223" t="str" cm="1">
+        <f t="array" ref="C270:D292">_xll.PE.trf.TransformList(D267,D268,,"")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D270" s="5">
+        <v>0</v>
+      </c>
       <c r="M270"/>
-      <c r="O270"/>
-    </row>
-    <row r="271" spans="10:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="271" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C271" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D271" s="219" t="str">
+        <v>Inverse of UTM zone 32N + UTM zone 33N</v>
+      </c>
       <c r="M271"/>
-      <c r="O271"/>
-    </row>
-    <row r="272" spans="10:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="272" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C272" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D272" s="219" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
       <c r="M272"/>
-      <c r="O272"/>
-    </row>
-    <row r="273" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="273" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C273" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D273" s="219" t="str">
+        <v/>
+      </c>
       <c r="M273"/>
-      <c r="O273"/>
-    </row>
-    <row r="274" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="274" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C274" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D274" s="219" t="str">
+        <v/>
+      </c>
       <c r="M274"/>
-      <c r="O274"/>
-    </row>
-    <row r="275" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="275" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C275" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D275" s="219" t="str">
+        <v>0</v>
+      </c>
       <c r="M275"/>
-      <c r="O275"/>
-    </row>
-    <row r="276" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="276" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C276" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D276" s="219" t="str">
+        <v>True</v>
+      </c>
       <c r="M276"/>
-      <c r="O276"/>
-    </row>
-    <row r="277" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="277" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C277" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D277" s="219" t="str">
+        <v>False</v>
+      </c>
       <c r="M277"/>
-      <c r="O277"/>
-    </row>
-    <row r="278" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="278" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C278" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D278" s="219" t="str">
+        <v>True</v>
+      </c>
       <c r="M278"/>
-      <c r="O278"/>
-    </row>
-    <row r="279" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="279" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C279" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D279" s="219" t="str">
+        <v/>
+      </c>
       <c r="M279"/>
-      <c r="O279"/>
-    </row>
-    <row r="280" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="280" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C280" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D280" s="219" t="str">
+        <v/>
+      </c>
       <c r="M280"/>
-      <c r="O280"/>
-    </row>
-    <row r="281" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="281" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C281" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D281" s="219" t="str">
+        <v/>
+      </c>
       <c r="M281"/>
-      <c r="O281"/>
-    </row>
-    <row r="282" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="282" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C282" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D282" s="219" t="str">
+        <v/>
+      </c>
       <c r="M282"/>
-      <c r="O282"/>
-    </row>
-    <row r="283" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="283" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C283" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D283" s="219" t="str">
+        <v/>
+      </c>
       <c r="M283"/>
-      <c r="O283"/>
-    </row>
-    <row r="284" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="284" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C284" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D284" s="219" t="str">
+        <v>ETRS89 / UTM zone 32N</v>
+      </c>
       <c r="M284"/>
-      <c r="O284"/>
-    </row>
-    <row r="285" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="285" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C285" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D285" s="219" t="str">
+        <v>ETRS89 / UTM zone 33N</v>
+      </c>
       <c r="M285"/>
-      <c r="O285"/>
-    </row>
-    <row r="286" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="286" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C286" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D286" s="219" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
       <c r="M286"/>
-      <c r="O286"/>
-    </row>
-    <row r="287" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="287" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C287" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D287" s="219" t="str">
+        <v>World</v>
+      </c>
       <c r="M287"/>
-      <c r="O287"/>
-    </row>
-    <row r="288" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="288" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C288" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D288" s="219" t="str">
+        <v>-180</v>
+      </c>
       <c r="M288"/>
-      <c r="O288"/>
-    </row>
-    <row r="289" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="289" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C289" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D289" s="219" t="str">
+        <v>-90</v>
+      </c>
       <c r="M289"/>
-      <c r="O289"/>
-    </row>
-    <row r="290" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="290" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C290" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D290" s="219" t="str">
+        <v>180</v>
+      </c>
       <c r="M290"/>
-      <c r="O290"/>
-    </row>
-    <row r="291" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C291" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D291" s="219" t="str">
+        <v>90</v>
+      </c>
       <c r="M291"/>
-      <c r="O291"/>
-    </row>
-    <row r="292" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C292" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D292" s="220" t="str">
+        <v>0, 0</v>
+      </c>
+      <c r="I292" t="str">
+        <f>I295</f>
+        <v>Inverse of UTM zone 32N</v>
+      </c>
       <c r="M292"/>
-      <c r="O292"/>
-    </row>
-    <row r="293" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="293" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I293" t="str">
+        <f>I296</f>
+        <v>UTM zone 33N</v>
+      </c>
       <c r="M293"/>
-      <c r="O293"/>
-    </row>
-    <row r="294" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="294" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C294" s="251" t="str" cm="1">
+        <f t="array" ref="C294:E308">_xll.PE.trf.TransformSteps(D267,D268,,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D294" s="4">
+        <v>0</v>
+      </c>
+      <c r="E294" s="5">
+        <v>1</v>
+      </c>
+      <c r="H294" s="182" t="str" cm="1">
+        <f t="array" ref="H294:L296">_xll.PE.xfm.ListTransformPipelines(D267,D268)</f>
+        <v>PipelineID</v>
+      </c>
+      <c r="I294" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="J294" s="183" t="str">
+        <v>Accuracy(m)</v>
+      </c>
+      <c r="K294" s="183" t="str">
+        <v>Grids</v>
+      </c>
+      <c r="L294" s="184" t="str">
+        <v>IsAvailable</v>
+      </c>
       <c r="M294"/>
-      <c r="O294"/>
-    </row>
-    <row r="295" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="295" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C295" s="235" t="str">
+        <v>Step Identifiers</v>
+      </c>
+      <c r="D295" s="178" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E295" s="179" t="str">
+        <v>EPSG</v>
+      </c>
+      <c r="H295" s="244">
+        <v>1</v>
+      </c>
+      <c r="I295" s="245" t="str">
+        <v>Inverse of UTM zone 32N</v>
+      </c>
+      <c r="J295" s="245" t="str">
+        <v/>
+      </c>
+      <c r="K295" s="245" t="str">
+        <v/>
+      </c>
+      <c r="L295" s="250" t="str">
+        <v>TRUE</v>
+      </c>
       <c r="M295"/>
-      <c r="O295"/>
-    </row>
-    <row r="296" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="296" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C296" s="235" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="D296" s="178" t="str">
+        <v>Inverse of UTM zone 32N</v>
+      </c>
+      <c r="E296" s="179" t="str">
+        <v>UTM zone 33N</v>
+      </c>
+      <c r="H296" s="200">
+        <v>2</v>
+      </c>
+      <c r="I296" s="201" t="str">
+        <v>UTM zone 33N</v>
+      </c>
+      <c r="J296" s="201" t="str">
+        <v/>
+      </c>
+      <c r="K296" s="201" t="str">
+        <v/>
+      </c>
+      <c r="L296" s="202" t="str">
+        <v>TRUE</v>
+      </c>
       <c r="M296"/>
-      <c r="O296"/>
-    </row>
-    <row r="297" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="297" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C297" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D297" s="178">
+        <v>0</v>
+      </c>
+      <c r="E297" s="179">
+        <v>0</v>
+      </c>
       <c r="M297"/>
-      <c r="O297"/>
-    </row>
-    <row r="298" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="298" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C298" s="235" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D298" s="178" t="str">
+        <v>Between 6°E and 12°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
+      <c r="E298" s="179" t="str">
+        <v>Between 12°E and 18°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
       <c r="M298"/>
-      <c r="O298"/>
-    </row>
-    <row r="299" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="299" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C299" s="235" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D299" s="178" t="str">
+        <v>Engineering survey, topographic mapping.</v>
+      </c>
+      <c r="E299" s="179" t="str">
+        <v>Engineering survey, topographic mapping.</v>
+      </c>
       <c r="M299"/>
-      <c r="O299"/>
-    </row>
-    <row r="300" spans="13:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="300" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C300" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D300" s="178" t="str">
+        <v>None</v>
+      </c>
+      <c r="E300" s="179" t="str">
+        <v>None</v>
+      </c>
+      <c r="J300" t="str">
+        <f>J303</f>
+        <v>Inverse of UTM zone 32N</v>
+      </c>
       <c r="M300"/>
-      <c r="O300"/>
-    </row>
-    <row r="301" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="O300" t="str">
+        <f>O303</f>
+        <v>Between 6°E and 12°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
+    </row>
+    <row r="301" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C301" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D301" s="178">
+        <v>6</v>
+      </c>
+      <c r="E301" s="179">
+        <v>12</v>
+      </c>
+      <c r="J301" t="str">
+        <f>J304</f>
+        <v>UTM zone 33N</v>
+      </c>
+      <c r="L301" s="61"/>
       <c r="M301"/>
-      <c r="O301"/>
-    </row>
-    <row r="302" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M302"/>
-      <c r="O302"/>
-    </row>
-    <row r="303" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M303"/>
-      <c r="O303"/>
-    </row>
-    <row r="304" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M304"/>
-      <c r="O304"/>
-    </row>
-    <row r="305" spans="13:15" x14ac:dyDescent="0.35">
+      <c r="O301" t="str">
+        <f>O304</f>
+        <v>Between 12°E and 18°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
+    </row>
+    <row r="302" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C302" s="235" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D302" s="178">
+        <v>12</v>
+      </c>
+      <c r="E302" s="179">
+        <v>18</v>
+      </c>
+      <c r="H302" s="182" t="str" cm="1">
+        <f t="array" ref="H302:Q304">_xll.PE.trf.ListTransformOptions(D267,D268)</f>
+        <v>CandidateIndex</v>
+      </c>
+      <c r="I302" s="183" t="str">
+        <v>DefaultSelection</v>
+      </c>
+      <c r="J302" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="K302" s="183" t="str">
+        <v>Type</v>
+      </c>
+      <c r="L302" s="183" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="M302" s="183" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="N302" s="183" t="str">
+        <v>HasBallPark</v>
+      </c>
+      <c r="O302" s="183" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="P302" s="203" t="str">
+        <v>Pros</v>
+      </c>
+      <c r="Q302" s="184" t="str">
+        <v>Cons</v>
+      </c>
+    </row>
+    <row r="303" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C303" s="235" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D303" s="178">
+        <v>0</v>
+      </c>
+      <c r="E303" s="179">
+        <v>0</v>
+      </c>
+      <c r="H303" s="244">
+        <v>0</v>
+      </c>
+      <c r="I303" s="245" t="str">
+        <v>Only</v>
+      </c>
+      <c r="J303" s="245" t="str">
+        <v>Inverse of UTM zone 32N</v>
+      </c>
+      <c r="K303" s="245" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="L303" s="245">
+        <v>0</v>
+      </c>
+      <c r="M303" s="245" t="b">
+        <v>1</v>
+      </c>
+      <c r="N303" s="245" t="b">
+        <v>0</v>
+      </c>
+      <c r="O303" s="245" t="str">
+        <v>Between 6°E and 12°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
+      <c r="P303" s="248" t="str">
+        <v>Available; Non-ballpark; Has usage area; Default selection</v>
+      </c>
+      <c r="Q303" s="249" t="str">
+        <v>No reported accuracy</v>
+      </c>
+    </row>
+    <row r="304" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C304" s="235" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D304" s="178">
+        <v>0</v>
+      </c>
+      <c r="E304" s="179">
+        <v>0</v>
+      </c>
+      <c r="H304" s="200">
+        <v>1</v>
+      </c>
+      <c r="I304" s="201" t="str">
+        <v>Only</v>
+      </c>
+      <c r="J304" s="201" t="str">
+        <v>UTM zone 33N</v>
+      </c>
+      <c r="K304" s="201" t="str">
+        <v>Conversion</v>
+      </c>
+      <c r="L304" s="201">
+        <v>0</v>
+      </c>
+      <c r="M304" s="201" t="b">
+        <v>1</v>
+      </c>
+      <c r="N304" s="201" t="b">
+        <v>0</v>
+      </c>
+      <c r="O304" s="201" t="str">
+        <v>Between 12°E and 18°E, northern hemisphere between equator and 84°N, onshore and offshore.</v>
+      </c>
+      <c r="P304" s="239" t="str">
+        <v>Available; Non-ballpark; Has usage area; Default selection</v>
+      </c>
+      <c r="Q304" s="240" t="str">
+        <v>No reported accuracy</v>
+      </c>
+    </row>
+    <row r="305" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C305" s="235" t="str">
+        <v>Nr grids</v>
+      </c>
+      <c r="D305" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E305" s="179" t="str">
+        <v>N.A.</v>
+      </c>
       <c r="M305"/>
       <c r="O305"/>
     </row>
-    <row r="306" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="306" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C306" s="235" t="str">
+        <v>1st grid</v>
+      </c>
+      <c r="D306" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E306" s="179" t="str">
+        <v>N.A.</v>
+      </c>
       <c r="M306"/>
       <c r="O306"/>
     </row>
-    <row r="307" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="307" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C307" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D307" s="178" t="str">
+        <v>+proj=pipeline +step +inv +proj=utm +zone=32 +ellps=GRS80 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E307" s="179" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=utm +zone=33 +ellps=GRS80</v>
+      </c>
       <c r="M307"/>
       <c r="O307"/>
     </row>
-    <row r="308" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="308" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C308" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D308" s="180">
+        <v>0</v>
+      </c>
+      <c r="E308" s="181">
+        <v>0</v>
+      </c>
       <c r="M308"/>
       <c r="O308"/>
     </row>
-    <row r="309" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="309" spans="3:16" x14ac:dyDescent="0.35">
       <c r="M309"/>
       <c r="O309"/>
     </row>
-    <row r="310" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="310" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C310" s="1"/>
       <c r="M310"/>
       <c r="O310"/>
     </row>
-    <row r="311" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="311" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C311" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D311" s="210">
+        <v>2964</v>
+      </c>
       <c r="M311"/>
       <c r="O311"/>
     </row>
-    <row r="312" spans="13:15" x14ac:dyDescent="0.35">
+    <row r="312" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C312" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D312" s="221">
+        <v>4326</v>
+      </c>
       <c r="M312"/>
       <c r="O312"/>
     </row>
-    <row r="313" spans="13:15" x14ac:dyDescent="0.35">
-      <c r="M313"/>
-      <c r="O313"/>
+    <row r="313" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C313" s="182" t="str" cm="1">
+        <f t="array" ref="C313">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D313" s="183"/>
+      <c r="E313" s="183"/>
+      <c r="F313" s="183"/>
+      <c r="G313" s="183"/>
+      <c r="H313" s="183"/>
+      <c r="I313" s="183"/>
+      <c r="J313" s="183"/>
+      <c r="K313" s="183"/>
+      <c r="L313" s="183"/>
+      <c r="M313" s="183"/>
+      <c r="N313" s="183"/>
+      <c r="O313" s="183"/>
+      <c r="P313" s="184"/>
+    </row>
+    <row r="314" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C314" s="226" t="str" cm="1">
+        <f t="array" ref="C314:M336">_xll.PE.trf.TransformList(D311,D312,,"")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D314" s="265">
+        <v>0</v>
+      </c>
+      <c r="E314" s="266">
+        <v>1</v>
+      </c>
+      <c r="F314" s="266">
+        <v>2</v>
+      </c>
+      <c r="G314" s="266">
+        <v>3</v>
+      </c>
+      <c r="H314" s="266">
+        <v>4</v>
+      </c>
+      <c r="I314" s="266">
+        <v>5</v>
+      </c>
+      <c r="J314" s="266">
+        <v>6</v>
+      </c>
+      <c r="K314" s="266">
+        <v>7</v>
+      </c>
+      <c r="L314" s="266">
+        <v>8</v>
+      </c>
+      <c r="M314" s="35">
+        <v>9</v>
+      </c>
+      <c r="O314"/>
+    </row>
+    <row r="315" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C315" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D315" s="257" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
+      </c>
+      <c r="E315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
+      </c>
+      <c r="F315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
+      </c>
+      <c r="G315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
+      </c>
+      <c r="H315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
+      </c>
+      <c r="I315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
+      </c>
+      <c r="J315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
+      </c>
+      <c r="K315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
+      </c>
+      <c r="L315" s="252" t="str">
+        <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
+      </c>
+      <c r="M315" s="179" t="str">
+        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="O315"/>
+    </row>
+    <row r="316" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C316" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D316" s="257" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="E316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="F316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="G316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="H316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="I316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="J316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="K316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="L316" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="M316" s="255" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+    </row>
+    <row r="317" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C317" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D317" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L317" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M317" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="318" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C318" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D318" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L318" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M318" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="319" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C319" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D319" s="257" t="str">
+        <v>5</v>
+      </c>
+      <c r="E319" s="252" t="str">
+        <v>12</v>
+      </c>
+      <c r="F319" s="252" t="str">
+        <v>2</v>
+      </c>
+      <c r="G319" s="252" t="str">
+        <v>20</v>
+      </c>
+      <c r="H319" s="252" t="str">
+        <v>8</v>
+      </c>
+      <c r="I319" s="252" t="str">
+        <v>10</v>
+      </c>
+      <c r="J319" s="252" t="str">
+        <v>13</v>
+      </c>
+      <c r="K319" s="252" t="str">
+        <v>15</v>
+      </c>
+      <c r="L319" s="252" t="str">
+        <v>18</v>
+      </c>
+      <c r="M319" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="320" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C320" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D320" s="257" t="str">
+        <v>True</v>
+      </c>
+      <c r="E320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="F320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="G320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="H320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="I320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="J320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="K320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="L320" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="M320" s="255" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="321" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C321" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D321" s="257" t="str">
+        <v>False</v>
+      </c>
+      <c r="E321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="F321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="G321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="H321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="I321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="J321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="K321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="L321" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="M321" s="255" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="322" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C322" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D322" s="257" t="str">
+        <v>True</v>
+      </c>
+      <c r="E322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="F322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="G322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="H322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="I322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="J322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="K322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="L322" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="M322" s="255" t="str">
+        <v>True</v>
+      </c>
+    </row>
+    <row r="323" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C323" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D323" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L323" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M323" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="324" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C324" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D324" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L324" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M324" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="325" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C325" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D325" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L325" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M325" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="326" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C326" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D326" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L326" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M326" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C327" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D327" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="G327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="H327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="I327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="J327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="K327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="L327" s="252" t="str">
+        <v/>
+      </c>
+      <c r="M327" s="255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C328" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D328" s="257" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="E328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="F328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="G328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="H328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="I328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="J328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="K328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="L328" s="252" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+      <c r="M328" s="255" t="str">
+        <v>NAD27 / Alaska Albers</v>
+      </c>
+    </row>
+    <row r="329" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C329" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D329" s="257" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="E329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="F329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="G329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="H329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="I329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="J329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="K329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="L329" s="252" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+      <c r="M329" s="255" t="str">
+        <v>WGS 84 (with axis order normalized for visualization)</v>
+      </c>
+    </row>
+    <row r="330" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C330" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D330" s="257" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="E330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="F330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="G330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="H330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="I330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="J330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="K330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="L330" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M330" s="255" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+    </row>
+    <row r="331" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C331" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D331" s="257" t="str">
+        <v>United States (USA) - Alaska including EEZ.</v>
+      </c>
+      <c r="E331" s="252" t="str">
+        <v>United States (USA) - Alaska mainland.</v>
+      </c>
+      <c r="F331" s="252" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="G331" s="252" t="str">
+        <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
+      </c>
+      <c r="H331" s="252" t="str">
+        <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
+      </c>
+      <c r="I331" s="252" t="str">
+        <v>Canada - Yukon.</v>
+      </c>
+      <c r="J331" s="252" t="str">
+        <v>Canada - Alberta; British Columbia.</v>
+      </c>
+      <c r="K331" s="252" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
+      </c>
+      <c r="L331" s="252" t="str">
+        <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
+      </c>
+      <c r="M331" s="255" t="str">
+        <v>World</v>
+      </c>
+    </row>
+    <row r="332" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C332" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D332" s="257" t="str">
+        <v>167.65</v>
+      </c>
+      <c r="E332" s="252" t="str">
+        <v>-168.26</v>
+      </c>
+      <c r="F332" s="252" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="G332" s="252" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="H332" s="252" t="str">
+        <v>-136.46</v>
+      </c>
+      <c r="I332" s="252" t="str">
+        <v>-141.01</v>
+      </c>
+      <c r="J332" s="252" t="str">
+        <v>-139.04</v>
+      </c>
+      <c r="K332" s="252" t="str">
+        <v>-178.3</v>
+      </c>
+      <c r="L332" s="252" t="str">
+        <v>172.42</v>
+      </c>
+      <c r="M332" s="255" t="str">
+        <v>-180</v>
+      </c>
+    </row>
+    <row r="333" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C333" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D333" s="257" t="str">
+        <v>47.88</v>
+      </c>
+      <c r="E333" s="252" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="F333" s="252" t="str">
+        <v>40</v>
+      </c>
+      <c r="G333" s="252" t="str">
+        <v>40</v>
+      </c>
+      <c r="H333" s="252" t="str">
+        <v>49</v>
+      </c>
+      <c r="I333" s="252" t="str">
+        <v>59.99</v>
+      </c>
+      <c r="J333" s="252" t="str">
+        <v>48.25</v>
+      </c>
+      <c r="K333" s="252" t="str">
+        <v>51.54</v>
+      </c>
+      <c r="L333" s="252" t="str">
+        <v>51.3</v>
+      </c>
+      <c r="M333" s="255" t="str">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="334" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C334" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D334" s="257" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="E334" s="252" t="str">
+        <v>-129.99</v>
+      </c>
+      <c r="F334" s="252" t="str">
+        <v>-44</v>
+      </c>
+      <c r="G334" s="252" t="str">
+        <v>-44</v>
+      </c>
+      <c r="H334" s="252" t="str">
+        <v>-60.72</v>
+      </c>
+      <c r="I334" s="252" t="str">
+        <v>-123.91</v>
+      </c>
+      <c r="J334" s="252" t="str">
+        <v>-109.98</v>
+      </c>
+      <c r="K334" s="252" t="str">
+        <v>-164.84</v>
+      </c>
+      <c r="L334" s="252" t="str">
+        <v>179.86</v>
+      </c>
+      <c r="M334" s="255" t="str">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="335" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C335" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D335" s="257" t="str">
+        <v>74.71</v>
+      </c>
+      <c r="E335" s="252" t="str">
+        <v>71.4</v>
+      </c>
+      <c r="F335" s="252" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="G335" s="252" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="H335" s="252" t="str">
+        <v>83.17</v>
+      </c>
+      <c r="I335" s="252" t="str">
+        <v>69.7</v>
+      </c>
+      <c r="J335" s="252" t="str">
+        <v>60.01</v>
+      </c>
+      <c r="K335" s="252" t="str">
+        <v>54.34</v>
+      </c>
+      <c r="L335" s="252" t="str">
+        <v>53.07</v>
+      </c>
+      <c r="M335" s="255" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="336" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C336" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D336" s="258" t="str">
+        <v>18.83, 61.295</v>
+      </c>
+      <c r="E336" s="214" t="str">
+        <v>-149.125, 62.87</v>
+      </c>
+      <c r="F336" s="214" t="str">
+        <v>-92.505, 61.585</v>
+      </c>
+      <c r="G336" s="214" t="str">
+        <v>-92.505, 61.585</v>
+      </c>
+      <c r="H336" s="214" t="str">
+        <v>-98.59, 66.085</v>
+      </c>
+      <c r="I336" s="214" t="str">
+        <v>-132.46, 64.845</v>
+      </c>
+      <c r="J336" s="214" t="str">
+        <v>-124.51, 54.13</v>
+      </c>
+      <c r="K336" s="214" t="str">
+        <v>-171.57, 52.94</v>
+      </c>
+      <c r="L336" s="214" t="str">
+        <v>176.14, 52.185</v>
+      </c>
+      <c r="M336" s="256" t="str">
+        <v>0, 0</v>
+      </c>
+    </row>
+    <row r="337" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="338" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C338" s="251" t="str" cm="1">
+        <f t="array" ref="C338:D352">_xll.PE.trf.TransformSteps(D311,D312,C313,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D338" s="4">
+        <v>0</v>
+      </c>
+      <c r="E338" s="5"/>
+    </row>
+    <row r="339" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C339" s="235" t="str">
+        <v>Step Identifiers</v>
+      </c>
+      <c r="D339" s="178">
+        <v>0</v>
+      </c>
+      <c r="E339" s="179"/>
+    </row>
+    <row r="340" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C340" s="235" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="D340" s="178" t="str">
+        <v>&lt;choose-coordinate-transform&gt;</v>
+      </c>
+      <c r="E340" s="179"/>
+    </row>
+    <row r="341" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C341" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D341" s="178">
+        <v>55</v>
+      </c>
+      <c r="E341" s="179"/>
+    </row>
+    <row r="342" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C342" s="235" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D342" s="178" t="str">
+        <v>United States (USA) - Alaska including EEZ.</v>
+      </c>
+      <c r="E342" s="179"/>
+    </row>
+    <row r="343" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C343" s="235" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D343" s="178" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="E343" s="179"/>
+    </row>
+    <row r="344" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C344" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D344" s="178" t="str">
+        <v>None</v>
+      </c>
+      <c r="E344" s="179"/>
+    </row>
+    <row r="345" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C345" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D345" s="178">
+        <v>167.65</v>
+      </c>
+      <c r="E345" s="179"/>
+    </row>
+    <row r="346" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C346" s="235" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D346" s="178">
+        <v>-129.99</v>
+      </c>
+      <c r="E346" s="179"/>
+    </row>
+    <row r="347" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C347" s="235" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D347" s="178">
+        <v>47.88</v>
+      </c>
+      <c r="E347" s="179"/>
+    </row>
+    <row r="348" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C348" s="235" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D348" s="178">
+        <v>74.709999999999994</v>
+      </c>
+      <c r="E348" s="179"/>
+    </row>
+    <row r="349" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C349" s="235" t="str">
+        <v>Nr grids</v>
+      </c>
+      <c r="D349" s="178">
+        <v>1</v>
+      </c>
+      <c r="E349" s="179"/>
+    </row>
+    <row r="350" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C350" s="235" t="str">
+        <v>1st grid</v>
+      </c>
+      <c r="D350" s="178" t="str">
+        <v/>
+      </c>
+      <c r="E350" s="179"/>
+    </row>
+    <row r="351" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="C351" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D351" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E351" s="179"/>
+    </row>
+    <row r="352" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C352" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D352" s="180">
+        <v>0</v>
+      </c>
+      <c r="E352" s="181"/>
+    </row>
+    <row r="354" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="355" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C355" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D355" s="210">
+        <v>28992</v>
+      </c>
+      <c r="M355"/>
+      <c r="O355"/>
+    </row>
+    <row r="356" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C356" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D356" s="221">
+        <v>3812</v>
+      </c>
+      <c r="M356"/>
+      <c r="O356"/>
+    </row>
+    <row r="357" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C357" s="182" t="str" cm="1">
+        <f t="array" ref="C357">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+      </c>
+      <c r="D357" s="183"/>
+      <c r="E357" s="183"/>
+      <c r="F357" s="183"/>
+      <c r="G357" s="183"/>
+      <c r="H357" s="183"/>
+      <c r="I357" s="183"/>
+      <c r="J357" s="183"/>
+      <c r="K357" s="183"/>
+      <c r="L357" s="183"/>
+      <c r="M357" s="183"/>
+      <c r="N357" s="183"/>
+      <c r="O357" s="183"/>
+      <c r="P357" s="184"/>
+    </row>
+    <row r="358" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C358" s="223" t="str" cm="1">
+        <f t="array" ref="C358:F380">_xll.PE.trf.TransformList(D355,D356,,"")</f>
+        <v>Transform Number</v>
+      </c>
+      <c r="D358" s="259">
+        <v>0</v>
+      </c>
+      <c r="E358" s="260">
+        <v>1</v>
+      </c>
+      <c r="F358" s="261">
+        <v>2</v>
+      </c>
+      <c r="M358"/>
+      <c r="O358"/>
+    </row>
+    <row r="359" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C359" s="12" t="str">
+        <v>Transform Name</v>
+      </c>
+      <c r="D359" s="257" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (9) + Belgian Lambert 2008</v>
+      </c>
+      <c r="E359" s="252" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (8) + Belgian Lambert 2008</v>
+      </c>
+      <c r="F359" s="179" t="str">
+        <v>Inverse of RD New + Ballpark geographic offset from Amersfoort to ETRS89 + Belgian Lambert 2008</v>
+      </c>
+      <c r="M359"/>
+      <c r="O359"/>
+    </row>
+    <row r="360" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C360" s="12" t="str">
+        <v>Transform Type</v>
+      </c>
+      <c r="D360" s="257" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="E360" s="252" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="F360" s="179" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="M360"/>
+    </row>
+    <row r="361" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C361" s="12" t="str">
+        <v>Identifier</v>
+      </c>
+      <c r="D361" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E361" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F361" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M361"/>
+    </row>
+    <row r="362" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C362" s="12" t="str">
+        <v>Identifiers</v>
+      </c>
+      <c r="D362" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E362" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F362" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M362"/>
+    </row>
+    <row r="363" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C363" s="12" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="D363" s="257" t="str">
+        <v>0</v>
+      </c>
+      <c r="E363" s="252" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="F363" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M363"/>
+    </row>
+    <row r="364" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C364" s="12" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="D364" s="257" t="str">
+        <v>True</v>
+      </c>
+      <c r="E364" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="F364" s="179" t="str">
+        <v>True</v>
+      </c>
+      <c r="M364"/>
+    </row>
+    <row r="365" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C365" s="12" t="str">
+        <v>HasBallParkTransformation</v>
+      </c>
+      <c r="D365" s="257" t="str">
+        <v>False</v>
+      </c>
+      <c r="E365" s="252" t="str">
+        <v>False</v>
+      </c>
+      <c r="F365" s="179" t="str">
+        <v>True</v>
+      </c>
+      <c r="M365"/>
+    </row>
+    <row r="366" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C366" s="12" t="str">
+        <v>HasInverse</v>
+      </c>
+      <c r="D366" s="257" t="str">
+        <v>True</v>
+      </c>
+      <c r="E366" s="252" t="str">
+        <v>True</v>
+      </c>
+      <c r="F366" s="179" t="str">
+        <v>True</v>
+      </c>
+      <c r="M366"/>
+    </row>
+    <row r="367" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C367" s="12" t="str">
+        <v>MethodName</v>
+      </c>
+      <c r="D367" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E367" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F367" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M367"/>
+    </row>
+    <row r="368" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C368" s="12" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D368" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E368" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F368" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M368"/>
+    </row>
+    <row r="369" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C369" s="12" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D369" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E369" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F369" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M369"/>
+    </row>
+    <row r="370" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C370" s="12" t="str">
+        <v>GridUsages</v>
+      </c>
+      <c r="D370" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E370" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F370" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M370"/>
+    </row>
+    <row r="371" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C371" s="12" t="str">
+        <v>Parameters</v>
+      </c>
+      <c r="D371" s="257" t="str">
+        <v/>
+      </c>
+      <c r="E371" s="252" t="str">
+        <v/>
+      </c>
+      <c r="F371" s="179" t="str">
+        <v/>
+      </c>
+      <c r="M371"/>
+    </row>
+    <row r="372" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C372" s="12" t="str">
+        <v>SourceCRS</v>
+      </c>
+      <c r="D372" s="257" t="str">
+        <v>Amersfoort / RD New</v>
+      </c>
+      <c r="E372" s="252" t="str">
+        <v>Amersfoort / RD New</v>
+      </c>
+      <c r="F372" s="179" t="str">
+        <v>Amersfoort / RD New</v>
+      </c>
+      <c r="M372"/>
+    </row>
+    <row r="373" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C373" s="12" t="str">
+        <v>TargetCRS</v>
+      </c>
+      <c r="D373" s="257" t="str">
+        <v>ETRS89 / Belgian Lambert 2008</v>
+      </c>
+      <c r="E373" s="252" t="str">
+        <v>ETRS89 / Belgian Lambert 2008</v>
+      </c>
+      <c r="F373" s="179" t="str">
+        <v>ETRS89 / Belgian Lambert 2008</v>
+      </c>
+      <c r="M373"/>
+    </row>
+    <row r="374" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C374" s="12" t="str">
+        <v>Context</v>
+      </c>
+      <c r="D374" s="257" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="E374" s="252" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="F374" s="179" t="str">
+        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
+      </c>
+      <c r="M374"/>
+    </row>
+    <row r="375" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C375" s="12" t="str">
+        <v>UsageArea.Name</v>
+      </c>
+      <c r="D375" s="257" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="E375" s="252" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="F375" s="179" t="str">
+        <v>World</v>
+      </c>
+      <c r="M375"/>
+    </row>
+    <row r="376" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C376" s="12" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D376" s="257" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="E376" s="252" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F376" s="179" t="str">
+        <v>-180</v>
+      </c>
+      <c r="M376"/>
+    </row>
+    <row r="377" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C377" s="12" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D377" s="257" t="str">
+        <v>50.75</v>
+      </c>
+      <c r="E377" s="252" t="str">
+        <v>50.75</v>
+      </c>
+      <c r="F377" s="179" t="str">
+        <v>-90</v>
+      </c>
+      <c r="M377"/>
+    </row>
+    <row r="378" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C378" s="12" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D378" s="257" t="str">
+        <v>7.22</v>
+      </c>
+      <c r="E378" s="252" t="str">
+        <v>7.22</v>
+      </c>
+      <c r="F378" s="179" t="str">
+        <v>180</v>
+      </c>
+      <c r="M378"/>
+    </row>
+    <row r="379" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C379" s="12" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D379" s="257" t="str">
+        <v>53.7</v>
+      </c>
+      <c r="E379" s="252" t="str">
+        <v>53.7</v>
+      </c>
+      <c r="F379" s="179" t="str">
+        <v>90</v>
+      </c>
+      <c r="M379"/>
+    </row>
+    <row r="380" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C380" s="13" t="str">
+        <v>UsageArea.Center</v>
+      </c>
+      <c r="D380" s="258" t="str">
+        <v>5.21, 52.225</v>
+      </c>
+      <c r="E380" s="214" t="str">
+        <v>5.21, 52.225</v>
+      </c>
+      <c r="F380" s="181" t="str">
+        <v>0, 0</v>
+      </c>
+      <c r="M380"/>
+    </row>
+    <row r="381" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M381"/>
+    </row>
+    <row r="382" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C382" s="251" t="str" cm="1">
+        <f t="array" ref="C382:D396">_xll.PE.trf.TransformSteps(D355,D356,C357,"proj")</f>
+        <v>Step Number</v>
+      </c>
+      <c r="D382" s="21">
+        <v>0</v>
+      </c>
+      <c r="H382" s="182" t="str" cm="1">
+        <f t="array" ref="H382:L385">_xll.PE.xfm.ListTransformPipelines(D355,D356)</f>
+        <v>PipelineID</v>
+      </c>
+      <c r="I382" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="J382" s="183" t="str">
+        <v>Accuracy(m)</v>
+      </c>
+      <c r="K382" s="183" t="str">
+        <v>Grids</v>
+      </c>
+      <c r="L382" s="184" t="str">
+        <v>IsAvailable</v>
+      </c>
+    </row>
+    <row r="383" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C383" s="235" t="str">
+        <v>Step Identifiers</v>
+      </c>
+      <c r="D383" s="262">
+        <v>0</v>
+      </c>
+      <c r="H383" s="244">
+        <v>1</v>
+      </c>
+      <c r="I383" s="245" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (9) + Belgian Lambert 2008</v>
+      </c>
+      <c r="J383" s="245">
+        <v>0</v>
+      </c>
+      <c r="K383" s="245" t="str">
+        <v/>
+      </c>
+      <c r="L383" s="250" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="384" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C384" s="235" t="str">
+        <v>Step Name</v>
+      </c>
+      <c r="D384" s="262" t="str">
+        <v>&lt;choose-coordinate-transform&gt;</v>
+      </c>
+      <c r="H384" s="200">
+        <v>2</v>
+      </c>
+      <c r="I384" s="201" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (8) + Belgian Lambert 2008</v>
+      </c>
+      <c r="J384" s="201">
+        <v>0.25</v>
+      </c>
+      <c r="K384" s="201" t="str">
+        <v/>
+      </c>
+      <c r="L384" s="202" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="385" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C385" s="235" t="str">
+        <v>Step sccuracy [m]</v>
+      </c>
+      <c r="D385" s="262">
+        <v>55</v>
+      </c>
+      <c r="H385">
+        <v>3</v>
+      </c>
+      <c r="I385" t="str">
+        <v>Inverse of RD New + Ballpark geographic offset from Amersfoort to ETRS89 + Belgian Lambert 2008</v>
+      </c>
+      <c r="J385" t="str">
+        <v/>
+      </c>
+      <c r="K385" t="str">
+        <v/>
+      </c>
+      <c r="L385" t="str">
+        <v>TRUE</v>
+      </c>
+    </row>
+    <row r="386" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C386" s="235" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="D386" s="262" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+    </row>
+    <row r="387" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C387" s="235" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="D387" s="262" t="str">
+        <v>Unknown</v>
+      </c>
+    </row>
+    <row r="388" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C388" s="235" t="str">
+        <v>Remarks</v>
+      </c>
+      <c r="D388" s="262" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="389" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C389" s="235" t="str">
+        <v>UsageArea.WestLongitude</v>
+      </c>
+      <c r="D389" s="262">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="390" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C390" s="235" t="str">
+        <v>UsageArea.SouthLatitude</v>
+      </c>
+      <c r="D390" s="262">
+        <v>7.22</v>
+      </c>
+      <c r="H390" s="182" t="str" cm="1">
+        <f t="array" ref="H390:Q393">_xll.PE.trf.ListTransformOptions(D355,D356)</f>
+        <v>CandidateIndex</v>
+      </c>
+      <c r="I390" s="183" t="str">
+        <v>DefaultSelection</v>
+      </c>
+      <c r="J390" s="183" t="str">
+        <v>Name</v>
+      </c>
+      <c r="K390" s="183" t="str">
+        <v>Type</v>
+      </c>
+      <c r="L390" s="183" t="str">
+        <v>Accuracy</v>
+      </c>
+      <c r="M390" s="183" t="str">
+        <v>IsAvailable</v>
+      </c>
+      <c r="N390" s="183" t="str">
+        <v>HasBallPark</v>
+      </c>
+      <c r="O390" s="183" t="str">
+        <v>UsageArea</v>
+      </c>
+      <c r="P390" s="203" t="str">
+        <v>Pros</v>
+      </c>
+      <c r="Q390" s="184" t="str">
+        <v>Cons</v>
+      </c>
+    </row>
+    <row r="391" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C391" s="235" t="str">
+        <v>UsageArea.EastLongitude</v>
+      </c>
+      <c r="D391" s="262">
+        <v>50.75</v>
+      </c>
+      <c r="H391" s="244">
+        <v>0</v>
+      </c>
+      <c r="I391" s="245" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J391" s="245" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (9) + Belgian Lambert 2008</v>
+      </c>
+      <c r="K391" s="245" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="L391" s="245">
+        <v>0</v>
+      </c>
+      <c r="M391" s="245" t="b">
+        <v>1</v>
+      </c>
+      <c r="N391" s="245" t="b">
+        <v>0</v>
+      </c>
+      <c r="O391" s="245" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="P391" s="248" t="str">
+        <v>Available; Non-ballpark; Accuracy=0; Has usage area; Default selection</v>
+      </c>
+      <c r="Q391" s="249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C392" s="235" t="str">
+        <v>UsageArea.NorthLatitude</v>
+      </c>
+      <c r="D392" s="262">
+        <v>53.7</v>
+      </c>
+      <c r="H392" s="198">
+        <v>1</v>
+      </c>
+      <c r="I392" s="253" t="str">
+        <v>No</v>
+      </c>
+      <c r="J392" s="253" t="str">
+        <v>Inverse of RD New + Amersfoort to ETRS89 (8) + Belgian Lambert 2008</v>
+      </c>
+      <c r="K392" s="253" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="L392" s="253">
+        <v>0.25</v>
+      </c>
+      <c r="M392" s="253" t="b">
+        <v>1</v>
+      </c>
+      <c r="N392" s="253" t="b">
+        <v>0</v>
+      </c>
+      <c r="O392" s="253" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="P392" s="264" t="str">
+        <v>Available; Non-ballpark; Accuracy=0.25; Has usage area</v>
+      </c>
+      <c r="Q392" s="238" t="str">
+        <v>Alternate candidate</v>
+      </c>
+    </row>
+    <row r="393" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C393" s="235" t="str">
+        <v>Nr grids</v>
+      </c>
+      <c r="D393" s="262">
+        <v>1</v>
+      </c>
+      <c r="H393" s="200">
+        <v>2</v>
+      </c>
+      <c r="I393" s="201" t="str">
+        <v>No</v>
+      </c>
+      <c r="J393" s="201" t="str">
+        <v>Inverse of RD New + Ballpark geographic offset from Amersfoort to ETRS89 + Belgian Lambert 2008</v>
+      </c>
+      <c r="K393" s="201" t="str">
+        <v>ConcatenatedOperation</v>
+      </c>
+      <c r="L393" s="201">
+        <v>0</v>
+      </c>
+      <c r="M393" s="243" t="b">
+        <v>1</v>
+      </c>
+      <c r="N393" s="201" t="b">
+        <v>1</v>
+      </c>
+      <c r="O393" s="204" t="str">
+        <v>World</v>
+      </c>
+      <c r="P393" s="201" t="str">
+        <v>Available; Has usage area</v>
+      </c>
+      <c r="Q393" s="202" t="str">
+        <v>Ballpark transformation; No reported accuracy; Alternate candidate</v>
+      </c>
+    </row>
+    <row r="394" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C394" s="235" t="str">
+        <v>1st grid</v>
+      </c>
+      <c r="D394" s="262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C395" s="235" t="str">
+        <v>2nd grid</v>
+      </c>
+      <c r="D395" s="262" t="str">
+        <v>N.A.</v>
+      </c>
+    </row>
+    <row r="396" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C396" s="236" t="str">
+        <v>Step ROJ string</v>
+      </c>
+      <c r="D396" s="263">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/DegreeTests.xlsx
+++ b/DegreeTests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\VS22\ProjExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766B9A21-4C8C-4160-A61A-707E5903CDEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733D7FDF-17D6-48A4-847D-39428E023CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1214,7 +1214,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1795,33 +1795,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -46965,14 +46949,18 @@
     </row>
     <row r="198" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C198" s="251" t="str" cm="1">
-        <f t="array" ref="C198:D212">_xll.PE.trf.TransformSteps(D171,D172,C173,"proj")</f>
+        <f t="array" ref="C198:F212">_xll.PE.trf.TransformSteps(D171,D172,C173,"proj")</f>
         <v>Step Number</v>
       </c>
       <c r="D198" s="4">
         <v>0</v>
       </c>
-      <c r="E198" s="215"/>
-      <c r="F198" s="215"/>
+      <c r="E198" s="215">
+        <v>1</v>
+      </c>
+      <c r="F198" s="215">
+        <v>2</v>
+      </c>
       <c r="G198" s="215"/>
       <c r="H198" s="215"/>
       <c r="I198" s="5"/>
@@ -46998,11 +46986,15 @@
       <c r="C199" s="235" t="str">
         <v>Step Identifiers</v>
       </c>
-      <c r="D199" s="178">
-        <v>0</v>
-      </c>
-      <c r="E199" s="172"/>
-      <c r="F199" s="172"/>
+      <c r="D199" s="178" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E199" s="172" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="F199" s="172" t="str">
+        <v>EPSG</v>
+      </c>
       <c r="G199" s="172"/>
       <c r="H199" s="172"/>
       <c r="I199" s="179"/>
@@ -47028,10 +47020,14 @@
         <v>Step Name</v>
       </c>
       <c r="D200" s="178" t="str">
-        <v>&lt;choose-coordinate-transform&gt;</v>
-      </c>
-      <c r="E200" s="172"/>
-      <c r="F200" s="172"/>
+        <v>Inverse of Popular Visualisation Pseudo-Mercator</v>
+      </c>
+      <c r="E200" s="172" t="str">
+        <v>Inverse of ED50 to WGS 84 (18)</v>
+      </c>
+      <c r="F200" s="172" t="str">
+        <v>TM 5 NE</v>
+      </c>
       <c r="G200" s="172"/>
       <c r="H200" s="172"/>
       <c r="I200" s="179"/>
@@ -47059,8 +47055,12 @@
       <c r="D201" s="178">
         <v>55</v>
       </c>
-      <c r="E201" s="172"/>
-      <c r="F201" s="172"/>
+      <c r="E201" s="172">
+        <v>55</v>
+      </c>
+      <c r="F201" s="172">
+        <v>55</v>
+      </c>
       <c r="G201" s="172"/>
       <c r="H201" s="172"/>
       <c r="I201" s="179"/>
@@ -47086,10 +47086,14 @@
         <v>UsageArea</v>
       </c>
       <c r="D202" s="178" t="str">
+        <v>World.</v>
+      </c>
+      <c r="E202" s="172" t="str">
         <v>Denmark - offshore North Sea; Ireland - offshore; Netherlands - offshore; United Kingdom - UKCS offshore.</v>
       </c>
-      <c r="E202" s="172"/>
-      <c r="F202" s="172"/>
+      <c r="F202" s="172" t="str">
+        <v>Netherlands - offshore North Sea.</v>
+      </c>
       <c r="G202" s="172"/>
       <c r="H202" s="172"/>
       <c r="I202" s="179"/>
@@ -47115,10 +47119,14 @@
         <v>Scope</v>
       </c>
       <c r="D203" s="178" t="str">
-        <v>Unknown</v>
-      </c>
-      <c r="E203" s="172"/>
-      <c r="F203" s="172"/>
+        <v>Web mapping and visualisation.</v>
+      </c>
+      <c r="E203" s="172" t="str">
+        <v>Oil and gas exploration and production.</v>
+      </c>
+      <c r="F203" s="172" t="str">
+        <v>Oil and gas exploration and production.</v>
+      </c>
       <c r="G203" s="172"/>
       <c r="H203" s="172"/>
       <c r="I203" s="179"/>
@@ -47147,8 +47155,12 @@
       <c r="D204" s="178" t="str">
         <v>None</v>
       </c>
-      <c r="E204" s="172"/>
-      <c r="F204" s="172"/>
+      <c r="E204" s="172" t="str">
+        <v>Recommended CT for UKCS and IrishCS petroleum purposes, known as "Common Offshore". Based on ED50 to WGS 72 (precise ephemeris) 6-nations agreement of 1981 with which precise to broadcast and broadcast to WGS 84 transformations have been concatenated.</v>
+      </c>
+      <c r="F204" s="172" t="str">
+        <v>None</v>
+      </c>
       <c r="G204" s="172"/>
       <c r="H204" s="172"/>
       <c r="I204" s="179"/>
@@ -47175,10 +47187,14 @@
         <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D205" s="178">
+        <v>-180</v>
+      </c>
+      <c r="E205" s="172">
         <v>-16.100000000000001</v>
       </c>
-      <c r="E205" s="172"/>
-      <c r="F205" s="172"/>
+      <c r="F205" s="172">
+        <v>2.5299999999999998</v>
+      </c>
       <c r="G205" s="172"/>
       <c r="H205" s="172"/>
       <c r="I205" s="179"/>
@@ -47188,10 +47204,14 @@
         <v>UsageArea.SouthLatitude</v>
       </c>
       <c r="D206" s="178">
+        <v>180</v>
+      </c>
+      <c r="E206" s="172">
         <v>10.86</v>
       </c>
-      <c r="E206" s="172"/>
-      <c r="F206" s="172"/>
+      <c r="F206" s="172">
+        <v>6.37</v>
+      </c>
       <c r="G206" s="172"/>
       <c r="H206" s="172"/>
       <c r="I206" s="179"/>
@@ -47232,10 +47252,14 @@
         <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D207" s="178">
+        <v>-90</v>
+      </c>
+      <c r="E207" s="172">
         <v>47.42</v>
       </c>
-      <c r="E207" s="172"/>
-      <c r="F207" s="172"/>
+      <c r="F207" s="172">
+        <v>51.44</v>
+      </c>
       <c r="G207" s="172"/>
       <c r="H207" s="172"/>
       <c r="I207" s="179"/>
@@ -47275,10 +47299,14 @@
         <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D208" s="178">
-        <v>63.89</v>
-      </c>
-      <c r="E208" s="172"/>
-      <c r="F208" s="172"/>
+        <v>0</v>
+      </c>
+      <c r="E208" s="172">
+        <v>0</v>
+      </c>
+      <c r="F208" s="172">
+        <v>0</v>
+      </c>
       <c r="G208" s="172"/>
       <c r="H208" s="172"/>
       <c r="I208" s="179"/>
@@ -47317,11 +47345,15 @@
       <c r="C209" s="235" t="str">
         <v>Nr grids</v>
       </c>
-      <c r="D209" s="178">
-        <v>0</v>
-      </c>
-      <c r="E209" s="172"/>
-      <c r="F209" s="172"/>
+      <c r="D209" s="178" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E209" s="172" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F209" s="172" t="str">
+        <v>N.A.</v>
+      </c>
       <c r="G209" s="172"/>
       <c r="H209" s="172"/>
       <c r="I209" s="179"/>
@@ -47363,8 +47395,12 @@
       <c r="D210" s="178" t="str">
         <v>N.A.</v>
       </c>
-      <c r="E210" s="172"/>
-      <c r="F210" s="172"/>
+      <c r="E210" s="172" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F210" s="172" t="str">
+        <v>N.A.</v>
+      </c>
       <c r="G210" s="172"/>
       <c r="H210" s="172"/>
       <c r="I210" s="179"/>
@@ -47404,10 +47440,14 @@
         <v>2nd grid</v>
       </c>
       <c r="D211" s="178" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="E211" s="172"/>
-      <c r="F211" s="172"/>
+        <v>+proj=pipeline +step +inv +proj=webmerc +lat_0=0 +lon_0=0 +x_0=0 +y_0=0 +ellps=WGS84 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E211" s="172" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=push +v_3 +step +proj=cart +ellps=WGS84 +step +inv +proj=helmert +x=-89.5 +y=-93.8 +z=-123.1 +rx=0 +ry=0 +rz=-0.156 +s=1.2 +convention=position_vector +step +inv +proj=cart +ellps=intl +step +proj=pop +v_3 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="F211" s="172" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=tmerc +lat_0=0 +lon_0=5 +k=0.9996 +x_0=500000 +y_0=0 +ellps=intl</v>
+      </c>
       <c r="G211" s="172"/>
       <c r="H211" s="172"/>
       <c r="I211" s="179"/>
@@ -47449,8 +47489,12 @@
       <c r="D212" s="180">
         <v>0</v>
       </c>
-      <c r="E212" s="214"/>
-      <c r="F212" s="214"/>
+      <c r="E212" s="214">
+        <v>0</v>
+      </c>
+      <c r="F212" s="214">
+        <v>0</v>
+      </c>
       <c r="G212" s="214"/>
       <c r="H212" s="214"/>
       <c r="I212" s="181"/>
@@ -47486,15 +47530,7 @@
       </c>
     </row>
     <row r="213" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="L213" s="253"/>
-      <c r="M213" s="253"/>
-      <c r="N213" s="253"/>
-      <c r="O213" s="254"/>
-      <c r="P213" s="253"/>
-      <c r="Q213" s="253"/>
-      <c r="R213" s="253"/>
-      <c r="S213" s="253"/>
-      <c r="T213" s="253"/>
+      <c r="M213"/>
     </row>
     <row r="214" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="M214"/>
@@ -48385,11 +48421,14 @@
     <row r="242" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B242"/>
       <c r="C242" s="251" t="str" cm="1">
-        <f t="array" ref="C242:D256">_xll.PE.trf.TransformSteps(D215,D216,C217,"proj")</f>
+        <f t="array" ref="C242:E256">_xll.PE.trf.TransformSteps(D215,D216,C217,"proj")</f>
         <v>Step Number</v>
       </c>
       <c r="D242" s="5">
         <v>0</v>
+      </c>
+      <c r="E242" s="5">
+        <v>1</v>
       </c>
       <c r="F242" t="str">
         <f>D219</f>
@@ -48418,8 +48457,11 @@
       <c r="C243" s="235" t="str">
         <v>Step Identifiers</v>
       </c>
-      <c r="D243" s="179">
-        <v>0</v>
+      <c r="D243" s="179" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E243" s="179" t="str">
+        <v>DERIVED_FROM(EPSG)</v>
       </c>
       <c r="F243" t="str">
         <f>E219</f>
@@ -48448,7 +48490,10 @@
         <v>Step Name</v>
       </c>
       <c r="D244" s="179" t="str">
-        <v>&lt;choose-coordinate-transform&gt;</v>
+        <v>Inverse of Alaska Albers</v>
+      </c>
+      <c r="E244" s="179" t="str">
+        <v>NAD27 to WGS 84 (85)</v>
       </c>
       <c r="F244" t="str">
         <f>F219</f>
@@ -48479,6 +48524,9 @@
       <c r="D245" s="179">
         <v>0</v>
       </c>
+      <c r="E245" s="179">
+        <v>0</v>
+      </c>
       <c r="F245" t="str">
         <f>G219</f>
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
@@ -48506,6 +48554,9 @@
         <v>UsageArea</v>
       </c>
       <c r="D246" s="179" t="str">
+        <v>United States (USA) - Alaska.</v>
+      </c>
+      <c r="E246" s="179" t="str">
         <v>United States (USA) - Alaska including EEZ.</v>
       </c>
       <c r="F246" t="str">
@@ -48535,7 +48586,10 @@
         <v>Scope</v>
       </c>
       <c r="D247" s="179" t="str">
-        <v>Unknown</v>
+        <v>Topographic mapping (small scale).</v>
+      </c>
+      <c r="E247" s="179" t="str">
+        <v>(null/copy) Approximation for medium and low accuracy applications assuming equality between plate-fixed static and earth-fixed dynamic CRSs, ignoring static/dynamic CRS differences.</v>
       </c>
       <c r="K247" s="198">
         <v>5</v>
@@ -48563,6 +48617,9 @@
       <c r="D248" s="179" t="str">
         <v>None</v>
       </c>
+      <c r="E248" s="179" t="str">
+        <v>Parameter files are from NAD27 to NAD83 (2) (code 1243) assuming that NAD83 is equivalent to WGS 84 within the accuracy of this tfm. Uses NADCON method which expects longitudes positive west; EPSG CRS codes 4267 and 4326 have longitudes positive east.</v>
+      </c>
       <c r="K248" s="198">
         <v>6</v>
       </c>
@@ -48587,6 +48644,9 @@
         <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D249" s="179">
+        <v>172.42</v>
+      </c>
+      <c r="E249" s="179">
         <v>167.65</v>
       </c>
       <c r="K249" s="198">
@@ -48613,6 +48673,9 @@
       <c r="D250" s="179">
         <v>-129.99</v>
       </c>
+      <c r="E250" s="179">
+        <v>-129.99</v>
+      </c>
       <c r="K250" s="198">
         <v>8</v>
       </c>
@@ -48635,6 +48698,9 @@
         <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D251" s="179">
+        <v>51.3</v>
+      </c>
+      <c r="E251" s="179">
         <v>47.88</v>
       </c>
       <c r="K251" s="198">
@@ -48658,7 +48724,10 @@
         <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D252" s="179">
-        <v>74.709999999999994</v>
+        <v>0</v>
+      </c>
+      <c r="E252" s="179">
+        <v>1</v>
       </c>
       <c r="K252" s="200">
         <v>10</v>
@@ -48680,8 +48749,11 @@
       <c r="C253" s="235" t="str">
         <v>Nr grids</v>
       </c>
-      <c r="D253" s="179">
-        <v>1</v>
+      <c r="D253" s="179" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E253" s="179" t="str">
+        <v/>
       </c>
     </row>
     <row r="254" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -48689,7 +48761,10 @@
         <v>1st grid</v>
       </c>
       <c r="D254" s="179" t="str">
-        <v/>
+        <v>N.A.</v>
+      </c>
+      <c r="E254" s="179" t="str">
+        <v>N.A.</v>
       </c>
       <c r="K254" s="182" t="str" cm="1">
         <f t="array" ref="K254:T264">_xll.PE.trf.ListTransformOptions(D215,D216)</f>
@@ -48728,7 +48803,10 @@
         <v>2nd grid</v>
       </c>
       <c r="D255" s="179" t="str">
-        <v>N.A.</v>
+        <v>+proj=pipeline +step +proj=unitconvert +xy_in=us-ft +xy_out=m +step +inv +proj=aea +lat_0=50 +lon_0=-154 +lat_1=55 +lat_2=65 +x_0=0 +y_0=0 +ellps=clrk66 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E255" s="179" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=hgridshift +grids=us_noaa_alaska.tif +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
       </c>
       <c r="K255" s="244">
         <v>0</v>
@@ -48766,6 +48844,9 @@
         <v>Step ROJ string</v>
       </c>
       <c r="D256" s="181">
+        <v>0</v>
+      </c>
+      <c r="E256" s="181">
         <v>0</v>
       </c>
       <c r="K256" s="198">
@@ -49319,7 +49400,7 @@
     </row>
     <row r="294" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C294" s="251" t="str" cm="1">
-        <f t="array" ref="C294:E308">_xll.PE.trf.TransformSteps(D267,D268,,"proj")</f>
+        <f t="array" ref="C294:E308">_xll.PE.trf.TransformSteps(D267,D268,C269,"proj")</f>
         <v>Step Number</v>
       </c>
       <c r="D294" s="4">
@@ -49405,10 +49486,10 @@
         <v>Step sccuracy [m]</v>
       </c>
       <c r="D297" s="178">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E297" s="179">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M297"/>
     </row>
@@ -49565,10 +49646,10 @@
         <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D304" s="178">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E304" s="179">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H304" s="200">
         <v>1</v>
@@ -49605,11 +49686,11 @@
       <c r="C305" s="235" t="str">
         <v>Nr grids</v>
       </c>
-      <c r="D305" s="178" t="str">
-        <v>N.A.</v>
-      </c>
-      <c r="E305" s="179" t="str">
-        <v>N.A.</v>
+      <c r="D305" s="178">
+        <v>0</v>
+      </c>
+      <c r="E305" s="179">
+        <v>0</v>
       </c>
       <c r="M305"/>
       <c r="O305"/>
@@ -49632,23 +49713,23 @@
         <v>2nd grid</v>
       </c>
       <c r="D307" s="178" t="str">
-        <v>+proj=pipeline +step +inv +proj=utm +zone=32 +ellps=GRS80 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+        <v>N.A.</v>
       </c>
       <c r="E307" s="179" t="str">
-        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=utm +zone=33 +ellps=GRS80</v>
+        <v>N.A.</v>
       </c>
       <c r="M307"/>
       <c r="O307"/>
     </row>
     <row r="308" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C308" s="236" t="str">
-        <v>Step ROJ string</v>
-      </c>
-      <c r="D308" s="180">
-        <v>0</v>
-      </c>
-      <c r="E308" s="181">
-        <v>0</v>
+        <v>Step PROJ string</v>
+      </c>
+      <c r="D308" s="180" t="str">
+        <v>+proj=pipeline +step +inv +proj=utm +zone=32 +ellps=GRS80 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E308" s="181" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=utm +zone=33 +ellps=GRS80</v>
       </c>
       <c r="M308"/>
       <c r="O308"/>
@@ -49684,8 +49765,8 @@
     </row>
     <row r="313" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C313" s="182" t="str" cm="1">
-        <f t="array" ref="C313">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
-        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+        <f t="array" ref="C313">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,6,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=6; AllowDeprecatedCrs=False</v>
       </c>
       <c r="D313" s="183"/>
       <c r="E313" s="183"/>
@@ -49702,783 +49783,739 @@
       <c r="P313" s="184"/>
     </row>
     <row r="314" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C314" s="226" t="str" cm="1">
-        <f t="array" ref="C314:M336">_xll.PE.trf.TransformList(D311,D312,,"")</f>
+      <c r="C314" s="223" t="str" cm="1">
+        <f t="array" ref="C314:L336">_xll.PE.trf.TransformList(D311,D312,C313,"")</f>
         <v>Transform Number</v>
       </c>
-      <c r="D314" s="265">
+      <c r="D314" s="4">
         <v>0</v>
       </c>
-      <c r="E314" s="266">
+      <c r="E314" s="215">
         <v>1</v>
       </c>
-      <c r="F314" s="266">
+      <c r="F314" s="215">
         <v>2</v>
       </c>
-      <c r="G314" s="266">
+      <c r="G314" s="215">
         <v>3</v>
       </c>
-      <c r="H314" s="266">
+      <c r="H314" s="215">
         <v>4</v>
       </c>
-      <c r="I314" s="266">
+      <c r="I314" s="215">
         <v>5</v>
       </c>
-      <c r="J314" s="266">
+      <c r="J314" s="215">
         <v>6</v>
       </c>
-      <c r="K314" s="266">
+      <c r="K314" s="215">
         <v>7</v>
       </c>
-      <c r="L314" s="266">
+      <c r="L314" s="5">
         <v>8</v>
       </c>
-      <c r="M314" s="35">
-        <v>9</v>
-      </c>
+      <c r="M314"/>
       <c r="O314"/>
     </row>
     <row r="315" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C315" s="12" t="str">
         <v>Transform Name</v>
       </c>
-      <c r="D315" s="257" t="str">
+      <c r="D315" s="252" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (85) + axis order change (2D)</v>
       </c>
-      <c r="E315" s="252" t="str">
+      <c r="E315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (7) + axis order change (2D)</v>
       </c>
-      <c r="F315" s="252" t="str">
+      <c r="F315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (33) + axis order change (2D)</v>
       </c>
-      <c r="G315" s="252" t="str">
+      <c r="G315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (3) + axis order change (2D)</v>
       </c>
-      <c r="H315" s="252" t="str">
+      <c r="H315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (13) + axis order change (2D)</v>
       </c>
-      <c r="I315" s="252" t="str">
+      <c r="I315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (14) + axis order change (2D)</v>
       </c>
-      <c r="J315" s="252" t="str">
+      <c r="J315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (10) + axis order change (2D)</v>
       </c>
-      <c r="K315" s="252" t="str">
+      <c r="K315" s="256" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (21) + axis order change (2D)</v>
       </c>
-      <c r="L315" s="252" t="str">
+      <c r="L315" s="179" t="str">
         <v>Inverse of Alaska Albers + NAD27 to WGS 84 (22) + axis order change (2D)</v>
       </c>
-      <c r="M315" s="179" t="str">
-        <v>Inverse of Alaska Albers + Ballpark geographic offset from NAD27 to WGS 84 (with axis order normalized for visualization)</v>
-      </c>
+      <c r="M315"/>
       <c r="O315"/>
     </row>
     <row r="316" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C316" s="12" t="str">
         <v>Transform Type</v>
       </c>
-      <c r="D316" s="257" t="str">
+      <c r="D316" s="252" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="E316" s="252" t="str">
+      <c r="E316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="F316" s="252" t="str">
+      <c r="F316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="G316" s="252" t="str">
+      <c r="G316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="H316" s="252" t="str">
+      <c r="H316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="I316" s="252" t="str">
+      <c r="I316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="J316" s="252" t="str">
+      <c r="J316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="K316" s="252" t="str">
+      <c r="K316" s="256" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="L316" s="252" t="str">
+      <c r="L316" s="179" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="M316" s="255" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
+      <c r="M316"/>
     </row>
     <row r="317" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C317" s="12" t="str">
         <v>Identifier</v>
       </c>
-      <c r="D317" s="257" t="str">
+      <c r="D317" s="252" t="str">
         <v/>
       </c>
-      <c r="E317" s="252" t="str">
+      <c r="E317" s="256" t="str">
         <v/>
       </c>
-      <c r="F317" s="252" t="str">
+      <c r="F317" s="256" t="str">
         <v/>
       </c>
-      <c r="G317" s="252" t="str">
+      <c r="G317" s="256" t="str">
         <v/>
       </c>
-      <c r="H317" s="252" t="str">
+      <c r="H317" s="256" t="str">
         <v/>
       </c>
-      <c r="I317" s="252" t="str">
+      <c r="I317" s="256" t="str">
         <v/>
       </c>
-      <c r="J317" s="252" t="str">
+      <c r="J317" s="256" t="str">
         <v/>
       </c>
-      <c r="K317" s="252" t="str">
+      <c r="K317" s="256" t="str">
         <v/>
       </c>
-      <c r="L317" s="252" t="str">
+      <c r="L317" s="179" t="str">
         <v/>
       </c>
-      <c r="M317" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M317"/>
     </row>
     <row r="318" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C318" s="12" t="str">
         <v>Identifiers</v>
       </c>
-      <c r="D318" s="257" t="str">
+      <c r="D318" s="252" t="str">
         <v/>
       </c>
-      <c r="E318" s="252" t="str">
+      <c r="E318" s="256" t="str">
         <v/>
       </c>
-      <c r="F318" s="252" t="str">
+      <c r="F318" s="256" t="str">
         <v/>
       </c>
-      <c r="G318" s="252" t="str">
+      <c r="G318" s="256" t="str">
         <v/>
       </c>
-      <c r="H318" s="252" t="str">
+      <c r="H318" s="256" t="str">
         <v/>
       </c>
-      <c r="I318" s="252" t="str">
+      <c r="I318" s="256" t="str">
         <v/>
       </c>
-      <c r="J318" s="252" t="str">
+      <c r="J318" s="256" t="str">
         <v/>
       </c>
-      <c r="K318" s="252" t="str">
+      <c r="K318" s="256" t="str">
         <v/>
       </c>
-      <c r="L318" s="252" t="str">
+      <c r="L318" s="179" t="str">
         <v/>
       </c>
-      <c r="M318" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M318"/>
     </row>
     <row r="319" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C319" s="12" t="str">
         <v>Accuracy</v>
       </c>
-      <c r="D319" s="257" t="str">
+      <c r="D319" s="252" t="str">
         <v>5</v>
       </c>
-      <c r="E319" s="252" t="str">
+      <c r="E319" s="256" t="str">
         <v>12</v>
       </c>
-      <c r="F319" s="252" t="str">
+      <c r="F319" s="256" t="str">
         <v>2</v>
       </c>
-      <c r="G319" s="252" t="str">
+      <c r="G319" s="256" t="str">
         <v>20</v>
       </c>
-      <c r="H319" s="252" t="str">
+      <c r="H319" s="256" t="str">
         <v>8</v>
       </c>
-      <c r="I319" s="252" t="str">
+      <c r="I319" s="256" t="str">
         <v>10</v>
       </c>
-      <c r="J319" s="252" t="str">
+      <c r="J319" s="256" t="str">
         <v>13</v>
       </c>
-      <c r="K319" s="252" t="str">
+      <c r="K319" s="256" t="str">
         <v>15</v>
       </c>
-      <c r="L319" s="252" t="str">
+      <c r="L319" s="179" t="str">
         <v>18</v>
       </c>
-      <c r="M319" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M319"/>
     </row>
     <row r="320" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C320" s="12" t="str">
         <v>IsAvailable</v>
       </c>
-      <c r="D320" s="257" t="str">
+      <c r="D320" s="252" t="str">
         <v>True</v>
       </c>
-      <c r="E320" s="252" t="str">
+      <c r="E320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="F320" s="252" t="str">
+      <c r="F320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="G320" s="252" t="str">
+      <c r="G320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="H320" s="252" t="str">
+      <c r="H320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="I320" s="252" t="str">
+      <c r="I320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="J320" s="252" t="str">
+      <c r="J320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="K320" s="252" t="str">
+      <c r="K320" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="L320" s="252" t="str">
+      <c r="L320" s="179" t="str">
         <v>True</v>
       </c>
-      <c r="M320" s="255" t="str">
-        <v>True</v>
-      </c>
+      <c r="M320"/>
     </row>
     <row r="321" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C321" s="12" t="str">
         <v>HasBallParkTransformation</v>
       </c>
-      <c r="D321" s="257" t="str">
+      <c r="D321" s="252" t="str">
         <v>False</v>
       </c>
-      <c r="E321" s="252" t="str">
+      <c r="E321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="F321" s="252" t="str">
+      <c r="F321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="G321" s="252" t="str">
+      <c r="G321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="H321" s="252" t="str">
+      <c r="H321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="I321" s="252" t="str">
+      <c r="I321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="J321" s="252" t="str">
+      <c r="J321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="K321" s="252" t="str">
+      <c r="K321" s="256" t="str">
         <v>False</v>
       </c>
-      <c r="L321" s="252" t="str">
+      <c r="L321" s="179" t="str">
         <v>False</v>
       </c>
-      <c r="M321" s="255" t="str">
-        <v>True</v>
-      </c>
+      <c r="M321"/>
     </row>
     <row r="322" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C322" s="12" t="str">
         <v>HasInverse</v>
       </c>
-      <c r="D322" s="257" t="str">
+      <c r="D322" s="252" t="str">
         <v>True</v>
       </c>
-      <c r="E322" s="252" t="str">
+      <c r="E322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="F322" s="252" t="str">
+      <c r="F322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="G322" s="252" t="str">
+      <c r="G322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="H322" s="252" t="str">
+      <c r="H322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="I322" s="252" t="str">
+      <c r="I322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="J322" s="252" t="str">
+      <c r="J322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="K322" s="252" t="str">
+      <c r="K322" s="256" t="str">
         <v>True</v>
       </c>
-      <c r="L322" s="252" t="str">
+      <c r="L322" s="179" t="str">
         <v>True</v>
       </c>
-      <c r="M322" s="255" t="str">
-        <v>True</v>
-      </c>
+      <c r="M322"/>
     </row>
     <row r="323" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C323" s="12" t="str">
         <v>MethodName</v>
       </c>
-      <c r="D323" s="257" t="str">
+      <c r="D323" s="252" t="str">
         <v/>
       </c>
-      <c r="E323" s="252" t="str">
+      <c r="E323" s="256" t="str">
         <v/>
       </c>
-      <c r="F323" s="252" t="str">
+      <c r="F323" s="256" t="str">
         <v/>
       </c>
-      <c r="G323" s="252" t="str">
+      <c r="G323" s="256" t="str">
         <v/>
       </c>
-      <c r="H323" s="252" t="str">
+      <c r="H323" s="256" t="str">
         <v/>
       </c>
-      <c r="I323" s="252" t="str">
+      <c r="I323" s="256" t="str">
         <v/>
       </c>
-      <c r="J323" s="252" t="str">
+      <c r="J323" s="256" t="str">
         <v/>
       </c>
-      <c r="K323" s="252" t="str">
+      <c r="K323" s="256" t="str">
         <v/>
       </c>
-      <c r="L323" s="252" t="str">
+      <c r="L323" s="179" t="str">
         <v/>
       </c>
-      <c r="M323" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M323"/>
     </row>
     <row r="324" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C324" s="12" t="str">
         <v>Scope</v>
       </c>
-      <c r="D324" s="257" t="str">
+      <c r="D324" s="252" t="str">
         <v/>
       </c>
-      <c r="E324" s="252" t="str">
+      <c r="E324" s="256" t="str">
         <v/>
       </c>
-      <c r="F324" s="252" t="str">
+      <c r="F324" s="256" t="str">
         <v/>
       </c>
-      <c r="G324" s="252" t="str">
+      <c r="G324" s="256" t="str">
         <v/>
       </c>
-      <c r="H324" s="252" t="str">
+      <c r="H324" s="256" t="str">
         <v/>
       </c>
-      <c r="I324" s="252" t="str">
+      <c r="I324" s="256" t="str">
         <v/>
       </c>
-      <c r="J324" s="252" t="str">
+      <c r="J324" s="256" t="str">
         <v/>
       </c>
-      <c r="K324" s="252" t="str">
+      <c r="K324" s="256" t="str">
         <v/>
       </c>
-      <c r="L324" s="252" t="str">
+      <c r="L324" s="179" t="str">
         <v/>
       </c>
-      <c r="M324" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M324"/>
     </row>
     <row r="325" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C325" s="12" t="str">
         <v>Remarks</v>
       </c>
-      <c r="D325" s="257" t="str">
+      <c r="D325" s="252" t="str">
         <v/>
       </c>
-      <c r="E325" s="252" t="str">
+      <c r="E325" s="256" t="str">
         <v/>
       </c>
-      <c r="F325" s="252" t="str">
+      <c r="F325" s="256" t="str">
         <v/>
       </c>
-      <c r="G325" s="252" t="str">
+      <c r="G325" s="256" t="str">
         <v/>
       </c>
-      <c r="H325" s="252" t="str">
+      <c r="H325" s="256" t="str">
         <v/>
       </c>
-      <c r="I325" s="252" t="str">
+      <c r="I325" s="256" t="str">
         <v/>
       </c>
-      <c r="J325" s="252" t="str">
+      <c r="J325" s="256" t="str">
         <v/>
       </c>
-      <c r="K325" s="252" t="str">
+      <c r="K325" s="256" t="str">
         <v/>
       </c>
-      <c r="L325" s="252" t="str">
+      <c r="L325" s="179" t="str">
         <v/>
       </c>
-      <c r="M325" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M325"/>
     </row>
     <row r="326" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C326" s="12" t="str">
         <v>GridUsages</v>
       </c>
-      <c r="D326" s="257" t="str">
+      <c r="D326" s="252" t="str">
         <v/>
       </c>
-      <c r="E326" s="252" t="str">
+      <c r="E326" s="256" t="str">
         <v/>
       </c>
-      <c r="F326" s="252" t="str">
+      <c r="F326" s="256" t="str">
         <v/>
       </c>
-      <c r="G326" s="252" t="str">
+      <c r="G326" s="256" t="str">
         <v/>
       </c>
-      <c r="H326" s="252" t="str">
+      <c r="H326" s="256" t="str">
         <v/>
       </c>
-      <c r="I326" s="252" t="str">
+      <c r="I326" s="256" t="str">
         <v/>
       </c>
-      <c r="J326" s="252" t="str">
+      <c r="J326" s="256" t="str">
         <v/>
       </c>
-      <c r="K326" s="252" t="str">
+      <c r="K326" s="256" t="str">
         <v/>
       </c>
-      <c r="L326" s="252" t="str">
+      <c r="L326" s="179" t="str">
         <v/>
       </c>
-      <c r="M326" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M326"/>
     </row>
     <row r="327" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C327" s="12" t="str">
         <v>Parameters</v>
       </c>
-      <c r="D327" s="257" t="str">
+      <c r="D327" s="252" t="str">
         <v/>
       </c>
-      <c r="E327" s="252" t="str">
+      <c r="E327" s="256" t="str">
         <v/>
       </c>
-      <c r="F327" s="252" t="str">
+      <c r="F327" s="256" t="str">
         <v/>
       </c>
-      <c r="G327" s="252" t="str">
+      <c r="G327" s="256" t="str">
         <v/>
       </c>
-      <c r="H327" s="252" t="str">
+      <c r="H327" s="256" t="str">
         <v/>
       </c>
-      <c r="I327" s="252" t="str">
+      <c r="I327" s="256" t="str">
         <v/>
       </c>
-      <c r="J327" s="252" t="str">
+      <c r="J327" s="256" t="str">
         <v/>
       </c>
-      <c r="K327" s="252" t="str">
+      <c r="K327" s="256" t="str">
         <v/>
       </c>
-      <c r="L327" s="252" t="str">
+      <c r="L327" s="179" t="str">
         <v/>
       </c>
-      <c r="M327" s="255" t="str">
-        <v/>
-      </c>
+      <c r="M327"/>
     </row>
     <row r="328" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C328" s="12" t="str">
         <v>SourceCRS</v>
       </c>
-      <c r="D328" s="257" t="str">
+      <c r="D328" s="252" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="E328" s="252" t="str">
+      <c r="E328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="F328" s="252" t="str">
+      <c r="F328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="G328" s="252" t="str">
+      <c r="G328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="H328" s="252" t="str">
+      <c r="H328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="I328" s="252" t="str">
+      <c r="I328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="J328" s="252" t="str">
+      <c r="J328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="K328" s="252" t="str">
+      <c r="K328" s="256" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="L328" s="252" t="str">
+      <c r="L328" s="179" t="str">
         <v>NAD27 / Alaska Albers</v>
       </c>
-      <c r="M328" s="255" t="str">
-        <v>NAD27 / Alaska Albers</v>
-      </c>
+      <c r="M328"/>
     </row>
     <row r="329" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C329" s="12" t="str">
         <v>TargetCRS</v>
       </c>
-      <c r="D329" s="257" t="str">
+      <c r="D329" s="252" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="E329" s="252" t="str">
+      <c r="E329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="F329" s="252" t="str">
+      <c r="F329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="G329" s="252" t="str">
+      <c r="G329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="H329" s="252" t="str">
+      <c r="H329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="I329" s="252" t="str">
+      <c r="I329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="J329" s="252" t="str">
+      <c r="J329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="K329" s="252" t="str">
+      <c r="K329" s="256" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="L329" s="252" t="str">
+      <c r="L329" s="179" t="str">
         <v>WGS 84 (with axis order normalized for visualization)</v>
       </c>
-      <c r="M329" s="255" t="str">
-        <v>WGS 84 (with axis order normalized for visualization)</v>
-      </c>
+      <c r="M329"/>
     </row>
     <row r="330" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C330" s="12" t="str">
         <v>Context</v>
       </c>
-      <c r="D330" s="257" t="str">
+      <c r="D330" s="252" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="E330" s="252" t="str">
+      <c r="E330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="F330" s="252" t="str">
+      <c r="F330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="G330" s="252" t="str">
+      <c r="G330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="H330" s="252" t="str">
+      <c r="H330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="I330" s="252" t="str">
+      <c r="I330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="J330" s="252" t="str">
+      <c r="J330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="K330" s="252" t="str">
+      <c r="K330" s="256" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="L330" s="252" t="str">
+      <c r="L330" s="179" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="M330" s="255" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
+      <c r="M330"/>
     </row>
     <row r="331" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C331" s="12" t="str">
         <v>UsageArea.Name</v>
       </c>
-      <c r="D331" s="257" t="str">
+      <c r="D331" s="252" t="str">
         <v>United States (USA) - Alaska including EEZ.</v>
       </c>
-      <c r="E331" s="252" t="str">
+      <c r="E331" s="256" t="str">
         <v>United States (USA) - Alaska mainland.</v>
       </c>
-      <c r="F331" s="252" t="str">
+      <c r="F331" s="256" t="str">
         <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
       </c>
-      <c r="G331" s="252" t="str">
+      <c r="G331" s="256" t="str">
         <v>Canada - onshore - Alberta; British Columbia; Manitoba; New Brunswick; Newfoundland and Labrador; Northwest Territories; Nova Scotia; Nunavut; Ontario; Prince Edward Island; Quebec; Saskatchewan; Yukon; offshore east coast west of 44°W and north of 40°N.</v>
       </c>
-      <c r="H331" s="252" t="str">
+      <c r="H331" s="256" t="str">
         <v>Canada - Northwest Territories; Nunavut; Saskatchewan.</v>
       </c>
-      <c r="I331" s="252" t="str">
+      <c r="I331" s="256" t="str">
         <v>Canada - Yukon.</v>
       </c>
-      <c r="J331" s="252" t="str">
+      <c r="J331" s="256" t="str">
         <v>Canada - Alberta; British Columbia.</v>
       </c>
-      <c r="K331" s="252" t="str">
+      <c r="K331" s="256" t="str">
         <v>United States (USA) - Alaska - Aleutian Islands onshore east of 180°E.</v>
       </c>
-      <c r="L331" s="252" t="str">
+      <c r="L331" s="179" t="str">
         <v>United States (USA) - Alaska - Aleutian Islands onshore west of 180°W.</v>
       </c>
-      <c r="M331" s="255" t="str">
-        <v>World</v>
-      </c>
+      <c r="M331"/>
     </row>
     <row r="332" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C332" s="12" t="str">
         <v>UsageArea.WestLongitude</v>
       </c>
-      <c r="D332" s="257" t="str">
+      <c r="D332" s="252" t="str">
         <v>167.65</v>
       </c>
-      <c r="E332" s="252" t="str">
+      <c r="E332" s="256" t="str">
         <v>-168.26</v>
       </c>
-      <c r="F332" s="252" t="str">
+      <c r="F332" s="256" t="str">
         <v>-141.01</v>
       </c>
-      <c r="G332" s="252" t="str">
+      <c r="G332" s="256" t="str">
         <v>-141.01</v>
       </c>
-      <c r="H332" s="252" t="str">
+      <c r="H332" s="256" t="str">
         <v>-136.46</v>
       </c>
-      <c r="I332" s="252" t="str">
+      <c r="I332" s="256" t="str">
         <v>-141.01</v>
       </c>
-      <c r="J332" s="252" t="str">
+      <c r="J332" s="256" t="str">
         <v>-139.04</v>
       </c>
-      <c r="K332" s="252" t="str">
+      <c r="K332" s="256" t="str">
         <v>-178.3</v>
       </c>
-      <c r="L332" s="252" t="str">
+      <c r="L332" s="179" t="str">
         <v>172.42</v>
       </c>
-      <c r="M332" s="255" t="str">
-        <v>-180</v>
-      </c>
+      <c r="M332"/>
     </row>
     <row r="333" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C333" s="12" t="str">
         <v>UsageArea.SouthLatitude</v>
       </c>
-      <c r="D333" s="257" t="str">
+      <c r="D333" s="252" t="str">
         <v>47.88</v>
       </c>
-      <c r="E333" s="252" t="str">
+      <c r="E333" s="256" t="str">
         <v>54.34</v>
       </c>
-      <c r="F333" s="252" t="str">
+      <c r="F333" s="256" t="str">
         <v>40</v>
       </c>
-      <c r="G333" s="252" t="str">
+      <c r="G333" s="256" t="str">
         <v>40</v>
       </c>
-      <c r="H333" s="252" t="str">
+      <c r="H333" s="256" t="str">
         <v>49</v>
       </c>
-      <c r="I333" s="252" t="str">
+      <c r="I333" s="256" t="str">
         <v>59.99</v>
       </c>
-      <c r="J333" s="252" t="str">
+      <c r="J333" s="256" t="str">
         <v>48.25</v>
       </c>
-      <c r="K333" s="252" t="str">
+      <c r="K333" s="256" t="str">
         <v>51.54</v>
       </c>
-      <c r="L333" s="252" t="str">
+      <c r="L333" s="179" t="str">
         <v>51.3</v>
       </c>
-      <c r="M333" s="255" t="str">
-        <v>-90</v>
-      </c>
+      <c r="M333"/>
     </row>
     <row r="334" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C334" s="12" t="str">
         <v>UsageArea.EastLongitude</v>
       </c>
-      <c r="D334" s="257" t="str">
+      <c r="D334" s="252" t="str">
         <v>-129.99</v>
       </c>
-      <c r="E334" s="252" t="str">
+      <c r="E334" s="256" t="str">
         <v>-129.99</v>
       </c>
-      <c r="F334" s="252" t="str">
+      <c r="F334" s="256" t="str">
         <v>-44</v>
       </c>
-      <c r="G334" s="252" t="str">
+      <c r="G334" s="256" t="str">
         <v>-44</v>
       </c>
-      <c r="H334" s="252" t="str">
+      <c r="H334" s="256" t="str">
         <v>-60.72</v>
       </c>
-      <c r="I334" s="252" t="str">
+      <c r="I334" s="256" t="str">
         <v>-123.91</v>
       </c>
-      <c r="J334" s="252" t="str">
+      <c r="J334" s="256" t="str">
         <v>-109.98</v>
       </c>
-      <c r="K334" s="252" t="str">
+      <c r="K334" s="256" t="str">
         <v>-164.84</v>
       </c>
-      <c r="L334" s="252" t="str">
+      <c r="L334" s="179" t="str">
         <v>179.86</v>
       </c>
-      <c r="M334" s="255" t="str">
-        <v>180</v>
-      </c>
+      <c r="M334"/>
     </row>
     <row r="335" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C335" s="12" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D335" s="257" t="str">
+      <c r="D335" s="252" t="str">
         <v>74.71</v>
       </c>
-      <c r="E335" s="252" t="str">
+      <c r="E335" s="256" t="str">
         <v>71.4</v>
       </c>
-      <c r="F335" s="252" t="str">
+      <c r="F335" s="256" t="str">
         <v>83.17</v>
       </c>
-      <c r="G335" s="252" t="str">
+      <c r="G335" s="256" t="str">
         <v>83.17</v>
       </c>
-      <c r="H335" s="252" t="str">
+      <c r="H335" s="256" t="str">
         <v>83.17</v>
       </c>
-      <c r="I335" s="252" t="str">
+      <c r="I335" s="256" t="str">
         <v>69.7</v>
       </c>
-      <c r="J335" s="252" t="str">
+      <c r="J335" s="256" t="str">
         <v>60.01</v>
       </c>
-      <c r="K335" s="252" t="str">
+      <c r="K335" s="256" t="str">
         <v>54.34</v>
       </c>
-      <c r="L335" s="252" t="str">
+      <c r="L335" s="179" t="str">
         <v>53.07</v>
       </c>
-      <c r="M335" s="255" t="str">
-        <v>90</v>
-      </c>
+      <c r="M335"/>
     </row>
     <row r="336" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C336" s="13" t="str">
         <v>UsageArea.Center</v>
       </c>
-      <c r="D336" s="258" t="str">
+      <c r="D336" s="253" t="str">
         <v>18.83, 61.295</v>
       </c>
       <c r="E336" s="214" t="str">
@@ -50502,149 +50539,226 @@
       <c r="K336" s="214" t="str">
         <v>-171.57, 52.94</v>
       </c>
-      <c r="L336" s="214" t="str">
+      <c r="L336" s="181" t="str">
         <v>176.14, 52.185</v>
       </c>
-      <c r="M336" s="256" t="str">
-        <v>0, 0</v>
-      </c>
-    </row>
-    <row r="337" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="338" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M336"/>
+    </row>
+    <row r="337" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M337"/>
+    </row>
+    <row r="338" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C338" s="251" t="str" cm="1">
-        <f t="array" ref="C338:D352">_xll.PE.trf.TransformSteps(D311,D312,C313,"proj")</f>
+        <f t="array" ref="C338:F352">_xll.PE.trf.TransformSteps(D311,D312,C313,"proj")</f>
         <v>Step Number</v>
       </c>
       <c r="D338" s="4">
         <v>0</v>
       </c>
-      <c r="E338" s="5"/>
-    </row>
-    <row r="339" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E338" s="215">
+        <v>1</v>
+      </c>
+      <c r="F338" s="5">
+        <v>2</v>
+      </c>
+      <c r="M338"/>
+    </row>
+    <row r="339" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C339" s="235" t="str">
         <v>Step Identifiers</v>
       </c>
-      <c r="D339" s="178">
-        <v>0</v>
-      </c>
-      <c r="E339" s="179"/>
-    </row>
-    <row r="340" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="D339" s="178" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E339" s="256" t="str">
+        <v>DERIVED_FROM(EPSG)</v>
+      </c>
+      <c r="F339" s="179" t="str">
+        <v>EPSG</v>
+      </c>
+      <c r="M339"/>
+    </row>
+    <row r="340" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C340" s="235" t="str">
         <v>Step Name</v>
       </c>
       <c r="D340" s="178" t="str">
-        <v>&lt;choose-coordinate-transform&gt;</v>
-      </c>
-      <c r="E340" s="179"/>
-    </row>
-    <row r="341" spans="3:5" x14ac:dyDescent="0.35">
+        <v>Inverse of Alaska Albers</v>
+      </c>
+      <c r="E340" s="256" t="str">
+        <v>NAD27 to WGS 84 (10)</v>
+      </c>
+      <c r="F340" s="179" t="str">
+        <v>axis order change (2D)</v>
+      </c>
+    </row>
+    <row r="341" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C341" s="235" t="str">
         <v>Step sccuracy [m]</v>
       </c>
       <c r="D341" s="178">
         <v>55</v>
       </c>
-      <c r="E341" s="179"/>
-    </row>
-    <row r="342" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E341" s="256">
+        <v>55</v>
+      </c>
+      <c r="F341" s="179">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="342" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C342" s="235" t="str">
         <v>UsageArea</v>
       </c>
       <c r="D342" s="178" t="str">
-        <v>United States (USA) - Alaska including EEZ.</v>
-      </c>
-      <c r="E342" s="179"/>
-    </row>
-    <row r="343" spans="3:5" x14ac:dyDescent="0.35">
+        <v>Unknown</v>
+      </c>
+      <c r="E342" s="256" t="str">
+        <v>Canada - Alberta; British Columbia.</v>
+      </c>
+      <c r="F342" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C343" s="235" t="str">
         <v>Scope</v>
       </c>
       <c r="D343" s="178" t="str">
+        <v>Topographic mapping (small scale).</v>
+      </c>
+      <c r="E343" s="256" t="str">
+        <v>Military survey.</v>
+      </c>
+      <c r="F343" s="179" t="str">
         <v>Unknown</v>
       </c>
-      <c r="E343" s="179"/>
-    </row>
-    <row r="344" spans="3:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="344" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C344" s="235" t="str">
         <v>Remarks</v>
       </c>
       <c r="D344" s="178" t="str">
         <v>None</v>
       </c>
-      <c r="E344" s="179"/>
-    </row>
-    <row r="345" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="E344" s="256" t="str">
+        <v>Derived at 25 stations. Accuracy 8m, 8m and 6m in X, Y and Z axes.</v>
+      </c>
+      <c r="F344" s="179" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="345" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C345" s="235" t="str">
         <v>UsageArea.WestLongitude</v>
       </c>
       <c r="D345" s="178">
-        <v>167.65</v>
-      </c>
-      <c r="E345" s="179"/>
-    </row>
-    <row r="346" spans="3:5" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+      <c r="E345" s="256">
+        <v>-139.04</v>
+      </c>
+      <c r="F345" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C346" s="235" t="str">
         <v>UsageArea.SouthLatitude</v>
       </c>
       <c r="D346" s="178">
-        <v>-129.99</v>
-      </c>
-      <c r="E346" s="179"/>
-    </row>
-    <row r="347" spans="3:5" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+      <c r="E346" s="256">
+        <v>-109.98</v>
+      </c>
+      <c r="F346" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C347" s="235" t="str">
         <v>UsageArea.EastLongitude</v>
       </c>
       <c r="D347" s="178">
-        <v>47.88</v>
-      </c>
-      <c r="E347" s="179"/>
-    </row>
-    <row r="348" spans="3:5" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+      <c r="E347" s="256">
+        <v>48.25</v>
+      </c>
+      <c r="F347" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C348" s="235" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
       <c r="D348" s="178">
-        <v>74.709999999999994</v>
-      </c>
-      <c r="E348" s="179"/>
-    </row>
-    <row r="349" spans="3:5" x14ac:dyDescent="0.35">
+        <v>-1000</v>
+      </c>
+      <c r="E348" s="256">
+        <v>60.01</v>
+      </c>
+      <c r="F348" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C349" s="235" t="str">
         <v>Nr grids</v>
       </c>
       <c r="D349" s="178">
-        <v>1</v>
-      </c>
-      <c r="E349" s="179"/>
-    </row>
-    <row r="350" spans="3:5" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="E349" s="256">
+        <v>0</v>
+      </c>
+      <c r="F349" s="179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C350" s="235" t="str">
         <v>1st grid</v>
       </c>
       <c r="D350" s="178" t="str">
-        <v/>
-      </c>
-      <c r="E350" s="179"/>
-    </row>
-    <row r="351" spans="3:5" x14ac:dyDescent="0.35">
+        <v>N.A.</v>
+      </c>
+      <c r="E350" s="256" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F350" s="179" t="str">
+        <v>N.A.</v>
+      </c>
+    </row>
+    <row r="351" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C351" s="235" t="str">
         <v>2nd grid</v>
       </c>
       <c r="D351" s="178" t="str">
         <v>N.A.</v>
       </c>
-      <c r="E351" s="179"/>
-    </row>
-    <row r="352" spans="3:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E351" s="256" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F351" s="179" t="str">
+        <v>N.A.</v>
+      </c>
+    </row>
+    <row r="352" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C352" s="236" t="str">
-        <v>Step ROJ string</v>
-      </c>
-      <c r="D352" s="180">
-        <v>0</v>
-      </c>
-      <c r="E352" s="181"/>
+        <v>Step PROJ string</v>
+      </c>
+      <c r="D352" s="180" t="str">
+        <v>+proj=pipeline +step +proj=unitconvert +xy_in=us-ft +xy_out=m +step +inv +proj=aea +lat_0=50 +lon_0=-154 +lat_1=55 +lat_2=65 +x_0=0 +y_0=0 +ellps=clrk66 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E352" s="214" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=push +v_3 +step +proj=cart +ellps=clrk66 +step +proj=helmert +x=-7 +y=162 +z=188 +step +inv +proj=cart +ellps=WGS84 +step +proj=pop +v_3 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="F352" s="181" t="str">
+        <v>+proj=axisswap +order=2,1</v>
+      </c>
     </row>
     <row r="354" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="355" spans="3:16" x14ac:dyDescent="0.35">
@@ -50669,8 +50783,8 @@
     </row>
     <row r="357" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C357" s="182" t="str" cm="1">
-        <f t="array" ref="C357">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,0,)</f>
-        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=0; AllowDeprecatedCrs=False</v>
+        <f t="array" ref="C357">_xll.PE.trf.Options(,,,,,55,,,,,,"Never",,,1,)</f>
+        <v>Authority=EPSG; Area=; Accuracy=55; NoBallparkConversions=False; NoDiscardIfMissing=False; UsePrimaryGridNames=False; UseSuperseded=False; StrictContains=False; IntermediateCrsUsage=Never; BestOnly=False; ForceOver=False; CandidateIndex=1; AllowDeprecatedCrs=False</v>
       </c>
       <c r="D357" s="183"/>
       <c r="E357" s="183"/>
@@ -50688,17 +50802,14 @@
     </row>
     <row r="358" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C358" s="223" t="str" cm="1">
-        <f t="array" ref="C358:F380">_xll.PE.trf.TransformList(D355,D356,,"")</f>
+        <f t="array" ref="C358:E380">_xll.PE.trf.TransformList(D355,D356,C357,"")</f>
         <v>Transform Number</v>
       </c>
-      <c r="D358" s="259">
+      <c r="D358" s="4">
         <v>0</v>
       </c>
-      <c r="E358" s="260">
+      <c r="E358" s="5">
         <v>1</v>
-      </c>
-      <c r="F358" s="261">
-        <v>2</v>
       </c>
       <c r="M358"/>
       <c r="O358"/>
@@ -50707,14 +50818,11 @@
       <c r="C359" s="12" t="str">
         <v>Transform Name</v>
       </c>
-      <c r="D359" s="257" t="str">
+      <c r="D359" s="252" t="str">
         <v>Inverse of RD New + Amersfoort to ETRS89 (9) + Belgian Lambert 2008</v>
       </c>
-      <c r="E359" s="252" t="str">
+      <c r="E359" s="179" t="str">
         <v>Inverse of RD New + Amersfoort to ETRS89 (8) + Belgian Lambert 2008</v>
-      </c>
-      <c r="F359" s="179" t="str">
-        <v>Inverse of RD New + Ballpark geographic offset from Amersfoort to ETRS89 + Belgian Lambert 2008</v>
       </c>
       <c r="M359"/>
       <c r="O359"/>
@@ -50723,13 +50831,10 @@
       <c r="C360" s="12" t="str">
         <v>Transform Type</v>
       </c>
-      <c r="D360" s="257" t="str">
+      <c r="D360" s="252" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="E360" s="252" t="str">
-        <v>ConcatenatedOperation</v>
-      </c>
-      <c r="F360" s="179" t="str">
+      <c r="E360" s="179" t="str">
         <v>ConcatenatedOperation</v>
       </c>
       <c r="M360"/>
@@ -50738,13 +50843,10 @@
       <c r="C361" s="12" t="str">
         <v>Identifier</v>
       </c>
-      <c r="D361" s="257" t="str">
+      <c r="D361" s="252" t="str">
         <v/>
       </c>
-      <c r="E361" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F361" s="179" t="str">
+      <c r="E361" s="179" t="str">
         <v/>
       </c>
       <c r="M361"/>
@@ -50753,13 +50855,10 @@
       <c r="C362" s="12" t="str">
         <v>Identifiers</v>
       </c>
-      <c r="D362" s="257" t="str">
+      <c r="D362" s="252" t="str">
         <v/>
       </c>
-      <c r="E362" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F362" s="179" t="str">
+      <c r="E362" s="179" t="str">
         <v/>
       </c>
       <c r="M362"/>
@@ -50768,14 +50867,11 @@
       <c r="C363" s="12" t="str">
         <v>Accuracy</v>
       </c>
-      <c r="D363" s="257" t="str">
+      <c r="D363" s="252" t="str">
         <v>0</v>
       </c>
-      <c r="E363" s="252" t="str">
+      <c r="E363" s="179" t="str">
         <v>0.25</v>
-      </c>
-      <c r="F363" s="179" t="str">
-        <v/>
       </c>
       <c r="M363"/>
     </row>
@@ -50783,13 +50879,10 @@
       <c r="C364" s="12" t="str">
         <v>IsAvailable</v>
       </c>
-      <c r="D364" s="257" t="str">
+      <c r="D364" s="252" t="str">
         <v>True</v>
       </c>
-      <c r="E364" s="252" t="str">
-        <v>True</v>
-      </c>
-      <c r="F364" s="179" t="str">
+      <c r="E364" s="179" t="str">
         <v>True</v>
       </c>
       <c r="M364"/>
@@ -50798,14 +50891,11 @@
       <c r="C365" s="12" t="str">
         <v>HasBallParkTransformation</v>
       </c>
-      <c r="D365" s="257" t="str">
+      <c r="D365" s="252" t="str">
         <v>False</v>
       </c>
-      <c r="E365" s="252" t="str">
+      <c r="E365" s="179" t="str">
         <v>False</v>
-      </c>
-      <c r="F365" s="179" t="str">
-        <v>True</v>
       </c>
       <c r="M365"/>
     </row>
@@ -50813,13 +50903,10 @@
       <c r="C366" s="12" t="str">
         <v>HasInverse</v>
       </c>
-      <c r="D366" s="257" t="str">
+      <c r="D366" s="252" t="str">
         <v>True</v>
       </c>
-      <c r="E366" s="252" t="str">
-        <v>True</v>
-      </c>
-      <c r="F366" s="179" t="str">
+      <c r="E366" s="179" t="str">
         <v>True</v>
       </c>
       <c r="M366"/>
@@ -50828,13 +50915,10 @@
       <c r="C367" s="12" t="str">
         <v>MethodName</v>
       </c>
-      <c r="D367" s="257" t="str">
+      <c r="D367" s="252" t="str">
         <v/>
       </c>
-      <c r="E367" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F367" s="179" t="str">
+      <c r="E367" s="179" t="str">
         <v/>
       </c>
       <c r="M367"/>
@@ -50843,13 +50927,10 @@
       <c r="C368" s="12" t="str">
         <v>Scope</v>
       </c>
-      <c r="D368" s="257" t="str">
+      <c r="D368" s="252" t="str">
         <v/>
       </c>
-      <c r="E368" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F368" s="179" t="str">
+      <c r="E368" s="179" t="str">
         <v/>
       </c>
       <c r="M368"/>
@@ -50858,13 +50939,10 @@
       <c r="C369" s="12" t="str">
         <v>Remarks</v>
       </c>
-      <c r="D369" s="257" t="str">
+      <c r="D369" s="252" t="str">
         <v/>
       </c>
-      <c r="E369" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F369" s="179" t="str">
+      <c r="E369" s="179" t="str">
         <v/>
       </c>
       <c r="M369"/>
@@ -50873,13 +50951,10 @@
       <c r="C370" s="12" t="str">
         <v>GridUsages</v>
       </c>
-      <c r="D370" s="257" t="str">
+      <c r="D370" s="252" t="str">
         <v/>
       </c>
-      <c r="E370" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F370" s="179" t="str">
+      <c r="E370" s="179" t="str">
         <v/>
       </c>
       <c r="M370"/>
@@ -50888,13 +50963,10 @@
       <c r="C371" s="12" t="str">
         <v>Parameters</v>
       </c>
-      <c r="D371" s="257" t="str">
+      <c r="D371" s="252" t="str">
         <v/>
       </c>
-      <c r="E371" s="252" t="str">
-        <v/>
-      </c>
-      <c r="F371" s="179" t="str">
+      <c r="E371" s="179" t="str">
         <v/>
       </c>
       <c r="M371"/>
@@ -50903,13 +50975,10 @@
       <c r="C372" s="12" t="str">
         <v>SourceCRS</v>
       </c>
-      <c r="D372" s="257" t="str">
+      <c r="D372" s="252" t="str">
         <v>Amersfoort / RD New</v>
       </c>
-      <c r="E372" s="252" t="str">
-        <v>Amersfoort / RD New</v>
-      </c>
-      <c r="F372" s="179" t="str">
+      <c r="E372" s="179" t="str">
         <v>Amersfoort / RD New</v>
       </c>
       <c r="M372"/>
@@ -50918,13 +50987,10 @@
       <c r="C373" s="12" t="str">
         <v>TargetCRS</v>
       </c>
-      <c r="D373" s="257" t="str">
+      <c r="D373" s="252" t="str">
         <v>ETRS89 / Belgian Lambert 2008</v>
       </c>
-      <c r="E373" s="252" t="str">
-        <v>ETRS89 / Belgian Lambert 2008</v>
-      </c>
-      <c r="F373" s="179" t="str">
+      <c r="E373" s="179" t="str">
         <v>ETRS89 / Belgian Lambert 2008</v>
       </c>
       <c r="M373"/>
@@ -50933,13 +50999,10 @@
       <c r="C374" s="12" t="str">
         <v>Context</v>
       </c>
-      <c r="D374" s="257" t="str">
+      <c r="D374" s="252" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
-      <c r="E374" s="252" t="str">
-        <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
-      </c>
-      <c r="F374" s="179" t="str">
+      <c r="E374" s="179" t="str">
         <v>LogLevel=Error; EndpointUrl=https://cdn.proj.org; EnableNetworkConnections=True</v>
       </c>
       <c r="M374"/>
@@ -50948,14 +51011,11 @@
       <c r="C375" s="12" t="str">
         <v>UsageArea.Name</v>
       </c>
-      <c r="D375" s="257" t="str">
+      <c r="D375" s="252" t="str">
         <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
       </c>
-      <c r="E375" s="252" t="str">
+      <c r="E375" s="179" t="str">
         <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
-      </c>
-      <c r="F375" s="179" t="str">
-        <v>World</v>
       </c>
       <c r="M375"/>
     </row>
@@ -50963,14 +51023,11 @@
       <c r="C376" s="12" t="str">
         <v>UsageArea.WestLongitude</v>
       </c>
-      <c r="D376" s="257" t="str">
+      <c r="D376" s="252" t="str">
         <v>3.2</v>
       </c>
-      <c r="E376" s="252" t="str">
+      <c r="E376" s="179" t="str">
         <v>3.2</v>
-      </c>
-      <c r="F376" s="179" t="str">
-        <v>-180</v>
       </c>
       <c r="M376"/>
     </row>
@@ -50978,14 +51035,11 @@
       <c r="C377" s="12" t="str">
         <v>UsageArea.SouthLatitude</v>
       </c>
-      <c r="D377" s="257" t="str">
+      <c r="D377" s="252" t="str">
         <v>50.75</v>
       </c>
-      <c r="E377" s="252" t="str">
+      <c r="E377" s="179" t="str">
         <v>50.75</v>
-      </c>
-      <c r="F377" s="179" t="str">
-        <v>-90</v>
       </c>
       <c r="M377"/>
     </row>
@@ -50993,14 +51047,11 @@
       <c r="C378" s="12" t="str">
         <v>UsageArea.EastLongitude</v>
       </c>
-      <c r="D378" s="257" t="str">
+      <c r="D378" s="252" t="str">
         <v>7.22</v>
       </c>
-      <c r="E378" s="252" t="str">
+      <c r="E378" s="179" t="str">
         <v>7.22</v>
-      </c>
-      <c r="F378" s="179" t="str">
-        <v>180</v>
       </c>
       <c r="M378"/>
     </row>
@@ -51008,14 +51059,11 @@
       <c r="C379" s="12" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D379" s="257" t="str">
+      <c r="D379" s="252" t="str">
         <v>53.7</v>
       </c>
-      <c r="E379" s="252" t="str">
+      <c r="E379" s="179" t="str">
         <v>53.7</v>
-      </c>
-      <c r="F379" s="179" t="str">
-        <v>90</v>
       </c>
       <c r="M379"/>
     </row>
@@ -51023,14 +51071,11 @@
       <c r="C380" s="13" t="str">
         <v>UsageArea.Center</v>
       </c>
-      <c r="D380" s="258" t="str">
+      <c r="D380" s="253" t="str">
         <v>5.21, 52.225</v>
       </c>
-      <c r="E380" s="214" t="str">
+      <c r="E380" s="181" t="str">
         <v>5.21, 52.225</v>
-      </c>
-      <c r="F380" s="181" t="str">
-        <v>0, 0</v>
       </c>
       <c r="M380"/>
     </row>
@@ -51039,11 +51084,17 @@
     </row>
     <row r="382" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C382" s="251" t="str" cm="1">
-        <f t="array" ref="C382:D396">_xll.PE.trf.TransformSteps(D355,D356,C357,"proj")</f>
+        <f t="array" ref="C382:F396">_xll.PE.trf.TransformSteps(D355,D356,C357,"proj")</f>
         <v>Step Number</v>
       </c>
-      <c r="D382" s="21">
+      <c r="D382" s="4">
         <v>0</v>
+      </c>
+      <c r="E382" s="215">
+        <v>1</v>
+      </c>
+      <c r="F382" s="5">
+        <v>2</v>
       </c>
       <c r="H382" s="182" t="str" cm="1">
         <f t="array" ref="H382:L385">_xll.PE.xfm.ListTransformPipelines(D355,D356)</f>
@@ -51066,8 +51117,14 @@
       <c r="C383" s="235" t="str">
         <v>Step Identifiers</v>
       </c>
-      <c r="D383" s="262">
-        <v>0</v>
+      <c r="D383" s="254" t="str">
+        <v>INVERSE(EPSG)</v>
+      </c>
+      <c r="E383" s="255" t="str">
+        <v>EPSG</v>
+      </c>
+      <c r="F383" s="177" t="str">
+        <v>EPSG</v>
       </c>
       <c r="H383" s="244">
         <v>1</v>
@@ -51089,8 +51146,14 @@
       <c r="C384" s="235" t="str">
         <v>Step Name</v>
       </c>
-      <c r="D384" s="262" t="str">
-        <v>&lt;choose-coordinate-transform&gt;</v>
+      <c r="D384" s="252" t="str">
+        <v>Inverse of RD New</v>
+      </c>
+      <c r="E384" s="172" t="str">
+        <v>Amersfoort to ETRS89 (8)</v>
+      </c>
+      <c r="F384" s="179" t="str">
+        <v>Belgian Lambert 2008</v>
       </c>
       <c r="H384" s="200">
         <v>2</v>
@@ -51112,7 +51175,13 @@
       <c r="C385" s="235" t="str">
         <v>Step sccuracy [m]</v>
       </c>
-      <c r="D385" s="262">
+      <c r="D385" s="252">
+        <v>55</v>
+      </c>
+      <c r="E385" s="172">
+        <v>55</v>
+      </c>
+      <c r="F385" s="179">
         <v>55</v>
       </c>
       <c r="H385">
@@ -51135,40 +51204,70 @@
       <c r="C386" s="235" t="str">
         <v>UsageArea</v>
       </c>
-      <c r="D386" s="262" t="str">
+      <c r="D386" s="252" t="str">
         <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="E386" s="172" t="str">
+        <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
+      </c>
+      <c r="F386" s="179" t="str">
+        <v>Belgium - onshore.</v>
       </c>
     </row>
     <row r="387" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C387" s="235" t="str">
         <v>Scope</v>
       </c>
-      <c r="D387" s="262" t="str">
-        <v>Unknown</v>
+      <c r="D387" s="252" t="str">
+        <v>Engineering survey, topographic mapping.</v>
+      </c>
+      <c r="E387" s="172" t="str">
+        <v>Transformation of coordinates at 0.25m level of accuracy.</v>
+      </c>
+      <c r="F387" s="179" t="str">
+        <v>Engineering survey, topographic mapping.</v>
       </c>
     </row>
     <row r="388" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C388" s="235" t="str">
         <v>Remarks</v>
       </c>
-      <c r="D388" s="262" t="str">
+      <c r="D388" s="252" t="str">
         <v>None</v>
+      </c>
+      <c r="E388" s="172" t="str">
+        <v>Replaces Amersfoort to ETRS89 (5) and (6) (tfm codes 4830 and 4831). Derived using ETRF2000. In official transformation used with an ellipsoidal height of 0m in Amersfoort or 43m in ETRS89 and with an additional correction grid (up to 0.25m).</v>
+      </c>
+      <c r="F388" s="179" t="str">
+        <v>Replaces Lambert 2005.</v>
       </c>
     </row>
     <row r="389" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C389" s="235" t="str">
         <v>UsageArea.WestLongitude</v>
       </c>
-      <c r="D389" s="262">
+      <c r="D389" s="252">
         <v>3.2</v>
+      </c>
+      <c r="E389" s="172">
+        <v>3.2</v>
+      </c>
+      <c r="F389" s="179">
+        <v>2.5</v>
       </c>
     </row>
     <row r="390" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C390" s="235" t="str">
         <v>UsageArea.SouthLatitude</v>
       </c>
-      <c r="D390" s="262">
+      <c r="D390" s="252">
         <v>7.22</v>
+      </c>
+      <c r="E390" s="172">
+        <v>7.22</v>
+      </c>
+      <c r="F390" s="179">
+        <v>6.4</v>
       </c>
       <c r="H390" s="182" t="str" cm="1">
         <f t="array" ref="H390:Q393">_xll.PE.trf.ListTransformOptions(D355,D356)</f>
@@ -51206,8 +51305,14 @@
       <c r="C391" s="235" t="str">
         <v>UsageArea.EastLongitude</v>
       </c>
-      <c r="D391" s="262">
+      <c r="D391" s="252">
         <v>50.75</v>
+      </c>
+      <c r="E391" s="172">
+        <v>50.75</v>
+      </c>
+      <c r="F391" s="179">
+        <v>49.5</v>
       </c>
       <c r="H391" s="244">
         <v>0</v>
@@ -51244,34 +51349,40 @@
       <c r="C392" s="235" t="str">
         <v>UsageArea.NorthLatitude</v>
       </c>
-      <c r="D392" s="262">
-        <v>53.7</v>
+      <c r="D392" s="252">
+        <v>0</v>
+      </c>
+      <c r="E392" s="172">
+        <v>0</v>
+      </c>
+      <c r="F392" s="179">
+        <v>0</v>
       </c>
       <c r="H392" s="198">
         <v>1</v>
       </c>
-      <c r="I392" s="253" t="str">
+      <c r="I392" t="str">
         <v>No</v>
       </c>
-      <c r="J392" s="253" t="str">
+      <c r="J392" t="str">
         <v>Inverse of RD New + Amersfoort to ETRS89 (8) + Belgian Lambert 2008</v>
       </c>
-      <c r="K392" s="253" t="str">
+      <c r="K392" t="str">
         <v>ConcatenatedOperation</v>
       </c>
-      <c r="L392" s="253">
+      <c r="L392">
         <v>0.25</v>
       </c>
-      <c r="M392" s="253" t="b">
+      <c r="M392" t="b">
         <v>1</v>
       </c>
-      <c r="N392" s="253" t="b">
+      <c r="N392" t="b">
         <v>0</v>
       </c>
-      <c r="O392" s="253" t="str">
+      <c r="O392" t="str">
         <v>Netherlands - onshore, including Waddenzee, Dutch Wadden Islands and 12-mile offshore coastal zone.</v>
       </c>
-      <c r="P392" s="264" t="str">
+      <c r="P392" s="237" t="str">
         <v>Available; Non-ballpark; Accuracy=0.25; Has usage area</v>
       </c>
       <c r="Q392" s="238" t="str">
@@ -51282,8 +51393,14 @@
       <c r="C393" s="235" t="str">
         <v>Nr grids</v>
       </c>
-      <c r="D393" s="262">
-        <v>1</v>
+      <c r="D393" s="252" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E393" s="172" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F393" s="179" t="str">
+        <v>N.A.</v>
       </c>
       <c r="H393" s="200">
         <v>2</v>
@@ -51320,23 +51437,41 @@
       <c r="C394" s="235" t="str">
         <v>1st grid</v>
       </c>
-      <c r="D394" s="262" t="str">
-        <v/>
+      <c r="D394" s="252" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="E394" s="172" t="str">
+        <v>N.A.</v>
+      </c>
+      <c r="F394" s="179" t="str">
+        <v>N.A.</v>
       </c>
     </row>
     <row r="395" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C395" s="235" t="str">
         <v>2nd grid</v>
       </c>
-      <c r="D395" s="262" t="str">
-        <v>N.A.</v>
+      <c r="D395" s="252" t="str">
+        <v>+proj=pipeline +step +inv +proj=sterea +lat_0=52.1561605555556 +lon_0=5.38763888888889 +k=0.9999079 +x_0=155000 +y_0=463000 +ellps=bessel +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="E395" s="172" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=push +v_3 +step +proj=cart +ellps=bessel +step +proj=helmert +x=565.7381 +y=50.4018 +z=465.2904 +rx=0.395025981036064 +ry=-0.330772431242031 +rz=1.87607329462821 +s=4.07244 +convention=coordinate_frame +step +inv +proj=cart +ellps=GRS80 +step +proj=pop +v_3 +step +proj=unitconvert +xy_in=rad +xy_out=deg +step +proj=axisswap +order=2,1</v>
+      </c>
+      <c r="F395" s="179" t="str">
+        <v>+proj=pipeline +step +proj=axisswap +order=2,1 +step +proj=unitconvert +xy_in=deg +xy_out=rad +step +proj=lcc +lat_0=50.797815 +lon_0=4.35921583333333 +lat_1=49.8333333333333 +lat_2=51.1666666666667 +x_0=649328 +y_0=665262 +ellps=GRS80</v>
       </c>
     </row>
     <row r="396" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C396" s="236" t="str">
         <v>Step ROJ string</v>
       </c>
-      <c r="D396" s="263">
+      <c r="D396" s="253">
+        <v>0</v>
+      </c>
+      <c r="E396" s="214">
+        <v>0</v>
+      </c>
+      <c r="F396" s="181">
         <v>0</v>
       </c>
     </row>
